--- a/5_Unova_Data.xlsx
+++ b/5_Unova_Data.xlsx
@@ -493,11 +493,14 @@
       <c r="C3" t="str">
         <v/>
       </c>
+      <c r="D3" t="str">
+        <v>Patrat</v>
+      </c>
       <c r="E3" t="str">
-        <v>undefined-undefined</v>
+        <v>2-3</v>
       </c>
       <c r="F3" t="str">
-        <v>0.5%</v>
+        <v>50%</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -531,11 +534,14 @@
       <c r="C4" t="str">
         <v/>
       </c>
+      <c r="D4" t="str">
+        <v>Purrloin</v>
+      </c>
       <c r="E4" t="str">
-        <v>undefined-undefined</v>
+        <v>2-3</v>
       </c>
       <c r="F4" t="str">
-        <v>0.5%</v>
+        <v>50%</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -569,11 +575,14 @@
       <c r="C5" t="str">
         <v/>
       </c>
+      <c r="D5" t="str">
+        <v>Audino</v>
+      </c>
       <c r="E5" t="str">
-        <v>undefined-undefined</v>
+        <v>3-4</v>
       </c>
       <c r="F5" t="str">
-        <v>0.1426%</v>
+        <v>14%</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -607,11 +616,14 @@
       <c r="C6" t="str">
         <v/>
       </c>
+      <c r="D6" t="str">
+        <v>Lillipup</v>
+      </c>
       <c r="E6" t="str">
-        <v>undefined-undefined</v>
+        <v>3-4</v>
       </c>
       <c r="F6" t="str">
-        <v>0.1429%</v>
+        <v>14%</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -645,11 +657,14 @@
       <c r="C7" t="str">
         <v/>
       </c>
+      <c r="D7" t="str">
+        <v>Psyduck</v>
+      </c>
       <c r="E7" t="str">
-        <v>undefined-undefined</v>
+        <v>3-4</v>
       </c>
       <c r="F7" t="str">
-        <v>0.1429%</v>
+        <v>14%</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -683,11 +698,14 @@
       <c r="C8" t="str">
         <v/>
       </c>
+      <c r="D8" t="str">
+        <v>Mareep</v>
+      </c>
       <c r="E8" t="str">
-        <v>undefined-undefined</v>
+        <v>3-4</v>
       </c>
       <c r="F8" t="str">
-        <v>0.1429%</v>
+        <v>14%</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -721,11 +739,14 @@
       <c r="C9" t="str">
         <v/>
       </c>
+      <c r="D9" t="str">
+        <v>Patrat</v>
+      </c>
       <c r="E9" t="str">
-        <v>undefined-undefined</v>
+        <v>3-4</v>
       </c>
       <c r="F9" t="str">
-        <v>0.1429%</v>
+        <v>14%</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -759,11 +780,14 @@
       <c r="C10" t="str">
         <v/>
       </c>
+      <c r="D10" t="str">
+        <v>Riolu</v>
+      </c>
       <c r="E10" t="str">
-        <v>undefined-undefined</v>
+        <v>3-4</v>
       </c>
       <c r="F10" t="str">
-        <v>0.1429%</v>
+        <v>14%</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -797,11 +821,14 @@
       <c r="C11" t="str">
         <v/>
       </c>
+      <c r="D11" t="str">
+        <v>Pidove</v>
+      </c>
       <c r="E11" t="str">
-        <v>undefined-undefined</v>
+        <v>3-4</v>
       </c>
       <c r="F11" t="str">
-        <v>0.1429%</v>
+        <v>14%</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -835,11 +862,14 @@
       <c r="C12" t="str">
         <v/>
       </c>
+      <c r="D12" t="str">
+        <v>Azurill</v>
+      </c>
       <c r="E12" t="str">
-        <v>undefined-undefined</v>
+        <v>4-5</v>
       </c>
       <c r="F12" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -873,11 +903,14 @@
       <c r="C13" t="str">
         <v/>
       </c>
+      <c r="D13" t="str">
+        <v>Buizel</v>
+      </c>
       <c r="E13" t="str">
-        <v>undefined-undefined</v>
+        <v>4-5</v>
       </c>
       <c r="F13" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -911,11 +944,14 @@
       <c r="C14" t="str">
         <v/>
       </c>
+      <c r="D14" t="str">
+        <v>Jellicent</v>
+      </c>
       <c r="E14" t="str">
-        <v>undefined-undefined</v>
+        <v>4-5</v>
       </c>
       <c r="F14" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -949,11 +985,14 @@
       <c r="C15" t="str">
         <v/>
       </c>
+      <c r="D15" t="str">
+        <v>Magikarp</v>
+      </c>
       <c r="E15" t="str">
-        <v>undefined-undefined</v>
+        <v>4-5</v>
       </c>
       <c r="F15" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -987,11 +1026,14 @@
       <c r="C16" t="str">
         <v/>
       </c>
+      <c r="D16" t="str">
+        <v>Seel</v>
+      </c>
       <c r="E16" t="str">
-        <v>undefined-undefined</v>
+        <v>4-5</v>
       </c>
       <c r="F16" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1025,11 +1067,14 @@
       <c r="C17" t="str">
         <v/>
       </c>
+      <c r="D17" t="str">
+        <v>Frillish</v>
+      </c>
       <c r="E17" t="str">
-        <v>undefined-undefined</v>
+        <v>4-5</v>
       </c>
       <c r="F17" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1063,11 +1108,14 @@
       <c r="C18" t="str">
         <v/>
       </c>
+      <c r="D18" t="str">
+        <v>Staryu</v>
+      </c>
       <c r="E18" t="str">
-        <v>undefined-undefined</v>
+        <v>4-5</v>
       </c>
       <c r="F18" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1101,11 +1149,14 @@
       <c r="C19" t="str">
         <v/>
       </c>
+      <c r="D19" t="str">
+        <v>Horsea</v>
+      </c>
       <c r="E19" t="str">
-        <v>undefined-undefined</v>
+        <v>4-5</v>
       </c>
       <c r="F19" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1139,11 +1190,14 @@
       <c r="C20" t="str">
         <v/>
       </c>
+      <c r="D20" t="str">
+        <v>Venipede</v>
+      </c>
       <c r="E20" t="str">
-        <v>undefined-undefined</v>
+        <v>6-7</v>
       </c>
       <c r="F20" t="str">
-        <v>0.1665%</v>
+        <v>17%</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1177,11 +1231,14 @@
       <c r="C21" t="str">
         <v/>
       </c>
+      <c r="D21" t="str">
+        <v>Sewaddle</v>
+      </c>
       <c r="E21" t="str">
-        <v>undefined-undefined</v>
+        <v>6-7</v>
       </c>
       <c r="F21" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1215,11 +1272,14 @@
       <c r="C22" t="str">
         <v/>
       </c>
+      <c r="D22" t="str">
+        <v>Pidove</v>
+      </c>
       <c r="E22" t="str">
-        <v>undefined-undefined</v>
+        <v>6-7</v>
       </c>
       <c r="F22" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1253,11 +1313,14 @@
       <c r="C23" t="str">
         <v/>
       </c>
+      <c r="D23" t="str">
+        <v>Patrat</v>
+      </c>
       <c r="E23" t="str">
-        <v>undefined-undefined</v>
+        <v>6-7</v>
       </c>
       <c r="F23" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1291,11 +1354,14 @@
       <c r="C24" t="str">
         <v/>
       </c>
+      <c r="D24" t="str">
+        <v>Purrloin</v>
+      </c>
       <c r="E24" t="str">
-        <v>undefined-undefined</v>
+        <v>6-7</v>
       </c>
       <c r="F24" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1329,11 +1395,14 @@
       <c r="C25" t="str">
         <v/>
       </c>
+      <c r="D25" t="str">
+        <v>Sunkern</v>
+      </c>
       <c r="E25" t="str">
-        <v>undefined-undefined</v>
+        <v>6-7</v>
       </c>
       <c r="F25" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1449,11 +1518,14 @@
       <c r="C28" t="str">
         <v/>
       </c>
+      <c r="D28" t="str">
+        <v>Magnemite</v>
+      </c>
       <c r="E28" t="str">
-        <v>undefined-undefined</v>
+        <v>9-10</v>
       </c>
       <c r="F28" t="str">
-        <v>0.1665%</v>
+        <v>17%</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1487,11 +1559,14 @@
       <c r="C29" t="str">
         <v/>
       </c>
+      <c r="D29" t="str">
+        <v>Elekid</v>
+      </c>
       <c r="E29" t="str">
-        <v>undefined-undefined</v>
+        <v>9-10</v>
       </c>
       <c r="F29" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1525,11 +1600,14 @@
       <c r="C30" t="str">
         <v/>
       </c>
+      <c r="D30" t="str">
+        <v>Magby</v>
+      </c>
       <c r="E30" t="str">
-        <v>undefined-undefined</v>
+        <v>9-10</v>
       </c>
       <c r="F30" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1563,11 +1641,14 @@
       <c r="C31" t="str">
         <v/>
       </c>
+      <c r="D31" t="str">
+        <v>Growlithe</v>
+      </c>
       <c r="E31" t="str">
-        <v>undefined-undefined</v>
+        <v>9-10</v>
       </c>
       <c r="F31" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1601,11 +1682,14 @@
       <c r="C32" t="str">
         <v/>
       </c>
+      <c r="D32" t="str">
+        <v>Koffing</v>
+      </c>
       <c r="E32" t="str">
-        <v>undefined-undefined</v>
+        <v>9-10</v>
       </c>
       <c r="F32" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1639,11 +1723,14 @@
       <c r="C33" t="str">
         <v/>
       </c>
+      <c r="D33" t="str">
+        <v>Patrat</v>
+      </c>
       <c r="E33" t="str">
-        <v>undefined-undefined</v>
+        <v>9-10</v>
       </c>
       <c r="F33" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1677,11 +1764,14 @@
       <c r="C34" t="str">
         <v/>
       </c>
+      <c r="D34" t="str">
+        <v>Marill</v>
+      </c>
       <c r="E34" t="str">
-        <v>undefined-undefined</v>
+        <v>10-11</v>
       </c>
       <c r="F34" t="str">
-        <v>0.1426%</v>
+        <v>14%</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1715,11 +1805,14 @@
       <c r="C35" t="str">
         <v/>
       </c>
+      <c r="D35" t="str">
+        <v>Remoraid</v>
+      </c>
       <c r="E35" t="str">
-        <v>undefined-undefined</v>
+        <v>10-11</v>
       </c>
       <c r="F35" t="str">
-        <v>0.1429%</v>
+        <v>14%</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1753,11 +1846,14 @@
       <c r="C36" t="str">
         <v/>
       </c>
+      <c r="D36" t="str">
+        <v>Mantyke</v>
+      </c>
       <c r="E36" t="str">
-        <v>undefined-undefined</v>
+        <v>10-11</v>
       </c>
       <c r="F36" t="str">
-        <v>0.1429%</v>
+        <v>14%</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1791,11 +1887,14 @@
       <c r="C37" t="str">
         <v/>
       </c>
+      <c r="D37" t="str">
+        <v>Basculin</v>
+      </c>
       <c r="E37" t="str">
-        <v>undefined-undefined</v>
+        <v>10-11</v>
       </c>
       <c r="F37" t="str">
-        <v>0.1429%</v>
+        <v>14%</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1829,11 +1928,14 @@
       <c r="C38" t="str">
         <v/>
       </c>
+      <c r="D38" t="str">
+        <v>Clamperl</v>
+      </c>
       <c r="E38" t="str">
-        <v>undefined-undefined</v>
+        <v>10-11</v>
       </c>
       <c r="F38" t="str">
-        <v>0.1429%</v>
+        <v>14%</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1867,11 +1969,14 @@
       <c r="C39" t="str">
         <v/>
       </c>
+      <c r="D39" t="str">
+        <v>Krabby</v>
+      </c>
       <c r="E39" t="str">
-        <v>undefined-undefined</v>
+        <v>10-11</v>
       </c>
       <c r="F39" t="str">
-        <v>0.1429%</v>
+        <v>14%</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1905,11 +2010,14 @@
       <c r="C40" t="str">
         <v/>
       </c>
+      <c r="D40" t="str">
+        <v>Spheal</v>
+      </c>
       <c r="E40" t="str">
-        <v>undefined-undefined</v>
+        <v>10-11</v>
       </c>
       <c r="F40" t="str">
-        <v>0.1429%</v>
+        <v>14%</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1984,11 +2092,14 @@
       <c r="C42" t="str">
         <v/>
       </c>
+      <c r="D42" t="str">
+        <v>Whimsicott</v>
+      </c>
       <c r="E42" t="str">
-        <v>undefined-undefined</v>
+        <v>13-14</v>
       </c>
       <c r="F42" t="str">
-        <v>0.1665%</v>
+        <v>17%</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2022,11 +2133,14 @@
       <c r="C43" t="str">
         <v/>
       </c>
+      <c r="D43" t="str">
+        <v>Lilligant</v>
+      </c>
       <c r="E43" t="str">
-        <v>undefined-undefined</v>
+        <v>13-14</v>
       </c>
       <c r="F43" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2060,11 +2174,14 @@
       <c r="C44" t="str">
         <v/>
       </c>
+      <c r="D44" t="str">
+        <v>Rattata</v>
+      </c>
       <c r="E44" t="str">
-        <v>undefined-undefined</v>
+        <v>13-14</v>
       </c>
       <c r="F44" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2098,11 +2215,14 @@
       <c r="C45" t="str">
         <v/>
       </c>
+      <c r="D45" t="str">
+        <v>Cottonee</v>
+      </c>
       <c r="E45" t="str">
-        <v>undefined-undefined</v>
+        <v>13-14</v>
       </c>
       <c r="F45" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2136,11 +2256,14 @@
       <c r="C46" t="str">
         <v/>
       </c>
+      <c r="D46" t="str">
+        <v>Petilil</v>
+      </c>
       <c r="E46" t="str">
-        <v>undefined-undefined</v>
+        <v>13-14</v>
       </c>
       <c r="F46" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2174,11 +2297,14 @@
       <c r="C47" t="str">
         <v/>
       </c>
+      <c r="D47" t="str">
+        <v>Pidove</v>
+      </c>
       <c r="E47" t="str">
-        <v>undefined-undefined</v>
+        <v>13-14</v>
       </c>
       <c r="F47" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2212,11 +2338,14 @@
       <c r="C48" t="str">
         <v/>
       </c>
+      <c r="D48" t="str">
+        <v>Muk</v>
+      </c>
       <c r="E48" t="str">
-        <v>undefined-undefined</v>
+        <v>14-15</v>
       </c>
       <c r="F48" t="str">
-        <v>0.3334%</v>
+        <v>33%</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2354,7 @@
         <v>Yes</v>
       </c>
       <c r="I48" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J48" t="str">
         <v>NONONO</v>
@@ -2250,11 +2379,14 @@
       <c r="C49" t="str">
         <v/>
       </c>
+      <c r="D49" t="str">
+        <v>Rattata</v>
+      </c>
       <c r="E49" t="str">
-        <v>undefined-undefined</v>
+        <v>14-15</v>
       </c>
       <c r="F49" t="str">
-        <v>0.3333%</v>
+        <v>33%</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2288,11 +2420,14 @@
       <c r="C50" t="str">
         <v/>
       </c>
+      <c r="D50" t="str">
+        <v>Zubat</v>
+      </c>
       <c r="E50" t="str">
-        <v>undefined-undefined</v>
+        <v>14-15</v>
       </c>
       <c r="F50" t="str">
-        <v>0.3333%</v>
+        <v>33%</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2326,11 +2461,14 @@
       <c r="C51" t="str">
         <v/>
       </c>
+      <c r="D51" t="str">
+        <v>Delcatty</v>
+      </c>
       <c r="E51" t="str">
-        <v>undefined-undefined</v>
+        <v>15-16</v>
       </c>
       <c r="F51" t="str">
-        <v>0.091%</v>
+        <v>9%</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2364,11 +2502,14 @@
       <c r="C52" t="str">
         <v/>
       </c>
+      <c r="D52" t="str">
+        <v>Skitty</v>
+      </c>
       <c r="E52" t="str">
-        <v>undefined-undefined</v>
+        <v>15-16</v>
       </c>
       <c r="F52" t="str">
-        <v>0.0909%</v>
+        <v>9%</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2402,11 +2543,14 @@
       <c r="C53" t="str">
         <v/>
       </c>
+      <c r="D53" t="str">
+        <v>Buneary</v>
+      </c>
       <c r="E53" t="str">
-        <v>undefined-undefined</v>
+        <v>15-16</v>
       </c>
       <c r="F53" t="str">
-        <v>0.0909%</v>
+        <v>9%</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2440,11 +2584,14 @@
       <c r="C54" t="str">
         <v/>
       </c>
+      <c r="D54" t="str">
+        <v>Eevee</v>
+      </c>
       <c r="E54" t="str">
-        <v>undefined-undefined</v>
+        <v>15-16</v>
       </c>
       <c r="F54" t="str">
-        <v>0.0909%</v>
+        <v>9%</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2478,11 +2625,14 @@
       <c r="C55" t="str">
         <v/>
       </c>
+      <c r="D55" t="str">
+        <v>Vaporeon</v>
+      </c>
       <c r="E55" t="str">
-        <v>undefined-undefined</v>
+        <v>15-16</v>
       </c>
       <c r="F55" t="str">
-        <v>0.0909%</v>
+        <v>9%</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2641,7 @@
         <v>Yes</v>
       </c>
       <c r="I55" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J55" t="str">
         <v>NONONO</v>
@@ -2516,11 +2666,14 @@
       <c r="C56" t="str">
         <v/>
       </c>
+      <c r="D56" t="str">
+        <v>Jolteon</v>
+      </c>
       <c r="E56" t="str">
-        <v>undefined-undefined</v>
+        <v>15-16</v>
       </c>
       <c r="F56" t="str">
-        <v>0.0909%</v>
+        <v>9%</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2682,7 @@
         <v>Yes</v>
       </c>
       <c r="I56" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J56" t="str">
         <v>NONONO</v>
@@ -2554,11 +2707,14 @@
       <c r="C57" t="str">
         <v/>
       </c>
+      <c r="D57" t="str">
+        <v>Flareon</v>
+      </c>
       <c r="E57" t="str">
-        <v>undefined-undefined</v>
+        <v>15-16</v>
       </c>
       <c r="F57" t="str">
-        <v>0.0909%</v>
+        <v>9%</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2723,7 @@
         <v>Yes</v>
       </c>
       <c r="I57" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J57" t="str">
         <v>NONONO</v>
@@ -2592,11 +2748,14 @@
       <c r="C58" t="str">
         <v/>
       </c>
+      <c r="D58" t="str">
+        <v>Espeon</v>
+      </c>
       <c r="E58" t="str">
-        <v>undefined-undefined</v>
+        <v>15-16</v>
       </c>
       <c r="F58" t="str">
-        <v>0.0909%</v>
+        <v>9%</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2764,7 @@
         <v>Yes</v>
       </c>
       <c r="I58" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J58" t="str">
         <v>NONONO</v>
@@ -2630,11 +2789,14 @@
       <c r="C59" t="str">
         <v/>
       </c>
+      <c r="D59" t="str">
+        <v>Umbreon</v>
+      </c>
       <c r="E59" t="str">
-        <v>undefined-undefined</v>
+        <v>15-16</v>
       </c>
       <c r="F59" t="str">
-        <v>0.0909%</v>
+        <v>9%</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2805,7 @@
         <v>Yes</v>
       </c>
       <c r="I59" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J59" t="str">
         <v>NONONO</v>
@@ -2668,11 +2830,14 @@
       <c r="C60" t="str">
         <v/>
       </c>
+      <c r="D60" t="str">
+        <v>Leafeon</v>
+      </c>
       <c r="E60" t="str">
-        <v>undefined-undefined</v>
+        <v>15-16</v>
       </c>
       <c r="F60" t="str">
-        <v>0.0909%</v>
+        <v>9%</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2846,7 @@
         <v>Yes</v>
       </c>
       <c r="I60" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J60" t="str">
         <v>NONONO</v>
@@ -2706,11 +2871,14 @@
       <c r="C61" t="str">
         <v/>
       </c>
+      <c r="D61" t="str">
+        <v>Glaceon</v>
+      </c>
       <c r="E61" t="str">
-        <v>undefined-undefined</v>
+        <v>15-16</v>
       </c>
       <c r="F61" t="str">
-        <v>0.0909%</v>
+        <v>9%</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2887,7 @@
         <v>Yes</v>
       </c>
       <c r="I61" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J61" t="str">
         <v>NONONO</v>
@@ -2785,11 +2953,14 @@
       <c r="C63" t="str">
         <v/>
       </c>
+      <c r="D63" t="str">
+        <v>Drilbur</v>
+      </c>
       <c r="E63" t="str">
-        <v>undefined-undefined</v>
+        <v>17-18</v>
       </c>
       <c r="F63" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2823,11 +2994,14 @@
       <c r="C64" t="str">
         <v/>
       </c>
+      <c r="D64" t="str">
+        <v>Woobat</v>
+      </c>
       <c r="E64" t="str">
-        <v>undefined-undefined</v>
+        <v>17-18</v>
       </c>
       <c r="F64" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2861,11 +3035,14 @@
       <c r="C65" t="str">
         <v/>
       </c>
+      <c r="D65" t="str">
+        <v>Rattata</v>
+      </c>
       <c r="E65" t="str">
-        <v>undefined-undefined</v>
+        <v>17-18</v>
       </c>
       <c r="F65" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2899,11 +3076,14 @@
       <c r="C66" t="str">
         <v/>
       </c>
+      <c r="D66" t="str">
+        <v>Timburr</v>
+      </c>
       <c r="E66" t="str">
-        <v>undefined-undefined</v>
+        <v>17-18</v>
       </c>
       <c r="F66" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2937,11 +3117,14 @@
       <c r="C67" t="str">
         <v/>
       </c>
+      <c r="D67" t="str">
+        <v>Darumaka</v>
+      </c>
       <c r="E67" t="str">
-        <v>undefined-undefined</v>
+        <v>18-19</v>
       </c>
       <c r="F67" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2975,11 +3158,14 @@
       <c r="C68" t="str">
         <v/>
       </c>
+      <c r="D68" t="str">
+        <v>Sandile</v>
+      </c>
       <c r="E68" t="str">
-        <v>undefined-undefined</v>
+        <v>18-19</v>
       </c>
       <c r="F68" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -3013,11 +3199,14 @@
       <c r="C69" t="str">
         <v/>
       </c>
+      <c r="D69" t="str">
+        <v>Trubbish</v>
+      </c>
       <c r="E69" t="str">
-        <v>undefined-undefined</v>
+        <v>18-19</v>
       </c>
       <c r="F69" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3051,11 +3240,14 @@
       <c r="C70" t="str">
         <v/>
       </c>
+      <c r="D70" t="str">
+        <v>Scraggy</v>
+      </c>
       <c r="E70" t="str">
-        <v>undefined-undefined</v>
+        <v>18-19</v>
       </c>
       <c r="F70" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3089,11 +3281,14 @@
       <c r="C71" t="str">
         <v/>
       </c>
+      <c r="D71" t="str">
+        <v>Sandshrew</v>
+      </c>
       <c r="E71" t="str">
-        <v>undefined-undefined</v>
+        <v>20-21</v>
       </c>
       <c r="F71" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3127,11 +3322,14 @@
       <c r="C72" t="str">
         <v/>
       </c>
+      <c r="D72" t="str">
+        <v>Trapinch</v>
+      </c>
       <c r="E72" t="str">
-        <v>undefined-undefined</v>
+        <v>20-21</v>
       </c>
       <c r="F72" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3165,11 +3363,14 @@
       <c r="C73" t="str">
         <v/>
       </c>
+      <c r="D73" t="str">
+        <v>Darumaka</v>
+      </c>
       <c r="E73" t="str">
-        <v>undefined-undefined</v>
+        <v>20-21</v>
       </c>
       <c r="F73" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3203,11 +3404,14 @@
       <c r="C74" t="str">
         <v/>
       </c>
+      <c r="D74" t="str">
+        <v>Maractus</v>
+      </c>
       <c r="E74" t="str">
-        <v>undefined-undefined</v>
+        <v>20-21</v>
       </c>
       <c r="F74" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3241,11 +3445,14 @@
       <c r="C75" t="str">
         <v/>
       </c>
+      <c r="D75" t="str">
+        <v>Dwebble</v>
+      </c>
       <c r="E75" t="str">
-        <v>undefined-undefined</v>
+        <v>20-21</v>
       </c>
       <c r="F75" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3279,11 +3486,14 @@
       <c r="C76" t="str">
         <v/>
       </c>
+      <c r="D76" t="str">
+        <v>Sigilyph</v>
+      </c>
       <c r="E76" t="str">
-        <v>undefined-undefined</v>
+        <v>20-21</v>
       </c>
       <c r="F76" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3317,11 +3527,14 @@
       <c r="C77" t="str">
         <v/>
       </c>
+      <c r="D77" t="str">
+        <v>Scraggy</v>
+      </c>
       <c r="E77" t="str">
-        <v>undefined-undefined</v>
+        <v>20-21</v>
       </c>
       <c r="F77" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3355,11 +3568,14 @@
       <c r="C78" t="str">
         <v/>
       </c>
+      <c r="D78" t="str">
+        <v>Darmanitan</v>
+      </c>
       <c r="E78" t="str">
-        <v>undefined-undefined</v>
+        <v>20-21</v>
       </c>
       <c r="F78" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3393,11 +3609,14 @@
       <c r="C79" t="str">
         <v/>
       </c>
+      <c r="D79" t="str">
+        <v>Krokorok</v>
+      </c>
       <c r="E79" t="str">
-        <v>undefined-undefined</v>
+        <v>20-21</v>
       </c>
       <c r="F79" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3431,11 +3650,14 @@
       <c r="C80" t="str">
         <v/>
       </c>
+      <c r="D80" t="str">
+        <v>Sandslash</v>
+      </c>
       <c r="E80" t="str">
-        <v>undefined-undefined</v>
+        <v>20-21</v>
       </c>
       <c r="F80" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3469,11 +3691,14 @@
       <c r="C81" t="str">
         <v/>
       </c>
+      <c r="D81" t="str">
+        <v>Yamask</v>
+      </c>
       <c r="E81" t="str">
-        <v>undefined-undefined</v>
+        <v>21-22</v>
       </c>
       <c r="F81" t="str">
-        <v>0.1112%</v>
+        <v>11%</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3507,11 +3732,14 @@
       <c r="C82" t="str">
         <v/>
       </c>
+      <c r="D82" t="str">
+        <v>Sandile</v>
+      </c>
       <c r="E82" t="str">
-        <v>undefined-undefined</v>
+        <v>21-22</v>
       </c>
       <c r="F82" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3545,11 +3773,14 @@
       <c r="C83" t="str">
         <v/>
       </c>
+      <c r="D83" t="str">
+        <v>Trubbish</v>
+      </c>
       <c r="E83" t="str">
-        <v>undefined-undefined</v>
+        <v>21-22</v>
       </c>
       <c r="F83" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3583,11 +3814,14 @@
       <c r="C84" t="str">
         <v/>
       </c>
+      <c r="D84" t="str">
+        <v>Archen</v>
+      </c>
       <c r="E84" t="str">
-        <v>undefined-undefined</v>
+        <v>21-22</v>
       </c>
       <c r="F84" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3621,11 +3855,14 @@
       <c r="C85" t="str">
         <v/>
       </c>
+      <c r="D85" t="str">
+        <v>Baltoy</v>
+      </c>
       <c r="E85" t="str">
-        <v>undefined-undefined</v>
+        <v>21-22</v>
       </c>
       <c r="F85" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3659,11 +3896,14 @@
       <c r="C86" t="str">
         <v/>
       </c>
+      <c r="D86" t="str">
+        <v>Larvesta</v>
+      </c>
       <c r="E86" t="str">
-        <v>undefined-undefined</v>
+        <v>21-22</v>
       </c>
       <c r="F86" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3697,11 +3937,14 @@
       <c r="C87" t="str">
         <v/>
       </c>
+      <c r="D87" t="str">
+        <v>Cofagrigus</v>
+      </c>
       <c r="E87" t="str">
-        <v>undefined-undefined</v>
+        <v>21-22</v>
       </c>
       <c r="F87" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3735,11 +3978,14 @@
       <c r="C88" t="str">
         <v/>
       </c>
+      <c r="D88" t="str">
+        <v>Krookodile</v>
+      </c>
       <c r="E88" t="str">
-        <v>undefined-undefined</v>
+        <v>21-22</v>
       </c>
       <c r="F88" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3748,7 +3994,7 @@
         <v>Yes</v>
       </c>
       <c r="I88" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J88" t="str">
         <v>NONONO</v>
@@ -3773,11 +4019,14 @@
       <c r="C89" t="str">
         <v/>
       </c>
+      <c r="D89" t="str">
+        <v>Volcarona</v>
+      </c>
       <c r="E89" t="str">
-        <v>undefined-undefined</v>
+        <v>21-22</v>
       </c>
       <c r="F89" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3786,7 +4035,7 @@
         <v>Yes</v>
       </c>
       <c r="I89" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J89" t="str">
         <v>NONONO</v>
@@ -3811,11 +4060,14 @@
       <c r="C90" t="str">
         <v/>
       </c>
+      <c r="D90" t="str">
+        <v>Pachirisu</v>
+      </c>
       <c r="E90" t="str">
-        <v>undefined-undefined</v>
+        <v>22-23</v>
       </c>
       <c r="F90" t="str">
-        <v>0.3334%</v>
+        <v>33%</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3849,11 +4101,14 @@
       <c r="C91" t="str">
         <v/>
       </c>
+      <c r="D91" t="str">
+        <v>Plusle</v>
+      </c>
       <c r="E91" t="str">
-        <v>undefined-undefined</v>
+        <v>22-23</v>
       </c>
       <c r="F91" t="str">
-        <v>0.3333%</v>
+        <v>33%</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3887,11 +4142,14 @@
       <c r="C92" t="str">
         <v/>
       </c>
+      <c r="D92" t="str">
+        <v>Minun</v>
+      </c>
       <c r="E92" t="str">
-        <v>undefined-undefined</v>
+        <v>22-23</v>
       </c>
       <c r="F92" t="str">
-        <v>0.3333%</v>
+        <v>33%</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3966,11 +4224,14 @@
       <c r="C94" t="str">
         <v/>
       </c>
+      <c r="D94" t="str">
+        <v>Gothitelle</v>
+      </c>
       <c r="E94" t="str">
-        <v>undefined-undefined</v>
+        <v>24-25</v>
       </c>
       <c r="F94" t="str">
-        <v>0.1665%</v>
+        <v>17%</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -4004,11 +4265,14 @@
       <c r="C95" t="str">
         <v/>
       </c>
+      <c r="D95" t="str">
+        <v>Reuniclus</v>
+      </c>
       <c r="E95" t="str">
-        <v>undefined-undefined</v>
+        <v>24-25</v>
       </c>
       <c r="F95" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4042,11 +4306,14 @@
       <c r="C96" t="str">
         <v/>
       </c>
+      <c r="D96" t="str">
+        <v>Trubbish</v>
+      </c>
       <c r="E96" t="str">
-        <v>undefined-undefined</v>
+        <v>24-25</v>
       </c>
       <c r="F96" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4080,11 +4347,14 @@
       <c r="C97" t="str">
         <v/>
       </c>
+      <c r="D97" t="str">
+        <v>Foongus</v>
+      </c>
       <c r="E97" t="str">
-        <v>undefined-undefined</v>
+        <v>24-25</v>
       </c>
       <c r="F97" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4118,11 +4388,14 @@
       <c r="C98" t="str">
         <v/>
       </c>
+      <c r="D98" t="str">
+        <v>Emolga</v>
+      </c>
       <c r="E98" t="str">
-        <v>undefined-undefined</v>
+        <v>24-25</v>
       </c>
       <c r="F98" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4156,11 +4429,14 @@
       <c r="C99" t="str">
         <v/>
       </c>
+      <c r="D99" t="str">
+        <v>Joltik</v>
+      </c>
       <c r="E99" t="str">
-        <v>undefined-undefined</v>
+        <v>24-25</v>
       </c>
       <c r="F99" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4194,11 +4470,14 @@
       <c r="C100" t="str">
         <v/>
       </c>
+      <c r="D100" t="str">
+        <v>Heracross</v>
+      </c>
       <c r="E100" t="str">
-        <v>undefined-undefined</v>
+        <v>25-26</v>
       </c>
       <c r="F100" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4207,7 +4486,7 @@
         <v>Yes</v>
       </c>
       <c r="I100" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J100" t="str">
         <v>NONONO</v>
@@ -4232,11 +4511,14 @@
       <c r="C101" t="str">
         <v/>
       </c>
+      <c r="D101" t="str">
+        <v>Pinsir</v>
+      </c>
       <c r="E101" t="str">
-        <v>undefined-undefined</v>
+        <v>25-26</v>
       </c>
       <c r="F101" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G101" t="str">
         <v/>
@@ -4245,7 +4527,7 @@
         <v>Yes</v>
       </c>
       <c r="I101" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J101" t="str">
         <v>NONONO</v>
@@ -4270,11 +4552,14 @@
       <c r="C102" t="str">
         <v/>
       </c>
+      <c r="D102" t="str">
+        <v>Gothita</v>
+      </c>
       <c r="E102" t="str">
-        <v>undefined-undefined</v>
+        <v>25-26</v>
       </c>
       <c r="F102" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G102" t="str">
         <v/>
@@ -4308,11 +4593,14 @@
       <c r="C103" t="str">
         <v/>
       </c>
+      <c r="D103" t="str">
+        <v>Minccino</v>
+      </c>
       <c r="E103" t="str">
-        <v>undefined-undefined</v>
+        <v>25-26</v>
       </c>
       <c r="F103" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G103" t="str">
         <v/>
@@ -4346,11 +4634,14 @@
       <c r="C104" t="str">
         <v/>
       </c>
+      <c r="D104" t="str">
+        <v>Trubbish</v>
+      </c>
       <c r="E104" t="str">
-        <v>undefined-undefined</v>
+        <v>25-26</v>
       </c>
       <c r="F104" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G104" t="str">
         <v/>
@@ -4384,11 +4675,14 @@
       <c r="C105" t="str">
         <v/>
       </c>
+      <c r="D105" t="str">
+        <v>Solosis</v>
+      </c>
       <c r="E105" t="str">
-        <v>undefined-undefined</v>
+        <v>25-26</v>
       </c>
       <c r="F105" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G105" t="str">
         <v/>
@@ -4422,11 +4716,14 @@
       <c r="C106" t="str">
         <v/>
       </c>
+      <c r="D106" t="str">
+        <v>Slakoth</v>
+      </c>
       <c r="E106" t="str">
-        <v>undefined-undefined</v>
+        <v>25-26</v>
       </c>
       <c r="F106" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G106" t="str">
         <v/>
@@ -4460,11 +4757,14 @@
       <c r="C107" t="str">
         <v/>
       </c>
+      <c r="D107" t="str">
+        <v>Leavanny</v>
+      </c>
       <c r="E107" t="str">
-        <v>undefined-undefined</v>
+        <v>25-26</v>
       </c>
       <c r="F107" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G107" t="str">
         <v/>
@@ -4473,7 +4773,7 @@
         <v>Yes</v>
       </c>
       <c r="I107" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J107" t="str">
         <v>NONONO</v>
@@ -4498,11 +4798,14 @@
       <c r="C108" t="str">
         <v/>
       </c>
+      <c r="D108" t="str">
+        <v>Cinccino</v>
+      </c>
       <c r="E108" t="str">
-        <v>undefined-undefined</v>
+        <v>25-26</v>
       </c>
       <c r="F108" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G108" t="str">
         <v/>
@@ -4536,11 +4839,14 @@
       <c r="C109" t="str">
         <v/>
       </c>
+      <c r="D109" t="str">
+        <v>Unfezant</v>
+      </c>
       <c r="E109" t="str">
-        <v>undefined-undefined</v>
+        <v>25-26</v>
       </c>
       <c r="F109" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G109" t="str">
         <v/>
@@ -4574,11 +4880,14 @@
       <c r="C110" t="str">
         <v/>
       </c>
+      <c r="D110" t="str">
+        <v>Remoraid</v>
+      </c>
       <c r="E110" t="str">
-        <v>undefined-undefined</v>
+        <v>27-28</v>
       </c>
       <c r="F110" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G110" t="str">
         <v/>
@@ -4612,11 +4921,14 @@
       <c r="C111" t="str">
         <v/>
       </c>
+      <c r="D111" t="str">
+        <v>Carvanha</v>
+      </c>
       <c r="E111" t="str">
-        <v>undefined-undefined</v>
+        <v>27-28</v>
       </c>
       <c r="F111" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G111" t="str">
         <v/>
@@ -4650,11 +4962,14 @@
       <c r="C112" t="str">
         <v/>
       </c>
+      <c r="D112" t="str">
+        <v>Chinchou</v>
+      </c>
       <c r="E112" t="str">
-        <v>undefined-undefined</v>
+        <v>27-28</v>
       </c>
       <c r="F112" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G112" t="str">
         <v/>
@@ -4688,11 +5003,14 @@
       <c r="C113" t="str">
         <v/>
       </c>
+      <c r="D113" t="str">
+        <v>Finneon</v>
+      </c>
       <c r="E113" t="str">
-        <v>undefined-undefined</v>
+        <v>27-28</v>
       </c>
       <c r="F113" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G113" t="str">
         <v/>
@@ -4726,11 +5044,14 @@
       <c r="C114" t="str">
         <v/>
       </c>
+      <c r="D114" t="str">
+        <v>Goldeen</v>
+      </c>
       <c r="E114" t="str">
-        <v>undefined-undefined</v>
+        <v>27-28</v>
       </c>
       <c r="F114" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G114" t="str">
         <v/>
@@ -4764,11 +5085,14 @@
       <c r="C115" t="str">
         <v/>
       </c>
+      <c r="D115" t="str">
+        <v>Luvdisc</v>
+      </c>
       <c r="E115" t="str">
-        <v>undefined-undefined</v>
+        <v>27-28</v>
       </c>
       <c r="F115" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G115" t="str">
         <v/>
@@ -4802,11 +5126,14 @@
       <c r="C116" t="str">
         <v/>
       </c>
+      <c r="D116" t="str">
+        <v>Shellder</v>
+      </c>
       <c r="E116" t="str">
-        <v>undefined-undefined</v>
+        <v>27-28</v>
       </c>
       <c r="F116" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G116" t="str">
         <v/>
@@ -4840,11 +5167,14 @@
       <c r="C117" t="str">
         <v/>
       </c>
+      <c r="D117" t="str">
+        <v>Swanna</v>
+      </c>
       <c r="E117" t="str">
-        <v>undefined-undefined</v>
+        <v>27-28</v>
       </c>
       <c r="F117" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G117" t="str">
         <v/>
@@ -4919,11 +5249,14 @@
       <c r="C119" t="str">
         <v/>
       </c>
+      <c r="D119" t="str">
+        <v>Deerling</v>
+      </c>
       <c r="E119" t="str">
-        <v>undefined-undefined</v>
+        <v>29-30</v>
       </c>
       <c r="F119" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G119" t="str">
         <v/>
@@ -4957,11 +5290,14 @@
       <c r="C120" t="str">
         <v/>
       </c>
+      <c r="D120" t="str">
+        <v>Karrablast</v>
+      </c>
       <c r="E120" t="str">
-        <v>undefined-undefined</v>
+        <v>29-30</v>
       </c>
       <c r="F120" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G120" t="str">
         <v/>
@@ -4995,11 +5331,14 @@
       <c r="C121" t="str">
         <v/>
       </c>
+      <c r="D121" t="str">
+        <v>Trubbish</v>
+      </c>
       <c r="E121" t="str">
-        <v>undefined-undefined</v>
+        <v>29-30</v>
       </c>
       <c r="F121" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G121" t="str">
         <v/>
@@ -5033,11 +5372,14 @@
       <c r="C122" t="str">
         <v/>
       </c>
+      <c r="D122" t="str">
+        <v>Foongus</v>
+      </c>
       <c r="E122" t="str">
-        <v>undefined-undefined</v>
+        <v>29-30</v>
       </c>
       <c r="F122" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G122" t="str">
         <v/>
@@ -5071,11 +5413,14 @@
       <c r="C123" t="str">
         <v/>
       </c>
+      <c r="D123" t="str">
+        <v>Vanillite</v>
+      </c>
       <c r="E123" t="str">
-        <v>undefined-undefined</v>
+        <v>29-30</v>
       </c>
       <c r="F123" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G123" t="str">
         <v/>
@@ -5109,11 +5454,14 @@
       <c r="C124" t="str">
         <v/>
       </c>
+      <c r="D124" t="str">
+        <v>Castform</v>
+      </c>
       <c r="E124" t="str">
-        <v>undefined-undefined</v>
+        <v>29-30</v>
       </c>
       <c r="F124" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G124" t="str">
         <v/>
@@ -5147,11 +5495,14 @@
       <c r="C125" t="str">
         <v/>
       </c>
+      <c r="D125" t="str">
+        <v>Swadloon</v>
+      </c>
       <c r="E125" t="str">
-        <v>undefined-undefined</v>
+        <v>29-30</v>
       </c>
       <c r="F125" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G125" t="str">
         <v/>
@@ -5185,11 +5536,14 @@
       <c r="C126" t="str">
         <v/>
       </c>
+      <c r="D126" t="str">
+        <v>Sawsbuck</v>
+      </c>
       <c r="E126" t="str">
-        <v>undefined-undefined</v>
+        <v>29-30</v>
       </c>
       <c r="F126" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G126" t="str">
         <v/>
@@ -5223,11 +5577,14 @@
       <c r="C127" t="str">
         <v/>
       </c>
+      <c r="D127" t="str">
+        <v>Escavalier</v>
+      </c>
       <c r="E127" t="str">
-        <v>undefined-undefined</v>
+        <v>29-30</v>
       </c>
       <c r="F127" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G127" t="str">
         <v/>
@@ -5261,11 +5618,14 @@
       <c r="C128" t="str">
         <v/>
       </c>
+      <c r="D128" t="str">
+        <v>Accelgor</v>
+      </c>
       <c r="E128" t="str">
-        <v>undefined-undefined</v>
+        <v>29-30</v>
       </c>
       <c r="F128" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G128" t="str">
         <v/>
@@ -5299,11 +5659,14 @@
       <c r="C129" t="str">
         <v/>
       </c>
+      <c r="D129" t="str">
+        <v>Joltik</v>
+      </c>
       <c r="E129" t="str">
-        <v>undefined-undefined</v>
+        <v>30-31</v>
       </c>
       <c r="F129" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G129" t="str">
         <v/>
@@ -5337,11 +5700,14 @@
       <c r="C130" t="str">
         <v/>
       </c>
+      <c r="D130" t="str">
+        <v>Klink</v>
+      </c>
       <c r="E130" t="str">
-        <v>undefined-undefined</v>
+        <v>30-31</v>
       </c>
       <c r="F130" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G130" t="str">
         <v/>
@@ -5375,11 +5741,14 @@
       <c r="C131" t="str">
         <v/>
       </c>
+      <c r="D131" t="str">
+        <v>Ferroseed</v>
+      </c>
       <c r="E131" t="str">
-        <v>undefined-undefined</v>
+        <v>30-31</v>
       </c>
       <c r="F131" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G131" t="str">
         <v/>
@@ -5413,11 +5782,14 @@
       <c r="C132" t="str">
         <v/>
       </c>
+      <c r="D132" t="str">
+        <v>Tynamo</v>
+      </c>
       <c r="E132" t="str">
-        <v>undefined-undefined</v>
+        <v>30-31</v>
       </c>
       <c r="F132" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G132" t="str">
         <v/>
@@ -5451,11 +5823,14 @@
       <c r="C133" t="str">
         <v/>
       </c>
+      <c r="D133" t="str">
+        <v>Aron</v>
+      </c>
       <c r="E133" t="str">
-        <v>undefined-undefined</v>
+        <v>30-31</v>
       </c>
       <c r="F133" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G133" t="str">
         <v/>
@@ -5489,11 +5864,14 @@
       <c r="C134" t="str">
         <v/>
       </c>
+      <c r="D134" t="str">
+        <v>Magneton</v>
+      </c>
       <c r="E134" t="str">
-        <v>undefined-undefined</v>
+        <v>30-31</v>
       </c>
       <c r="F134" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G134" t="str">
         <v/>
@@ -5527,11 +5905,14 @@
       <c r="C135" t="str">
         <v/>
       </c>
+      <c r="D135" t="str">
+        <v>Klang</v>
+      </c>
       <c r="E135" t="str">
-        <v>undefined-undefined</v>
+        <v>30-31</v>
       </c>
       <c r="F135" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G135" t="str">
         <v/>
@@ -5565,11 +5946,14 @@
       <c r="C136" t="str">
         <v/>
       </c>
+      <c r="D136" t="str">
+        <v>Galvantula</v>
+      </c>
       <c r="E136" t="str">
-        <v>undefined-undefined</v>
+        <v>30-31</v>
       </c>
       <c r="F136" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G136" t="str">
         <v/>
@@ -5644,11 +6028,14 @@
       <c r="C138" t="str">
         <v/>
       </c>
+      <c r="D138" t="str">
+        <v>Deerling</v>
+      </c>
       <c r="E138" t="str">
-        <v>undefined-undefined</v>
+        <v>32-33</v>
       </c>
       <c r="F138" t="str">
-        <v>0.1112%</v>
+        <v>11%</v>
       </c>
       <c r="G138" t="str">
         <v/>
@@ -5682,11 +6069,14 @@
       <c r="C139" t="str">
         <v/>
       </c>
+      <c r="D139" t="str">
+        <v>Watchog</v>
+      </c>
       <c r="E139" t="str">
-        <v>undefined-undefined</v>
+        <v>32-33</v>
       </c>
       <c r="F139" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G139" t="str">
         <v/>
@@ -5720,11 +6110,14 @@
       <c r="C140" t="str">
         <v/>
       </c>
+      <c r="D140" t="str">
+        <v>Foongus</v>
+      </c>
       <c r="E140" t="str">
-        <v>undefined-undefined</v>
+        <v>32-33</v>
       </c>
       <c r="F140" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G140" t="str">
         <v/>
@@ -5758,11 +6151,14 @@
       <c r="C141" t="str">
         <v/>
       </c>
+      <c r="D141" t="str">
+        <v>Cubchoo</v>
+      </c>
       <c r="E141" t="str">
-        <v>undefined-undefined</v>
+        <v>32-33</v>
       </c>
       <c r="F141" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G141" t="str">
         <v/>
@@ -5796,11 +6192,14 @@
       <c r="C142" t="str">
         <v/>
       </c>
+      <c r="D142" t="str">
+        <v>Zebstrika</v>
+      </c>
       <c r="E142" t="str">
-        <v>undefined-undefined</v>
+        <v>32-33</v>
       </c>
       <c r="F142" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G142" t="str">
         <v/>
@@ -5834,11 +6233,14 @@
       <c r="C143" t="str">
         <v/>
       </c>
+      <c r="D143" t="str">
+        <v>Zangoose</v>
+      </c>
       <c r="E143" t="str">
-        <v>undefined-undefined</v>
+        <v>32-33</v>
       </c>
       <c r="F143" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G143" t="str">
         <v/>
@@ -5872,11 +6274,14 @@
       <c r="C144" t="str">
         <v/>
       </c>
+      <c r="D144" t="str">
+        <v>Seviper</v>
+      </c>
       <c r="E144" t="str">
-        <v>undefined-undefined</v>
+        <v>32-33</v>
       </c>
       <c r="F144" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G144" t="str">
         <v/>
@@ -5910,11 +6315,14 @@
       <c r="C145" t="str">
         <v/>
       </c>
+      <c r="D145" t="str">
+        <v>Zoroark</v>
+      </c>
       <c r="E145" t="str">
-        <v>undefined-undefined</v>
+        <v>32-33</v>
       </c>
       <c r="F145" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G145" t="str">
         <v/>
@@ -5923,7 +6331,7 @@
         <v>Yes</v>
       </c>
       <c r="I145" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J145" t="str">
         <v>NONONO</v>
@@ -5948,11 +6356,14 @@
       <c r="C146" t="str">
         <v/>
       </c>
+      <c r="D146" t="str">
+        <v>Tranquill</v>
+      </c>
       <c r="E146" t="str">
-        <v>undefined-undefined</v>
+        <v>32-33</v>
       </c>
       <c r="F146" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G146" t="str">
         <v/>
@@ -5986,11 +6397,14 @@
       <c r="C147" t="str">
         <v/>
       </c>
+      <c r="D147" t="str">
+        <v>Litwick</v>
+      </c>
       <c r="E147" t="str">
-        <v>undefined-undefined</v>
+        <v>34-35</v>
       </c>
       <c r="F147" t="str">
-        <v>0.1665%</v>
+        <v>17%</v>
       </c>
       <c r="G147" t="str">
         <v/>
@@ -6024,11 +6438,14 @@
       <c r="C148" t="str">
         <v/>
       </c>
+      <c r="D148" t="str">
+        <v>Elgyem</v>
+      </c>
       <c r="E148" t="str">
-        <v>undefined-undefined</v>
+        <v>34-35</v>
       </c>
       <c r="F148" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G148" t="str">
         <v/>
@@ -6062,11 +6479,14 @@
       <c r="C149" t="str">
         <v/>
       </c>
+      <c r="D149" t="str">
+        <v>Golbat</v>
+      </c>
       <c r="E149" t="str">
-        <v>undefined-undefined</v>
+        <v>34-35</v>
       </c>
       <c r="F149" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G149" t="str">
         <v/>
@@ -6100,11 +6520,14 @@
       <c r="C150" t="str">
         <v/>
       </c>
+      <c r="D150" t="str">
+        <v>Lampent</v>
+      </c>
       <c r="E150" t="str">
-        <v>undefined-undefined</v>
+        <v>34-35</v>
       </c>
       <c r="F150" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G150" t="str">
         <v/>
@@ -6138,11 +6561,14 @@
       <c r="C151" t="str">
         <v/>
       </c>
+      <c r="D151" t="str">
+        <v>Musharna</v>
+      </c>
       <c r="E151" t="str">
-        <v>undefined-undefined</v>
+        <v>34-35</v>
       </c>
       <c r="F151" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G151" t="str">
         <v/>
@@ -6176,11 +6602,14 @@
       <c r="C152" t="str">
         <v/>
       </c>
+      <c r="D152" t="str">
+        <v>Swoobat</v>
+      </c>
       <c r="E152" t="str">
-        <v>undefined-undefined</v>
+        <v>34-35</v>
       </c>
       <c r="F152" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G152" t="str">
         <v/>
@@ -6296,11 +6725,14 @@
       <c r="C155" t="str">
         <v/>
       </c>
+      <c r="D155" t="str">
+        <v>Skarmory</v>
+      </c>
       <c r="E155" t="str">
-        <v>undefined-undefined</v>
+        <v>37-38</v>
       </c>
       <c r="F155" t="str">
-        <v>0.1112%</v>
+        <v>11%</v>
       </c>
       <c r="G155" t="str">
         <v/>
@@ -6334,11 +6766,14 @@
       <c r="C156" t="str">
         <v/>
       </c>
+      <c r="D156" t="str">
+        <v>Camerupt</v>
+      </c>
       <c r="E156" t="str">
-        <v>undefined-undefined</v>
+        <v>37-38</v>
       </c>
       <c r="F156" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G156" t="str">
         <v/>
@@ -6372,11 +6807,14 @@
       <c r="C157" t="str">
         <v/>
       </c>
+      <c r="D157" t="str">
+        <v>Excadrill</v>
+      </c>
       <c r="E157" t="str">
-        <v>undefined-undefined</v>
+        <v>37-38</v>
       </c>
       <c r="F157" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G157" t="str">
         <v/>
@@ -6385,7 +6823,7 @@
         <v>Yes</v>
       </c>
       <c r="I157" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J157" t="str">
         <v>NONONO</v>
@@ -6410,11 +6848,14 @@
       <c r="C158" t="str">
         <v/>
       </c>
+      <c r="D158" t="str">
+        <v>Lopunny</v>
+      </c>
       <c r="E158" t="str">
-        <v>undefined-undefined</v>
+        <v>37-38</v>
       </c>
       <c r="F158" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G158" t="str">
         <v/>
@@ -6448,11 +6889,14 @@
       <c r="C159" t="str">
         <v/>
       </c>
+      <c r="D159" t="str">
+        <v>Skorupi</v>
+      </c>
       <c r="E159" t="str">
-        <v>undefined-undefined</v>
+        <v>37-38</v>
       </c>
       <c r="F159" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G159" t="str">
         <v/>
@@ -6486,11 +6930,14 @@
       <c r="C160" t="str">
         <v/>
       </c>
+      <c r="D160" t="str">
+        <v>Numel</v>
+      </c>
       <c r="E160" t="str">
-        <v>undefined-undefined</v>
+        <v>37-38</v>
       </c>
       <c r="F160" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G160" t="str">
         <v/>
@@ -6524,11 +6971,14 @@
       <c r="C161" t="str">
         <v/>
       </c>
+      <c r="D161" t="str">
+        <v>Magmar</v>
+      </c>
       <c r="E161" t="str">
-        <v>undefined-undefined</v>
+        <v>37-38</v>
       </c>
       <c r="F161" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G161" t="str">
         <v/>
@@ -6562,11 +7012,14 @@
       <c r="C162" t="str">
         <v/>
       </c>
+      <c r="D162" t="str">
+        <v>Vibrava</v>
+      </c>
       <c r="E162" t="str">
-        <v>undefined-undefined</v>
+        <v>37-38</v>
       </c>
       <c r="F162" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G162" t="str">
         <v/>
@@ -6600,11 +7053,14 @@
       <c r="C163" t="str">
         <v/>
       </c>
+      <c r="D163" t="str">
+        <v>Flygon</v>
+      </c>
       <c r="E163" t="str">
-        <v>undefined-undefined</v>
+        <v>37-38</v>
       </c>
       <c r="F163" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G163" t="str">
         <v/>
@@ -6613,7 +7069,7 @@
         <v>Yes</v>
       </c>
       <c r="I163" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J163" t="str">
         <v>NONONO</v>
@@ -6638,11 +7094,14 @@
       <c r="C164" t="str">
         <v/>
       </c>
+      <c r="D164" t="str">
+        <v>Litwick</v>
+      </c>
       <c r="E164" t="str">
-        <v>undefined-undefined</v>
+        <v>38-39</v>
       </c>
       <c r="F164" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G164" t="str">
         <v/>
@@ -6676,11 +7135,14 @@
       <c r="C165" t="str">
         <v/>
       </c>
+      <c r="D165" t="str">
+        <v>Raticate</v>
+      </c>
       <c r="E165" t="str">
-        <v>undefined-undefined</v>
+        <v>38-39</v>
       </c>
       <c r="F165" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G165" t="str">
         <v/>
@@ -6714,11 +7176,14 @@
       <c r="C166" t="str">
         <v/>
       </c>
+      <c r="D166" t="str">
+        <v>Golbat</v>
+      </c>
       <c r="E166" t="str">
-        <v>undefined-undefined</v>
+        <v>38-39</v>
       </c>
       <c r="F166" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G166" t="str">
         <v/>
@@ -6752,11 +7217,14 @@
       <c r="C167" t="str">
         <v/>
       </c>
+      <c r="D167" t="str">
+        <v>Banette</v>
+      </c>
       <c r="E167" t="str">
-        <v>undefined-undefined</v>
+        <v>38-39</v>
       </c>
       <c r="F167" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G167" t="str">
         <v/>
@@ -6790,11 +7258,14 @@
       <c r="C168" t="str">
         <v/>
       </c>
+      <c r="D168" t="str">
+        <v>Gothita</v>
+      </c>
       <c r="E168" t="str">
-        <v>undefined-undefined</v>
+        <v>38-39</v>
       </c>
       <c r="F168" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G168" t="str">
         <v/>
@@ -6828,11 +7299,14 @@
       <c r="C169" t="str">
         <v/>
       </c>
+      <c r="D169" t="str">
+        <v>Solosis</v>
+      </c>
       <c r="E169" t="str">
-        <v>undefined-undefined</v>
+        <v>38-39</v>
       </c>
       <c r="F169" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G169" t="str">
         <v/>
@@ -6866,11 +7340,14 @@
       <c r="C170" t="str">
         <v/>
       </c>
+      <c r="D170" t="str">
+        <v>Gothorita</v>
+      </c>
       <c r="E170" t="str">
-        <v>undefined-undefined</v>
+        <v>38-39</v>
       </c>
       <c r="F170" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G170" t="str">
         <v/>
@@ -6904,11 +7381,14 @@
       <c r="C171" t="str">
         <v/>
       </c>
+      <c r="D171" t="str">
+        <v>Duosion</v>
+      </c>
       <c r="E171" t="str">
-        <v>undefined-undefined</v>
+        <v>38-39</v>
       </c>
       <c r="F171" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G171" t="str">
         <v/>
@@ -6942,11 +7422,14 @@
       <c r="C172" t="str">
         <v/>
       </c>
+      <c r="D172" t="str">
+        <v>Shuppet</v>
+      </c>
       <c r="E172" t="str">
-        <v>undefined-undefined</v>
+        <v>38-39</v>
       </c>
       <c r="F172" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G172" t="str">
         <v/>
@@ -6980,11 +7463,14 @@
       <c r="C173" t="str">
         <v/>
       </c>
+      <c r="D173" t="str">
+        <v>Chandelure</v>
+      </c>
       <c r="E173" t="str">
-        <v>undefined-undefined</v>
+        <v>38-39</v>
       </c>
       <c r="F173" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G173" t="str">
         <v/>
@@ -6993,7 +7479,7 @@
         <v>Yes</v>
       </c>
       <c r="I173" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J173" t="str">
         <v>NONONO</v>
@@ -7059,11 +7545,14 @@
       <c r="C175" t="str">
         <v/>
       </c>
+      <c r="D175" t="str">
+        <v>Barboach</v>
+      </c>
       <c r="E175" t="str">
-        <v>undefined-undefined</v>
+        <v>41-42</v>
       </c>
       <c r="F175" t="str">
-        <v>0.0837%</v>
+        <v>8%</v>
       </c>
       <c r="G175" t="str">
         <v/>
@@ -7097,11 +7586,14 @@
       <c r="C176" t="str">
         <v/>
       </c>
+      <c r="D176" t="str">
+        <v>Poliwag</v>
+      </c>
       <c r="E176" t="str">
-        <v>undefined-undefined</v>
+        <v>41-42</v>
       </c>
       <c r="F176" t="str">
-        <v>0.0833%</v>
+        <v>8%</v>
       </c>
       <c r="G176" t="str">
         <v/>
@@ -7135,11 +7627,14 @@
       <c r="C177" t="str">
         <v/>
       </c>
+      <c r="D177" t="str">
+        <v>Buizel</v>
+      </c>
       <c r="E177" t="str">
-        <v>undefined-undefined</v>
+        <v>41-42</v>
       </c>
       <c r="F177" t="str">
-        <v>0.0833%</v>
+        <v>8%</v>
       </c>
       <c r="G177" t="str">
         <v/>
@@ -7173,11 +7668,14 @@
       <c r="C178" t="str">
         <v/>
       </c>
+      <c r="D178" t="str">
+        <v>Lumineon</v>
+      </c>
       <c r="E178" t="str">
-        <v>undefined-undefined</v>
+        <v>41-42</v>
       </c>
       <c r="F178" t="str">
-        <v>0.0833%</v>
+        <v>8%</v>
       </c>
       <c r="G178" t="str">
         <v/>
@@ -7211,11 +7709,14 @@
       <c r="C179" t="str">
         <v/>
       </c>
+      <c r="D179" t="str">
+        <v>Corphish</v>
+      </c>
       <c r="E179" t="str">
-        <v>undefined-undefined</v>
+        <v>41-42</v>
       </c>
       <c r="F179" t="str">
-        <v>0.0833%</v>
+        <v>8%</v>
       </c>
       <c r="G179" t="str">
         <v/>
@@ -7249,11 +7750,14 @@
       <c r="C180" t="str">
         <v/>
       </c>
+      <c r="D180" t="str">
+        <v>Frillish</v>
+      </c>
       <c r="E180" t="str">
-        <v>undefined-undefined</v>
+        <v>41-42</v>
       </c>
       <c r="F180" t="str">
-        <v>0.0833%</v>
+        <v>8%</v>
       </c>
       <c r="G180" t="str">
         <v/>
@@ -7287,11 +7791,14 @@
       <c r="C181" t="str">
         <v/>
       </c>
+      <c r="D181" t="str">
+        <v>Kingler</v>
+      </c>
       <c r="E181" t="str">
-        <v>undefined-undefined</v>
+        <v>41-42</v>
       </c>
       <c r="F181" t="str">
-        <v>0.0833%</v>
+        <v>8%</v>
       </c>
       <c r="G181" t="str">
         <v/>
@@ -7325,11 +7832,14 @@
       <c r="C182" t="str">
         <v/>
       </c>
+      <c r="D182" t="str">
+        <v>Marill</v>
+      </c>
       <c r="E182" t="str">
-        <v>undefined-undefined</v>
+        <v>41-42</v>
       </c>
       <c r="F182" t="str">
-        <v>0.0833%</v>
+        <v>8%</v>
       </c>
       <c r="G182" t="str">
         <v/>
@@ -7363,11 +7873,14 @@
       <c r="C183" t="str">
         <v/>
       </c>
+      <c r="D183" t="str">
+        <v>Wailmer</v>
+      </c>
       <c r="E183" t="str">
-        <v>undefined-undefined</v>
+        <v>41-42</v>
       </c>
       <c r="F183" t="str">
-        <v>0.0833%</v>
+        <v>8%</v>
       </c>
       <c r="G183" t="str">
         <v/>
@@ -7401,11 +7914,14 @@
       <c r="C184" t="str">
         <v/>
       </c>
+      <c r="D184" t="str">
+        <v>Mantine</v>
+      </c>
       <c r="E184" t="str">
-        <v>undefined-undefined</v>
+        <v>41-42</v>
       </c>
       <c r="F184" t="str">
-        <v>0.0833%</v>
+        <v>8%</v>
       </c>
       <c r="G184" t="str">
         <v/>
@@ -7439,11 +7955,14 @@
       <c r="C185" t="str">
         <v/>
       </c>
+      <c r="D185" t="str">
+        <v>Starmie</v>
+      </c>
       <c r="E185" t="str">
-        <v>undefined-undefined</v>
+        <v>41-42</v>
       </c>
       <c r="F185" t="str">
-        <v>0.0833%</v>
+        <v>8%</v>
       </c>
       <c r="G185" t="str">
         <v/>
@@ -7452,7 +7971,7 @@
         <v>Yes</v>
       </c>
       <c r="I185" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J185" t="str">
         <v>NONONO</v>
@@ -7477,11 +7996,14 @@
       <c r="C186" t="str">
         <v/>
       </c>
+      <c r="D186" t="str">
+        <v>Wailord</v>
+      </c>
       <c r="E186" t="str">
-        <v>undefined-undefined</v>
+        <v>41-42</v>
       </c>
       <c r="F186" t="str">
-        <v>0.0833%</v>
+        <v>8%</v>
       </c>
       <c r="G186" t="str">
         <v/>
@@ -7490,7 +8012,7 @@
         <v>Yes</v>
       </c>
       <c r="I186" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J186" t="str">
         <v>NONONO</v>
@@ -7515,11 +8037,14 @@
       <c r="C187" t="str">
         <v/>
       </c>
+      <c r="D187" t="str">
+        <v>Tangela</v>
+      </c>
       <c r="E187" t="str">
-        <v>undefined-undefined</v>
+        <v>42-43</v>
       </c>
       <c r="F187" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G187" t="str">
         <v/>
@@ -7553,11 +8078,14 @@
       <c r="C188" t="str">
         <v/>
       </c>
+      <c r="D188" t="str">
+        <v>Drifblim</v>
+      </c>
       <c r="E188" t="str">
-        <v>undefined-undefined</v>
+        <v>42-43</v>
       </c>
       <c r="F188" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G188" t="str">
         <v/>
@@ -7591,11 +8119,14 @@
       <c r="C189" t="str">
         <v/>
       </c>
+      <c r="D189" t="str">
+        <v>Pelipper</v>
+      </c>
       <c r="E189" t="str">
-        <v>undefined-undefined</v>
+        <v>42-43</v>
       </c>
       <c r="F189" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G189" t="str">
         <v/>
@@ -7629,11 +8160,14 @@
       <c r="C190" t="str">
         <v/>
       </c>
+      <c r="D190" t="str">
+        <v>Absol</v>
+      </c>
       <c r="E190" t="str">
-        <v>undefined-undefined</v>
+        <v>42-43</v>
       </c>
       <c r="F190" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G190" t="str">
         <v/>
@@ -7667,11 +8201,14 @@
       <c r="C191" t="str">
         <v/>
       </c>
+      <c r="D191" t="str">
+        <v>Floatzel</v>
+      </c>
       <c r="E191" t="str">
-        <v>undefined-undefined</v>
+        <v>42-43</v>
       </c>
       <c r="F191" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G191" t="str">
         <v/>
@@ -7705,11 +8242,14 @@
       <c r="C192" t="str">
         <v/>
       </c>
+      <c r="D192" t="str">
+        <v>Drifloon</v>
+      </c>
       <c r="E192" t="str">
-        <v>undefined-undefined</v>
+        <v>42-43</v>
       </c>
       <c r="F192" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G192" t="str">
         <v/>
@@ -7743,11 +8283,14 @@
       <c r="C193" t="str">
         <v/>
       </c>
+      <c r="D193" t="str">
+        <v>Swanna</v>
+      </c>
       <c r="E193" t="str">
-        <v>undefined-undefined</v>
+        <v>42-43</v>
       </c>
       <c r="F193" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G193" t="str">
         <v/>
@@ -7781,11 +8324,14 @@
       <c r="C194" t="str">
         <v/>
       </c>
+      <c r="D194" t="str">
+        <v>Seismitoad</v>
+      </c>
       <c r="E194" t="str">
-        <v>undefined-undefined</v>
+        <v>42-43</v>
       </c>
       <c r="F194" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G194" t="str">
         <v/>
@@ -7794,7 +8340,7 @@
         <v>Yes</v>
       </c>
       <c r="I194" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J194" t="str">
         <v>NONONO</v>
@@ -7819,11 +8365,14 @@
       <c r="C195" t="str">
         <v/>
       </c>
+      <c r="D195" t="str">
+        <v>Altaria</v>
+      </c>
       <c r="E195" t="str">
-        <v>undefined-undefined</v>
+        <v>43-44</v>
       </c>
       <c r="F195" t="str">
-        <v>0.1665%</v>
+        <v>17%</v>
       </c>
       <c r="G195" t="str">
         <v/>
@@ -7857,11 +8406,14 @@
       <c r="C196" t="str">
         <v/>
       </c>
+      <c r="D196" t="str">
+        <v>Absol</v>
+      </c>
       <c r="E196" t="str">
-        <v>undefined-undefined</v>
+        <v>43-44</v>
       </c>
       <c r="F196" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G196" t="str">
         <v/>
@@ -7895,11 +8447,14 @@
       <c r="C197" t="str">
         <v/>
       </c>
+      <c r="D197" t="str">
+        <v>Mienfoo</v>
+      </c>
       <c r="E197" t="str">
-        <v>undefined-undefined</v>
+        <v>43-44</v>
       </c>
       <c r="F197" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G197" t="str">
         <v/>
@@ -7933,11 +8488,14 @@
       <c r="C198" t="str">
         <v/>
       </c>
+      <c r="D198" t="str">
+        <v>Golduck</v>
+      </c>
       <c r="E198" t="str">
-        <v>undefined-undefined</v>
+        <v>43-44</v>
       </c>
       <c r="F198" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G198" t="str">
         <v/>
@@ -7946,7 +8504,7 @@
         <v>Yes</v>
       </c>
       <c r="I198" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J198" t="str">
         <v>NONONO</v>
@@ -7971,11 +8529,14 @@
       <c r="C199" t="str">
         <v/>
       </c>
+      <c r="D199" t="str">
+        <v>Swablu</v>
+      </c>
       <c r="E199" t="str">
-        <v>undefined-undefined</v>
+        <v>43-44</v>
       </c>
       <c r="F199" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G199" t="str">
         <v/>
@@ -8009,11 +8570,14 @@
       <c r="C200" t="str">
         <v/>
       </c>
+      <c r="D200" t="str">
+        <v>Tropius</v>
+      </c>
       <c r="E200" t="str">
-        <v>undefined-undefined</v>
+        <v>43-44</v>
       </c>
       <c r="F200" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G200" t="str">
         <v/>
@@ -8047,11 +8611,14 @@
       <c r="C201" t="str">
         <v/>
       </c>
+      <c r="D201" t="str">
+        <v>Vulpix</v>
+      </c>
       <c r="E201" t="str">
-        <v>undefined-undefined</v>
+        <v>44-45</v>
       </c>
       <c r="F201" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G201" t="str">
         <v/>
@@ -8085,11 +8652,14 @@
       <c r="C202" t="str">
         <v/>
       </c>
+      <c r="D202" t="str">
+        <v>Bronzong</v>
+      </c>
       <c r="E202" t="str">
-        <v>undefined-undefined</v>
+        <v>44-45</v>
       </c>
       <c r="F202" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G202" t="str">
         <v/>
@@ -8098,7 +8668,7 @@
         <v>Yes</v>
       </c>
       <c r="I202" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J202" t="str">
         <v>NONONO</v>
@@ -8123,11 +8693,14 @@
       <c r="C203" t="str">
         <v/>
       </c>
+      <c r="D203" t="str">
+        <v>Swablu</v>
+      </c>
       <c r="E203" t="str">
-        <v>undefined-undefined</v>
+        <v>44-45</v>
       </c>
       <c r="F203" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G203" t="str">
         <v/>
@@ -8161,11 +8734,14 @@
       <c r="C204" t="str">
         <v/>
       </c>
+      <c r="D204" t="str">
+        <v>Chimecho</v>
+      </c>
       <c r="E204" t="str">
-        <v>undefined-undefined</v>
+        <v>44-45</v>
       </c>
       <c r="F204" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G204" t="str">
         <v/>
@@ -8199,11 +8775,14 @@
       <c r="C205" t="str">
         <v/>
       </c>
+      <c r="D205" t="str">
+        <v>Gothitelle</v>
+      </c>
       <c r="E205" t="str">
-        <v>undefined-undefined</v>
+        <v>44-45</v>
       </c>
       <c r="F205" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G205" t="str">
         <v/>
@@ -8319,11 +8898,14 @@
       <c r="C208" t="str">
         <v/>
       </c>
+      <c r="D208" t="str">
+        <v>Gligar</v>
+      </c>
       <c r="E208" t="str">
-        <v>undefined-undefined</v>
+        <v>48-49</v>
       </c>
       <c r="F208" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G208" t="str">
         <v/>
@@ -8357,11 +8939,14 @@
       <c r="C209" t="str">
         <v/>
       </c>
+      <c r="D209" t="str">
+        <v>Zangoose</v>
+      </c>
       <c r="E209" t="str">
-        <v>undefined-undefined</v>
+        <v>48-49</v>
       </c>
       <c r="F209" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G209" t="str">
         <v/>
@@ -8395,11 +8980,14 @@
       <c r="C210" t="str">
         <v/>
       </c>
+      <c r="D210" t="str">
+        <v>Seviper</v>
+      </c>
       <c r="E210" t="str">
-        <v>undefined-undefined</v>
+        <v>48-49</v>
       </c>
       <c r="F210" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G210" t="str">
         <v/>
@@ -8433,11 +9021,14 @@
       <c r="C211" t="str">
         <v/>
       </c>
+      <c r="D211" t="str">
+        <v>Karrablast</v>
+      </c>
       <c r="E211" t="str">
-        <v>undefined-undefined</v>
+        <v>48-49</v>
       </c>
       <c r="F211" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G211" t="str">
         <v/>
@@ -8471,11 +9062,14 @@
       <c r="C212" t="str">
         <v/>
       </c>
+      <c r="D212" t="str">
+        <v>Shelmet</v>
+      </c>
       <c r="E212" t="str">
-        <v>undefined-undefined</v>
+        <v>48-49</v>
       </c>
       <c r="F212" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G212" t="str">
         <v/>
@@ -8509,11 +9103,14 @@
       <c r="C213" t="str">
         <v/>
       </c>
+      <c r="D213" t="str">
+        <v>Bibarel</v>
+      </c>
       <c r="E213" t="str">
-        <v>undefined-undefined</v>
+        <v>49-50</v>
       </c>
       <c r="F213" t="str">
-        <v>0.1665%</v>
+        <v>17%</v>
       </c>
       <c r="G213" t="str">
         <v/>
@@ -8547,11 +9144,14 @@
       <c r="C214" t="str">
         <v/>
       </c>
+      <c r="D214" t="str">
+        <v>Zebstrika</v>
+      </c>
       <c r="E214" t="str">
-        <v>undefined-undefined</v>
+        <v>49-50</v>
       </c>
       <c r="F214" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G214" t="str">
         <v/>
@@ -8585,11 +9185,14 @@
       <c r="C215" t="str">
         <v/>
       </c>
+      <c r="D215" t="str">
+        <v>Pelipper</v>
+      </c>
       <c r="E215" t="str">
-        <v>undefined-undefined</v>
+        <v>49-50</v>
       </c>
       <c r="F215" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G215" t="str">
         <v/>
@@ -8623,11 +9226,14 @@
       <c r="C216" t="str">
         <v/>
       </c>
+      <c r="D216" t="str">
+        <v>Dunsparce</v>
+      </c>
       <c r="E216" t="str">
-        <v>undefined-undefined</v>
+        <v>49-50</v>
       </c>
       <c r="F216" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G216" t="str">
         <v/>
@@ -8661,11 +9267,14 @@
       <c r="C217" t="str">
         <v/>
       </c>
+      <c r="D217" t="str">
+        <v>Loudred</v>
+      </c>
       <c r="E217" t="str">
-        <v>undefined-undefined</v>
+        <v>49-50</v>
       </c>
       <c r="F217" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G217" t="str">
         <v/>
@@ -8699,11 +9308,14 @@
       <c r="C218" t="str">
         <v/>
       </c>
+      <c r="D218" t="str">
+        <v>Azumarill</v>
+      </c>
       <c r="E218" t="str">
-        <v>undefined-undefined</v>
+        <v>49-50</v>
       </c>
       <c r="F218" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G218" t="str">
         <v/>
@@ -8737,11 +9349,14 @@
       <c r="C219" t="str">
         <v/>
       </c>
+      <c r="D219" t="str">
+        <v>Sewaddle</v>
+      </c>
       <c r="E219" t="str">
-        <v>undefined-undefined</v>
+        <v>50-51</v>
       </c>
       <c r="F219" t="str">
-        <v>0.1426%</v>
+        <v>14%</v>
       </c>
       <c r="G219" t="str">
         <v/>
@@ -8775,11 +9390,14 @@
       <c r="C220" t="str">
         <v/>
       </c>
+      <c r="D220" t="str">
+        <v>Tranquill</v>
+      </c>
       <c r="E220" t="str">
-        <v>undefined-undefined</v>
+        <v>50-51</v>
       </c>
       <c r="F220" t="str">
-        <v>0.1429%</v>
+        <v>14%</v>
       </c>
       <c r="G220" t="str">
         <v/>
@@ -8813,11 +9431,14 @@
       <c r="C221" t="str">
         <v/>
       </c>
+      <c r="D221" t="str">
+        <v>Roselia</v>
+      </c>
       <c r="E221" t="str">
-        <v>undefined-undefined</v>
+        <v>50-51</v>
       </c>
       <c r="F221" t="str">
-        <v>0.1429%</v>
+        <v>14%</v>
       </c>
       <c r="G221" t="str">
         <v/>
@@ -8851,11 +9472,14 @@
       <c r="C222" t="str">
         <v/>
       </c>
+      <c r="D222" t="str">
+        <v>Combee</v>
+      </c>
       <c r="E222" t="str">
-        <v>undefined-undefined</v>
+        <v>50-51</v>
       </c>
       <c r="F222" t="str">
-        <v>0.1429%</v>
+        <v>14%</v>
       </c>
       <c r="G222" t="str">
         <v/>
@@ -8889,11 +9513,14 @@
       <c r="C223" t="str">
         <v/>
       </c>
+      <c r="D223" t="str">
+        <v>Pinsir</v>
+      </c>
       <c r="E223" t="str">
-        <v>undefined-undefined</v>
+        <v>50-51</v>
       </c>
       <c r="F223" t="str">
-        <v>0.1429%</v>
+        <v>14%</v>
       </c>
       <c r="G223" t="str">
         <v/>
@@ -8927,11 +9554,14 @@
       <c r="C224" t="str">
         <v/>
       </c>
+      <c r="D224" t="str">
+        <v>Sunflora</v>
+      </c>
       <c r="E224" t="str">
-        <v>undefined-undefined</v>
+        <v>50-51</v>
       </c>
       <c r="F224" t="str">
-        <v>0.1429%</v>
+        <v>14%</v>
       </c>
       <c r="G224" t="str">
         <v/>
@@ -8965,11 +9595,14 @@
       <c r="C225" t="str">
         <v/>
       </c>
+      <c r="D225" t="str">
+        <v>Vespiquen</v>
+      </c>
       <c r="E225" t="str">
-        <v>undefined-undefined</v>
+        <v>50-51</v>
       </c>
       <c r="F225" t="str">
-        <v>0.1429%</v>
+        <v>14%</v>
       </c>
       <c r="G225" t="str">
         <v/>
@@ -9003,11 +9636,14 @@
       <c r="C226" t="str">
         <v/>
       </c>
+      <c r="D226" t="str">
+        <v>Garbodor</v>
+      </c>
       <c r="E226" t="str">
-        <v>undefined-undefined</v>
+        <v>51-52</v>
       </c>
       <c r="F226" t="str">
-        <v>0.1665%</v>
+        <v>17%</v>
       </c>
       <c r="G226" t="str">
         <v/>
@@ -9041,11 +9677,14 @@
       <c r="C227" t="str">
         <v/>
       </c>
+      <c r="D227" t="str">
+        <v>Liepard</v>
+      </c>
       <c r="E227" t="str">
-        <v>undefined-undefined</v>
+        <v>51-52</v>
       </c>
       <c r="F227" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G227" t="str">
         <v/>
@@ -9079,11 +9718,14 @@
       <c r="C228" t="str">
         <v/>
       </c>
+      <c r="D228" t="str">
+        <v>Muk</v>
+      </c>
       <c r="E228" t="str">
-        <v>undefined-undefined</v>
+        <v>51-52</v>
       </c>
       <c r="F228" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G228" t="str">
         <v/>
@@ -9117,11 +9759,14 @@
       <c r="C229" t="str">
         <v/>
       </c>
+      <c r="D229" t="str">
+        <v>Minccino</v>
+      </c>
       <c r="E229" t="str">
-        <v>undefined-undefined</v>
+        <v>51-52</v>
       </c>
       <c r="F229" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G229" t="str">
         <v/>
@@ -9155,11 +9800,14 @@
       <c r="C230" t="str">
         <v/>
       </c>
+      <c r="D230" t="str">
+        <v>Duosion</v>
+      </c>
       <c r="E230" t="str">
-        <v>undefined-undefined</v>
+        <v>51-52</v>
       </c>
       <c r="F230" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G230" t="str">
         <v/>
@@ -9193,11 +9841,14 @@
       <c r="C231" t="str">
         <v/>
       </c>
+      <c r="D231" t="str">
+        <v>Gigalith</v>
+      </c>
       <c r="E231" t="str">
-        <v>undefined-undefined</v>
+        <v>51-52</v>
       </c>
       <c r="F231" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G231" t="str">
         <v/>
@@ -9272,11 +9923,14 @@
       <c r="C233" t="str">
         <v/>
       </c>
+      <c r="D233" t="str">
+        <v>Feebas</v>
+      </c>
       <c r="E233" t="str">
-        <v>undefined-undefined</v>
+        <v>53-54</v>
       </c>
       <c r="F233" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G233" t="str">
         <v/>
@@ -9310,11 +9964,14 @@
       <c r="C234" t="str">
         <v/>
       </c>
+      <c r="D234" t="str">
+        <v>Finneon</v>
+      </c>
       <c r="E234" t="str">
-        <v>undefined-undefined</v>
+        <v>53-54</v>
       </c>
       <c r="F234" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G234" t="str">
         <v/>
@@ -9348,11 +10005,14 @@
       <c r="C235" t="str">
         <v/>
       </c>
+      <c r="D235" t="str">
+        <v>Qwilfish</v>
+      </c>
       <c r="E235" t="str">
-        <v>undefined-undefined</v>
+        <v>53-54</v>
       </c>
       <c r="F235" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G235" t="str">
         <v/>
@@ -9386,11 +10046,14 @@
       <c r="C236" t="str">
         <v/>
       </c>
+      <c r="D236" t="str">
+        <v>Stunfisk</v>
+      </c>
       <c r="E236" t="str">
-        <v>undefined-undefined</v>
+        <v>53-54</v>
       </c>
       <c r="F236" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G236" t="str">
         <v/>
@@ -9424,11 +10087,14 @@
       <c r="C237" t="str">
         <v/>
       </c>
+      <c r="D237" t="str">
+        <v>Palpitoad</v>
+      </c>
       <c r="E237" t="str">
-        <v>undefined-undefined</v>
+        <v>53-54</v>
       </c>
       <c r="F237" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G237" t="str">
         <v/>
@@ -9462,11 +10128,14 @@
       <c r="C238" t="str">
         <v/>
       </c>
+      <c r="D238" t="str">
+        <v>Poliwhirl</v>
+      </c>
       <c r="E238" t="str">
-        <v>undefined-undefined</v>
+        <v>53-54</v>
       </c>
       <c r="F238" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G238" t="str">
         <v/>
@@ -9500,11 +10169,14 @@
       <c r="C239" t="str">
         <v/>
       </c>
+      <c r="D239" t="str">
+        <v>Politoed</v>
+      </c>
       <c r="E239" t="str">
-        <v>undefined-undefined</v>
+        <v>53-54</v>
       </c>
       <c r="F239" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G239" t="str">
         <v/>
@@ -9538,11 +10210,14 @@
       <c r="C240" t="str">
         <v/>
       </c>
+      <c r="D240" t="str">
+        <v>Sealeo</v>
+      </c>
       <c r="E240" t="str">
-        <v>undefined-undefined</v>
+        <v>53-54</v>
       </c>
       <c r="F240" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G240" t="str">
         <v/>
@@ -9576,11 +10251,14 @@
       <c r="C241" t="str">
         <v/>
       </c>
+      <c r="D241" t="str">
+        <v>Walrein</v>
+      </c>
       <c r="E241" t="str">
-        <v>undefined-undefined</v>
+        <v>53-54</v>
       </c>
       <c r="F241" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G241" t="str">
         <v/>
@@ -9614,11 +10292,14 @@
       <c r="C242" t="str">
         <v/>
       </c>
+      <c r="D242" t="str">
+        <v>Dewgong</v>
+      </c>
       <c r="E242" t="str">
-        <v>undefined-undefined</v>
+        <v>53-54</v>
       </c>
       <c r="F242" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G242" t="str">
         <v/>
@@ -9693,11 +10374,14 @@
       <c r="C244" t="str">
         <v/>
       </c>
+      <c r="D244" t="str">
+        <v>Mantyke</v>
+      </c>
       <c r="E244" t="str">
-        <v>undefined-undefined</v>
+        <v>56-57</v>
       </c>
       <c r="F244" t="str">
-        <v>0.1426%</v>
+        <v>14%</v>
       </c>
       <c r="G244" t="str">
         <v/>
@@ -9731,11 +10415,14 @@
       <c r="C245" t="str">
         <v/>
       </c>
+      <c r="D245" t="str">
+        <v>Luvdisc</v>
+      </c>
       <c r="E245" t="str">
-        <v>undefined-undefined</v>
+        <v>56-57</v>
       </c>
       <c r="F245" t="str">
-        <v>0.1429%</v>
+        <v>14%</v>
       </c>
       <c r="G245" t="str">
         <v/>
@@ -9769,11 +10456,14 @@
       <c r="C246" t="str">
         <v/>
       </c>
+      <c r="D246" t="str">
+        <v>Corsola</v>
+      </c>
       <c r="E246" t="str">
-        <v>undefined-undefined</v>
+        <v>56-57</v>
       </c>
       <c r="F246" t="str">
-        <v>0.1429%</v>
+        <v>14%</v>
       </c>
       <c r="G246" t="str">
         <v/>
@@ -9807,11 +10497,14 @@
       <c r="C247" t="str">
         <v/>
       </c>
+      <c r="D247" t="str">
+        <v>Wingull</v>
+      </c>
       <c r="E247" t="str">
-        <v>undefined-undefined</v>
+        <v>56-57</v>
       </c>
       <c r="F247" t="str">
-        <v>0.1429%</v>
+        <v>14%</v>
       </c>
       <c r="G247" t="str">
         <v/>
@@ -9845,11 +10538,14 @@
       <c r="C248" t="str">
         <v/>
       </c>
+      <c r="D248" t="str">
+        <v>Pelipper</v>
+      </c>
       <c r="E248" t="str">
-        <v>undefined-undefined</v>
+        <v>56-57</v>
       </c>
       <c r="F248" t="str">
-        <v>0.1429%</v>
+        <v>14%</v>
       </c>
       <c r="G248" t="str">
         <v/>
@@ -9883,11 +10579,14 @@
       <c r="C249" t="str">
         <v/>
       </c>
+      <c r="D249" t="str">
+        <v>Octillery</v>
+      </c>
       <c r="E249" t="str">
-        <v>undefined-undefined</v>
+        <v>56-57</v>
       </c>
       <c r="F249" t="str">
-        <v>0.1429%</v>
+        <v>14%</v>
       </c>
       <c r="G249" t="str">
         <v/>
@@ -9921,11 +10620,14 @@
       <c r="C250" t="str">
         <v/>
       </c>
+      <c r="D250" t="str">
+        <v>Crawdaunt</v>
+      </c>
       <c r="E250" t="str">
-        <v>undefined-undefined</v>
+        <v>56-57</v>
       </c>
       <c r="F250" t="str">
-        <v>0.1429%</v>
+        <v>14%</v>
       </c>
       <c r="G250" t="str">
         <v/>
@@ -9959,11 +10661,14 @@
       <c r="C251" t="str">
         <v/>
       </c>
+      <c r="D251" t="str">
+        <v>Boldore</v>
+      </c>
       <c r="E251" t="str">
-        <v>undefined-undefined</v>
+        <v>57-58</v>
       </c>
       <c r="F251" t="str">
-        <v>0.1665%</v>
+        <v>17%</v>
       </c>
       <c r="G251" t="str">
         <v/>
@@ -9997,11 +10702,14 @@
       <c r="C252" t="str">
         <v/>
       </c>
+      <c r="D252" t="str">
+        <v>Feebas</v>
+      </c>
       <c r="E252" t="str">
-        <v>undefined-undefined</v>
+        <v>57-58</v>
       </c>
       <c r="F252" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G252" t="str">
         <v/>
@@ -10035,11 +10743,14 @@
       <c r="C253" t="str">
         <v/>
       </c>
+      <c r="D253" t="str">
+        <v>Alomomola</v>
+      </c>
       <c r="E253" t="str">
-        <v>undefined-undefined</v>
+        <v>57-58</v>
       </c>
       <c r="F253" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G253" t="str">
         <v/>
@@ -10073,11 +10784,14 @@
       <c r="C254" t="str">
         <v/>
       </c>
+      <c r="D254" t="str">
+        <v>Woobat</v>
+      </c>
       <c r="E254" t="str">
-        <v>undefined-undefined</v>
+        <v>57-58</v>
       </c>
       <c r="F254" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G254" t="str">
         <v/>
@@ -10111,11 +10825,14 @@
       <c r="C255" t="str">
         <v/>
       </c>
+      <c r="D255" t="str">
+        <v>Shuckle</v>
+      </c>
       <c r="E255" t="str">
-        <v>undefined-undefined</v>
+        <v>57-58</v>
       </c>
       <c r="F255" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G255" t="str">
         <v/>
@@ -10149,11 +10866,14 @@
       <c r="C256" t="str">
         <v/>
       </c>
+      <c r="D256" t="str">
+        <v>Carracosta</v>
+      </c>
       <c r="E256" t="str">
-        <v>undefined-undefined</v>
+        <v>57-58</v>
       </c>
       <c r="F256" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G256" t="str">
         <v/>
@@ -10187,11 +10907,14 @@
       <c r="C257" t="str">
         <v/>
       </c>
+      <c r="D257" t="str">
+        <v>Pelipper</v>
+      </c>
       <c r="E257" t="str">
-        <v>undefined-undefined</v>
+        <v>58-59</v>
       </c>
       <c r="F257" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G257" t="str">
         <v/>
@@ -10225,11 +10948,14 @@
       <c r="C258" t="str">
         <v/>
       </c>
+      <c r="D258" t="str">
+        <v>Golduck</v>
+      </c>
       <c r="E258" t="str">
-        <v>undefined-undefined</v>
+        <v>58-59</v>
       </c>
       <c r="F258" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G258" t="str">
         <v/>
@@ -10263,11 +10989,14 @@
       <c r="C259" t="str">
         <v/>
       </c>
+      <c r="D259" t="str">
+        <v>Marill</v>
+      </c>
       <c r="E259" t="str">
-        <v>undefined-undefined</v>
+        <v>58-59</v>
       </c>
       <c r="F259" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G259" t="str">
         <v/>
@@ -10301,11 +11030,14 @@
       <c r="C260" t="str">
         <v/>
       </c>
+      <c r="D260" t="str">
+        <v>Amoonguss</v>
+      </c>
       <c r="E260" t="str">
-        <v>undefined-undefined</v>
+        <v>58-59</v>
       </c>
       <c r="F260" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G260" t="str">
         <v/>
@@ -10339,11 +11071,14 @@
       <c r="C261" t="str">
         <v/>
       </c>
+      <c r="D261" t="str">
+        <v>Beldum</v>
+      </c>
       <c r="E261" t="str">
-        <v>undefined-undefined</v>
+        <v>59-60</v>
       </c>
       <c r="F261" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G261" t="str">
         <v/>
@@ -10377,11 +11112,14 @@
       <c r="C262" t="str">
         <v/>
       </c>
+      <c r="D262" t="str">
+        <v>Pawniard</v>
+      </c>
       <c r="E262" t="str">
-        <v>undefined-undefined</v>
+        <v>59-60</v>
       </c>
       <c r="F262" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G262" t="str">
         <v/>
@@ -10415,11 +11153,14 @@
       <c r="C263" t="str">
         <v/>
       </c>
+      <c r="D263" t="str">
+        <v>Magnezone</v>
+      </c>
       <c r="E263" t="str">
-        <v>undefined-undefined</v>
+        <v>59-60</v>
       </c>
       <c r="F263" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G263" t="str">
         <v/>
@@ -10453,11 +11194,14 @@
       <c r="C264" t="str">
         <v/>
       </c>
+      <c r="D264" t="str">
+        <v>Klinklang</v>
+      </c>
       <c r="E264" t="str">
-        <v>undefined-undefined</v>
+        <v>59-60</v>
       </c>
       <c r="F264" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G264" t="str">
         <v/>
@@ -10491,11 +11235,14 @@
       <c r="C265" t="str">
         <v/>
       </c>
+      <c r="D265" t="str">
+        <v>Grimer</v>
+      </c>
       <c r="E265" t="str">
-        <v>undefined-undefined</v>
+        <v>60-61</v>
       </c>
       <c r="F265" t="str">
-        <v>0.3334%</v>
+        <v>33%</v>
       </c>
       <c r="G265" t="str">
         <v/>
@@ -10529,11 +11276,14 @@
       <c r="C266" t="str">
         <v/>
       </c>
+      <c r="D266" t="str">
+        <v>Bronzor</v>
+      </c>
       <c r="E266" t="str">
-        <v>undefined-undefined</v>
+        <v>60-61</v>
       </c>
       <c r="F266" t="str">
-        <v>0.3333%</v>
+        <v>33%</v>
       </c>
       <c r="G266" t="str">
         <v/>
@@ -10567,11 +11317,14 @@
       <c r="C267" t="str">
         <v/>
       </c>
+      <c r="D267" t="str">
+        <v>Weezing</v>
+      </c>
       <c r="E267" t="str">
-        <v>undefined-undefined</v>
+        <v>60-61</v>
       </c>
       <c r="F267" t="str">
-        <v>0.3333%</v>
+        <v>33%</v>
       </c>
       <c r="G267" t="str">
         <v/>
@@ -10605,11 +11358,14 @@
       <c r="C268" t="str">
         <v/>
       </c>
+      <c r="D268" t="str">
+        <v>Delibird</v>
+      </c>
       <c r="E268" t="str">
-        <v>undefined-undefined</v>
+        <v>62-63</v>
       </c>
       <c r="F268" t="str">
-        <v>0.091%</v>
+        <v>9%</v>
       </c>
       <c r="G268" t="str">
         <v/>
@@ -10643,11 +11399,14 @@
       <c r="C269" t="str">
         <v/>
       </c>
+      <c r="D269" t="str">
+        <v>Swinub</v>
+      </c>
       <c r="E269" t="str">
-        <v>undefined-undefined</v>
+        <v>62-63</v>
       </c>
       <c r="F269" t="str">
-        <v>0.0909%</v>
+        <v>9%</v>
       </c>
       <c r="G269" t="str">
         <v/>
@@ -10681,11 +11440,14 @@
       <c r="C270" t="str">
         <v/>
       </c>
+      <c r="D270" t="str">
+        <v>Piloswine</v>
+      </c>
       <c r="E270" t="str">
-        <v>undefined-undefined</v>
+        <v>62-63</v>
       </c>
       <c r="F270" t="str">
-        <v>0.0909%</v>
+        <v>9%</v>
       </c>
       <c r="G270" t="str">
         <v/>
@@ -10719,11 +11481,14 @@
       <c r="C271" t="str">
         <v/>
       </c>
+      <c r="D271" t="str">
+        <v>Ditto</v>
+      </c>
       <c r="E271" t="str">
-        <v>undefined-undefined</v>
+        <v>62-63</v>
       </c>
       <c r="F271" t="str">
-        <v>0.0909%</v>
+        <v>9%</v>
       </c>
       <c r="G271" t="str">
         <v/>
@@ -10757,11 +11522,14 @@
       <c r="C272" t="str">
         <v/>
       </c>
+      <c r="D272" t="str">
+        <v>Clefairy</v>
+      </c>
       <c r="E272" t="str">
-        <v>undefined-undefined</v>
+        <v>62-63</v>
       </c>
       <c r="F272" t="str">
-        <v>0.0909%</v>
+        <v>9%</v>
       </c>
       <c r="G272" t="str">
         <v/>
@@ -10795,11 +11563,14 @@
       <c r="C273" t="str">
         <v/>
       </c>
+      <c r="D273" t="str">
+        <v>Metang</v>
+      </c>
       <c r="E273" t="str">
-        <v>undefined-undefined</v>
+        <v>62-63</v>
       </c>
       <c r="F273" t="str">
-        <v>0.0909%</v>
+        <v>9%</v>
       </c>
       <c r="G273" t="str">
         <v/>
@@ -10833,11 +11604,14 @@
       <c r="C274" t="str">
         <v/>
       </c>
+      <c r="D274" t="str">
+        <v>Lunatone</v>
+      </c>
       <c r="E274" t="str">
-        <v>undefined-undefined</v>
+        <v>62-63</v>
       </c>
       <c r="F274" t="str">
-        <v>0.0909%</v>
+        <v>9%</v>
       </c>
       <c r="G274" t="str">
         <v/>
@@ -10871,11 +11645,14 @@
       <c r="C275" t="str">
         <v/>
       </c>
+      <c r="D275" t="str">
+        <v>Solrock</v>
+      </c>
       <c r="E275" t="str">
-        <v>undefined-undefined</v>
+        <v>62-63</v>
       </c>
       <c r="F275" t="str">
-        <v>0.0909%</v>
+        <v>9%</v>
       </c>
       <c r="G275" t="str">
         <v/>
@@ -10909,11 +11686,14 @@
       <c r="C276" t="str">
         <v/>
       </c>
+      <c r="D276" t="str">
+        <v>Metagross</v>
+      </c>
       <c r="E276" t="str">
-        <v>undefined-undefined</v>
+        <v>62-63</v>
       </c>
       <c r="F276" t="str">
-        <v>0.0909%</v>
+        <v>9%</v>
       </c>
       <c r="G276" t="str">
         <v/>
@@ -10947,11 +11727,14 @@
       <c r="C277" t="str">
         <v/>
       </c>
+      <c r="D277" t="str">
+        <v>Clefable</v>
+      </c>
       <c r="E277" t="str">
-        <v>undefined-undefined</v>
+        <v>62-63</v>
       </c>
       <c r="F277" t="str">
-        <v>0.0909%</v>
+        <v>9%</v>
       </c>
       <c r="G277" t="str">
         <v/>
@@ -10985,11 +11768,14 @@
       <c r="C278" t="str">
         <v/>
       </c>
+      <c r="D278" t="str">
+        <v>Weavile</v>
+      </c>
       <c r="E278" t="str">
-        <v>undefined-undefined</v>
+        <v>62-63</v>
       </c>
       <c r="F278" t="str">
-        <v>0.0909%</v>
+        <v>9%</v>
       </c>
       <c r="G278" t="str">
         <v/>
@@ -11023,11 +11809,14 @@
       <c r="C279" t="str">
         <v/>
       </c>
+      <c r="D279" t="str">
+        <v>Sneasel</v>
+      </c>
       <c r="E279" t="str">
-        <v>undefined-undefined</v>
+        <v>63-64</v>
       </c>
       <c r="F279" t="str">
-        <v>0.1112%</v>
+        <v>11%</v>
       </c>
       <c r="G279" t="str">
         <v/>
@@ -11061,11 +11850,14 @@
       <c r="C280" t="str">
         <v/>
       </c>
+      <c r="D280" t="str">
+        <v>Amoonguss</v>
+      </c>
       <c r="E280" t="str">
-        <v>undefined-undefined</v>
+        <v>63-64</v>
       </c>
       <c r="F280" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G280" t="str">
         <v/>
@@ -11099,11 +11891,14 @@
       <c r="C281" t="str">
         <v/>
       </c>
+      <c r="D281" t="str">
+        <v>Bouffalant</v>
+      </c>
       <c r="E281" t="str">
-        <v>undefined-undefined</v>
+        <v>63-64</v>
       </c>
       <c r="F281" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G281" t="str">
         <v/>
@@ -11137,11 +11932,14 @@
       <c r="C282" t="str">
         <v/>
       </c>
+      <c r="D282" t="str">
+        <v>Roserade</v>
+      </c>
       <c r="E282" t="str">
-        <v>undefined-undefined</v>
+        <v>63-64</v>
       </c>
       <c r="F282" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G282" t="str">
         <v/>
@@ -11175,11 +11973,14 @@
       <c r="C283" t="str">
         <v/>
       </c>
+      <c r="D283" t="str">
+        <v>Gurdurr</v>
+      </c>
       <c r="E283" t="str">
-        <v>undefined-undefined</v>
+        <v>63-64</v>
       </c>
       <c r="F283" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G283" t="str">
         <v/>
@@ -11213,11 +12014,14 @@
       <c r="C284" t="str">
         <v/>
       </c>
+      <c r="D284" t="str">
+        <v>Serperior</v>
+      </c>
       <c r="E284" t="str">
-        <v>undefined-undefined</v>
+        <v>63-64</v>
       </c>
       <c r="F284" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G284" t="str">
         <v/>
@@ -11251,11 +12055,14 @@
       <c r="C285" t="str">
         <v/>
       </c>
+      <c r="D285" t="str">
+        <v>Mienshao</v>
+      </c>
       <c r="E285" t="str">
-        <v>undefined-undefined</v>
+        <v>63-64</v>
       </c>
       <c r="F285" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G285" t="str">
         <v/>
@@ -11289,11 +12096,14 @@
       <c r="C286" t="str">
         <v/>
       </c>
+      <c r="D286" t="str">
+        <v>Bisharp</v>
+      </c>
       <c r="E286" t="str">
-        <v>undefined-undefined</v>
+        <v>63-64</v>
       </c>
       <c r="F286" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G286" t="str">
         <v/>
@@ -11327,11 +12137,14 @@
       <c r="C287" t="str">
         <v/>
       </c>
+      <c r="D287" t="str">
+        <v>Gliscor</v>
+      </c>
       <c r="E287" t="str">
-        <v>undefined-undefined</v>
+        <v>63-64</v>
       </c>
       <c r="F287" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G287" t="str">
         <v/>
@@ -11365,11 +12178,14 @@
       <c r="C288" t="str">
         <v/>
       </c>
+      <c r="D288" t="str">
+        <v>Durant</v>
+      </c>
       <c r="E288" t="str">
-        <v>undefined-undefined</v>
+        <v>64-65</v>
       </c>
       <c r="F288" t="str">
-        <v>0.1426%</v>
+        <v>14%</v>
       </c>
       <c r="G288" t="str">
         <v/>
@@ -11403,11 +12219,14 @@
       <c r="C289" t="str">
         <v/>
       </c>
+      <c r="D289" t="str">
+        <v>Heatmor</v>
+      </c>
       <c r="E289" t="str">
-        <v>undefined-undefined</v>
+        <v>64-65</v>
       </c>
       <c r="F289" t="str">
-        <v>0.1429%</v>
+        <v>14%</v>
       </c>
       <c r="G289" t="str">
         <v/>
@@ -11441,11 +12260,14 @@
       <c r="C290" t="str">
         <v/>
       </c>
+      <c r="D290" t="str">
+        <v>Deino</v>
+      </c>
       <c r="E290" t="str">
-        <v>undefined-undefined</v>
+        <v>64-65</v>
       </c>
       <c r="F290" t="str">
-        <v>0.1429%</v>
+        <v>14%</v>
       </c>
       <c r="G290" t="str">
         <v/>
@@ -11479,11 +12301,14 @@
       <c r="C291" t="str">
         <v/>
       </c>
+      <c r="D291" t="str">
+        <v>Druddigon</v>
+      </c>
       <c r="E291" t="str">
-        <v>undefined-undefined</v>
+        <v>64-65</v>
       </c>
       <c r="F291" t="str">
-        <v>0.1429%</v>
+        <v>14%</v>
       </c>
       <c r="G291" t="str">
         <v/>
@@ -11517,11 +12342,14 @@
       <c r="C292" t="str">
         <v/>
       </c>
+      <c r="D292" t="str">
+        <v>Zweilous</v>
+      </c>
       <c r="E292" t="str">
-        <v>undefined-undefined</v>
+        <v>64-65</v>
       </c>
       <c r="F292" t="str">
-        <v>0.1429%</v>
+        <v>14%</v>
       </c>
       <c r="G292" t="str">
         <v/>
@@ -11555,11 +12383,14 @@
       <c r="C293" t="str">
         <v/>
       </c>
+      <c r="D293" t="str">
+        <v>Hydreigon</v>
+      </c>
       <c r="E293" t="str">
-        <v>undefined-undefined</v>
+        <v>64-65</v>
       </c>
       <c r="F293" t="str">
-        <v>0.1429%</v>
+        <v>14%</v>
       </c>
       <c r="G293" t="str">
         <v/>
@@ -11593,11 +12424,14 @@
       <c r="C294" t="str">
         <v/>
       </c>
+      <c r="D294" t="str">
+        <v>Golurk</v>
+      </c>
       <c r="E294" t="str">
-        <v>undefined-undefined</v>
+        <v>64-65</v>
       </c>
       <c r="F294" t="str">
-        <v>0.1429%</v>
+        <v>14%</v>
       </c>
       <c r="G294" t="str">
         <v/>
@@ -11672,11 +12506,14 @@
       <c r="C296" t="str">
         <v/>
       </c>
+      <c r="D296" t="str">
+        <v>Palpitoad</v>
+      </c>
       <c r="E296" t="str">
-        <v>undefined-undefined</v>
+        <v>25-26</v>
       </c>
       <c r="F296" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G296" t="str">
         <v/>
@@ -11710,11 +12547,14 @@
       <c r="C297" t="str">
         <v/>
       </c>
+      <c r="D297" t="str">
+        <v>Stunfisk</v>
+      </c>
       <c r="E297" t="str">
-        <v>undefined-undefined</v>
+        <v>25-26</v>
       </c>
       <c r="F297" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G297" t="str">
         <v/>
@@ -11748,11 +12588,14 @@
       <c r="C298" t="str">
         <v/>
       </c>
+      <c r="D298" t="str">
+        <v>Shellder</v>
+      </c>
       <c r="E298" t="str">
-        <v>undefined-undefined</v>
+        <v>25-26</v>
       </c>
       <c r="F298" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G298" t="str">
         <v/>
@@ -11786,11 +12629,14 @@
       <c r="C299" t="str">
         <v/>
       </c>
+      <c r="D299" t="str">
+        <v>Croagunk</v>
+      </c>
       <c r="E299" t="str">
-        <v>undefined-undefined</v>
+        <v>25-26</v>
       </c>
       <c r="F299" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G299" t="str">
         <v/>
@@ -11824,11 +12670,14 @@
       <c r="C300" t="str">
         <v/>
       </c>
+      <c r="D300" t="str">
+        <v>Crobat</v>
+      </c>
       <c r="E300" t="str">
-        <v>undefined-undefined</v>
+        <v>25-26</v>
       </c>
       <c r="F300" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G300" t="str">
         <v/>
@@ -11862,11 +12711,14 @@
       <c r="C301" t="str">
         <v/>
       </c>
+      <c r="D301" t="str">
+        <v>Shelmet</v>
+      </c>
       <c r="E301" t="str">
-        <v>undefined-undefined</v>
+        <v>32-33</v>
       </c>
       <c r="F301" t="str">
-        <v>0.3334%</v>
+        <v>33%</v>
       </c>
       <c r="G301" t="str">
         <v/>
@@ -11900,11 +12752,14 @@
       <c r="C302" t="str">
         <v/>
       </c>
+      <c r="D302" t="str">
+        <v>Ducklett</v>
+      </c>
       <c r="E302" t="str">
-        <v>undefined-undefined</v>
+        <v>32-33</v>
       </c>
       <c r="F302" t="str">
-        <v>0.3333%</v>
+        <v>33%</v>
       </c>
       <c r="G302" t="str">
         <v/>
@@ -11938,11 +12793,14 @@
       <c r="C303" t="str">
         <v/>
       </c>
+      <c r="D303" t="str">
+        <v>Toxicroak</v>
+      </c>
       <c r="E303" t="str">
-        <v>undefined-undefined</v>
+        <v>32-33</v>
       </c>
       <c r="F303" t="str">
-        <v>0.3333%</v>
+        <v>33%</v>
       </c>
       <c r="G303" t="str">
         <v/>
@@ -11976,11 +12834,14 @@
       <c r="C304" t="str">
         <v/>
       </c>
+      <c r="D304" t="str">
+        <v>Lapras</v>
+      </c>
       <c r="E304" t="str">
-        <v>undefined-undefined</v>
+        <v>39-40</v>
       </c>
       <c r="F304" t="str">
-        <v>0.3334%</v>
+        <v>33%</v>
       </c>
       <c r="G304" t="str">
         <v/>
@@ -12014,11 +12875,14 @@
       <c r="C305" t="str">
         <v/>
       </c>
+      <c r="D305" t="str">
+        <v>Tirtouga</v>
+      </c>
       <c r="E305" t="str">
-        <v>undefined-undefined</v>
+        <v>39-40</v>
       </c>
       <c r="F305" t="str">
-        <v>0.3333%</v>
+        <v>33%</v>
       </c>
       <c r="G305" t="str">
         <v/>
@@ -12052,11 +12916,14 @@
       <c r="C306" t="str">
         <v/>
       </c>
+      <c r="D306" t="str">
+        <v>Beheeyem</v>
+      </c>
       <c r="E306" t="str">
-        <v>undefined-undefined</v>
+        <v>39-40</v>
       </c>
       <c r="F306" t="str">
-        <v>0.3333%</v>
+        <v>33%</v>
       </c>
       <c r="G306" t="str">
         <v/>
@@ -12090,11 +12957,14 @@
       <c r="C307" t="str">
         <v/>
       </c>
+      <c r="D307" t="str">
+        <v>Golett</v>
+      </c>
       <c r="E307" t="str">
-        <v>undefined-undefined</v>
+        <v>46-47</v>
       </c>
       <c r="F307" t="str">
-        <v>0.1426%</v>
+        <v>14%</v>
       </c>
       <c r="G307" t="str">
         <v/>
@@ -12128,11 +12998,14 @@
       <c r="C308" t="str">
         <v/>
       </c>
+      <c r="D308" t="str">
+        <v>Druddigon</v>
+      </c>
       <c r="E308" t="str">
-        <v>undefined-undefined</v>
+        <v>46-47</v>
       </c>
       <c r="F308" t="str">
-        <v>0.1429%</v>
+        <v>14%</v>
       </c>
       <c r="G308" t="str">
         <v/>
@@ -12166,11 +13039,14 @@
       <c r="C309" t="str">
         <v/>
       </c>
+      <c r="D309" t="str">
+        <v>Mienfoo</v>
+      </c>
       <c r="E309" t="str">
-        <v>undefined-undefined</v>
+        <v>46-47</v>
       </c>
       <c r="F309" t="str">
-        <v>0.1429%</v>
+        <v>14%</v>
       </c>
       <c r="G309" t="str">
         <v/>
@@ -12204,11 +13080,14 @@
       <c r="C310" t="str">
         <v/>
       </c>
+      <c r="D310" t="str">
+        <v>Golbat</v>
+      </c>
       <c r="E310" t="str">
-        <v>undefined-undefined</v>
+        <v>46-47</v>
       </c>
       <c r="F310" t="str">
-        <v>0.1429%</v>
+        <v>14%</v>
       </c>
       <c r="G310" t="str">
         <v/>
@@ -12242,11 +13121,14 @@
       <c r="C311" t="str">
         <v/>
       </c>
+      <c r="D311" t="str">
+        <v>Fraxure</v>
+      </c>
       <c r="E311" t="str">
-        <v>undefined-undefined</v>
+        <v>46-47</v>
       </c>
       <c r="F311" t="str">
-        <v>0.1429%</v>
+        <v>14%</v>
       </c>
       <c r="G311" t="str">
         <v/>
@@ -12280,11 +13162,14 @@
       <c r="C312" t="str">
         <v/>
       </c>
+      <c r="D312" t="str">
+        <v>Haxorus</v>
+      </c>
       <c r="E312" t="str">
-        <v>undefined-undefined</v>
+        <v>46-47</v>
       </c>
       <c r="F312" t="str">
-        <v>0.1429%</v>
+        <v>14%</v>
       </c>
       <c r="G312" t="str">
         <v/>
@@ -12318,11 +13203,14 @@
       <c r="C313" t="str">
         <v/>
       </c>
+      <c r="D313" t="str">
+        <v>Beartic</v>
+      </c>
       <c r="E313" t="str">
-        <v>undefined-undefined</v>
+        <v>46-47</v>
       </c>
       <c r="F313" t="str">
-        <v>0.1429%</v>
+        <v>14%</v>
       </c>
       <c r="G313" t="str">
         <v/>
@@ -12356,11 +13244,14 @@
       <c r="C314" t="str">
         <v/>
       </c>
+      <c r="D314" t="str">
+        <v>Boldore</v>
+      </c>
       <c r="E314" t="str">
-        <v>undefined-undefined</v>
+        <v>53-54</v>
       </c>
       <c r="F314" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G314" t="str">
         <v/>
@@ -12394,11 +13285,14 @@
       <c r="C315" t="str">
         <v/>
       </c>
+      <c r="D315" t="str">
+        <v>Gurdurr</v>
+      </c>
       <c r="E315" t="str">
-        <v>undefined-undefined</v>
+        <v>53-54</v>
       </c>
       <c r="F315" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G315" t="str">
         <v/>
@@ -12432,11 +13326,14 @@
       <c r="C316" t="str">
         <v/>
       </c>
+      <c r="D316" t="str">
+        <v>Cryogonal</v>
+      </c>
       <c r="E316" t="str">
-        <v>undefined-undefined</v>
+        <v>53-54</v>
       </c>
       <c r="F316" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G316" t="str">
         <v/>
@@ -12470,11 +13367,14 @@
       <c r="C317" t="str">
         <v/>
       </c>
+      <c r="D317" t="str">
+        <v>Woobat</v>
+      </c>
       <c r="E317" t="str">
-        <v>undefined-undefined</v>
+        <v>53-54</v>
       </c>
       <c r="F317" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G317" t="str">
         <v/>
@@ -12508,11 +13408,14 @@
       <c r="C318" t="str">
         <v/>
       </c>
+      <c r="D318" t="str">
+        <v>Larvitar</v>
+      </c>
       <c r="E318" t="str">
-        <v>undefined-undefined</v>
+        <v>53-54</v>
       </c>
       <c r="F318" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G318" t="str">
         <v/>
@@ -12546,11 +13449,14 @@
       <c r="C319" t="str">
         <v/>
       </c>
+      <c r="D319" t="str">
+        <v>Mamoswine</v>
+      </c>
       <c r="E319" t="str">
-        <v>undefined-undefined</v>
+        <v>53-54</v>
       </c>
       <c r="F319" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G319" t="str">
         <v/>
@@ -12584,11 +13490,14 @@
       <c r="C320" t="str">
         <v/>
       </c>
+      <c r="D320" t="str">
+        <v>Vanillish</v>
+      </c>
       <c r="E320" t="str">
-        <v>undefined-undefined</v>
+        <v>53-54</v>
       </c>
       <c r="F320" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G320" t="str">
         <v/>
@@ -12622,11 +13531,14 @@
       <c r="C321" t="str">
         <v/>
       </c>
+      <c r="D321" t="str">
+        <v>Vanilluxe</v>
+      </c>
       <c r="E321" t="str">
-        <v>undefined-undefined</v>
+        <v>53-54</v>
       </c>
       <c r="F321" t="str">
-        <v>0.125%</v>
+        <v>13%</v>
       </c>
       <c r="G321" t="str">
         <v/>
@@ -12660,11 +13572,14 @@
       <c r="C322" t="str">
         <v/>
       </c>
+      <c r="D322" t="str">
+        <v>Boldore</v>
+      </c>
       <c r="E322" t="str">
-        <v>undefined-undefined</v>
+        <v>60-60</v>
       </c>
       <c r="F322" t="str">
-        <v>0.1112%</v>
+        <v>11%</v>
       </c>
       <c r="G322" t="str">
         <v/>
@@ -12698,11 +13613,14 @@
       <c r="C323" t="str">
         <v/>
       </c>
+      <c r="D323" t="str">
+        <v>Nosepass</v>
+      </c>
       <c r="E323" t="str">
-        <v>undefined-undefined</v>
+        <v>60-60</v>
       </c>
       <c r="F323" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G323" t="str">
         <v/>
@@ -12736,11 +13654,14 @@
       <c r="C324" t="str">
         <v/>
       </c>
+      <c r="D324" t="str">
+        <v>Lairon</v>
+      </c>
       <c r="E324" t="str">
-        <v>undefined-undefined</v>
+        <v>60-60</v>
       </c>
       <c r="F324" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G324" t="str">
         <v/>
@@ -12774,11 +13695,14 @@
       <c r="C325" t="str">
         <v/>
       </c>
+      <c r="D325" t="str">
+        <v>Woobat</v>
+      </c>
       <c r="E325" t="str">
-        <v>undefined-undefined</v>
+        <v>60-60</v>
       </c>
       <c r="F325" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G325" t="str">
         <v/>
@@ -12812,11 +13736,14 @@
       <c r="C326" t="str">
         <v/>
       </c>
+      <c r="D326" t="str">
+        <v>Durant</v>
+      </c>
       <c r="E326" t="str">
-        <v>undefined-undefined</v>
+        <v>60-60</v>
       </c>
       <c r="F326" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G326" t="str">
         <v/>
@@ -12850,11 +13777,14 @@
       <c r="C327" t="str">
         <v/>
       </c>
+      <c r="D327" t="str">
+        <v>Onix</v>
+      </c>
       <c r="E327" t="str">
-        <v>undefined-undefined</v>
+        <v>60-60</v>
       </c>
       <c r="F327" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G327" t="str">
         <v/>
@@ -12888,11 +13818,14 @@
       <c r="C328" t="str">
         <v/>
       </c>
+      <c r="D328" t="str">
+        <v>Steelix</v>
+      </c>
       <c r="E328" t="str">
-        <v>undefined-undefined</v>
+        <v>60-60</v>
       </c>
       <c r="F328" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G328" t="str">
         <v/>
@@ -12926,11 +13859,14 @@
       <c r="C329" t="str">
         <v/>
       </c>
+      <c r="D329" t="str">
+        <v>Aggron</v>
+      </c>
       <c r="E329" t="str">
-        <v>undefined-undefined</v>
+        <v>60-60</v>
       </c>
       <c r="F329" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G329" t="str">
         <v/>
@@ -12964,11 +13900,14 @@
       <c r="C330" t="str">
         <v/>
       </c>
+      <c r="D330" t="str">
+        <v>Probopass</v>
+      </c>
       <c r="E330" t="str">
-        <v>undefined-undefined</v>
+        <v>60-60</v>
       </c>
       <c r="F330" t="str">
-        <v>0.1111%</v>
+        <v>11%</v>
       </c>
       <c r="G330" t="str">
         <v/>
@@ -13002,11 +13941,14 @@
       <c r="C331" t="str">
         <v/>
       </c>
+      <c r="D331" t="str">
+        <v>Gligar</v>
+      </c>
       <c r="E331" t="str">
-        <v>undefined-undefined</v>
+        <v>35-36</v>
       </c>
       <c r="F331" t="str">
-        <v>0.1665%</v>
+        <v>17%</v>
       </c>
       <c r="G331" t="str">
         <v/>
@@ -13040,11 +13982,14 @@
       <c r="C332" t="str">
         <v/>
       </c>
+      <c r="D332" t="str">
+        <v>Pupitar</v>
+      </c>
       <c r="E332" t="str">
-        <v>undefined-undefined</v>
+        <v>35-36</v>
       </c>
       <c r="F332" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G332" t="str">
         <v/>
@@ -13078,11 +14023,14 @@
       <c r="C333" t="str">
         <v/>
       </c>
+      <c r="D333" t="str">
+        <v>Scraggy</v>
+      </c>
       <c r="E333" t="str">
-        <v>undefined-undefined</v>
+        <v>35-36</v>
       </c>
       <c r="F333" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G333" t="str">
         <v/>
@@ -13091,7 +14039,7 @@
         <v>Yes</v>
       </c>
       <c r="I333" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J333" t="str">
         <v>NONONO</v>
@@ -13116,11 +14064,14 @@
       <c r="C334" t="str">
         <v/>
       </c>
+      <c r="D334" t="str">
+        <v>Foongus</v>
+      </c>
       <c r="E334" t="str">
-        <v>undefined-undefined</v>
+        <v>35-36</v>
       </c>
       <c r="F334" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G334" t="str">
         <v/>
@@ -13129,7 +14080,7 @@
         <v>Yes</v>
       </c>
       <c r="I334" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J334" t="str">
         <v>NONONO</v>
@@ -13154,11 +14105,14 @@
       <c r="C335" t="str">
         <v/>
       </c>
+      <c r="D335" t="str">
+        <v>Koffing</v>
+      </c>
       <c r="E335" t="str">
-        <v>undefined-undefined</v>
+        <v>35-36</v>
       </c>
       <c r="F335" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G335" t="str">
         <v/>
@@ -13167,7 +14121,7 @@
         <v>Yes</v>
       </c>
       <c r="I335" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J335" t="str">
         <v>NONONO</v>
@@ -13192,11 +14146,14 @@
       <c r="C336" t="str">
         <v/>
       </c>
+      <c r="D336" t="str">
+        <v>Tyranitar</v>
+      </c>
       <c r="E336" t="str">
-        <v>undefined-undefined</v>
+        <v>35-36</v>
       </c>
       <c r="F336" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G336" t="str">
         <v/>
@@ -13230,11 +14187,14 @@
       <c r="C337" t="str">
         <v/>
       </c>
+      <c r="D337" t="str">
+        <v>Panpour</v>
+      </c>
       <c r="E337" t="str">
-        <v>undefined-undefined</v>
+        <v>44-45</v>
       </c>
       <c r="F337" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G337" t="str">
         <v/>
@@ -13243,7 +14203,7 @@
         <v>Yes</v>
       </c>
       <c r="I337" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J337" t="str">
         <v>NONONO</v>
@@ -13268,11 +14228,14 @@
       <c r="C338" t="str">
         <v/>
       </c>
+      <c r="D338" t="str">
+        <v>Pansear</v>
+      </c>
       <c r="E338" t="str">
-        <v>undefined-undefined</v>
+        <v>44-45</v>
       </c>
       <c r="F338" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G338" t="str">
         <v/>
@@ -13281,7 +14244,7 @@
         <v>Yes</v>
       </c>
       <c r="I338" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J338" t="str">
         <v>NONONO</v>
@@ -13306,11 +14269,14 @@
       <c r="C339" t="str">
         <v/>
       </c>
+      <c r="D339" t="str">
+        <v>Jigglypuff</v>
+      </c>
       <c r="E339" t="str">
-        <v>undefined-undefined</v>
+        <v>44-45</v>
       </c>
       <c r="F339" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G339" t="str">
         <v/>
@@ -13319,7 +14285,7 @@
         <v>Yes</v>
       </c>
       <c r="I339" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J339" t="str">
         <v>NONONO</v>
@@ -13344,11 +14310,14 @@
       <c r="C340" t="str">
         <v/>
       </c>
+      <c r="D340" t="str">
+        <v>Wigglytuff</v>
+      </c>
       <c r="E340" t="str">
-        <v>undefined-undefined</v>
+        <v>44-45</v>
       </c>
       <c r="F340" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G340" t="str">
         <v/>
@@ -13382,11 +14351,14 @@
       <c r="C341" t="str">
         <v/>
       </c>
+      <c r="D341" t="str">
+        <v>Munna</v>
+      </c>
       <c r="E341" t="str">
-        <v>undefined-undefined</v>
+        <v>53-54</v>
       </c>
       <c r="F341" t="str">
-        <v>0.3334%</v>
+        <v>33%</v>
       </c>
       <c r="G341" t="str">
         <v/>
@@ -13395,7 +14367,7 @@
         <v>Yes</v>
       </c>
       <c r="I341" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J341" t="str">
         <v>NONONO</v>
@@ -13420,11 +14392,14 @@
       <c r="C342" t="str">
         <v/>
       </c>
+      <c r="D342" t="str">
+        <v>Rufflet</v>
+      </c>
       <c r="E342" t="str">
-        <v>undefined-undefined</v>
+        <v>53-54</v>
       </c>
       <c r="F342" t="str">
-        <v>0.3333%</v>
+        <v>33%</v>
       </c>
       <c r="G342" t="str">
         <v/>
@@ -13458,11 +14433,14 @@
       <c r="C343" t="str">
         <v/>
       </c>
+      <c r="D343" t="str">
+        <v>Musharna</v>
+      </c>
       <c r="E343" t="str">
-        <v>undefined-undefined</v>
+        <v>53-54</v>
       </c>
       <c r="F343" t="str">
-        <v>0.3333%</v>
+        <v>33%</v>
       </c>
       <c r="G343" t="str">
         <v/>
@@ -13496,11 +14474,14 @@
       <c r="C344" t="str">
         <v/>
       </c>
+      <c r="D344" t="str">
+        <v>Scraggy</v>
+      </c>
       <c r="E344" t="str">
-        <v>undefined-undefined</v>
+        <v>61-62</v>
       </c>
       <c r="F344" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G344" t="str">
         <v/>
@@ -13509,7 +14490,7 @@
         <v>Yes</v>
       </c>
       <c r="I344" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J344" t="str">
         <v>NONONO</v>
@@ -13534,11 +14515,14 @@
       <c r="C345" t="str">
         <v/>
       </c>
+      <c r="D345" t="str">
+        <v>Crustle</v>
+      </c>
       <c r="E345" t="str">
-        <v>undefined-undefined</v>
+        <v>61-62</v>
       </c>
       <c r="F345" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G345" t="str">
         <v/>
@@ -13572,11 +14556,14 @@
       <c r="C346" t="str">
         <v/>
       </c>
+      <c r="D346" t="str">
+        <v>Carnivine</v>
+      </c>
       <c r="E346" t="str">
-        <v>undefined-undefined</v>
+        <v>61-62</v>
       </c>
       <c r="F346" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G346" t="str">
         <v/>
@@ -13610,11 +14597,14 @@
       <c r="C347" t="str">
         <v/>
       </c>
+      <c r="D347" t="str">
+        <v>Drifblim</v>
+      </c>
       <c r="E347" t="str">
-        <v>undefined-undefined</v>
+        <v>61-62</v>
       </c>
       <c r="F347" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G347" t="str">
         <v/>
@@ -13648,11 +14638,14 @@
       <c r="C348" t="str">
         <v/>
       </c>
+      <c r="D348" t="str">
+        <v>Scrafty</v>
+      </c>
       <c r="E348" t="str">
-        <v>undefined-undefined</v>
+        <v>61-62</v>
       </c>
       <c r="F348" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G348" t="str">
         <v/>
@@ -13686,11 +14679,14 @@
       <c r="C349" t="str">
         <v/>
       </c>
+      <c r="D349" t="str">
+        <v>Frillish</v>
+      </c>
       <c r="E349" t="str">
-        <v>undefined-undefined</v>
+        <v>70-70</v>
       </c>
       <c r="F349" t="str">
-        <v>0.5%</v>
+        <v>50%</v>
       </c>
       <c r="G349" t="str">
         <v/>
@@ -13699,7 +14695,7 @@
         <v>Yes</v>
       </c>
       <c r="I349" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J349" t="str">
         <v>NONONO</v>
@@ -13724,11 +14720,14 @@
       <c r="C350" t="str">
         <v/>
       </c>
+      <c r="D350" t="str">
+        <v>Alomomola</v>
+      </c>
       <c r="E350" t="str">
-        <v>undefined-undefined</v>
+        <v>70-70</v>
       </c>
       <c r="F350" t="str">
-        <v>0.5%</v>
+        <v>50%</v>
       </c>
       <c r="G350" t="str">
         <v/>
@@ -13762,11 +14761,14 @@
       <c r="C351" t="str">
         <v/>
       </c>
+      <c r="D351" t="str">
+        <v>Tepig</v>
+      </c>
       <c r="E351" t="str">
-        <v>undefined-undefined</v>
+        <v>65-66</v>
       </c>
       <c r="F351" t="str">
-        <v>0.5%</v>
+        <v>50%</v>
       </c>
       <c r="G351" t="str">
         <v/>
@@ -13775,7 +14777,7 @@
         <v>Yes</v>
       </c>
       <c r="I351" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J351" t="str">
         <v>NONONO</v>
@@ -13800,11 +14802,14 @@
       <c r="C352" t="str">
         <v/>
       </c>
+      <c r="D352" t="str">
+        <v>Oshawott</v>
+      </c>
       <c r="E352" t="str">
-        <v>undefined-undefined</v>
+        <v>65-66</v>
       </c>
       <c r="F352" t="str">
-        <v>0.5%</v>
+        <v>50%</v>
       </c>
       <c r="G352" t="str">
         <v/>
@@ -13813,7 +14818,7 @@
         <v>Yes</v>
       </c>
       <c r="I352" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J352" t="str">
         <v>NONONO</v>
@@ -13838,11 +14843,14 @@
       <c r="C353" t="str">
         <v/>
       </c>
+      <c r="D353" t="str">
+        <v>Cleffa</v>
+      </c>
       <c r="E353" t="str">
-        <v>undefined-undefined</v>
+        <v>76-77</v>
       </c>
       <c r="F353" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G353" t="str">
         <v/>
@@ -13851,7 +14859,7 @@
         <v>Yes</v>
       </c>
       <c r="I353" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J353" t="str">
         <v>NONONO</v>
@@ -13876,11 +14884,14 @@
       <c r="C354" t="str">
         <v/>
       </c>
+      <c r="D354" t="str">
+        <v>Igglybuff</v>
+      </c>
       <c r="E354" t="str">
-        <v>undefined-undefined</v>
+        <v>76-77</v>
       </c>
       <c r="F354" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G354" t="str">
         <v/>
@@ -13889,7 +14900,7 @@
         <v>Yes</v>
       </c>
       <c r="I354" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J354" t="str">
         <v>NONONO</v>
@@ -13914,11 +14925,14 @@
       <c r="C355" t="str">
         <v/>
       </c>
+      <c r="D355" t="str">
+        <v>Ampharos</v>
+      </c>
       <c r="E355" t="str">
-        <v>undefined-undefined</v>
+        <v>76-77</v>
       </c>
       <c r="F355" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G355" t="str">
         <v/>
@@ -13952,11 +14966,14 @@
       <c r="C356" t="str">
         <v/>
       </c>
+      <c r="D356" t="str">
+        <v>Flaaffy</v>
+      </c>
       <c r="E356" t="str">
-        <v>undefined-undefined</v>
+        <v>76-77</v>
       </c>
       <c r="F356" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G356" t="str">
         <v/>
@@ -13990,11 +15007,14 @@
       <c r="C357" t="str">
         <v/>
       </c>
+      <c r="D357" t="str">
+        <v>Blitzle</v>
+      </c>
       <c r="E357" t="str">
-        <v>undefined-undefined</v>
+        <v>88-89</v>
       </c>
       <c r="F357" t="str">
-        <v>0.1665%</v>
+        <v>17%</v>
       </c>
       <c r="G357" t="str">
         <v/>
@@ -14003,7 +15023,7 @@
         <v>Yes</v>
       </c>
       <c r="I357" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J357" t="str">
         <v>NONONO</v>
@@ -14028,11 +15048,14 @@
       <c r="C358" t="str">
         <v/>
       </c>
+      <c r="D358" t="str">
+        <v>Spoink</v>
+      </c>
       <c r="E358" t="str">
-        <v>undefined-undefined</v>
+        <v>88-89</v>
       </c>
       <c r="F358" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G358" t="str">
         <v/>
@@ -14041,7 +15064,7 @@
         <v>Yes</v>
       </c>
       <c r="I358" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J358" t="str">
         <v>NONONO</v>
@@ -14066,11 +15089,14 @@
       <c r="C359" t="str">
         <v/>
       </c>
+      <c r="D359" t="str">
+        <v>Lickitung</v>
+      </c>
       <c r="E359" t="str">
-        <v>undefined-undefined</v>
+        <v>88-89</v>
       </c>
       <c r="F359" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G359" t="str">
         <v/>
@@ -14104,11 +15130,14 @@
       <c r="C360" t="str">
         <v/>
       </c>
+      <c r="D360" t="str">
+        <v>Lickilicky</v>
+      </c>
       <c r="E360" t="str">
-        <v>undefined-undefined</v>
+        <v>88-89</v>
       </c>
       <c r="F360" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G360" t="str">
         <v/>
@@ -14142,11 +15171,14 @@
       <c r="C361" t="str">
         <v/>
       </c>
+      <c r="D361" t="str">
+        <v>Vigoroth</v>
+      </c>
       <c r="E361" t="str">
-        <v>undefined-undefined</v>
+        <v>88-89</v>
       </c>
       <c r="F361" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G361" t="str">
         <v/>
@@ -14180,11 +15212,14 @@
       <c r="C362" t="str">
         <v/>
       </c>
+      <c r="D362" t="str">
+        <v>Slaking</v>
+      </c>
       <c r="E362" t="str">
-        <v>undefined-undefined</v>
+        <v>88-89</v>
       </c>
       <c r="F362" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G362" t="str">
         <v/>
@@ -14218,11 +15253,14 @@
       <c r="C363" t="str">
         <v/>
       </c>
+      <c r="D363" t="str">
+        <v>Throh</v>
+      </c>
       <c r="E363" t="str">
-        <v>undefined-undefined</v>
+        <v>99-100</v>
       </c>
       <c r="F363" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G363" t="str">
         <v/>
@@ -14256,11 +15294,14 @@
       <c r="C364" t="str">
         <v/>
       </c>
+      <c r="D364" t="str">
+        <v>Sawk</v>
+      </c>
       <c r="E364" t="str">
-        <v>undefined-undefined</v>
+        <v>99-100</v>
       </c>
       <c r="F364" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G364" t="str">
         <v/>
@@ -14294,11 +15335,14 @@
       <c r="C365" t="str">
         <v/>
       </c>
+      <c r="D365" t="str">
+        <v>Conkeldurr</v>
+      </c>
       <c r="E365" t="str">
-        <v>undefined-undefined</v>
+        <v>99-100</v>
       </c>
       <c r="F365" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G365" t="str">
         <v/>
@@ -14332,11 +15376,14 @@
       <c r="C366" t="str">
         <v/>
       </c>
+      <c r="D366" t="str">
+        <v>Electabuzz</v>
+      </c>
       <c r="E366" t="str">
-        <v>undefined-undefined</v>
+        <v>99-100</v>
       </c>
       <c r="F366" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G366" t="str">
         <v/>
@@ -14370,11 +15417,14 @@
       <c r="C367" t="str">
         <v/>
       </c>
+      <c r="D367" t="str">
+        <v>Electivire</v>
+      </c>
       <c r="E367" t="str">
-        <v>undefined-undefined</v>
+        <v>99-100</v>
       </c>
       <c r="F367" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G367" t="str">
         <v/>
@@ -14408,11 +15458,14 @@
       <c r="C368" t="str">
         <v/>
       </c>
+      <c r="D368" t="str">
+        <v>Cobalion</v>
+      </c>
       <c r="E368" t="str">
-        <v>undefined-undefined</v>
+        <v>110-110</v>
       </c>
       <c r="F368" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G368" t="str">
         <v/>
@@ -14446,11 +15499,14 @@
       <c r="C369" t="str">
         <v/>
       </c>
+      <c r="D369" t="str">
+        <v>Terrakion</v>
+      </c>
       <c r="E369" t="str">
-        <v>undefined-undefined</v>
+        <v>110-110</v>
       </c>
       <c r="F369" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G369" t="str">
         <v/>
@@ -14484,11 +15540,14 @@
       <c r="C370" t="str">
         <v/>
       </c>
+      <c r="D370" t="str">
+        <v>Virizion</v>
+      </c>
       <c r="E370" t="str">
-        <v>undefined-undefined</v>
+        <v>110-110</v>
       </c>
       <c r="F370" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G370" t="str">
         <v/>
@@ -14522,11 +15581,14 @@
       <c r="C371" t="str">
         <v/>
       </c>
+      <c r="D371" t="str">
+        <v>Keldeo</v>
+      </c>
       <c r="E371" t="str">
-        <v>undefined-undefined</v>
+        <v>110-115</v>
       </c>
       <c r="F371" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G371" t="str">
         <v/>
@@ -14601,11 +15663,14 @@
       <c r="C373" t="str">
         <v/>
       </c>
+      <c r="D373" t="str">
+        <v>Tympole</v>
+      </c>
       <c r="E373" t="str">
-        <v>undefined-undefined</v>
+        <v>76-77</v>
       </c>
       <c r="F373" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G373" t="str">
         <v/>
@@ -14614,7 +15679,7 @@
         <v>Yes</v>
       </c>
       <c r="I373" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J373" t="str">
         <v>NONONO</v>
@@ -14639,11 +15704,14 @@
       <c r="C374" t="str">
         <v/>
       </c>
+      <c r="D374" t="str">
+        <v>Budew</v>
+      </c>
       <c r="E374" t="str">
-        <v>undefined-undefined</v>
+        <v>76-77</v>
       </c>
       <c r="F374" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G374" t="str">
         <v/>
@@ -14652,7 +15720,7 @@
         <v>Yes</v>
       </c>
       <c r="I374" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J374" t="str">
         <v>NONONO</v>
@@ -14677,11 +15745,14 @@
       <c r="C375" t="str">
         <v/>
       </c>
+      <c r="D375" t="str">
+        <v>Herdier</v>
+      </c>
       <c r="E375" t="str">
-        <v>undefined-undefined</v>
+        <v>76-77</v>
       </c>
       <c r="F375" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G375" t="str">
         <v/>
@@ -14715,11 +15786,14 @@
       <c r="C376" t="str">
         <v/>
       </c>
+      <c r="D376" t="str">
+        <v>Stoutland</v>
+      </c>
       <c r="E376" t="str">
-        <v>undefined-undefined</v>
+        <v>76-77</v>
       </c>
       <c r="F376" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G376" t="str">
         <v/>
@@ -14753,11 +15827,14 @@
       <c r="C377" t="str">
         <v/>
       </c>
+      <c r="D377" t="str">
+        <v>Snivy</v>
+      </c>
       <c r="E377" t="str">
-        <v>undefined-undefined</v>
+        <v>88-89</v>
       </c>
       <c r="F377" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G377" t="str">
         <v/>
@@ -14766,7 +15843,7 @@
         <v>Yes</v>
       </c>
       <c r="I377" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J377" t="str">
         <v>NONONO</v>
@@ -14791,11 +15868,14 @@
       <c r="C378" t="str">
         <v/>
       </c>
+      <c r="D378" t="str">
+        <v>Pansage</v>
+      </c>
       <c r="E378" t="str">
-        <v>undefined-undefined</v>
+        <v>88-89</v>
       </c>
       <c r="F378" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G378" t="str">
         <v/>
@@ -14804,7 +15884,7 @@
         <v>Yes</v>
       </c>
       <c r="I378" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J378" t="str">
         <v>NONONO</v>
@@ -14829,11 +15909,14 @@
       <c r="C379" t="str">
         <v/>
       </c>
+      <c r="D379" t="str">
+        <v>Yanmega</v>
+      </c>
       <c r="E379" t="str">
-        <v>undefined-undefined</v>
+        <v>88-89</v>
       </c>
       <c r="F379" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G379" t="str">
         <v/>
@@ -14867,11 +15950,14 @@
       <c r="C380" t="str">
         <v/>
       </c>
+      <c r="D380" t="str">
+        <v>Tangrowth</v>
+      </c>
       <c r="E380" t="str">
-        <v>undefined-undefined</v>
+        <v>88-89</v>
       </c>
       <c r="F380" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G380" t="str">
         <v/>
@@ -14905,11 +15991,14 @@
       <c r="C381" t="str">
         <v/>
       </c>
+      <c r="D381" t="str">
+        <v>Roggenrola</v>
+      </c>
       <c r="E381" t="str">
-        <v>undefined-undefined</v>
+        <v>99-100</v>
       </c>
       <c r="F381" t="str">
-        <v>0.1665%</v>
+        <v>17%</v>
       </c>
       <c r="G381" t="str">
         <v/>
@@ -14918,7 +16007,7 @@
         <v>Yes</v>
       </c>
       <c r="I381" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J381" t="str">
         <v>NONONO</v>
@@ -14943,11 +16032,14 @@
       <c r="C382" t="str">
         <v/>
       </c>
+      <c r="D382" t="str">
+        <v>Axew</v>
+      </c>
       <c r="E382" t="str">
-        <v>undefined-undefined</v>
+        <v>99-100</v>
       </c>
       <c r="F382" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G382" t="str">
         <v/>
@@ -14956,7 +16048,7 @@
         <v>Yes</v>
       </c>
       <c r="I382" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J382" t="str">
         <v>NONONO</v>
@@ -14981,11 +16073,14 @@
       <c r="C383" t="str">
         <v/>
       </c>
+      <c r="D383" t="str">
+        <v>Lucario</v>
+      </c>
       <c r="E383" t="str">
-        <v>undefined-undefined</v>
+        <v>99-100</v>
       </c>
       <c r="F383" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G383" t="str">
         <v/>
@@ -15019,11 +16114,14 @@
       <c r="C384" t="str">
         <v/>
       </c>
+      <c r="D384" t="str">
+        <v>Simisage</v>
+      </c>
       <c r="E384" t="str">
-        <v>undefined-undefined</v>
+        <v>99-100</v>
       </c>
       <c r="F384" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G384" t="str">
         <v/>
@@ -15057,11 +16155,14 @@
       <c r="C385" t="str">
         <v/>
       </c>
+      <c r="D385" t="str">
+        <v>Simisear</v>
+      </c>
       <c r="E385" t="str">
-        <v>undefined-undefined</v>
+        <v>99-100</v>
       </c>
       <c r="F385" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G385" t="str">
         <v/>
@@ -15095,11 +16196,14 @@
       <c r="C386" t="str">
         <v/>
       </c>
+      <c r="D386" t="str">
+        <v>Simipour</v>
+      </c>
       <c r="E386" t="str">
-        <v>undefined-undefined</v>
+        <v>99-100</v>
       </c>
       <c r="F386" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G386" t="str">
         <v/>
@@ -15133,11 +16237,14 @@
       <c r="C387" t="str">
         <v/>
       </c>
+      <c r="D387" t="str">
+        <v>Victini</v>
+      </c>
       <c r="E387" t="str">
-        <v>undefined-undefined</v>
+        <v>110-115</v>
       </c>
       <c r="F387" t="str">
-        <v>0.3334%</v>
+        <v>33%</v>
       </c>
       <c r="G387" t="str">
         <v/>
@@ -15171,11 +16278,14 @@
       <c r="C388" t="str">
         <v/>
       </c>
+      <c r="D388" t="str">
+        <v>Meloetta</v>
+      </c>
       <c r="E388" t="str">
-        <v>undefined-undefined</v>
+        <v>110-115</v>
       </c>
       <c r="F388" t="str">
-        <v>0.3333%</v>
+        <v>33%</v>
       </c>
       <c r="G388" t="str">
         <v/>
@@ -15209,11 +16319,14 @@
       <c r="C389" t="str">
         <v/>
       </c>
+      <c r="D389" t="str">
+        <v>Genesect</v>
+      </c>
       <c r="E389" t="str">
-        <v>undefined-undefined</v>
+        <v>110-110</v>
       </c>
       <c r="F389" t="str">
-        <v>0.3333%</v>
+        <v>33%</v>
       </c>
       <c r="G389" t="str">
         <v/>
@@ -15247,11 +16360,14 @@
       <c r="C390" t="str">
         <v/>
       </c>
+      <c r="D390" t="str">
+        <v>Bouffalant</v>
+      </c>
       <c r="E390" t="str">
-        <v>undefined-undefined</v>
+        <v>65-66</v>
       </c>
       <c r="F390" t="str">
-        <v>0.1665%</v>
+        <v>17%</v>
       </c>
       <c r="G390" t="str">
         <v/>
@@ -15285,11 +16401,14 @@
       <c r="C391" t="str">
         <v/>
       </c>
+      <c r="D391" t="str">
+        <v>Braviary</v>
+      </c>
       <c r="E391" t="str">
-        <v>undefined-undefined</v>
+        <v>65-66</v>
       </c>
       <c r="F391" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G391" t="str">
         <v/>
@@ -15323,11 +16442,14 @@
       <c r="C392" t="str">
         <v/>
       </c>
+      <c r="D392" t="str">
+        <v>Mandibuzz</v>
+      </c>
       <c r="E392" t="str">
-        <v>undefined-undefined</v>
+        <v>65-66</v>
       </c>
       <c r="F392" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G392" t="str">
         <v/>
@@ -15361,11 +16483,14 @@
       <c r="C393" t="str">
         <v/>
       </c>
+      <c r="D393" t="str">
+        <v>Amoonguss</v>
+      </c>
       <c r="E393" t="str">
-        <v>undefined-undefined</v>
+        <v>65-66</v>
       </c>
       <c r="F393" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G393" t="str">
         <v/>
@@ -15399,11 +16524,14 @@
       <c r="C394" t="str">
         <v/>
       </c>
+      <c r="D394" t="str">
+        <v>Eelektrik</v>
+      </c>
       <c r="E394" t="str">
-        <v>undefined-undefined</v>
+        <v>65-66</v>
       </c>
       <c r="F394" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G394" t="str">
         <v/>
@@ -15437,11 +16565,14 @@
       <c r="C395" t="str">
         <v/>
       </c>
+      <c r="D395" t="str">
+        <v>Vullaby</v>
+      </c>
       <c r="E395" t="str">
-        <v>undefined-undefined</v>
+        <v>65-66</v>
       </c>
       <c r="F395" t="str">
-        <v>0.1667%</v>
+        <v>17%</v>
       </c>
       <c r="G395" t="str">
         <v/>
@@ -15475,11 +16606,14 @@
       <c r="C396" t="str">
         <v/>
       </c>
+      <c r="D396" t="str">
+        <v>Yanma</v>
+      </c>
       <c r="E396" t="str">
-        <v>undefined-undefined</v>
+        <v>76-77</v>
       </c>
       <c r="F396" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G396" t="str">
         <v/>
@@ -15513,11 +16647,14 @@
       <c r="C397" t="str">
         <v/>
       </c>
+      <c r="D397" t="str">
+        <v>Zorua</v>
+      </c>
       <c r="E397" t="str">
-        <v>undefined-undefined</v>
+        <v>76-77</v>
       </c>
       <c r="F397" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G397" t="str">
         <v/>
@@ -15526,7 +16663,7 @@
         <v>Yes</v>
       </c>
       <c r="I397" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J397" t="str">
         <v>NONONO</v>
@@ -15551,11 +16688,14 @@
       <c r="C398" t="str">
         <v/>
       </c>
+      <c r="D398" t="str">
+        <v>Arcanine</v>
+      </c>
       <c r="E398" t="str">
-        <v>undefined-undefined</v>
+        <v>76-77</v>
       </c>
       <c r="F398" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G398" t="str">
         <v/>
@@ -15589,11 +16729,14 @@
       <c r="C399" t="str">
         <v/>
       </c>
+      <c r="D399" t="str">
+        <v>Ninetales</v>
+      </c>
       <c r="E399" t="str">
-        <v>undefined-undefined</v>
+        <v>76-77</v>
       </c>
       <c r="F399" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G399" t="str">
         <v/>
@@ -15627,11 +16770,14 @@
       <c r="C400" t="str">
         <v/>
       </c>
+      <c r="D400" t="str">
+        <v>Cryogonal</v>
+      </c>
       <c r="E400" t="str">
-        <v>undefined-undefined</v>
+        <v>88-89</v>
       </c>
       <c r="F400" t="str">
-        <v>0.5%</v>
+        <v>50%</v>
       </c>
       <c r="G400" t="str">
         <v/>
@@ -15665,11 +16811,14 @@
       <c r="C401" t="str">
         <v/>
       </c>
+      <c r="D401" t="str">
+        <v>Beartic</v>
+      </c>
       <c r="E401" t="str">
-        <v>undefined-undefined</v>
+        <v>88-89</v>
       </c>
       <c r="F401" t="str">
-        <v>0.5%</v>
+        <v>50%</v>
       </c>
       <c r="G401" t="str">
         <v/>
@@ -15703,11 +16852,14 @@
       <c r="C402" t="str">
         <v/>
       </c>
+      <c r="D402" t="str">
+        <v>Stunfisk</v>
+      </c>
       <c r="E402" t="str">
-        <v>undefined-undefined</v>
+        <v>99-100</v>
       </c>
       <c r="F402" t="str">
-        <v>0.5%</v>
+        <v>50%</v>
       </c>
       <c r="G402" t="str">
         <v/>
@@ -15741,11 +16893,14 @@
       <c r="C403" t="str">
         <v/>
       </c>
+      <c r="D403" t="str">
+        <v>Bouffalant</v>
+      </c>
       <c r="E403" t="str">
-        <v>undefined-undefined</v>
+        <v>99-100</v>
       </c>
       <c r="F403" t="str">
-        <v>0.5%</v>
+        <v>50%</v>
       </c>
       <c r="G403" t="str">
         <v/>
@@ -15779,11 +16934,14 @@
       <c r="C404" t="str">
         <v/>
       </c>
+      <c r="D404" t="str">
+        <v>Landorus</v>
+      </c>
       <c r="E404" t="str">
-        <v>undefined-undefined</v>
+        <v>115-115</v>
       </c>
       <c r="F404" t="str">
-        <v>0.3334%</v>
+        <v>33%</v>
       </c>
       <c r="G404" t="str">
         <v/>
@@ -15817,11 +16975,14 @@
       <c r="C405" t="str">
         <v/>
       </c>
+      <c r="D405" t="str">
+        <v>Thundurus</v>
+      </c>
       <c r="E405" t="str">
-        <v>undefined-undefined</v>
+        <v>110-110</v>
       </c>
       <c r="F405" t="str">
-        <v>0.3333%</v>
+        <v>33%</v>
       </c>
       <c r="G405" t="str">
         <v/>
@@ -15855,11 +17016,14 @@
       <c r="C406" t="str">
         <v/>
       </c>
+      <c r="D406" t="str">
+        <v>Tornadus</v>
+      </c>
       <c r="E406" t="str">
-        <v>undefined-undefined</v>
+        <v>110-110</v>
       </c>
       <c r="F406" t="str">
-        <v>0.3333%</v>
+        <v>33%</v>
       </c>
       <c r="G406" t="str">
         <v/>
@@ -15893,11 +17057,14 @@
       <c r="C407" t="str">
         <v/>
       </c>
+      <c r="D407" t="str">
+        <v>Kyurem</v>
+      </c>
       <c r="E407" t="str">
-        <v>undefined-undefined</v>
+        <v>120-121</v>
       </c>
       <c r="F407" t="str">
-        <v>0.3334%</v>
+        <v>33%</v>
       </c>
       <c r="G407" t="str">
         <v/>
@@ -15931,11 +17098,14 @@
       <c r="C408" t="str">
         <v/>
       </c>
+      <c r="D408" t="str">
+        <v>Reshiram</v>
+      </c>
       <c r="E408" t="str">
-        <v>undefined-undefined</v>
+        <v>120-121</v>
       </c>
       <c r="F408" t="str">
-        <v>0.3333%</v>
+        <v>33%</v>
       </c>
       <c r="G408" t="str">
         <v/>
@@ -15969,11 +17139,14 @@
       <c r="C409" t="str">
         <v/>
       </c>
+      <c r="D409" t="str">
+        <v>Zekrom</v>
+      </c>
       <c r="E409" t="str">
-        <v>undefined-undefined</v>
+        <v>120-121</v>
       </c>
       <c r="F409" t="str">
-        <v>0.3333%</v>
+        <v>33%</v>
       </c>
       <c r="G409" t="str">
         <v/>
@@ -17445,7 +18618,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B157"/>
+  <dimension ref="A1:B11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -17457,1255 +18630,87 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Victini</v>
+        <v>Servine</v>
       </c>
       <c r="B2" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Snivy</v>
+        <v>Pignite</v>
       </c>
       <c r="B3" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Servine</v>
+        <v>Emboar</v>
       </c>
       <c r="B4" t="str">
-        <v>No</v>
+        <v>2xEvolution</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Serperior</v>
+        <v>Dewott</v>
       </c>
       <c r="B5" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Tepig</v>
+        <v>Samurott</v>
       </c>
       <c r="B6" t="str">
-        <v>No</v>
+        <v>2xEvolution</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Pignite</v>
+        <v>Whirlipede</v>
       </c>
       <c r="B7" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Emboar</v>
+        <v>Scolipede</v>
       </c>
       <c r="B8" t="str">
-        <v>No</v>
+        <v>2xEvolution</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Oshawott</v>
+        <v>Archeops</v>
       </c>
       <c r="B9" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Dewott</v>
+        <v>Ferrothorn</v>
       </c>
       <c r="B10" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Samurott</v>
+        <v>Eelektross</v>
       </c>
       <c r="B11" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Patrat</v>
-      </c>
-      <c r="B12" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Watchog</v>
-      </c>
-      <c r="B13" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Lillipup</v>
-      </c>
-      <c r="B14" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Herdier</v>
-      </c>
-      <c r="B15" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>Stoutland</v>
-      </c>
-      <c r="B16" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>Purrloin</v>
-      </c>
-      <c r="B17" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>Liepard</v>
-      </c>
-      <c r="B18" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Pansage</v>
-      </c>
-      <c r="B19" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>Simisage</v>
-      </c>
-      <c r="B20" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>Pansear</v>
-      </c>
-      <c r="B21" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>Simisear</v>
-      </c>
-      <c r="B22" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>Panpour</v>
-      </c>
-      <c r="B23" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>Simipour</v>
-      </c>
-      <c r="B24" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>Munna</v>
-      </c>
-      <c r="B25" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>Musharna</v>
-      </c>
-      <c r="B26" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>Pidove</v>
-      </c>
-      <c r="B27" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>Tranquill</v>
-      </c>
-      <c r="B28" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>Unfezant</v>
-      </c>
-      <c r="B29" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>Blitzle</v>
-      </c>
-      <c r="B30" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>Zebstrika</v>
-      </c>
-      <c r="B31" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>Roggenrola</v>
-      </c>
-      <c r="B32" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>Boldore</v>
-      </c>
-      <c r="B33" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>Gigalith</v>
-      </c>
-      <c r="B34" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>Woobat</v>
-      </c>
-      <c r="B35" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v>Swoobat</v>
-      </c>
-      <c r="B36" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v>Drilbur</v>
-      </c>
-      <c r="B37" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v>Excadrill</v>
-      </c>
-      <c r="B38" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="str">
-        <v>Audino</v>
-      </c>
-      <c r="B39" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="str">
-        <v>Timburr</v>
-      </c>
-      <c r="B40" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="str">
-        <v>Gurdurr</v>
-      </c>
-      <c r="B41" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="str">
-        <v>Conkeldurr</v>
-      </c>
-      <c r="B42" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="str">
-        <v>Tympole</v>
-      </c>
-      <c r="B43" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <v>Palpitoad</v>
-      </c>
-      <c r="B44" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="str">
-        <v>Seismitoad</v>
-      </c>
-      <c r="B45" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="str">
-        <v>Throh</v>
-      </c>
-      <c r="B46" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v>Sawk</v>
-      </c>
-      <c r="B47" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="str">
-        <v>Sewaddle</v>
-      </c>
-      <c r="B48" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="str">
-        <v>Swadloon</v>
-      </c>
-      <c r="B49" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="str">
-        <v>Leavanny</v>
-      </c>
-      <c r="B50" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="str">
-        <v>Venipede</v>
-      </c>
-      <c r="B51" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="str">
-        <v>Whirlipede</v>
-      </c>
-      <c r="B52" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="str">
-        <v>Scolipede</v>
-      </c>
-      <c r="B53" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="str">
-        <v>Cottonee</v>
-      </c>
-      <c r="B54" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="str">
-        <v>Whimsicott</v>
-      </c>
-      <c r="B55" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="str">
-        <v>Petilil</v>
-      </c>
-      <c r="B56" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="str">
-        <v>Lilligant</v>
-      </c>
-      <c r="B57" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="str">
-        <v>Basculin</v>
-      </c>
-      <c r="B58" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="str">
-        <v>Sandile</v>
-      </c>
-      <c r="B59" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="str">
-        <v>Krokorok</v>
-      </c>
-      <c r="B60" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="str">
-        <v>Krookodile</v>
-      </c>
-      <c r="B61" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <v>Darumaka</v>
-      </c>
-      <c r="B62" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="str">
-        <v>Darmanitan</v>
-      </c>
-      <c r="B63" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="str">
-        <v>Maractus</v>
-      </c>
-      <c r="B64" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="str">
-        <v>Dwebble</v>
-      </c>
-      <c r="B65" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
-        <v>Crustle</v>
-      </c>
-      <c r="B66" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="str">
-        <v>Scraggy</v>
-      </c>
-      <c r="B67" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="str">
-        <v>Scrafty</v>
-      </c>
-      <c r="B68" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="str">
-        <v>Sigilyph</v>
-      </c>
-      <c r="B69" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="str">
-        <v>Yamask</v>
-      </c>
-      <c r="B70" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="str">
-        <v>Cofagrigus</v>
-      </c>
-      <c r="B71" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="str">
-        <v>Tirtouga</v>
-      </c>
-      <c r="B72" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="str">
-        <v>Carracosta</v>
-      </c>
-      <c r="B73" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="str">
-        <v>Archen</v>
-      </c>
-      <c r="B74" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="str">
-        <v>Archeops</v>
-      </c>
-      <c r="B75" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="str">
-        <v>Trubbish</v>
-      </c>
-      <c r="B76" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="str">
-        <v>Garbodor</v>
-      </c>
-      <c r="B77" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="str">
-        <v>Zorua</v>
-      </c>
-      <c r="B78" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="str">
-        <v>Zoroark</v>
-      </c>
-      <c r="B79" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="str">
-        <v>Minccino</v>
-      </c>
-      <c r="B80" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="str">
-        <v>Cinccino</v>
-      </c>
-      <c r="B81" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="str">
-        <v>Gothita</v>
-      </c>
-      <c r="B82" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="str">
-        <v>Gothorita</v>
-      </c>
-      <c r="B83" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="str">
-        <v>Gothitelle</v>
-      </c>
-      <c r="B84" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="str">
-        <v>Solosis</v>
-      </c>
-      <c r="B85" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="str">
-        <v>Duosion</v>
-      </c>
-      <c r="B86" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="str">
-        <v>Reuniclus</v>
-      </c>
-      <c r="B87" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="str">
-        <v>Ducklett</v>
-      </c>
-      <c r="B88" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="str">
-        <v>Swanna</v>
-      </c>
-      <c r="B89" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="str">
-        <v>Vanillite</v>
-      </c>
-      <c r="B90" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="str">
-        <v>Vanillish</v>
-      </c>
-      <c r="B91" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="str">
-        <v>Vanilluxe</v>
-      </c>
-      <c r="B92" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="str">
-        <v>Deerling</v>
-      </c>
-      <c r="B93" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="str">
-        <v>Sawsbuck</v>
-      </c>
-      <c r="B94" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="str">
-        <v>Emolga</v>
-      </c>
-      <c r="B95" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="str">
-        <v>Karrablast</v>
-      </c>
-      <c r="B96" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="str">
-        <v>Escavalier</v>
-      </c>
-      <c r="B97" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="str">
-        <v>Foongus</v>
-      </c>
-      <c r="B98" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="str">
-        <v>Amoonguss</v>
-      </c>
-      <c r="B99" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="str">
-        <v>Frillish</v>
-      </c>
-      <c r="B100" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="str">
-        <v>Jellicent</v>
-      </c>
-      <c r="B101" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>Alomomola</v>
-      </c>
-      <c r="B102" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>Joltik</v>
-      </c>
-      <c r="B103" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>Galvantula</v>
-      </c>
-      <c r="B104" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="str">
-        <v>Ferroseed</v>
-      </c>
-      <c r="B105" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="str">
-        <v>Ferrothorn</v>
-      </c>
-      <c r="B106" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>Klink</v>
-      </c>
-      <c r="B107" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="str">
-        <v>Klang</v>
-      </c>
-      <c r="B108" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="str">
-        <v>Klinklang</v>
-      </c>
-      <c r="B109" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="str">
-        <v>Tynamo</v>
-      </c>
-      <c r="B110" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="str">
-        <v>Eelektrik</v>
-      </c>
-      <c r="B111" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="str">
-        <v>Eelektross</v>
-      </c>
-      <c r="B112" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="str">
-        <v>Elgyem</v>
-      </c>
-      <c r="B113" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="str">
-        <v>Beheeyem</v>
-      </c>
-      <c r="B114" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="str">
-        <v>Litwick</v>
-      </c>
-      <c r="B115" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="str">
-        <v>Lampent</v>
-      </c>
-      <c r="B116" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="str">
-        <v>Chandelure</v>
-      </c>
-      <c r="B117" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="str">
-        <v>Axew</v>
-      </c>
-      <c r="B118" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="str">
-        <v>Fraxure</v>
-      </c>
-      <c r="B119" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="str">
-        <v>Haxorus</v>
-      </c>
-      <c r="B120" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="str">
-        <v>Cubchoo</v>
-      </c>
-      <c r="B121" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="str">
-        <v>Beartic</v>
-      </c>
-      <c r="B122" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="str">
-        <v>Cryogonal</v>
-      </c>
-      <c r="B123" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="str">
-        <v>Shelmet</v>
-      </c>
-      <c r="B124" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="str">
-        <v>Accelgor</v>
-      </c>
-      <c r="B125" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="str">
-        <v>Stunfisk</v>
-      </c>
-      <c r="B126" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="str">
-        <v>Mienfoo</v>
-      </c>
-      <c r="B127" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="str">
-        <v>Mienshao</v>
-      </c>
-      <c r="B128" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="str">
-        <v>Druddigon</v>
-      </c>
-      <c r="B129" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="str">
-        <v>Golett</v>
-      </c>
-      <c r="B130" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="str">
-        <v>Golurk</v>
-      </c>
-      <c r="B131" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="str">
-        <v>Pawniard</v>
-      </c>
-      <c r="B132" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="str">
-        <v>Bisharp</v>
-      </c>
-      <c r="B133" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="str">
-        <v>Bouffalant</v>
-      </c>
-      <c r="B134" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="str">
-        <v>Rufflet</v>
-      </c>
-      <c r="B135" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="str">
-        <v>Braviary</v>
-      </c>
-      <c r="B136" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="str">
-        <v>Vullaby</v>
-      </c>
-      <c r="B137" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="str">
-        <v>Mandibuzz</v>
-      </c>
-      <c r="B138" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="str">
-        <v>Heatmor</v>
-      </c>
-      <c r="B139" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="str">
-        <v>Durant</v>
-      </c>
-      <c r="B140" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="str">
-        <v>Deino</v>
-      </c>
-      <c r="B141" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="str">
-        <v>Zweilous</v>
-      </c>
-      <c r="B142" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="str">
-        <v>Hydreigon</v>
-      </c>
-      <c r="B143" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="str">
-        <v>Larvesta</v>
-      </c>
-      <c r="B144" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="str">
-        <v>Volcarona</v>
-      </c>
-      <c r="B145" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="str">
-        <v>Cobalion</v>
-      </c>
-      <c r="B146" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="str">
-        <v>Terrakion</v>
-      </c>
-      <c r="B147" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="str">
-        <v>Virizion</v>
-      </c>
-      <c r="B148" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="str">
-        <v>Tornadus</v>
-      </c>
-      <c r="B149" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="str">
-        <v>Thundurus</v>
-      </c>
-      <c r="B150" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="str">
-        <v>Reshiram</v>
-      </c>
-      <c r="B151" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="str">
-        <v>Zekrom</v>
-      </c>
-      <c r="B152" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="str">
-        <v>Landorus</v>
-      </c>
-      <c r="B153" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="str">
-        <v>Kyurem</v>
-      </c>
-      <c r="B154" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="str">
-        <v>Keldeo</v>
-      </c>
-      <c r="B155" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="str">
-        <v>Meloetta</v>
-      </c>
-      <c r="B156" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="str">
-        <v>Genesect</v>
-      </c>
-      <c r="B157" t="str">
-        <v>No</v>
+        <v>2xEvolution</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B157"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/5_Unova_Data.xlsx
+++ b/5_Unova_Data.xlsx
@@ -939,7 +939,7 @@
         <v>4-5</v>
       </c>
       <c r="G12" t="str">
-        <v>2-4</v>
+        <v>1-3</v>
       </c>
       <c r="H12" s="1">
         <v>0.125</v>
@@ -986,7 +986,7 @@
         <v>4-5</v>
       </c>
       <c r="G13" t="str">
-        <v>2-4</v>
+        <v>1-3</v>
       </c>
       <c r="H13" s="1">
         <v>0.125</v>
@@ -1033,7 +1033,7 @@
         <v>4-5</v>
       </c>
       <c r="G14" t="str">
-        <v>2-4</v>
+        <v>1-3</v>
       </c>
       <c r="H14" s="1">
         <v>0.125</v>
@@ -1080,7 +1080,7 @@
         <v>4-5</v>
       </c>
       <c r="G15" t="str">
-        <v>2-4</v>
+        <v>1-3</v>
       </c>
       <c r="H15" s="1">
         <v>0.125</v>
@@ -1127,7 +1127,7 @@
         <v>4-5</v>
       </c>
       <c r="G16" t="str">
-        <v>2-4</v>
+        <v>1-3</v>
       </c>
       <c r="H16" s="1">
         <v>0.125</v>
@@ -1174,7 +1174,7 @@
         <v>4-5</v>
       </c>
       <c r="G17" t="str">
-        <v>2-4</v>
+        <v>1-3</v>
       </c>
       <c r="H17" s="1">
         <v>0.125</v>
@@ -1221,7 +1221,7 @@
         <v>4-5</v>
       </c>
       <c r="G18" t="str">
-        <v>2-4</v>
+        <v>1-3</v>
       </c>
       <c r="H18" s="1">
         <v>0.125</v>
@@ -1268,7 +1268,7 @@
         <v>4-5</v>
       </c>
       <c r="G19" t="str">
-        <v>2-4</v>
+        <v>1-3</v>
       </c>
       <c r="H19" s="1">
         <v>0.125</v>
@@ -1973,7 +1973,7 @@
         <v>10-11</v>
       </c>
       <c r="G34" t="str">
-        <v>9-11</v>
+        <v>8-10</v>
       </c>
       <c r="H34" s="1">
         <v>0.1426</v>
@@ -2020,7 +2020,7 @@
         <v>10-11</v>
       </c>
       <c r="G35" t="str">
-        <v>9-11</v>
+        <v>8-10</v>
       </c>
       <c r="H35" s="1">
         <v>0.1429</v>
@@ -2067,7 +2067,7 @@
         <v>10-11</v>
       </c>
       <c r="G36" t="str">
-        <v>9-11</v>
+        <v>8-10</v>
       </c>
       <c r="H36" s="1">
         <v>0.1429</v>
@@ -2114,7 +2114,7 @@
         <v>10-11</v>
       </c>
       <c r="G37" t="str">
-        <v>9-11</v>
+        <v>8-10</v>
       </c>
       <c r="H37" s="1">
         <v>0.1429</v>
@@ -2161,7 +2161,7 @@
         <v>10-11</v>
       </c>
       <c r="G38" t="str">
-        <v>9-11</v>
+        <v>8-10</v>
       </c>
       <c r="H38" s="1">
         <v>0.1429</v>
@@ -2208,7 +2208,7 @@
         <v>10-11</v>
       </c>
       <c r="G39" t="str">
-        <v>9-11</v>
+        <v>8-10</v>
       </c>
       <c r="H39" s="1">
         <v>0.1429</v>
@@ -2255,7 +2255,7 @@
         <v>10-11</v>
       </c>
       <c r="G40" t="str">
-        <v>9-11</v>
+        <v>8-10</v>
       </c>
       <c r="H40" s="1">
         <v>0.1429</v>
@@ -4605,7 +4605,7 @@
         <v>22-23</v>
       </c>
       <c r="G90" t="str">
-        <v>23-26</v>
+        <v>22-25</v>
       </c>
       <c r="H90" s="1">
         <v>0.3334</v>
@@ -4652,7 +4652,7 @@
         <v>22-23</v>
       </c>
       <c r="G91" t="str">
-        <v>23-26</v>
+        <v>22-25</v>
       </c>
       <c r="H91" s="1">
         <v>0.3333</v>
@@ -4699,7 +4699,7 @@
         <v>22-23</v>
       </c>
       <c r="G92" t="str">
-        <v>23-26</v>
+        <v>22-25</v>
       </c>
       <c r="H92" s="1">
         <v>0.3333</v>
@@ -5968,7 +5968,7 @@
         <v>29-30</v>
       </c>
       <c r="G119" t="str">
-        <v>30-34</v>
+        <v>29-32</v>
       </c>
       <c r="H119" s="1">
         <v>0.1</v>
@@ -6015,7 +6015,7 @@
         <v>29-30</v>
       </c>
       <c r="G120" t="str">
-        <v>30-34</v>
+        <v>29-32</v>
       </c>
       <c r="H120" s="1">
         <v>0.1</v>
@@ -6062,7 +6062,7 @@
         <v>29-30</v>
       </c>
       <c r="G121" t="str">
-        <v>30-34</v>
+        <v>29-32</v>
       </c>
       <c r="H121" s="1">
         <v>0.1</v>
@@ -6109,7 +6109,7 @@
         <v>29-30</v>
       </c>
       <c r="G122" t="str">
-        <v>30-34</v>
+        <v>29-32</v>
       </c>
       <c r="H122" s="1">
         <v>0.1</v>
@@ -6156,7 +6156,7 @@
         <v>29-30</v>
       </c>
       <c r="G123" t="str">
-        <v>30-34</v>
+        <v>29-32</v>
       </c>
       <c r="H123" s="1">
         <v>0.1</v>
@@ -6203,7 +6203,7 @@
         <v>29-30</v>
       </c>
       <c r="G124" t="str">
-        <v>30-34</v>
+        <v>29-32</v>
       </c>
       <c r="H124" s="1">
         <v>0.1</v>
@@ -6250,7 +6250,7 @@
         <v>29-30</v>
       </c>
       <c r="G125" t="str">
-        <v>30-34</v>
+        <v>29-32</v>
       </c>
       <c r="H125" s="1">
         <v>0.1</v>
@@ -6297,7 +6297,7 @@
         <v>29-30</v>
       </c>
       <c r="G126" t="str">
-        <v>30-34</v>
+        <v>29-32</v>
       </c>
       <c r="H126" s="1">
         <v>0.1</v>
@@ -6344,7 +6344,7 @@
         <v>29-30</v>
       </c>
       <c r="G127" t="str">
-        <v>30-34</v>
+        <v>29-32</v>
       </c>
       <c r="H127" s="1">
         <v>0.1</v>
@@ -6391,7 +6391,7 @@
         <v>29-30</v>
       </c>
       <c r="G128" t="str">
-        <v>30-34</v>
+        <v>29-32</v>
       </c>
       <c r="H128" s="1">
         <v>0.1</v>
@@ -6438,7 +6438,7 @@
         <v>30-31</v>
       </c>
       <c r="G129" t="str">
-        <v>31-35</v>
+        <v>31-34</v>
       </c>
       <c r="H129" s="1">
         <v>0.125</v>
@@ -6485,7 +6485,7 @@
         <v>30-31</v>
       </c>
       <c r="G130" t="str">
-        <v>31-35</v>
+        <v>31-34</v>
       </c>
       <c r="H130" s="1">
         <v>0.125</v>
@@ -6532,7 +6532,7 @@
         <v>30-31</v>
       </c>
       <c r="G131" t="str">
-        <v>31-35</v>
+        <v>31-34</v>
       </c>
       <c r="H131" s="1">
         <v>0.125</v>
@@ -6579,7 +6579,7 @@
         <v>30-31</v>
       </c>
       <c r="G132" t="str">
-        <v>31-35</v>
+        <v>31-34</v>
       </c>
       <c r="H132" s="1">
         <v>0.125</v>
@@ -6626,7 +6626,7 @@
         <v>30-31</v>
       </c>
       <c r="G133" t="str">
-        <v>31-35</v>
+        <v>31-34</v>
       </c>
       <c r="H133" s="1">
         <v>0.125</v>
@@ -6673,7 +6673,7 @@
         <v>30-31</v>
       </c>
       <c r="G134" t="str">
-        <v>31-35</v>
+        <v>31-34</v>
       </c>
       <c r="H134" s="1">
         <v>0.125</v>
@@ -6720,7 +6720,7 @@
         <v>30-31</v>
       </c>
       <c r="G135" t="str">
-        <v>31-35</v>
+        <v>31-34</v>
       </c>
       <c r="H135" s="1">
         <v>0.125</v>
@@ -6767,7 +6767,7 @@
         <v>30-31</v>
       </c>
       <c r="G136" t="str">
-        <v>31-35</v>
+        <v>31-34</v>
       </c>
       <c r="H136" s="1">
         <v>0.125</v>
@@ -6861,7 +6861,7 @@
         <v>32-33</v>
       </c>
       <c r="G138" t="str">
-        <v>34-38</v>
+        <v>34-37</v>
       </c>
       <c r="H138" s="1">
         <v>0.1112</v>
@@ -6908,7 +6908,7 @@
         <v>32-33</v>
       </c>
       <c r="G139" t="str">
-        <v>34-38</v>
+        <v>34-37</v>
       </c>
       <c r="H139" s="1">
         <v>0.1111</v>
@@ -6955,7 +6955,7 @@
         <v>32-33</v>
       </c>
       <c r="G140" t="str">
-        <v>34-38</v>
+        <v>34-37</v>
       </c>
       <c r="H140" s="1">
         <v>0.1111</v>
@@ -7002,7 +7002,7 @@
         <v>32-33</v>
       </c>
       <c r="G141" t="str">
-        <v>34-38</v>
+        <v>34-37</v>
       </c>
       <c r="H141" s="1">
         <v>0.1111</v>
@@ -7049,7 +7049,7 @@
         <v>32-33</v>
       </c>
       <c r="G142" t="str">
-        <v>34-38</v>
+        <v>34-37</v>
       </c>
       <c r="H142" s="1">
         <v>0.1111</v>
@@ -7096,7 +7096,7 @@
         <v>32-33</v>
       </c>
       <c r="G143" t="str">
-        <v>34-38</v>
+        <v>34-37</v>
       </c>
       <c r="H143" s="1">
         <v>0.1111</v>
@@ -7143,7 +7143,7 @@
         <v>32-33</v>
       </c>
       <c r="G144" t="str">
-        <v>34-38</v>
+        <v>34-37</v>
       </c>
       <c r="H144" s="1">
         <v>0.1111</v>
@@ -7190,7 +7190,7 @@
         <v>32-33</v>
       </c>
       <c r="G145" t="str">
-        <v>34-38</v>
+        <v>34-37</v>
       </c>
       <c r="H145" s="1">
         <v>0.1111</v>
@@ -7237,7 +7237,7 @@
         <v>32-33</v>
       </c>
       <c r="G146" t="str">
-        <v>34-38</v>
+        <v>34-37</v>
       </c>
       <c r="H146" s="1">
         <v>0.1111</v>
@@ -7284,7 +7284,7 @@
         <v>34-35</v>
       </c>
       <c r="G147" t="str">
-        <v>35-39</v>
+        <v>35-38</v>
       </c>
       <c r="H147" s="1">
         <v>0.1665</v>
@@ -7331,7 +7331,7 @@
         <v>34-35</v>
       </c>
       <c r="G148" t="str">
-        <v>35-39</v>
+        <v>35-38</v>
       </c>
       <c r="H148" s="1">
         <v>0.1667</v>
@@ -7378,7 +7378,7 @@
         <v>34-35</v>
       </c>
       <c r="G149" t="str">
-        <v>35-39</v>
+        <v>35-38</v>
       </c>
       <c r="H149" s="1">
         <v>0.1667</v>
@@ -7425,7 +7425,7 @@
         <v>34-35</v>
       </c>
       <c r="G150" t="str">
-        <v>35-39</v>
+        <v>35-38</v>
       </c>
       <c r="H150" s="1">
         <v>0.1667</v>
@@ -7472,7 +7472,7 @@
         <v>34-35</v>
       </c>
       <c r="G151" t="str">
-        <v>35-39</v>
+        <v>35-38</v>
       </c>
       <c r="H151" s="1">
         <v>0.1667</v>
@@ -7519,7 +7519,7 @@
         <v>34-35</v>
       </c>
       <c r="G152" t="str">
-        <v>35-39</v>
+        <v>35-38</v>
       </c>
       <c r="H152" s="1">
         <v>0.1667</v>
@@ -7660,7 +7660,7 @@
         <v>37-38</v>
       </c>
       <c r="G155" t="str">
-        <v>38-42</v>
+        <v>38-41</v>
       </c>
       <c r="H155" s="1">
         <v>0.1112</v>
@@ -7707,7 +7707,7 @@
         <v>37-38</v>
       </c>
       <c r="G156" t="str">
-        <v>38-42</v>
+        <v>38-41</v>
       </c>
       <c r="H156" s="1">
         <v>0.1111</v>
@@ -7754,7 +7754,7 @@
         <v>37-38</v>
       </c>
       <c r="G157" t="str">
-        <v>38-42</v>
+        <v>38-41</v>
       </c>
       <c r="H157" s="1">
         <v>0.1111</v>
@@ -7801,7 +7801,7 @@
         <v>37-38</v>
       </c>
       <c r="G158" t="str">
-        <v>38-42</v>
+        <v>38-41</v>
       </c>
       <c r="H158" s="1">
         <v>0.1111</v>
@@ -7848,7 +7848,7 @@
         <v>37-38</v>
       </c>
       <c r="G159" t="str">
-        <v>38-42</v>
+        <v>38-41</v>
       </c>
       <c r="H159" s="1">
         <v>0.1111</v>
@@ -7895,7 +7895,7 @@
         <v>37-38</v>
       </c>
       <c r="G160" t="str">
-        <v>38-42</v>
+        <v>38-41</v>
       </c>
       <c r="H160" s="1">
         <v>0.1111</v>
@@ -7942,7 +7942,7 @@
         <v>37-38</v>
       </c>
       <c r="G161" t="str">
-        <v>38-42</v>
+        <v>38-41</v>
       </c>
       <c r="H161" s="1">
         <v>0.1111</v>
@@ -7989,7 +7989,7 @@
         <v>37-38</v>
       </c>
       <c r="G162" t="str">
-        <v>38-42</v>
+        <v>38-41</v>
       </c>
       <c r="H162" s="1">
         <v>0.1111</v>
@@ -8036,7 +8036,7 @@
         <v>37-38</v>
       </c>
       <c r="G163" t="str">
-        <v>38-42</v>
+        <v>38-41</v>
       </c>
       <c r="H163" s="1">
         <v>0.1111</v>
@@ -8083,7 +8083,7 @@
         <v>38-39</v>
       </c>
       <c r="G164" t="str">
-        <v>40-45</v>
+        <v>39-42</v>
       </c>
       <c r="H164" s="1">
         <v>0.1</v>
@@ -8130,7 +8130,7 @@
         <v>38-39</v>
       </c>
       <c r="G165" t="str">
-        <v>40-45</v>
+        <v>39-42</v>
       </c>
       <c r="H165" s="1">
         <v>0.1</v>
@@ -8177,7 +8177,7 @@
         <v>38-39</v>
       </c>
       <c r="G166" t="str">
-        <v>40-45</v>
+        <v>39-42</v>
       </c>
       <c r="H166" s="1">
         <v>0.1</v>
@@ -8224,7 +8224,7 @@
         <v>38-39</v>
       </c>
       <c r="G167" t="str">
-        <v>40-45</v>
+        <v>39-42</v>
       </c>
       <c r="H167" s="1">
         <v>0.1</v>
@@ -8271,7 +8271,7 @@
         <v>38-39</v>
       </c>
       <c r="G168" t="str">
-        <v>40-45</v>
+        <v>39-42</v>
       </c>
       <c r="H168" s="1">
         <v>0.1</v>
@@ -8318,7 +8318,7 @@
         <v>38-39</v>
       </c>
       <c r="G169" t="str">
-        <v>40-45</v>
+        <v>39-42</v>
       </c>
       <c r="H169" s="1">
         <v>0.1</v>
@@ -8365,7 +8365,7 @@
         <v>38-39</v>
       </c>
       <c r="G170" t="str">
-        <v>40-45</v>
+        <v>39-42</v>
       </c>
       <c r="H170" s="1">
         <v>0.1</v>
@@ -8412,7 +8412,7 @@
         <v>38-39</v>
       </c>
       <c r="G171" t="str">
-        <v>40-45</v>
+        <v>39-42</v>
       </c>
       <c r="H171" s="1">
         <v>0.1</v>
@@ -8459,7 +8459,7 @@
         <v>38-39</v>
       </c>
       <c r="G172" t="str">
-        <v>40-45</v>
+        <v>39-42</v>
       </c>
       <c r="H172" s="1">
         <v>0.1</v>
@@ -8506,7 +8506,7 @@
         <v>38-39</v>
       </c>
       <c r="G173" t="str">
-        <v>40-45</v>
+        <v>39-42</v>
       </c>
       <c r="H173" s="1">
         <v>0.1</v>
@@ -8600,7 +8600,7 @@
         <v>41-42</v>
       </c>
       <c r="G175" t="str">
-        <v>42-47</v>
+        <v>42-46</v>
       </c>
       <c r="H175" s="1">
         <v>0.0837</v>
@@ -8647,7 +8647,7 @@
         <v>41-42</v>
       </c>
       <c r="G176" t="str">
-        <v>42-47</v>
+        <v>42-46</v>
       </c>
       <c r="H176" s="1">
         <v>0.0833</v>
@@ -8694,7 +8694,7 @@
         <v>41-42</v>
       </c>
       <c r="G177" t="str">
-        <v>42-47</v>
+        <v>42-46</v>
       </c>
       <c r="H177" s="1">
         <v>0.0833</v>
@@ -8741,7 +8741,7 @@
         <v>41-42</v>
       </c>
       <c r="G178" t="str">
-        <v>42-47</v>
+        <v>42-46</v>
       </c>
       <c r="H178" s="1">
         <v>0.0833</v>
@@ -8788,7 +8788,7 @@
         <v>41-42</v>
       </c>
       <c r="G179" t="str">
-        <v>42-47</v>
+        <v>42-46</v>
       </c>
       <c r="H179" s="1">
         <v>0.0833</v>
@@ -8835,7 +8835,7 @@
         <v>41-42</v>
       </c>
       <c r="G180" t="str">
-        <v>42-47</v>
+        <v>42-46</v>
       </c>
       <c r="H180" s="1">
         <v>0.0833</v>
@@ -8882,7 +8882,7 @@
         <v>41-42</v>
       </c>
       <c r="G181" t="str">
-        <v>42-47</v>
+        <v>42-46</v>
       </c>
       <c r="H181" s="1">
         <v>0.0833</v>
@@ -8929,7 +8929,7 @@
         <v>41-42</v>
       </c>
       <c r="G182" t="str">
-        <v>42-47</v>
+        <v>42-46</v>
       </c>
       <c r="H182" s="1">
         <v>0.0833</v>
@@ -8976,7 +8976,7 @@
         <v>41-42</v>
       </c>
       <c r="G183" t="str">
-        <v>42-47</v>
+        <v>42-46</v>
       </c>
       <c r="H183" s="1">
         <v>0.0833</v>
@@ -9023,7 +9023,7 @@
         <v>41-42</v>
       </c>
       <c r="G184" t="str">
-        <v>42-47</v>
+        <v>42-46</v>
       </c>
       <c r="H184" s="1">
         <v>0.0833</v>
@@ -9070,7 +9070,7 @@
         <v>41-42</v>
       </c>
       <c r="G185" t="str">
-        <v>42-47</v>
+        <v>42-46</v>
       </c>
       <c r="H185" s="1">
         <v>0.0833</v>
@@ -9117,7 +9117,7 @@
         <v>41-42</v>
       </c>
       <c r="G186" t="str">
-        <v>42-47</v>
+        <v>42-46</v>
       </c>
       <c r="H186" s="1">
         <v>0.0833</v>
@@ -9164,7 +9164,7 @@
         <v>42-43</v>
       </c>
       <c r="G187" t="str">
-        <v>44-49</v>
+        <v>44-48</v>
       </c>
       <c r="H187" s="1">
         <v>0.125</v>
@@ -9211,7 +9211,7 @@
         <v>42-43</v>
       </c>
       <c r="G188" t="str">
-        <v>44-49</v>
+        <v>44-48</v>
       </c>
       <c r="H188" s="1">
         <v>0.125</v>
@@ -9258,7 +9258,7 @@
         <v>42-43</v>
       </c>
       <c r="G189" t="str">
-        <v>44-49</v>
+        <v>44-48</v>
       </c>
       <c r="H189" s="1">
         <v>0.125</v>
@@ -9305,7 +9305,7 @@
         <v>42-43</v>
       </c>
       <c r="G190" t="str">
-        <v>44-49</v>
+        <v>44-48</v>
       </c>
       <c r="H190" s="1">
         <v>0.125</v>
@@ -9352,7 +9352,7 @@
         <v>42-43</v>
       </c>
       <c r="G191" t="str">
-        <v>44-49</v>
+        <v>44-48</v>
       </c>
       <c r="H191" s="1">
         <v>0.125</v>
@@ -9399,7 +9399,7 @@
         <v>42-43</v>
       </c>
       <c r="G192" t="str">
-        <v>44-49</v>
+        <v>44-48</v>
       </c>
       <c r="H192" s="1">
         <v>0.125</v>
@@ -9446,7 +9446,7 @@
         <v>42-43</v>
       </c>
       <c r="G193" t="str">
-        <v>44-49</v>
+        <v>44-48</v>
       </c>
       <c r="H193" s="1">
         <v>0.125</v>
@@ -9493,7 +9493,7 @@
         <v>42-43</v>
       </c>
       <c r="G194" t="str">
-        <v>44-49</v>
+        <v>44-48</v>
       </c>
       <c r="H194" s="1">
         <v>0.125</v>
@@ -9540,7 +9540,7 @@
         <v>43-44</v>
       </c>
       <c r="G195" t="str">
-        <v>45-50</v>
+        <v>45-49</v>
       </c>
       <c r="H195" s="1">
         <v>0.1665</v>
@@ -9587,7 +9587,7 @@
         <v>43-44</v>
       </c>
       <c r="G196" t="str">
-        <v>45-50</v>
+        <v>45-49</v>
       </c>
       <c r="H196" s="1">
         <v>0.1667</v>
@@ -9634,7 +9634,7 @@
         <v>43-44</v>
       </c>
       <c r="G197" t="str">
-        <v>45-50</v>
+        <v>45-49</v>
       </c>
       <c r="H197" s="1">
         <v>0.1667</v>
@@ -9681,7 +9681,7 @@
         <v>43-44</v>
       </c>
       <c r="G198" t="str">
-        <v>45-50</v>
+        <v>45-49</v>
       </c>
       <c r="H198" s="1">
         <v>0.1667</v>
@@ -9728,7 +9728,7 @@
         <v>43-44</v>
       </c>
       <c r="G199" t="str">
-        <v>45-50</v>
+        <v>45-49</v>
       </c>
       <c r="H199" s="1">
         <v>0.1667</v>
@@ -9775,7 +9775,7 @@
         <v>43-44</v>
       </c>
       <c r="G200" t="str">
-        <v>45-50</v>
+        <v>45-49</v>
       </c>
       <c r="H200" s="1">
         <v>0.1667</v>
@@ -9822,7 +9822,7 @@
         <v>44-45</v>
       </c>
       <c r="G201" t="str">
-        <v>47-52</v>
+        <v>46-50</v>
       </c>
       <c r="H201" s="1">
         <v>0.2</v>
@@ -9869,7 +9869,7 @@
         <v>44-45</v>
       </c>
       <c r="G202" t="str">
-        <v>47-52</v>
+        <v>46-50</v>
       </c>
       <c r="H202" s="1">
         <v>0.2</v>
@@ -9916,7 +9916,7 @@
         <v>44-45</v>
       </c>
       <c r="G203" t="str">
-        <v>47-52</v>
+        <v>46-50</v>
       </c>
       <c r="H203" s="1">
         <v>0.2</v>
@@ -9963,7 +9963,7 @@
         <v>44-45</v>
       </c>
       <c r="G204" t="str">
-        <v>47-52</v>
+        <v>46-50</v>
       </c>
       <c r="H204" s="1">
         <v>0.2</v>
@@ -10010,7 +10010,7 @@
         <v>44-45</v>
       </c>
       <c r="G205" t="str">
-        <v>47-52</v>
+        <v>46-50</v>
       </c>
       <c r="H205" s="1">
         <v>0.2</v>
@@ -10151,7 +10151,7 @@
         <v>48-49</v>
       </c>
       <c r="G208" t="str">
-        <v>51-57</v>
+        <v>51-56</v>
       </c>
       <c r="H208" s="1">
         <v>0.2</v>
@@ -10198,7 +10198,7 @@
         <v>48-49</v>
       </c>
       <c r="G209" t="str">
-        <v>51-57</v>
+        <v>51-56</v>
       </c>
       <c r="H209" s="1">
         <v>0.2</v>
@@ -10245,7 +10245,7 @@
         <v>48-49</v>
       </c>
       <c r="G210" t="str">
-        <v>51-57</v>
+        <v>51-56</v>
       </c>
       <c r="H210" s="1">
         <v>0.2</v>
@@ -10292,7 +10292,7 @@
         <v>48-49</v>
       </c>
       <c r="G211" t="str">
-        <v>51-57</v>
+        <v>51-56</v>
       </c>
       <c r="H211" s="1">
         <v>0.2</v>
@@ -10339,7 +10339,7 @@
         <v>48-49</v>
       </c>
       <c r="G212" t="str">
-        <v>51-57</v>
+        <v>51-56</v>
       </c>
       <c r="H212" s="1">
         <v>0.2</v>
@@ -10386,7 +10386,7 @@
         <v>49-50</v>
       </c>
       <c r="G213" t="str">
-        <v>52-58</v>
+        <v>52-57</v>
       </c>
       <c r="H213" s="1">
         <v>0.1665</v>
@@ -10433,7 +10433,7 @@
         <v>49-50</v>
       </c>
       <c r="G214" t="str">
-        <v>52-58</v>
+        <v>52-57</v>
       </c>
       <c r="H214" s="1">
         <v>0.1667</v>
@@ -10480,7 +10480,7 @@
         <v>49-50</v>
       </c>
       <c r="G215" t="str">
-        <v>52-58</v>
+        <v>52-57</v>
       </c>
       <c r="H215" s="1">
         <v>0.1667</v>
@@ -10527,7 +10527,7 @@
         <v>49-50</v>
       </c>
       <c r="G216" t="str">
-        <v>52-58</v>
+        <v>52-57</v>
       </c>
       <c r="H216" s="1">
         <v>0.1667</v>
@@ -10574,7 +10574,7 @@
         <v>49-50</v>
       </c>
       <c r="G217" t="str">
-        <v>52-58</v>
+        <v>52-57</v>
       </c>
       <c r="H217" s="1">
         <v>0.1667</v>
@@ -10621,7 +10621,7 @@
         <v>49-50</v>
       </c>
       <c r="G218" t="str">
-        <v>52-58</v>
+        <v>52-57</v>
       </c>
       <c r="H218" s="1">
         <v>0.1667</v>
@@ -10668,7 +10668,7 @@
         <v>50-51</v>
       </c>
       <c r="G219" t="str">
-        <v>54-60</v>
+        <v>53-58</v>
       </c>
       <c r="H219" s="1">
         <v>0.1426</v>
@@ -10715,7 +10715,7 @@
         <v>50-51</v>
       </c>
       <c r="G220" t="str">
-        <v>54-60</v>
+        <v>53-58</v>
       </c>
       <c r="H220" s="1">
         <v>0.1429</v>
@@ -10762,7 +10762,7 @@
         <v>50-51</v>
       </c>
       <c r="G221" t="str">
-        <v>54-60</v>
+        <v>53-58</v>
       </c>
       <c r="H221" s="1">
         <v>0.1429</v>
@@ -10809,7 +10809,7 @@
         <v>50-51</v>
       </c>
       <c r="G222" t="str">
-        <v>54-60</v>
+        <v>53-58</v>
       </c>
       <c r="H222" s="1">
         <v>0.1429</v>
@@ -10856,7 +10856,7 @@
         <v>50-51</v>
       </c>
       <c r="G223" t="str">
-        <v>54-60</v>
+        <v>53-58</v>
       </c>
       <c r="H223" s="1">
         <v>0.1429</v>
@@ -10903,7 +10903,7 @@
         <v>50-51</v>
       </c>
       <c r="G224" t="str">
-        <v>54-60</v>
+        <v>53-58</v>
       </c>
       <c r="H224" s="1">
         <v>0.1429</v>
@@ -10950,7 +10950,7 @@
         <v>50-51</v>
       </c>
       <c r="G225" t="str">
-        <v>54-60</v>
+        <v>53-58</v>
       </c>
       <c r="H225" s="1">
         <v>0.1429</v>
@@ -10997,7 +10997,7 @@
         <v>51-52</v>
       </c>
       <c r="G226" t="str">
-        <v>55-61</v>
+        <v>55-60</v>
       </c>
       <c r="H226" s="1">
         <v>0.1665</v>
@@ -11044,7 +11044,7 @@
         <v>51-52</v>
       </c>
       <c r="G227" t="str">
-        <v>55-61</v>
+        <v>55-60</v>
       </c>
       <c r="H227" s="1">
         <v>0.1667</v>
@@ -11091,7 +11091,7 @@
         <v>51-52</v>
       </c>
       <c r="G228" t="str">
-        <v>55-61</v>
+        <v>55-60</v>
       </c>
       <c r="H228" s="1">
         <v>0.1667</v>
@@ -11138,7 +11138,7 @@
         <v>51-52</v>
       </c>
       <c r="G229" t="str">
-        <v>55-61</v>
+        <v>55-60</v>
       </c>
       <c r="H229" s="1">
         <v>0.1667</v>
@@ -11185,7 +11185,7 @@
         <v>51-52</v>
       </c>
       <c r="G230" t="str">
-        <v>55-61</v>
+        <v>55-60</v>
       </c>
       <c r="H230" s="1">
         <v>0.1667</v>
@@ -11232,7 +11232,7 @@
         <v>51-52</v>
       </c>
       <c r="G231" t="str">
-        <v>55-61</v>
+        <v>55-60</v>
       </c>
       <c r="H231" s="1">
         <v>0.1667</v>
@@ -11326,7 +11326,7 @@
         <v>53-54</v>
       </c>
       <c r="G233" t="str">
-        <v>58-64</v>
+        <v>58-63</v>
       </c>
       <c r="H233" s="1">
         <v>0.1</v>
@@ -11373,7 +11373,7 @@
         <v>53-54</v>
       </c>
       <c r="G234" t="str">
-        <v>58-64</v>
+        <v>58-63</v>
       </c>
       <c r="H234" s="1">
         <v>0.1</v>
@@ -11420,7 +11420,7 @@
         <v>53-54</v>
       </c>
       <c r="G235" t="str">
-        <v>58-64</v>
+        <v>58-63</v>
       </c>
       <c r="H235" s="1">
         <v>0.1</v>
@@ -11467,7 +11467,7 @@
         <v>53-54</v>
       </c>
       <c r="G236" t="str">
-        <v>58-64</v>
+        <v>58-63</v>
       </c>
       <c r="H236" s="1">
         <v>0.1</v>
@@ -11514,7 +11514,7 @@
         <v>53-54</v>
       </c>
       <c r="G237" t="str">
-        <v>58-64</v>
+        <v>58-63</v>
       </c>
       <c r="H237" s="1">
         <v>0.1</v>
@@ -11561,7 +11561,7 @@
         <v>53-54</v>
       </c>
       <c r="G238" t="str">
-        <v>58-64</v>
+        <v>58-63</v>
       </c>
       <c r="H238" s="1">
         <v>0.1</v>
@@ -11608,7 +11608,7 @@
         <v>53-54</v>
       </c>
       <c r="G239" t="str">
-        <v>58-64</v>
+        <v>58-63</v>
       </c>
       <c r="H239" s="1">
         <v>0.1</v>
@@ -11655,7 +11655,7 @@
         <v>53-54</v>
       </c>
       <c r="G240" t="str">
-        <v>58-64</v>
+        <v>58-63</v>
       </c>
       <c r="H240" s="1">
         <v>0.1</v>
@@ -11702,7 +11702,7 @@
         <v>53-54</v>
       </c>
       <c r="G241" t="str">
-        <v>58-64</v>
+        <v>58-63</v>
       </c>
       <c r="H241" s="1">
         <v>0.1</v>
@@ -11749,7 +11749,7 @@
         <v>53-54</v>
       </c>
       <c r="G242" t="str">
-        <v>58-64</v>
+        <v>58-63</v>
       </c>
       <c r="H242" s="1">
         <v>0.1</v>
@@ -11843,7 +11843,7 @@
         <v>56-57</v>
       </c>
       <c r="G244" t="str">
-        <v>61-68</v>
+        <v>60-66</v>
       </c>
       <c r="H244" s="1">
         <v>0.1426</v>
@@ -11890,7 +11890,7 @@
         <v>56-57</v>
       </c>
       <c r="G245" t="str">
-        <v>61-68</v>
+        <v>60-66</v>
       </c>
       <c r="H245" s="1">
         <v>0.1429</v>
@@ -11937,7 +11937,7 @@
         <v>56-57</v>
       </c>
       <c r="G246" t="str">
-        <v>61-68</v>
+        <v>60-66</v>
       </c>
       <c r="H246" s="1">
         <v>0.1429</v>
@@ -11984,7 +11984,7 @@
         <v>56-57</v>
       </c>
       <c r="G247" t="str">
-        <v>61-68</v>
+        <v>60-66</v>
       </c>
       <c r="H247" s="1">
         <v>0.1429</v>
@@ -12031,7 +12031,7 @@
         <v>56-57</v>
       </c>
       <c r="G248" t="str">
-        <v>61-68</v>
+        <v>60-66</v>
       </c>
       <c r="H248" s="1">
         <v>0.1429</v>
@@ -12078,7 +12078,7 @@
         <v>56-57</v>
       </c>
       <c r="G249" t="str">
-        <v>61-68</v>
+        <v>60-66</v>
       </c>
       <c r="H249" s="1">
         <v>0.1429</v>
@@ -12125,7 +12125,7 @@
         <v>56-57</v>
       </c>
       <c r="G250" t="str">
-        <v>61-68</v>
+        <v>60-66</v>
       </c>
       <c r="H250" s="1">
         <v>0.1429</v>
@@ -12172,7 +12172,7 @@
         <v>57-58</v>
       </c>
       <c r="G251" t="str">
-        <v>62-69</v>
+        <v>62-68</v>
       </c>
       <c r="H251" s="1">
         <v>0.1665</v>
@@ -12219,7 +12219,7 @@
         <v>57-58</v>
       </c>
       <c r="G252" t="str">
-        <v>62-69</v>
+        <v>62-68</v>
       </c>
       <c r="H252" s="1">
         <v>0.1667</v>
@@ -12266,7 +12266,7 @@
         <v>57-58</v>
       </c>
       <c r="G253" t="str">
-        <v>62-69</v>
+        <v>62-68</v>
       </c>
       <c r="H253" s="1">
         <v>0.1667</v>
@@ -12313,7 +12313,7 @@
         <v>57-58</v>
       </c>
       <c r="G254" t="str">
-        <v>62-69</v>
+        <v>62-68</v>
       </c>
       <c r="H254" s="1">
         <v>0.1667</v>
@@ -12360,7 +12360,7 @@
         <v>57-58</v>
       </c>
       <c r="G255" t="str">
-        <v>62-69</v>
+        <v>62-68</v>
       </c>
       <c r="H255" s="1">
         <v>0.1667</v>
@@ -12407,7 +12407,7 @@
         <v>57-58</v>
       </c>
       <c r="G256" t="str">
-        <v>62-69</v>
+        <v>62-68</v>
       </c>
       <c r="H256" s="1">
         <v>0.1667</v>
@@ -12454,7 +12454,7 @@
         <v>58-59</v>
       </c>
       <c r="G257" t="str">
-        <v>63-70</v>
+        <v>63-69</v>
       </c>
       <c r="H257" s="1">
         <v>0.25</v>
@@ -12501,7 +12501,7 @@
         <v>58-59</v>
       </c>
       <c r="G258" t="str">
-        <v>63-70</v>
+        <v>63-69</v>
       </c>
       <c r="H258" s="1">
         <v>0.25</v>
@@ -12548,7 +12548,7 @@
         <v>58-59</v>
       </c>
       <c r="G259" t="str">
-        <v>63-70</v>
+        <v>63-69</v>
       </c>
       <c r="H259" s="1">
         <v>0.25</v>
@@ -12595,7 +12595,7 @@
         <v>58-59</v>
       </c>
       <c r="G260" t="str">
-        <v>63-70</v>
+        <v>63-69</v>
       </c>
       <c r="H260" s="1">
         <v>0.25</v>
@@ -12642,7 +12642,7 @@
         <v>59-60</v>
       </c>
       <c r="G261" t="str">
-        <v>65-72</v>
+        <v>65-71</v>
       </c>
       <c r="H261" s="1">
         <v>0.25</v>
@@ -12689,7 +12689,7 @@
         <v>59-60</v>
       </c>
       <c r="G262" t="str">
-        <v>65-72</v>
+        <v>65-71</v>
       </c>
       <c r="H262" s="1">
         <v>0.25</v>
@@ -12736,7 +12736,7 @@
         <v>59-60</v>
       </c>
       <c r="G263" t="str">
-        <v>65-72</v>
+        <v>65-71</v>
       </c>
       <c r="H263" s="1">
         <v>0.25</v>
@@ -12783,7 +12783,7 @@
         <v>59-60</v>
       </c>
       <c r="G264" t="str">
-        <v>65-72</v>
+        <v>65-71</v>
       </c>
       <c r="H264" s="1">
         <v>0.25</v>
@@ -12830,7 +12830,7 @@
         <v>60-61</v>
       </c>
       <c r="G265" t="str">
-        <v>66-73</v>
+        <v>66-72</v>
       </c>
       <c r="H265" s="1">
         <v>0.3334</v>
@@ -12877,7 +12877,7 @@
         <v>60-61</v>
       </c>
       <c r="G266" t="str">
-        <v>66-73</v>
+        <v>66-72</v>
       </c>
       <c r="H266" s="1">
         <v>0.3333</v>
@@ -12924,7 +12924,7 @@
         <v>60-61</v>
       </c>
       <c r="G267" t="str">
-        <v>66-73</v>
+        <v>66-72</v>
       </c>
       <c r="H267" s="1">
         <v>0.3333</v>
@@ -12971,7 +12971,7 @@
         <v>62-63</v>
       </c>
       <c r="G268" t="str">
-        <v>68-75</v>
+        <v>68-74</v>
       </c>
       <c r="H268" s="1">
         <v>0.091</v>
@@ -13018,7 +13018,7 @@
         <v>62-63</v>
       </c>
       <c r="G269" t="str">
-        <v>68-75</v>
+        <v>68-74</v>
       </c>
       <c r="H269" s="1">
         <v>0.0909</v>
@@ -13065,7 +13065,7 @@
         <v>62-63</v>
       </c>
       <c r="G270" t="str">
-        <v>68-75</v>
+        <v>68-74</v>
       </c>
       <c r="H270" s="1">
         <v>0.0909</v>
@@ -13112,7 +13112,7 @@
         <v>62-63</v>
       </c>
       <c r="G271" t="str">
-        <v>68-75</v>
+        <v>68-74</v>
       </c>
       <c r="H271" s="1">
         <v>0.0909</v>
@@ -13159,7 +13159,7 @@
         <v>62-63</v>
       </c>
       <c r="G272" t="str">
-        <v>68-75</v>
+        <v>68-74</v>
       </c>
       <c r="H272" s="1">
         <v>0.0909</v>
@@ -13206,7 +13206,7 @@
         <v>62-63</v>
       </c>
       <c r="G273" t="str">
-        <v>68-75</v>
+        <v>68-74</v>
       </c>
       <c r="H273" s="1">
         <v>0.0909</v>
@@ -13253,7 +13253,7 @@
         <v>62-63</v>
       </c>
       <c r="G274" t="str">
-        <v>68-75</v>
+        <v>68-74</v>
       </c>
       <c r="H274" s="1">
         <v>0.0909</v>
@@ -13300,7 +13300,7 @@
         <v>62-63</v>
       </c>
       <c r="G275" t="str">
-        <v>68-75</v>
+        <v>68-74</v>
       </c>
       <c r="H275" s="1">
         <v>0.0909</v>
@@ -13347,7 +13347,7 @@
         <v>62-63</v>
       </c>
       <c r="G276" t="str">
-        <v>68-75</v>
+        <v>68-74</v>
       </c>
       <c r="H276" s="1">
         <v>0.0909</v>
@@ -13394,7 +13394,7 @@
         <v>62-63</v>
       </c>
       <c r="G277" t="str">
-        <v>68-75</v>
+        <v>68-74</v>
       </c>
       <c r="H277" s="1">
         <v>0.0909</v>
@@ -13441,7 +13441,7 @@
         <v>62-63</v>
       </c>
       <c r="G278" t="str">
-        <v>68-75</v>
+        <v>68-74</v>
       </c>
       <c r="H278" s="1">
         <v>0.0909</v>
@@ -13488,7 +13488,7 @@
         <v>63-64</v>
       </c>
       <c r="G279" t="str">
-        <v>69-76</v>
+        <v>69-75</v>
       </c>
       <c r="H279" s="1">
         <v>0.1112</v>
@@ -13535,7 +13535,7 @@
         <v>63-64</v>
       </c>
       <c r="G280" t="str">
-        <v>69-76</v>
+        <v>69-75</v>
       </c>
       <c r="H280" s="1">
         <v>0.1111</v>
@@ -13582,7 +13582,7 @@
         <v>63-64</v>
       </c>
       <c r="G281" t="str">
-        <v>69-76</v>
+        <v>69-75</v>
       </c>
       <c r="H281" s="1">
         <v>0.1111</v>
@@ -13629,7 +13629,7 @@
         <v>63-64</v>
       </c>
       <c r="G282" t="str">
-        <v>69-76</v>
+        <v>69-75</v>
       </c>
       <c r="H282" s="1">
         <v>0.1111</v>
@@ -13676,7 +13676,7 @@
         <v>63-64</v>
       </c>
       <c r="G283" t="str">
-        <v>69-76</v>
+        <v>69-75</v>
       </c>
       <c r="H283" s="1">
         <v>0.1111</v>
@@ -13723,7 +13723,7 @@
         <v>63-64</v>
       </c>
       <c r="G284" t="str">
-        <v>69-76</v>
+        <v>69-75</v>
       </c>
       <c r="H284" s="1">
         <v>0.1111</v>
@@ -13770,7 +13770,7 @@
         <v>63-64</v>
       </c>
       <c r="G285" t="str">
-        <v>69-76</v>
+        <v>69-75</v>
       </c>
       <c r="H285" s="1">
         <v>0.1111</v>
@@ -13817,7 +13817,7 @@
         <v>63-64</v>
       </c>
       <c r="G286" t="str">
-        <v>69-76</v>
+        <v>69-75</v>
       </c>
       <c r="H286" s="1">
         <v>0.1111</v>
@@ -13864,7 +13864,7 @@
         <v>63-64</v>
       </c>
       <c r="G287" t="str">
-        <v>69-76</v>
+        <v>69-75</v>
       </c>
       <c r="H287" s="1">
         <v>0.1111</v>
@@ -13911,7 +13911,7 @@
         <v>64-65</v>
       </c>
       <c r="G288" t="str">
-        <v>70-78</v>
+        <v>70-77</v>
       </c>
       <c r="H288" s="1">
         <v>0.1426</v>
@@ -13958,7 +13958,7 @@
         <v>64-65</v>
       </c>
       <c r="G289" t="str">
-        <v>70-78</v>
+        <v>70-77</v>
       </c>
       <c r="H289" s="1">
         <v>0.1429</v>
@@ -14005,7 +14005,7 @@
         <v>64-65</v>
       </c>
       <c r="G290" t="str">
-        <v>70-78</v>
+        <v>70-77</v>
       </c>
       <c r="H290" s="1">
         <v>0.1429</v>
@@ -14052,7 +14052,7 @@
         <v>64-65</v>
       </c>
       <c r="G291" t="str">
-        <v>70-78</v>
+        <v>70-77</v>
       </c>
       <c r="H291" s="1">
         <v>0.1429</v>
@@ -14099,7 +14099,7 @@
         <v>64-65</v>
       </c>
       <c r="G292" t="str">
-        <v>70-78</v>
+        <v>70-77</v>
       </c>
       <c r="H292" s="1">
         <v>0.1429</v>
@@ -14146,7 +14146,7 @@
         <v>64-65</v>
       </c>
       <c r="G293" t="str">
-        <v>70-78</v>
+        <v>70-77</v>
       </c>
       <c r="H293" s="1">
         <v>0.1429</v>
@@ -14193,7 +14193,7 @@
         <v>64-65</v>
       </c>
       <c r="G294" t="str">
-        <v>70-78</v>
+        <v>70-77</v>
       </c>
       <c r="H294" s="1">
         <v>0.1429</v>
@@ -14287,7 +14287,7 @@
         <v>25-26</v>
       </c>
       <c r="G296" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H296" s="1">
         <v>0.2</v>
@@ -14334,7 +14334,7 @@
         <v>25-26</v>
       </c>
       <c r="G297" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H297" s="1">
         <v>0.2</v>
@@ -14381,7 +14381,7 @@
         <v>25-26</v>
       </c>
       <c r="G298" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H298" s="1">
         <v>0.2</v>
@@ -14428,7 +14428,7 @@
         <v>25-26</v>
       </c>
       <c r="G299" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H299" s="1">
         <v>0.2</v>
@@ -14475,7 +14475,7 @@
         <v>25-26</v>
       </c>
       <c r="G300" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H300" s="1">
         <v>0.2</v>
@@ -14522,7 +14522,7 @@
         <v>32-33</v>
       </c>
       <c r="G301" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H301" s="1">
         <v>0.3334</v>
@@ -14569,7 +14569,7 @@
         <v>32-33</v>
       </c>
       <c r="G302" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H302" s="1">
         <v>0.3333</v>
@@ -14616,7 +14616,7 @@
         <v>32-33</v>
       </c>
       <c r="G303" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H303" s="1">
         <v>0.3333</v>
@@ -14663,7 +14663,7 @@
         <v>39-40</v>
       </c>
       <c r="G304" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H304" s="1">
         <v>0.3334</v>
@@ -14710,7 +14710,7 @@
         <v>39-40</v>
       </c>
       <c r="G305" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H305" s="1">
         <v>0.3333</v>
@@ -14757,7 +14757,7 @@
         <v>39-40</v>
       </c>
       <c r="G306" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H306" s="1">
         <v>0.3333</v>
@@ -14804,7 +14804,7 @@
         <v>46-47</v>
       </c>
       <c r="G307" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H307" s="1">
         <v>0.1426</v>
@@ -14851,7 +14851,7 @@
         <v>46-47</v>
       </c>
       <c r="G308" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H308" s="1">
         <v>0.1429</v>
@@ -14898,7 +14898,7 @@
         <v>46-47</v>
       </c>
       <c r="G309" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H309" s="1">
         <v>0.1429</v>
@@ -14945,7 +14945,7 @@
         <v>46-47</v>
       </c>
       <c r="G310" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H310" s="1">
         <v>0.1429</v>
@@ -14992,7 +14992,7 @@
         <v>46-47</v>
       </c>
       <c r="G311" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H311" s="1">
         <v>0.1429</v>
@@ -15039,7 +15039,7 @@
         <v>46-47</v>
       </c>
       <c r="G312" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H312" s="1">
         <v>0.1429</v>
@@ -15086,7 +15086,7 @@
         <v>46-47</v>
       </c>
       <c r="G313" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H313" s="1">
         <v>0.1429</v>
@@ -15133,7 +15133,7 @@
         <v>53-54</v>
       </c>
       <c r="G314" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H314" s="1">
         <v>0.125</v>
@@ -15180,7 +15180,7 @@
         <v>53-54</v>
       </c>
       <c r="G315" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H315" s="1">
         <v>0.125</v>
@@ -15227,7 +15227,7 @@
         <v>53-54</v>
       </c>
       <c r="G316" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H316" s="1">
         <v>0.125</v>
@@ -15274,7 +15274,7 @@
         <v>53-54</v>
       </c>
       <c r="G317" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H317" s="1">
         <v>0.125</v>
@@ -15321,7 +15321,7 @@
         <v>53-54</v>
       </c>
       <c r="G318" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H318" s="1">
         <v>0.125</v>
@@ -15368,7 +15368,7 @@
         <v>53-54</v>
       </c>
       <c r="G319" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H319" s="1">
         <v>0.125</v>
@@ -15415,7 +15415,7 @@
         <v>53-54</v>
       </c>
       <c r="G320" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H320" s="1">
         <v>0.125</v>
@@ -15462,7 +15462,7 @@
         <v>53-54</v>
       </c>
       <c r="G321" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H321" s="1">
         <v>0.125</v>
@@ -15509,7 +15509,7 @@
         <v>60-60</v>
       </c>
       <c r="G322" t="str">
-        <v>72-80</v>
+        <v>72-79</v>
       </c>
       <c r="H322" s="1">
         <v>0.1112</v>
@@ -15556,7 +15556,7 @@
         <v>60-60</v>
       </c>
       <c r="G323" t="str">
-        <v>72-80</v>
+        <v>72-79</v>
       </c>
       <c r="H323" s="1">
         <v>0.1111</v>
@@ -15603,7 +15603,7 @@
         <v>60-60</v>
       </c>
       <c r="G324" t="str">
-        <v>72-80</v>
+        <v>72-79</v>
       </c>
       <c r="H324" s="1">
         <v>0.1111</v>
@@ -15650,7 +15650,7 @@
         <v>60-60</v>
       </c>
       <c r="G325" t="str">
-        <v>72-80</v>
+        <v>72-79</v>
       </c>
       <c r="H325" s="1">
         <v>0.1111</v>
@@ -15697,7 +15697,7 @@
         <v>60-60</v>
       </c>
       <c r="G326" t="str">
-        <v>72-80</v>
+        <v>72-79</v>
       </c>
       <c r="H326" s="1">
         <v>0.1111</v>
@@ -15744,7 +15744,7 @@
         <v>60-60</v>
       </c>
       <c r="G327" t="str">
-        <v>72-80</v>
+        <v>72-79</v>
       </c>
       <c r="H327" s="1">
         <v>0.1111</v>
@@ -15791,7 +15791,7 @@
         <v>60-60</v>
       </c>
       <c r="G328" t="str">
-        <v>72-80</v>
+        <v>72-79</v>
       </c>
       <c r="H328" s="1">
         <v>0.1111</v>
@@ -15838,7 +15838,7 @@
         <v>60-60</v>
       </c>
       <c r="G329" t="str">
-        <v>72-80</v>
+        <v>72-79</v>
       </c>
       <c r="H329" s="1">
         <v>0.1111</v>
@@ -15885,7 +15885,7 @@
         <v>60-60</v>
       </c>
       <c r="G330" t="str">
-        <v>72-80</v>
+        <v>72-79</v>
       </c>
       <c r="H330" s="1">
         <v>0.1111</v>
@@ -15932,7 +15932,7 @@
         <v>35-36</v>
       </c>
       <c r="G331" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H331" s="1">
         <v>0.1665</v>
@@ -15979,7 +15979,7 @@
         <v>35-36</v>
       </c>
       <c r="G332" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H332" s="1">
         <v>0.1667</v>
@@ -16026,7 +16026,7 @@
         <v>35-36</v>
       </c>
       <c r="G333" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H333" s="1">
         <v>0.1667</v>
@@ -16073,7 +16073,7 @@
         <v>35-36</v>
       </c>
       <c r="G334" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H334" s="1">
         <v>0.1667</v>
@@ -16120,7 +16120,7 @@
         <v>35-36</v>
       </c>
       <c r="G335" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H335" s="1">
         <v>0.1667</v>
@@ -16167,7 +16167,7 @@
         <v>35-36</v>
       </c>
       <c r="G336" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H336" s="1">
         <v>0.1667</v>
@@ -16214,7 +16214,7 @@
         <v>44-45</v>
       </c>
       <c r="G337" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H337" s="1">
         <v>0.25</v>
@@ -16261,7 +16261,7 @@
         <v>44-45</v>
       </c>
       <c r="G338" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H338" s="1">
         <v>0.25</v>
@@ -16308,7 +16308,7 @@
         <v>44-45</v>
       </c>
       <c r="G339" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H339" s="1">
         <v>0.25</v>
@@ -16355,7 +16355,7 @@
         <v>44-45</v>
       </c>
       <c r="G340" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H340" s="1">
         <v>0.25</v>
@@ -16402,7 +16402,7 @@
         <v>53-54</v>
       </c>
       <c r="G341" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H341" s="1">
         <v>0.3334</v>
@@ -16449,7 +16449,7 @@
         <v>53-54</v>
       </c>
       <c r="G342" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H342" s="1">
         <v>0.3333</v>
@@ -16496,7 +16496,7 @@
         <v>53-54</v>
       </c>
       <c r="G343" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H343" s="1">
         <v>0.3333</v>
@@ -16543,7 +16543,7 @@
         <v>61-62</v>
       </c>
       <c r="G344" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H344" s="1">
         <v>0.2</v>
@@ -16590,7 +16590,7 @@
         <v>61-62</v>
       </c>
       <c r="G345" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H345" s="1">
         <v>0.2</v>
@@ -16637,7 +16637,7 @@
         <v>61-62</v>
       </c>
       <c r="G346" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H346" s="1">
         <v>0.2</v>
@@ -16684,7 +16684,7 @@
         <v>61-62</v>
       </c>
       <c r="G347" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H347" s="1">
         <v>0.2</v>
@@ -16731,7 +16731,7 @@
         <v>61-62</v>
       </c>
       <c r="G348" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H348" s="1">
         <v>0.2</v>
@@ -16778,7 +16778,7 @@
         <v>70-70</v>
       </c>
       <c r="G349" t="str">
-        <v>72-80</v>
+        <v>72-79</v>
       </c>
       <c r="H349" s="1">
         <v>0.5</v>
@@ -16825,7 +16825,7 @@
         <v>70-70</v>
       </c>
       <c r="G350" t="str">
-        <v>72-80</v>
+        <v>72-79</v>
       </c>
       <c r="H350" s="1">
         <v>0.5</v>
@@ -16872,7 +16872,7 @@
         <v>65-66</v>
       </c>
       <c r="G351" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H351" s="1">
         <v>0.5</v>
@@ -16919,7 +16919,7 @@
         <v>65-66</v>
       </c>
       <c r="G352" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H352" s="1">
         <v>0.5</v>
@@ -16966,7 +16966,7 @@
         <v>76-77</v>
       </c>
       <c r="G353" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H353" s="1">
         <v>0.25</v>
@@ -17013,7 +17013,7 @@
         <v>76-77</v>
       </c>
       <c r="G354" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H354" s="1">
         <v>0.25</v>
@@ -17060,7 +17060,7 @@
         <v>76-77</v>
       </c>
       <c r="G355" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H355" s="1">
         <v>0.25</v>
@@ -17107,7 +17107,7 @@
         <v>76-77</v>
       </c>
       <c r="G356" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H356" s="1">
         <v>0.25</v>
@@ -17154,7 +17154,7 @@
         <v>88-89</v>
       </c>
       <c r="G357" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H357" s="1">
         <v>0.1665</v>
@@ -17201,7 +17201,7 @@
         <v>88-89</v>
       </c>
       <c r="G358" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H358" s="1">
         <v>0.1667</v>
@@ -17248,7 +17248,7 @@
         <v>88-89</v>
       </c>
       <c r="G359" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H359" s="1">
         <v>0.1667</v>
@@ -17295,7 +17295,7 @@
         <v>88-89</v>
       </c>
       <c r="G360" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H360" s="1">
         <v>0.1667</v>
@@ -17342,7 +17342,7 @@
         <v>88-89</v>
       </c>
       <c r="G361" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H361" s="1">
         <v>0.1667</v>
@@ -17389,7 +17389,7 @@
         <v>88-89</v>
       </c>
       <c r="G362" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H362" s="1">
         <v>0.1667</v>
@@ -17436,7 +17436,7 @@
         <v>99-100</v>
       </c>
       <c r="G363" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H363" s="1">
         <v>0.2</v>
@@ -17483,7 +17483,7 @@
         <v>99-100</v>
       </c>
       <c r="G364" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H364" s="1">
         <v>0.2</v>
@@ -17530,7 +17530,7 @@
         <v>99-100</v>
       </c>
       <c r="G365" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H365" s="1">
         <v>0.2</v>
@@ -17577,7 +17577,7 @@
         <v>99-100</v>
       </c>
       <c r="G366" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H366" s="1">
         <v>0.2</v>
@@ -17624,7 +17624,7 @@
         <v>99-100</v>
       </c>
       <c r="G367" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H367" s="1">
         <v>0.2</v>
@@ -17671,7 +17671,7 @@
         <v>110-110</v>
       </c>
       <c r="G368" t="str">
-        <v>72-80</v>
+        <v>110-110</v>
       </c>
       <c r="H368" s="1">
         <v>0.25</v>
@@ -17718,7 +17718,7 @@
         <v>110-110</v>
       </c>
       <c r="G369" t="str">
-        <v>72-80</v>
+        <v>110-110</v>
       </c>
       <c r="H369" s="1">
         <v>0.25</v>
@@ -17765,7 +17765,7 @@
         <v>110-110</v>
       </c>
       <c r="G370" t="str">
-        <v>72-80</v>
+        <v>110-110</v>
       </c>
       <c r="H370" s="1">
         <v>0.25</v>
@@ -17812,7 +17812,7 @@
         <v>110-115</v>
       </c>
       <c r="G371" t="str">
-        <v>72-80</v>
+        <v>110-115</v>
       </c>
       <c r="H371" s="1">
         <v>0.25</v>
@@ -17906,7 +17906,7 @@
         <v>76-77</v>
       </c>
       <c r="G373" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H373" s="1">
         <v>0.25</v>
@@ -17953,7 +17953,7 @@
         <v>76-77</v>
       </c>
       <c r="G374" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H374" s="1">
         <v>0.25</v>
@@ -18000,7 +18000,7 @@
         <v>76-77</v>
       </c>
       <c r="G375" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H375" s="1">
         <v>0.25</v>
@@ -18047,7 +18047,7 @@
         <v>76-77</v>
       </c>
       <c r="G376" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H376" s="1">
         <v>0.25</v>
@@ -18094,7 +18094,7 @@
         <v>88-89</v>
       </c>
       <c r="G377" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H377" s="1">
         <v>0.25</v>
@@ -18141,7 +18141,7 @@
         <v>88-89</v>
       </c>
       <c r="G378" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H378" s="1">
         <v>0.25</v>
@@ -18188,7 +18188,7 @@
         <v>88-89</v>
       </c>
       <c r="G379" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H379" s="1">
         <v>0.25</v>
@@ -18235,7 +18235,7 @@
         <v>88-89</v>
       </c>
       <c r="G380" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H380" s="1">
         <v>0.25</v>
@@ -18282,7 +18282,7 @@
         <v>99-100</v>
       </c>
       <c r="G381" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H381" s="1">
         <v>0.1665</v>
@@ -18329,7 +18329,7 @@
         <v>99-100</v>
       </c>
       <c r="G382" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H382" s="1">
         <v>0.1667</v>
@@ -18376,7 +18376,7 @@
         <v>99-100</v>
       </c>
       <c r="G383" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H383" s="1">
         <v>0.1667</v>
@@ -18423,7 +18423,7 @@
         <v>99-100</v>
       </c>
       <c r="G384" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H384" s="1">
         <v>0.1667</v>
@@ -18470,7 +18470,7 @@
         <v>99-100</v>
       </c>
       <c r="G385" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H385" s="1">
         <v>0.1667</v>
@@ -18517,7 +18517,7 @@
         <v>99-100</v>
       </c>
       <c r="G386" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H386" s="1">
         <v>0.1667</v>
@@ -18564,7 +18564,7 @@
         <v>110-115</v>
       </c>
       <c r="G387" t="str">
-        <v>72-80</v>
+        <v>110-115</v>
       </c>
       <c r="H387" s="1">
         <v>0.3334</v>
@@ -18611,7 +18611,7 @@
         <v>110-115</v>
       </c>
       <c r="G388" t="str">
-        <v>72-80</v>
+        <v>110-115</v>
       </c>
       <c r="H388" s="1">
         <v>0.3333</v>
@@ -18658,7 +18658,7 @@
         <v>110-110</v>
       </c>
       <c r="G389" t="str">
-        <v>72-80</v>
+        <v>110-110</v>
       </c>
       <c r="H389" s="1">
         <v>0.3333</v>
@@ -18705,7 +18705,7 @@
         <v>65-66</v>
       </c>
       <c r="G390" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H390" s="1">
         <v>0.1665</v>
@@ -18752,7 +18752,7 @@
         <v>65-66</v>
       </c>
       <c r="G391" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H391" s="1">
         <v>0.1667</v>
@@ -18799,7 +18799,7 @@
         <v>65-66</v>
       </c>
       <c r="G392" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H392" s="1">
         <v>0.1667</v>
@@ -18846,7 +18846,7 @@
         <v>65-66</v>
       </c>
       <c r="G393" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H393" s="1">
         <v>0.1667</v>
@@ -18893,7 +18893,7 @@
         <v>65-66</v>
       </c>
       <c r="G394" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H394" s="1">
         <v>0.1667</v>
@@ -18940,7 +18940,7 @@
         <v>65-66</v>
       </c>
       <c r="G395" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H395" s="1">
         <v>0.1667</v>
@@ -18987,7 +18987,7 @@
         <v>76-77</v>
       </c>
       <c r="G396" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H396" s="1">
         <v>0.25</v>
@@ -19034,7 +19034,7 @@
         <v>76-77</v>
       </c>
       <c r="G397" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H397" s="1">
         <v>0.25</v>
@@ -19081,7 +19081,7 @@
         <v>76-77</v>
       </c>
       <c r="G398" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H398" s="1">
         <v>0.25</v>
@@ -19128,7 +19128,7 @@
         <v>76-77</v>
       </c>
       <c r="G399" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H399" s="1">
         <v>0.25</v>
@@ -19175,7 +19175,7 @@
         <v>88-89</v>
       </c>
       <c r="G400" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H400" s="1">
         <v>0.5</v>
@@ -19222,7 +19222,7 @@
         <v>88-89</v>
       </c>
       <c r="G401" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H401" s="1">
         <v>0.5</v>
@@ -19269,7 +19269,7 @@
         <v>99-100</v>
       </c>
       <c r="G402" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H402" s="1">
         <v>0.5</v>
@@ -19316,7 +19316,7 @@
         <v>99-100</v>
       </c>
       <c r="G403" t="str">
-        <v>72-80</v>
+        <v>96-104</v>
       </c>
       <c r="H403" s="1">
         <v>0.5</v>
@@ -19363,7 +19363,7 @@
         <v>115-115</v>
       </c>
       <c r="G404" t="str">
-        <v>72-80</v>
+        <v>115-115</v>
       </c>
       <c r="H404" s="1">
         <v>0.3334</v>
@@ -19410,7 +19410,7 @@
         <v>110-110</v>
       </c>
       <c r="G405" t="str">
-        <v>72-80</v>
+        <v>110-110</v>
       </c>
       <c r="H405" s="1">
         <v>0.3333</v>
@@ -19457,7 +19457,7 @@
         <v>110-110</v>
       </c>
       <c r="G406" t="str">
-        <v>72-80</v>
+        <v>110-110</v>
       </c>
       <c r="H406" s="1">
         <v>0.3333</v>
@@ -19504,7 +19504,7 @@
         <v>120-121</v>
       </c>
       <c r="G407" t="str">
-        <v>72-80</v>
+        <v>120-121</v>
       </c>
       <c r="H407" s="1">
         <v>0.3334</v>
@@ -19551,7 +19551,7 @@
         <v>120-121</v>
       </c>
       <c r="G408" t="str">
-        <v>72-80</v>
+        <v>120-121</v>
       </c>
       <c r="H408" s="1">
         <v>0.3333</v>
@@ -19598,7 +19598,7 @@
         <v>120-121</v>
       </c>
       <c r="G409" t="str">
-        <v>72-80</v>
+        <v>120-121</v>
       </c>
       <c r="H409" s="1">
         <v>0.3333</v>

--- a/5_Unova_Data.xlsx
+++ b/5_Unova_Data.xlsx
@@ -545,10 +545,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v/>
+        <v>Challenge 1</v>
       </c>
       <c r="B4" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="C4" t="str">
         <v>Route 19</v>
@@ -581,10 +581,10 @@
         <v>Yes</v>
       </c>
       <c r="M4" t="str">
-        <v/>
+        <v>Floccesy Ranch</v>
       </c>
       <c r="N4" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Purrloin","count":1}]}</v>
       </c>
       <c r="O4" t="str">
         <v/>
@@ -639,10 +639,10 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="B6" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="C6" t="str">
         <v>Floccesy Ranch</v>
@@ -675,10 +675,10 @@
         <v>Yes</v>
       </c>
       <c r="M6" t="str">
-        <v/>
+        <v>Floccesy Pond</v>
       </c>
       <c r="N6" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Pidove","count":1}]}</v>
       </c>
       <c r="O6" t="str">
         <v/>
@@ -686,10 +686,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="B7" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="C7" t="str">
         <v>Floccesy Ranch</v>
@@ -722,10 +722,10 @@
         <v>Yes</v>
       </c>
       <c r="M7" t="str">
-        <v/>
+        <v>Floccesy Pond</v>
       </c>
       <c r="N7" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Pidove","count":1}]}</v>
       </c>
       <c r="O7" t="str">
         <v/>
@@ -733,10 +733,10 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="B8" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="C8" t="str">
         <v>Floccesy Ranch</v>
@@ -769,10 +769,10 @@
         <v>Yes</v>
       </c>
       <c r="M8" t="str">
-        <v/>
+        <v>Floccesy Pond</v>
       </c>
       <c r="N8" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Pidove","count":1}]}</v>
       </c>
       <c r="O8" t="str">
         <v/>
@@ -780,10 +780,10 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="B9" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="C9" t="str">
         <v>Floccesy Ranch</v>
@@ -816,10 +816,10 @@
         <v>Yes</v>
       </c>
       <c r="M9" t="str">
-        <v/>
+        <v>Floccesy Pond</v>
       </c>
       <c r="N9" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Pidove","count":1}]}</v>
       </c>
       <c r="O9" t="str">
         <v/>
@@ -827,10 +827,10 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="B10" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="C10" t="str">
         <v>Floccesy Ranch</v>
@@ -863,10 +863,10 @@
         <v>Yes</v>
       </c>
       <c r="M10" t="str">
-        <v/>
+        <v>Floccesy Pond</v>
       </c>
       <c r="N10" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Pidove","count":1}]}</v>
       </c>
       <c r="O10" t="str">
         <v/>
@@ -874,10 +874,10 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="B11" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="C11" t="str">
         <v>Floccesy Ranch</v>
@@ -910,10 +910,10 @@
         <v>Yes</v>
       </c>
       <c r="M11" t="str">
-        <v/>
+        <v>Floccesy Pond</v>
       </c>
       <c r="N11" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Pidove","count":1}]}</v>
       </c>
       <c r="O11" t="str">
         <v/>
@@ -968,10 +968,10 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="B13" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="C13" t="str">
         <v>Floccesy Pond</v>
@@ -1004,10 +1004,10 @@
         <v>No</v>
       </c>
       <c r="M13" t="str">
-        <v/>
+        <v>Route 20</v>
       </c>
       <c r="N13" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Horsea","count":1}]}</v>
       </c>
       <c r="O13" t="str">
         <v/>
@@ -1015,10 +1015,10 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="B14" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="C14" t="str">
         <v>Floccesy Pond</v>
@@ -1051,10 +1051,10 @@
         <v>No</v>
       </c>
       <c r="M14" t="str">
-        <v/>
+        <v>Route 20</v>
       </c>
       <c r="N14" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Horsea","count":1}]}</v>
       </c>
       <c r="O14" t="str">
         <v/>
@@ -1062,10 +1062,10 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="B15" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="C15" t="str">
         <v>Floccesy Pond</v>
@@ -1098,10 +1098,10 @@
         <v>No</v>
       </c>
       <c r="M15" t="str">
-        <v/>
+        <v>Route 20</v>
       </c>
       <c r="N15" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Horsea","count":1}]}</v>
       </c>
       <c r="O15" t="str">
         <v/>
@@ -1109,10 +1109,10 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="B16" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="C16" t="str">
         <v>Floccesy Pond</v>
@@ -1145,10 +1145,10 @@
         <v>No</v>
       </c>
       <c r="M16" t="str">
-        <v/>
+        <v>Route 20</v>
       </c>
       <c r="N16" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Horsea","count":1}]}</v>
       </c>
       <c r="O16" t="str">
         <v/>
@@ -1156,10 +1156,10 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="B17" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="C17" t="str">
         <v>Floccesy Pond</v>
@@ -1192,10 +1192,10 @@
         <v>No</v>
       </c>
       <c r="M17" t="str">
-        <v/>
+        <v>Route 20</v>
       </c>
       <c r="N17" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Horsea","count":1}]}</v>
       </c>
       <c r="O17" t="str">
         <v/>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="B18" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="C18" t="str">
         <v>Floccesy Pond</v>
@@ -1239,10 +1239,10 @@
         <v>No</v>
       </c>
       <c r="M18" t="str">
-        <v/>
+        <v>Route 20</v>
       </c>
       <c r="N18" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Horsea","count":1}]}</v>
       </c>
       <c r="O18" t="str">
         <v/>
@@ -1250,10 +1250,10 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="B19" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="C19" t="str">
         <v>Floccesy Pond</v>
@@ -1286,10 +1286,10 @@
         <v>No</v>
       </c>
       <c r="M19" t="str">
-        <v/>
+        <v>Route 20</v>
       </c>
       <c r="N19" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Horsea","count":1}]}</v>
       </c>
       <c r="O19" t="str">
         <v/>
@@ -1344,10 +1344,10 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="B21" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="C21" t="str">
         <v>Route 20</v>
@@ -1380,10 +1380,10 @@
         <v>No</v>
       </c>
       <c r="M21" t="str">
-        <v/>
+        <v>Aspertia Gym</v>
       </c>
       <c r="N21" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Sunkern","count":1}]}</v>
       </c>
       <c r="O21" t="str">
         <v/>
@@ -1391,10 +1391,10 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="B22" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="C22" t="str">
         <v>Route 20</v>
@@ -1427,10 +1427,10 @@
         <v>No</v>
       </c>
       <c r="M22" t="str">
-        <v/>
+        <v>Aspertia Gym</v>
       </c>
       <c r="N22" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Sunkern","count":1}]}</v>
       </c>
       <c r="O22" t="str">
         <v/>
@@ -1438,10 +1438,10 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="B23" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="C23" t="str">
         <v>Route 20</v>
@@ -1474,10 +1474,10 @@
         <v>No</v>
       </c>
       <c r="M23" t="str">
-        <v/>
+        <v>Aspertia Gym</v>
       </c>
       <c r="N23" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Sunkern","count":1}]}</v>
       </c>
       <c r="O23" t="str">
         <v/>
@@ -1485,10 +1485,10 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="B24" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="C24" t="str">
         <v>Route 20</v>
@@ -1521,10 +1521,10 @@
         <v>No</v>
       </c>
       <c r="M24" t="str">
-        <v/>
+        <v>Aspertia Gym</v>
       </c>
       <c r="N24" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Sunkern","count":1}]}</v>
       </c>
       <c r="O24" t="str">
         <v/>
@@ -1532,10 +1532,10 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="B25" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="C25" t="str">
         <v>Route 20</v>
@@ -1568,10 +1568,10 @@
         <v>No</v>
       </c>
       <c r="M25" t="str">
-        <v/>
+        <v>Aspertia Gym</v>
       </c>
       <c r="N25" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Sunkern","count":1}]}</v>
       </c>
       <c r="O25" t="str">
         <v/>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="B29" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="C29" t="str">
         <v>Virbank Complex</v>
@@ -1756,10 +1756,10 @@
         <v>Yes</v>
       </c>
       <c r="M29" t="str">
-        <v/>
+        <v>Virbank Bay</v>
       </c>
       <c r="N29" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Patrat","count":1}]}</v>
       </c>
       <c r="O29" t="str">
         <v/>
@@ -1767,10 +1767,10 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="B30" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="C30" t="str">
         <v>Virbank Complex</v>
@@ -1803,10 +1803,10 @@
         <v>Yes</v>
       </c>
       <c r="M30" t="str">
-        <v/>
+        <v>Virbank Bay</v>
       </c>
       <c r="N30" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Patrat","count":1}]}</v>
       </c>
       <c r="O30" t="str">
         <v/>
@@ -1814,10 +1814,10 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="B31" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="C31" t="str">
         <v>Virbank Complex</v>
@@ -1850,10 +1850,10 @@
         <v>Yes</v>
       </c>
       <c r="M31" t="str">
-        <v/>
+        <v>Virbank Bay</v>
       </c>
       <c r="N31" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Patrat","count":1}]}</v>
       </c>
       <c r="O31" t="str">
         <v/>
@@ -1861,10 +1861,10 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="B32" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="C32" t="str">
         <v>Virbank Complex</v>
@@ -1897,10 +1897,10 @@
         <v>Yes</v>
       </c>
       <c r="M32" t="str">
-        <v/>
+        <v>Virbank Bay</v>
       </c>
       <c r="N32" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Patrat","count":1}]}</v>
       </c>
       <c r="O32" t="str">
         <v/>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="B33" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="C33" t="str">
         <v>Virbank Complex</v>
@@ -1944,10 +1944,10 @@
         <v>Yes</v>
       </c>
       <c r="M33" t="str">
-        <v/>
+        <v>Virbank Bay</v>
       </c>
       <c r="N33" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Patrat","count":1}]}</v>
       </c>
       <c r="O33" t="str">
         <v/>
@@ -2002,10 +2002,10 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="B35" t="str">
-        <v/>
+        <v>Challenge 9</v>
       </c>
       <c r="C35" t="str">
         <v>Virbank Bay</v>
@@ -2038,10 +2038,10 @@
         <v>No</v>
       </c>
       <c r="M35" t="str">
-        <v/>
+        <v>Virbank Gym</v>
       </c>
       <c r="N35" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Spheal","count":1}]}</v>
       </c>
       <c r="O35" t="str">
         <v/>
@@ -2049,10 +2049,10 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="B36" t="str">
-        <v/>
+        <v>Challenge 9</v>
       </c>
       <c r="C36" t="str">
         <v>Virbank Bay</v>
@@ -2085,10 +2085,10 @@
         <v>No</v>
       </c>
       <c r="M36" t="str">
-        <v/>
+        <v>Virbank Gym</v>
       </c>
       <c r="N36" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Spheal","count":1}]}</v>
       </c>
       <c r="O36" t="str">
         <v/>
@@ -2096,10 +2096,10 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="B37" t="str">
-        <v/>
+        <v>Challenge 9</v>
       </c>
       <c r="C37" t="str">
         <v>Virbank Bay</v>
@@ -2132,10 +2132,10 @@
         <v>No</v>
       </c>
       <c r="M37" t="str">
-        <v/>
+        <v>Virbank Gym</v>
       </c>
       <c r="N37" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Spheal","count":1}]}</v>
       </c>
       <c r="O37" t="str">
         <v/>
@@ -2143,10 +2143,10 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="B38" t="str">
-        <v/>
+        <v>Challenge 9</v>
       </c>
       <c r="C38" t="str">
         <v>Virbank Bay</v>
@@ -2179,10 +2179,10 @@
         <v>No</v>
       </c>
       <c r="M38" t="str">
-        <v/>
+        <v>Virbank Gym</v>
       </c>
       <c r="N38" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Spheal","count":1}]}</v>
       </c>
       <c r="O38" t="str">
         <v/>
@@ -2190,10 +2190,10 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="B39" t="str">
-        <v/>
+        <v>Challenge 9</v>
       </c>
       <c r="C39" t="str">
         <v>Virbank Bay</v>
@@ -2226,10 +2226,10 @@
         <v>No</v>
       </c>
       <c r="M39" t="str">
-        <v/>
+        <v>Virbank Gym</v>
       </c>
       <c r="N39" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Spheal","count":1}]}</v>
       </c>
       <c r="O39" t="str">
         <v/>
@@ -2237,10 +2237,10 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="B40" t="str">
-        <v/>
+        <v>Challenge 9</v>
       </c>
       <c r="C40" t="str">
         <v>Virbank Bay</v>
@@ -2273,10 +2273,10 @@
         <v>No</v>
       </c>
       <c r="M40" t="str">
-        <v/>
+        <v>Virbank Gym</v>
       </c>
       <c r="N40" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Spheal","count":1}]}</v>
       </c>
       <c r="O40" t="str">
         <v/>
@@ -2378,10 +2378,10 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v/>
+        <v>Challenge 10</v>
       </c>
       <c r="B43" t="str">
-        <v/>
+        <v>Challenge 11</v>
       </c>
       <c r="C43" t="str">
         <v>Castelia City</v>
@@ -2414,10 +2414,10 @@
         <v>Yes</v>
       </c>
       <c r="M43" t="str">
-        <v/>
+        <v>Castelia Sewers</v>
       </c>
       <c r="N43" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Pidove","count":1}]}</v>
       </c>
       <c r="O43" t="str">
         <v/>
@@ -2425,10 +2425,10 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v/>
+        <v>Challenge 10</v>
       </c>
       <c r="B44" t="str">
-        <v/>
+        <v>Challenge 11</v>
       </c>
       <c r="C44" t="str">
         <v>Castelia City</v>
@@ -2461,10 +2461,10 @@
         <v>Yes</v>
       </c>
       <c r="M44" t="str">
-        <v/>
+        <v>Castelia Sewers</v>
       </c>
       <c r="N44" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Pidove","count":1}]}</v>
       </c>
       <c r="O44" t="str">
         <v/>
@@ -2472,10 +2472,10 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v/>
+        <v>Challenge 10</v>
       </c>
       <c r="B45" t="str">
-        <v/>
+        <v>Challenge 11</v>
       </c>
       <c r="C45" t="str">
         <v>Castelia City</v>
@@ -2508,10 +2508,10 @@
         <v>Yes</v>
       </c>
       <c r="M45" t="str">
-        <v/>
+        <v>Castelia Sewers</v>
       </c>
       <c r="N45" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Pidove","count":1}]}</v>
       </c>
       <c r="O45" t="str">
         <v/>
@@ -2519,10 +2519,10 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v/>
+        <v>Challenge 10</v>
       </c>
       <c r="B46" t="str">
-        <v/>
+        <v>Challenge 11</v>
       </c>
       <c r="C46" t="str">
         <v>Castelia City</v>
@@ -2555,10 +2555,10 @@
         <v>Yes</v>
       </c>
       <c r="M46" t="str">
-        <v/>
+        <v>Castelia Sewers</v>
       </c>
       <c r="N46" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Pidove","count":1}]}</v>
       </c>
       <c r="O46" t="str">
         <v/>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v/>
+        <v>Challenge 10</v>
       </c>
       <c r="B47" t="str">
-        <v/>
+        <v>Challenge 11</v>
       </c>
       <c r="C47" t="str">
         <v>Castelia City</v>
@@ -2602,10 +2602,10 @@
         <v>Yes</v>
       </c>
       <c r="M47" t="str">
-        <v/>
+        <v>Castelia Sewers</v>
       </c>
       <c r="N47" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Pidove","count":1}]}</v>
       </c>
       <c r="O47" t="str">
         <v/>
@@ -2660,10 +2660,10 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v/>
+        <v>Challenge 11</v>
       </c>
       <c r="B49" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="C49" t="str">
         <v>Castelia Sewers</v>
@@ -2696,10 +2696,10 @@
         <v>Yes</v>
       </c>
       <c r="M49" t="str">
-        <v/>
+        <v>Castelia Park</v>
       </c>
       <c r="N49" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Muk","count":1}]}</v>
       </c>
       <c r="O49" t="str">
         <v/>
@@ -2707,10 +2707,10 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v/>
+        <v>Challenge 11</v>
       </c>
       <c r="B50" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="C50" t="str">
         <v>Castelia Sewers</v>
@@ -2743,10 +2743,10 @@
         <v>Yes</v>
       </c>
       <c r="M50" t="str">
-        <v/>
+        <v>Castelia Park</v>
       </c>
       <c r="N50" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Muk","count":1}]}</v>
       </c>
       <c r="O50" t="str">
         <v/>
@@ -2801,10 +2801,10 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="B52" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="C52" t="str">
         <v>Castelia Park</v>
@@ -2837,10 +2837,10 @@
         <v>No</v>
       </c>
       <c r="M52" t="str">
-        <v/>
+        <v>Castelia Gym</v>
       </c>
       <c r="N52" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Delcatty","count":1}]}</v>
       </c>
       <c r="O52" t="str">
         <v/>
@@ -2848,10 +2848,10 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="B53" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="C53" t="str">
         <v>Castelia Park</v>
@@ -2884,10 +2884,10 @@
         <v>No</v>
       </c>
       <c r="M53" t="str">
-        <v/>
+        <v>Castelia Gym</v>
       </c>
       <c r="N53" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Delcatty","count":1}]}</v>
       </c>
       <c r="O53" t="str">
         <v/>
@@ -2895,10 +2895,10 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="B54" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="C54" t="str">
         <v>Castelia Park</v>
@@ -2931,10 +2931,10 @@
         <v>No</v>
       </c>
       <c r="M54" t="str">
-        <v/>
+        <v>Castelia Gym</v>
       </c>
       <c r="N54" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Delcatty","count":1}]}</v>
       </c>
       <c r="O54" t="str">
         <v/>
@@ -2942,10 +2942,10 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="B55" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="C55" t="str">
         <v>Castelia Park</v>
@@ -2978,10 +2978,10 @@
         <v>No</v>
       </c>
       <c r="M55" t="str">
-        <v/>
+        <v>Castelia Gym</v>
       </c>
       <c r="N55" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Delcatty","count":1}]}</v>
       </c>
       <c r="O55" t="str">
         <v/>
@@ -2989,10 +2989,10 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="B56" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="C56" t="str">
         <v>Castelia Park</v>
@@ -3025,10 +3025,10 @@
         <v>No</v>
       </c>
       <c r="M56" t="str">
-        <v/>
+        <v>Castelia Gym</v>
       </c>
       <c r="N56" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Delcatty","count":1}]}</v>
       </c>
       <c r="O56" t="str">
         <v/>
@@ -3036,10 +3036,10 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="B57" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="C57" t="str">
         <v>Castelia Park</v>
@@ -3072,10 +3072,10 @@
         <v>No</v>
       </c>
       <c r="M57" t="str">
-        <v/>
+        <v>Castelia Gym</v>
       </c>
       <c r="N57" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Delcatty","count":1}]}</v>
       </c>
       <c r="O57" t="str">
         <v/>
@@ -3083,10 +3083,10 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="B58" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="C58" t="str">
         <v>Castelia Park</v>
@@ -3119,10 +3119,10 @@
         <v>No</v>
       </c>
       <c r="M58" t="str">
-        <v/>
+        <v>Castelia Gym</v>
       </c>
       <c r="N58" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Delcatty","count":1}]}</v>
       </c>
       <c r="O58" t="str">
         <v/>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="B59" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="C59" t="str">
         <v>Castelia Park</v>
@@ -3166,10 +3166,10 @@
         <v>No</v>
       </c>
       <c r="M59" t="str">
-        <v/>
+        <v>Castelia Gym</v>
       </c>
       <c r="N59" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Delcatty","count":1}]}</v>
       </c>
       <c r="O59" t="str">
         <v/>
@@ -3177,10 +3177,10 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="B60" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="C60" t="str">
         <v>Castelia Park</v>
@@ -3213,10 +3213,10 @@
         <v>No</v>
       </c>
       <c r="M60" t="str">
-        <v/>
+        <v>Castelia Gym</v>
       </c>
       <c r="N60" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Delcatty","count":1}]}</v>
       </c>
       <c r="O60" t="str">
         <v/>
@@ -3224,10 +3224,10 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="B61" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="C61" t="str">
         <v>Castelia Park</v>
@@ -3260,10 +3260,10 @@
         <v>No</v>
       </c>
       <c r="M61" t="str">
-        <v/>
+        <v>Castelia Gym</v>
       </c>
       <c r="N61" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Delcatty","count":1}]}</v>
       </c>
       <c r="O61" t="str">
         <v/>
@@ -3365,10 +3365,10 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="B64" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="C64" t="str">
         <v>Relic Passage</v>
@@ -3401,10 +3401,10 @@
         <v>Yes</v>
       </c>
       <c r="M64" t="str">
-        <v/>
+        <v>Route 4</v>
       </c>
       <c r="N64" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Timburr","count":1}]}</v>
       </c>
       <c r="O64" t="str">
         <v/>
@@ -3412,10 +3412,10 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="B65" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="C65" t="str">
         <v>Relic Passage</v>
@@ -3448,10 +3448,10 @@
         <v>Yes</v>
       </c>
       <c r="M65" t="str">
-        <v/>
+        <v>Route 4</v>
       </c>
       <c r="N65" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Timburr","count":1}]}</v>
       </c>
       <c r="O65" t="str">
         <v/>
@@ -3459,10 +3459,10 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="B66" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="C66" t="str">
         <v>Relic Passage</v>
@@ -3495,10 +3495,10 @@
         <v>Yes</v>
       </c>
       <c r="M66" t="str">
-        <v/>
+        <v>Route 4</v>
       </c>
       <c r="N66" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Timburr","count":1}]}</v>
       </c>
       <c r="O66" t="str">
         <v/>
@@ -3524,7 +3524,7 @@
         <v>18-19</v>
       </c>
       <c r="G67" t="str">
-        <v>18-21</v>
+        <v>19-22</v>
       </c>
       <c r="H67" s="1">
         <v>0.25</v>
@@ -3553,10 +3553,10 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="B68" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="C68" t="str">
         <v>Route 4</v>
@@ -3571,7 +3571,7 @@
         <v>18-19</v>
       </c>
       <c r="G68" t="str">
-        <v>18-21</v>
+        <v>19-22</v>
       </c>
       <c r="H68" s="1">
         <v>0.25</v>
@@ -3589,10 +3589,10 @@
         <v>Yes</v>
       </c>
       <c r="M68" t="str">
-        <v/>
+        <v>Desert Resort</v>
       </c>
       <c r="N68" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Scraggy","count":1}]}</v>
       </c>
       <c r="O68" t="str">
         <v/>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="B69" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="C69" t="str">
         <v>Route 4</v>
@@ -3618,7 +3618,7 @@
         <v>18-19</v>
       </c>
       <c r="G69" t="str">
-        <v>18-21</v>
+        <v>19-22</v>
       </c>
       <c r="H69" s="1">
         <v>0.25</v>
@@ -3636,10 +3636,10 @@
         <v>Yes</v>
       </c>
       <c r="M69" t="str">
-        <v/>
+        <v>Desert Resort</v>
       </c>
       <c r="N69" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Scraggy","count":1}]}</v>
       </c>
       <c r="O69" t="str">
         <v/>
@@ -3647,10 +3647,10 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="B70" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="C70" t="str">
         <v>Route 4</v>
@@ -3665,7 +3665,7 @@
         <v>18-19</v>
       </c>
       <c r="G70" t="str">
-        <v>18-21</v>
+        <v>19-22</v>
       </c>
       <c r="H70" s="1">
         <v>0.25</v>
@@ -3683,10 +3683,10 @@
         <v>Yes</v>
       </c>
       <c r="M70" t="str">
-        <v/>
+        <v>Desert Resort</v>
       </c>
       <c r="N70" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Scraggy","count":1}]}</v>
       </c>
       <c r="O70" t="str">
         <v/>
@@ -3741,10 +3741,10 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B72" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="C72" t="str">
         <v>Desert Resort</v>
@@ -3777,10 +3777,10 @@
         <v>Yes</v>
       </c>
       <c r="M72" t="str">
-        <v/>
+        <v>Relic Castle</v>
       </c>
       <c r="N72" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Sandslash","count":1}]}</v>
       </c>
       <c r="O72" t="str">
         <v/>
@@ -3788,10 +3788,10 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B73" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="C73" t="str">
         <v>Desert Resort</v>
@@ -3824,10 +3824,10 @@
         <v>Yes</v>
       </c>
       <c r="M73" t="str">
-        <v/>
+        <v>Relic Castle</v>
       </c>
       <c r="N73" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Sandslash","count":1}]}</v>
       </c>
       <c r="O73" t="str">
         <v/>
@@ -3835,10 +3835,10 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B74" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="C74" t="str">
         <v>Desert Resort</v>
@@ -3871,10 +3871,10 @@
         <v>Yes</v>
       </c>
       <c r="M74" t="str">
-        <v/>
+        <v>Relic Castle</v>
       </c>
       <c r="N74" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Sandslash","count":1}]}</v>
       </c>
       <c r="O74" t="str">
         <v/>
@@ -3882,10 +3882,10 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B75" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="C75" t="str">
         <v>Desert Resort</v>
@@ -3918,10 +3918,10 @@
         <v>Yes</v>
       </c>
       <c r="M75" t="str">
-        <v/>
+        <v>Relic Castle</v>
       </c>
       <c r="N75" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Sandslash","count":1}]}</v>
       </c>
       <c r="O75" t="str">
         <v/>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B76" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="C76" t="str">
         <v>Desert Resort</v>
@@ -3965,10 +3965,10 @@
         <v>Yes</v>
       </c>
       <c r="M76" t="str">
-        <v/>
+        <v>Relic Castle</v>
       </c>
       <c r="N76" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Sandslash","count":1}]}</v>
       </c>
       <c r="O76" t="str">
         <v/>
@@ -3976,10 +3976,10 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B77" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="C77" t="str">
         <v>Desert Resort</v>
@@ -4012,10 +4012,10 @@
         <v>Yes</v>
       </c>
       <c r="M77" t="str">
-        <v/>
+        <v>Relic Castle</v>
       </c>
       <c r="N77" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Sandslash","count":1}]}</v>
       </c>
       <c r="O77" t="str">
         <v/>
@@ -4023,10 +4023,10 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B78" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="C78" t="str">
         <v>Desert Resort</v>
@@ -4059,10 +4059,10 @@
         <v>Yes</v>
       </c>
       <c r="M78" t="str">
-        <v/>
+        <v>Relic Castle</v>
       </c>
       <c r="N78" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Sandslash","count":1}]}</v>
       </c>
       <c r="O78" t="str">
         <v/>
@@ -4070,10 +4070,10 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B79" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="C79" t="str">
         <v>Desert Resort</v>
@@ -4106,10 +4106,10 @@
         <v>Yes</v>
       </c>
       <c r="M79" t="str">
-        <v/>
+        <v>Relic Castle</v>
       </c>
       <c r="N79" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Sandslash","count":1}]}</v>
       </c>
       <c r="O79" t="str">
         <v/>
@@ -4117,10 +4117,10 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B80" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="C80" t="str">
         <v>Desert Resort</v>
@@ -4153,10 +4153,10 @@
         <v>Yes</v>
       </c>
       <c r="M80" t="str">
-        <v/>
+        <v>Relic Castle</v>
       </c>
       <c r="N80" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Sandslash","count":1}]}</v>
       </c>
       <c r="O80" t="str">
         <v/>
@@ -4211,10 +4211,10 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="B82" t="str">
-        <v/>
+        <v>Challenge 18</v>
       </c>
       <c r="C82" t="str">
         <v>Relic Castle</v>
@@ -4247,10 +4247,10 @@
         <v>Yes</v>
       </c>
       <c r="M82" t="str">
-        <v/>
+        <v>Nimbasa City</v>
       </c>
       <c r="N82" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Yamask","count":1}]}</v>
       </c>
       <c r="O82" t="str">
         <v/>
@@ -4258,10 +4258,10 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="B83" t="str">
-        <v/>
+        <v>Challenge 18</v>
       </c>
       <c r="C83" t="str">
         <v>Relic Castle</v>
@@ -4294,10 +4294,10 @@
         <v>Yes</v>
       </c>
       <c r="M83" t="str">
-        <v/>
+        <v>Nimbasa City</v>
       </c>
       <c r="N83" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Yamask","count":1}]}</v>
       </c>
       <c r="O83" t="str">
         <v/>
@@ -4305,10 +4305,10 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="B84" t="str">
-        <v/>
+        <v>Challenge 18</v>
       </c>
       <c r="C84" t="str">
         <v>Relic Castle</v>
@@ -4341,10 +4341,10 @@
         <v>Yes</v>
       </c>
       <c r="M84" t="str">
-        <v/>
+        <v>Nimbasa City</v>
       </c>
       <c r="N84" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Yamask","count":1}]}</v>
       </c>
       <c r="O84" t="str">
         <v/>
@@ -4352,10 +4352,10 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="B85" t="str">
-        <v/>
+        <v>Challenge 18</v>
       </c>
       <c r="C85" t="str">
         <v>Relic Castle</v>
@@ -4388,10 +4388,10 @@
         <v>Yes</v>
       </c>
       <c r="M85" t="str">
-        <v/>
+        <v>Nimbasa City</v>
       </c>
       <c r="N85" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Yamask","count":1}]}</v>
       </c>
       <c r="O85" t="str">
         <v/>
@@ -4399,10 +4399,10 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="B86" t="str">
-        <v/>
+        <v>Challenge 18</v>
       </c>
       <c r="C86" t="str">
         <v>Relic Castle</v>
@@ -4435,10 +4435,10 @@
         <v>Yes</v>
       </c>
       <c r="M86" t="str">
-        <v/>
+        <v>Nimbasa City</v>
       </c>
       <c r="N86" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Yamask","count":1}]}</v>
       </c>
       <c r="O86" t="str">
         <v/>
@@ -4446,10 +4446,10 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="B87" t="str">
-        <v/>
+        <v>Challenge 18</v>
       </c>
       <c r="C87" t="str">
         <v>Relic Castle</v>
@@ -4482,10 +4482,10 @@
         <v>Yes</v>
       </c>
       <c r="M87" t="str">
-        <v/>
+        <v>Nimbasa City</v>
       </c>
       <c r="N87" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Yamask","count":1}]}</v>
       </c>
       <c r="O87" t="str">
         <v/>
@@ -4493,10 +4493,10 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="B88" t="str">
-        <v/>
+        <v>Challenge 18</v>
       </c>
       <c r="C88" t="str">
         <v>Relic Castle</v>
@@ -4529,10 +4529,10 @@
         <v>Yes</v>
       </c>
       <c r="M88" t="str">
-        <v/>
+        <v>Nimbasa City</v>
       </c>
       <c r="N88" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Yamask","count":1}]}</v>
       </c>
       <c r="O88" t="str">
         <v/>
@@ -4540,10 +4540,10 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="B89" t="str">
-        <v/>
+        <v>Challenge 18</v>
       </c>
       <c r="C89" t="str">
         <v>Relic Castle</v>
@@ -4576,10 +4576,10 @@
         <v>Yes</v>
       </c>
       <c r="M89" t="str">
-        <v/>
+        <v>Nimbasa City</v>
       </c>
       <c r="N89" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Yamask","count":1}]}</v>
       </c>
       <c r="O89" t="str">
         <v/>
@@ -4605,7 +4605,7 @@
         <v>22-23</v>
       </c>
       <c r="G90" t="str">
-        <v>22-25</v>
+        <v>23-26</v>
       </c>
       <c r="H90" s="1">
         <v>0.3334</v>
@@ -4634,10 +4634,10 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v/>
+        <v>Challenge 18</v>
       </c>
       <c r="B91" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="C91" t="str">
         <v>Nimbasa City</v>
@@ -4652,7 +4652,7 @@
         <v>22-23</v>
       </c>
       <c r="G91" t="str">
-        <v>22-25</v>
+        <v>23-26</v>
       </c>
       <c r="H91" s="1">
         <v>0.3333</v>
@@ -4670,10 +4670,10 @@
         <v>Yes</v>
       </c>
       <c r="M91" t="str">
-        <v/>
+        <v>Nimbasa Gym</v>
       </c>
       <c r="N91" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Pachirisu","count":1}]}</v>
       </c>
       <c r="O91" t="str">
         <v/>
@@ -4681,10 +4681,10 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v/>
+        <v>Challenge 18</v>
       </c>
       <c r="B92" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="C92" t="str">
         <v>Nimbasa City</v>
@@ -4699,7 +4699,7 @@
         <v>22-23</v>
       </c>
       <c r="G92" t="str">
-        <v>22-25</v>
+        <v>23-26</v>
       </c>
       <c r="H92" s="1">
         <v>0.3333</v>
@@ -4717,10 +4717,10 @@
         <v>Yes</v>
       </c>
       <c r="M92" t="str">
-        <v/>
+        <v>Nimbasa Gym</v>
       </c>
       <c r="N92" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Pachirisu","count":1}]}</v>
       </c>
       <c r="O92" t="str">
         <v/>
@@ -4822,10 +4822,10 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="B95" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="C95" t="str">
         <v>Route 16</v>
@@ -4858,10 +4858,10 @@
         <v>Yes</v>
       </c>
       <c r="M95" t="str">
-        <v/>
+        <v>Lostlorn Forest</v>
       </c>
       <c r="N95" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Joltik","count":1}]}</v>
       </c>
       <c r="O95" t="str">
         <v/>
@@ -4869,10 +4869,10 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="B96" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="C96" t="str">
         <v>Route 16</v>
@@ -4905,10 +4905,10 @@
         <v>Yes</v>
       </c>
       <c r="M96" t="str">
-        <v/>
+        <v>Lostlorn Forest</v>
       </c>
       <c r="N96" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Joltik","count":1}]}</v>
       </c>
       <c r="O96" t="str">
         <v/>
@@ -4916,10 +4916,10 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="B97" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="C97" t="str">
         <v>Route 16</v>
@@ -4952,10 +4952,10 @@
         <v>Yes</v>
       </c>
       <c r="M97" t="str">
-        <v/>
+        <v>Lostlorn Forest</v>
       </c>
       <c r="N97" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Joltik","count":1}]}</v>
       </c>
       <c r="O97" t="str">
         <v/>
@@ -4963,10 +4963,10 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="B98" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="C98" t="str">
         <v>Route 16</v>
@@ -4999,10 +4999,10 @@
         <v>Yes</v>
       </c>
       <c r="M98" t="str">
-        <v/>
+        <v>Lostlorn Forest</v>
       </c>
       <c r="N98" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Joltik","count":1}]}</v>
       </c>
       <c r="O98" t="str">
         <v/>
@@ -5010,10 +5010,10 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="B99" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="C99" t="str">
         <v>Route 16</v>
@@ -5046,10 +5046,10 @@
         <v>Yes</v>
       </c>
       <c r="M99" t="str">
-        <v/>
+        <v>Lostlorn Forest</v>
       </c>
       <c r="N99" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Joltik","count":1}]}</v>
       </c>
       <c r="O99" t="str">
         <v/>
@@ -5075,7 +5075,7 @@
         <v>25-26</v>
       </c>
       <c r="G100" t="str">
-        <v>25-28</v>
+        <v>26-29</v>
       </c>
       <c r="H100" s="1">
         <v>0.1</v>
@@ -5104,10 +5104,10 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="B101" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="C101" t="str">
         <v>Lostlorn Forest</v>
@@ -5122,7 +5122,7 @@
         <v>25-26</v>
       </c>
       <c r="G101" t="str">
-        <v>25-28</v>
+        <v>26-29</v>
       </c>
       <c r="H101" s="1">
         <v>0.1</v>
@@ -5140,10 +5140,10 @@
         <v>No</v>
       </c>
       <c r="M101" t="str">
-        <v/>
+        <v>Driftveil Drawbridge</v>
       </c>
       <c r="N101" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Unfezant","count":1}]}</v>
       </c>
       <c r="O101" t="str">
         <v/>
@@ -5151,10 +5151,10 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="C102" t="str">
         <v>Lostlorn Forest</v>
@@ -5169,7 +5169,7 @@
         <v>25-26</v>
       </c>
       <c r="G102" t="str">
-        <v>25-28</v>
+        <v>26-29</v>
       </c>
       <c r="H102" s="1">
         <v>0.1</v>
@@ -5187,10 +5187,10 @@
         <v>No</v>
       </c>
       <c r="M102" t="str">
-        <v/>
+        <v>Driftveil Drawbridge</v>
       </c>
       <c r="N102" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Unfezant","count":1}]}</v>
       </c>
       <c r="O102" t="str">
         <v/>
@@ -5198,10 +5198,10 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="B103" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="C103" t="str">
         <v>Lostlorn Forest</v>
@@ -5216,7 +5216,7 @@
         <v>25-26</v>
       </c>
       <c r="G103" t="str">
-        <v>25-28</v>
+        <v>26-29</v>
       </c>
       <c r="H103" s="1">
         <v>0.1</v>
@@ -5234,10 +5234,10 @@
         <v>No</v>
       </c>
       <c r="M103" t="str">
-        <v/>
+        <v>Driftveil Drawbridge</v>
       </c>
       <c r="N103" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Unfezant","count":1}]}</v>
       </c>
       <c r="O103" t="str">
         <v/>
@@ -5245,10 +5245,10 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="C104" t="str">
         <v>Lostlorn Forest</v>
@@ -5263,7 +5263,7 @@
         <v>25-26</v>
       </c>
       <c r="G104" t="str">
-        <v>25-28</v>
+        <v>26-29</v>
       </c>
       <c r="H104" s="1">
         <v>0.1</v>
@@ -5281,10 +5281,10 @@
         <v>No</v>
       </c>
       <c r="M104" t="str">
-        <v/>
+        <v>Driftveil Drawbridge</v>
       </c>
       <c r="N104" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Unfezant","count":1}]}</v>
       </c>
       <c r="O104" t="str">
         <v/>
@@ -5292,10 +5292,10 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="C105" t="str">
         <v>Lostlorn Forest</v>
@@ -5310,7 +5310,7 @@
         <v>25-26</v>
       </c>
       <c r="G105" t="str">
-        <v>25-28</v>
+        <v>26-29</v>
       </c>
       <c r="H105" s="1">
         <v>0.1</v>
@@ -5328,10 +5328,10 @@
         <v>No</v>
       </c>
       <c r="M105" t="str">
-        <v/>
+        <v>Driftveil Drawbridge</v>
       </c>
       <c r="N105" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Unfezant","count":1}]}</v>
       </c>
       <c r="O105" t="str">
         <v/>
@@ -5339,10 +5339,10 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="C106" t="str">
         <v>Lostlorn Forest</v>
@@ -5357,7 +5357,7 @@
         <v>25-26</v>
       </c>
       <c r="G106" t="str">
-        <v>25-28</v>
+        <v>26-29</v>
       </c>
       <c r="H106" s="1">
         <v>0.1</v>
@@ -5375,10 +5375,10 @@
         <v>No</v>
       </c>
       <c r="M106" t="str">
-        <v/>
+        <v>Driftveil Drawbridge</v>
       </c>
       <c r="N106" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Unfezant","count":1}]}</v>
       </c>
       <c r="O106" t="str">
         <v/>
@@ -5386,10 +5386,10 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="B107" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="C107" t="str">
         <v>Lostlorn Forest</v>
@@ -5404,7 +5404,7 @@
         <v>25-26</v>
       </c>
       <c r="G107" t="str">
-        <v>25-28</v>
+        <v>26-29</v>
       </c>
       <c r="H107" s="1">
         <v>0.1</v>
@@ -5422,10 +5422,10 @@
         <v>No</v>
       </c>
       <c r="M107" t="str">
-        <v/>
+        <v>Driftveil Drawbridge</v>
       </c>
       <c r="N107" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Unfezant","count":1}]}</v>
       </c>
       <c r="O107" t="str">
         <v/>
@@ -5433,10 +5433,10 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="B108" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="C108" t="str">
         <v>Lostlorn Forest</v>
@@ -5451,7 +5451,7 @@
         <v>25-26</v>
       </c>
       <c r="G108" t="str">
-        <v>25-28</v>
+        <v>26-29</v>
       </c>
       <c r="H108" s="1">
         <v>0.1</v>
@@ -5469,10 +5469,10 @@
         <v>No</v>
       </c>
       <c r="M108" t="str">
-        <v/>
+        <v>Driftveil Drawbridge</v>
       </c>
       <c r="N108" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Unfezant","count":1}]}</v>
       </c>
       <c r="O108" t="str">
         <v/>
@@ -5480,10 +5480,10 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="B109" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="C109" t="str">
         <v>Lostlorn Forest</v>
@@ -5498,7 +5498,7 @@
         <v>25-26</v>
       </c>
       <c r="G109" t="str">
-        <v>25-28</v>
+        <v>26-29</v>
       </c>
       <c r="H109" s="1">
         <v>0.1</v>
@@ -5516,10 +5516,10 @@
         <v>No</v>
       </c>
       <c r="M109" t="str">
-        <v/>
+        <v>Driftveil Drawbridge</v>
       </c>
       <c r="N109" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Unfezant","count":1}]}</v>
       </c>
       <c r="O109" t="str">
         <v/>
@@ -5574,10 +5574,10 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="B111" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="C111" t="str">
         <v>Driftveil Drawbridge</v>
@@ -5610,10 +5610,10 @@
         <v>No</v>
       </c>
       <c r="M111" t="str">
-        <v/>
+        <v>Driftveil City</v>
       </c>
       <c r="N111" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Swanna","count":1}]}</v>
       </c>
       <c r="O111" t="str">
         <v/>
@@ -5621,10 +5621,10 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="B112" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="C112" t="str">
         <v>Driftveil Drawbridge</v>
@@ -5657,10 +5657,10 @@
         <v>No</v>
       </c>
       <c r="M112" t="str">
-        <v/>
+        <v>Driftveil City</v>
       </c>
       <c r="N112" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Swanna","count":1}]}</v>
       </c>
       <c r="O112" t="str">
         <v/>
@@ -5668,10 +5668,10 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="B113" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="C113" t="str">
         <v>Driftveil Drawbridge</v>
@@ -5704,10 +5704,10 @@
         <v>No</v>
       </c>
       <c r="M113" t="str">
-        <v/>
+        <v>Driftveil City</v>
       </c>
       <c r="N113" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Swanna","count":1}]}</v>
       </c>
       <c r="O113" t="str">
         <v/>
@@ -5715,10 +5715,10 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="B114" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="C114" t="str">
         <v>Driftveil Drawbridge</v>
@@ -5751,10 +5751,10 @@
         <v>No</v>
       </c>
       <c r="M114" t="str">
-        <v/>
+        <v>Driftveil City</v>
       </c>
       <c r="N114" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Swanna","count":1}]}</v>
       </c>
       <c r="O114" t="str">
         <v/>
@@ -5762,10 +5762,10 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="B115" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="C115" t="str">
         <v>Driftveil Drawbridge</v>
@@ -5798,10 +5798,10 @@
         <v>No</v>
       </c>
       <c r="M115" t="str">
-        <v/>
+        <v>Driftveil City</v>
       </c>
       <c r="N115" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Swanna","count":1}]}</v>
       </c>
       <c r="O115" t="str">
         <v/>
@@ -5809,10 +5809,10 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="B116" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="C116" t="str">
         <v>Driftveil Drawbridge</v>
@@ -5845,10 +5845,10 @@
         <v>No</v>
       </c>
       <c r="M116" t="str">
-        <v/>
+        <v>Driftveil City</v>
       </c>
       <c r="N116" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Swanna","count":1}]}</v>
       </c>
       <c r="O116" t="str">
         <v/>
@@ -5856,10 +5856,10 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="B117" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="C117" t="str">
         <v>Driftveil Drawbridge</v>
@@ -5892,10 +5892,10 @@
         <v>No</v>
       </c>
       <c r="M117" t="str">
-        <v/>
+        <v>Driftveil City</v>
       </c>
       <c r="N117" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Swanna","count":1}]}</v>
       </c>
       <c r="O117" t="str">
         <v/>
@@ -5968,7 +5968,7 @@
         <v>29-30</v>
       </c>
       <c r="G119" t="str">
-        <v>29-32</v>
+        <v>30-33</v>
       </c>
       <c r="H119" s="1">
         <v>0.1</v>
@@ -5997,10 +5997,10 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="B120" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="C120" t="str">
         <v>Route 6</v>
@@ -6015,7 +6015,7 @@
         <v>29-30</v>
       </c>
       <c r="G120" t="str">
-        <v>29-32</v>
+        <v>30-33</v>
       </c>
       <c r="H120" s="1">
         <v>0.1</v>
@@ -6033,10 +6033,10 @@
         <v>Yes</v>
       </c>
       <c r="M120" t="str">
-        <v/>
+        <v>Chargestone Cave</v>
       </c>
       <c r="N120" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Accelgor","count":1}]}</v>
       </c>
       <c r="O120" t="str">
         <v/>
@@ -6044,10 +6044,10 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="B121" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="C121" t="str">
         <v>Route 6</v>
@@ -6062,7 +6062,7 @@
         <v>29-30</v>
       </c>
       <c r="G121" t="str">
-        <v>29-32</v>
+        <v>30-33</v>
       </c>
       <c r="H121" s="1">
         <v>0.1</v>
@@ -6080,10 +6080,10 @@
         <v>Yes</v>
       </c>
       <c r="M121" t="str">
-        <v/>
+        <v>Chargestone Cave</v>
       </c>
       <c r="N121" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Accelgor","count":1}]}</v>
       </c>
       <c r="O121" t="str">
         <v/>
@@ -6091,10 +6091,10 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="B122" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="C122" t="str">
         <v>Route 6</v>
@@ -6109,7 +6109,7 @@
         <v>29-30</v>
       </c>
       <c r="G122" t="str">
-        <v>29-32</v>
+        <v>30-33</v>
       </c>
       <c r="H122" s="1">
         <v>0.1</v>
@@ -6127,10 +6127,10 @@
         <v>Yes</v>
       </c>
       <c r="M122" t="str">
-        <v/>
+        <v>Chargestone Cave</v>
       </c>
       <c r="N122" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Accelgor","count":1}]}</v>
       </c>
       <c r="O122" t="str">
         <v/>
@@ -6138,10 +6138,10 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="B123" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="C123" t="str">
         <v>Route 6</v>
@@ -6156,7 +6156,7 @@
         <v>29-30</v>
       </c>
       <c r="G123" t="str">
-        <v>29-32</v>
+        <v>30-33</v>
       </c>
       <c r="H123" s="1">
         <v>0.1</v>
@@ -6174,10 +6174,10 @@
         <v>Yes</v>
       </c>
       <c r="M123" t="str">
-        <v/>
+        <v>Chargestone Cave</v>
       </c>
       <c r="N123" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Accelgor","count":1}]}</v>
       </c>
       <c r="O123" t="str">
         <v/>
@@ -6185,10 +6185,10 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="B124" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="C124" t="str">
         <v>Route 6</v>
@@ -6203,7 +6203,7 @@
         <v>29-30</v>
       </c>
       <c r="G124" t="str">
-        <v>29-32</v>
+        <v>30-33</v>
       </c>
       <c r="H124" s="1">
         <v>0.1</v>
@@ -6221,10 +6221,10 @@
         <v>Yes</v>
       </c>
       <c r="M124" t="str">
-        <v/>
+        <v>Chargestone Cave</v>
       </c>
       <c r="N124" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Accelgor","count":1}]}</v>
       </c>
       <c r="O124" t="str">
         <v/>
@@ -6232,10 +6232,10 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="B125" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="C125" t="str">
         <v>Route 6</v>
@@ -6250,7 +6250,7 @@
         <v>29-30</v>
       </c>
       <c r="G125" t="str">
-        <v>29-32</v>
+        <v>30-33</v>
       </c>
       <c r="H125" s="1">
         <v>0.1</v>
@@ -6268,10 +6268,10 @@
         <v>Yes</v>
       </c>
       <c r="M125" t="str">
-        <v/>
+        <v>Chargestone Cave</v>
       </c>
       <c r="N125" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Accelgor","count":1}]}</v>
       </c>
       <c r="O125" t="str">
         <v/>
@@ -6279,10 +6279,10 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="B126" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="C126" t="str">
         <v>Route 6</v>
@@ -6297,7 +6297,7 @@
         <v>29-30</v>
       </c>
       <c r="G126" t="str">
-        <v>29-32</v>
+        <v>30-33</v>
       </c>
       <c r="H126" s="1">
         <v>0.1</v>
@@ -6315,10 +6315,10 @@
         <v>Yes</v>
       </c>
       <c r="M126" t="str">
-        <v/>
+        <v>Chargestone Cave</v>
       </c>
       <c r="N126" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Accelgor","count":1}]}</v>
       </c>
       <c r="O126" t="str">
         <v/>
@@ -6326,10 +6326,10 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="B127" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="C127" t="str">
         <v>Route 6</v>
@@ -6344,7 +6344,7 @@
         <v>29-30</v>
       </c>
       <c r="G127" t="str">
-        <v>29-32</v>
+        <v>30-33</v>
       </c>
       <c r="H127" s="1">
         <v>0.1</v>
@@ -6362,10 +6362,10 @@
         <v>Yes</v>
       </c>
       <c r="M127" t="str">
-        <v/>
+        <v>Chargestone Cave</v>
       </c>
       <c r="N127" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Accelgor","count":1}]}</v>
       </c>
       <c r="O127" t="str">
         <v/>
@@ -6373,10 +6373,10 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="B128" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="C128" t="str">
         <v>Route 6</v>
@@ -6391,7 +6391,7 @@
         <v>29-30</v>
       </c>
       <c r="G128" t="str">
-        <v>29-32</v>
+        <v>30-33</v>
       </c>
       <c r="H128" s="1">
         <v>0.1</v>
@@ -6409,10 +6409,10 @@
         <v>Yes</v>
       </c>
       <c r="M128" t="str">
-        <v/>
+        <v>Chargestone Cave</v>
       </c>
       <c r="N128" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Accelgor","count":1}]}</v>
       </c>
       <c r="O128" t="str">
         <v/>
@@ -6467,10 +6467,10 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="B130" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="C130" t="str">
         <v>Chargestone Cave</v>
@@ -6503,10 +6503,10 @@
         <v>Yes</v>
       </c>
       <c r="M130" t="str">
-        <v/>
+        <v>Driftveil Gym</v>
       </c>
       <c r="N130" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Galvantula","count":1}]}</v>
       </c>
       <c r="O130" t="str">
         <v/>
@@ -6514,10 +6514,10 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="B131" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="C131" t="str">
         <v>Chargestone Cave</v>
@@ -6550,10 +6550,10 @@
         <v>Yes</v>
       </c>
       <c r="M131" t="str">
-        <v/>
+        <v>Driftveil Gym</v>
       </c>
       <c r="N131" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Galvantula","count":1}]}</v>
       </c>
       <c r="O131" t="str">
         <v/>
@@ -6561,10 +6561,10 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="B132" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="C132" t="str">
         <v>Chargestone Cave</v>
@@ -6597,10 +6597,10 @@
         <v>Yes</v>
       </c>
       <c r="M132" t="str">
-        <v/>
+        <v>Driftveil Gym</v>
       </c>
       <c r="N132" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Galvantula","count":1}]}</v>
       </c>
       <c r="O132" t="str">
         <v/>
@@ -6608,10 +6608,10 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="B133" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="C133" t="str">
         <v>Chargestone Cave</v>
@@ -6644,10 +6644,10 @@
         <v>Yes</v>
       </c>
       <c r="M133" t="str">
-        <v/>
+        <v>Driftveil Gym</v>
       </c>
       <c r="N133" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Galvantula","count":1}]}</v>
       </c>
       <c r="O133" t="str">
         <v/>
@@ -6655,10 +6655,10 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="B134" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="C134" t="str">
         <v>Chargestone Cave</v>
@@ -6691,10 +6691,10 @@
         <v>Yes</v>
       </c>
       <c r="M134" t="str">
-        <v/>
+        <v>Driftveil Gym</v>
       </c>
       <c r="N134" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Galvantula","count":1}]}</v>
       </c>
       <c r="O134" t="str">
         <v/>
@@ -6702,10 +6702,10 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="B135" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="C135" t="str">
         <v>Chargestone Cave</v>
@@ -6738,10 +6738,10 @@
         <v>Yes</v>
       </c>
       <c r="M135" t="str">
-        <v/>
+        <v>Driftveil Gym</v>
       </c>
       <c r="N135" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Galvantula","count":1}]}</v>
       </c>
       <c r="O135" t="str">
         <v/>
@@ -6749,10 +6749,10 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="B136" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="C136" t="str">
         <v>Chargestone Cave</v>
@@ -6785,10 +6785,10 @@
         <v>Yes</v>
       </c>
       <c r="M136" t="str">
-        <v/>
+        <v>Driftveil Gym</v>
       </c>
       <c r="N136" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Galvantula","count":1}]}</v>
       </c>
       <c r="O136" t="str">
         <v/>
@@ -6890,10 +6890,10 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B139" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="C139" t="str">
         <v>Route 7</v>
@@ -6926,10 +6926,10 @@
         <v>Yes</v>
       </c>
       <c r="M139" t="str">
-        <v/>
+        <v>Celestial Tower</v>
       </c>
       <c r="N139" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Deerling","count":1}]}</v>
       </c>
       <c r="O139" t="str">
         <v/>
@@ -6937,10 +6937,10 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B140" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="C140" t="str">
         <v>Route 7</v>
@@ -6973,10 +6973,10 @@
         <v>Yes</v>
       </c>
       <c r="M140" t="str">
-        <v/>
+        <v>Celestial Tower</v>
       </c>
       <c r="N140" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Deerling","count":1}]}</v>
       </c>
       <c r="O140" t="str">
         <v/>
@@ -6984,10 +6984,10 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B141" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="C141" t="str">
         <v>Route 7</v>
@@ -7020,10 +7020,10 @@
         <v>Yes</v>
       </c>
       <c r="M141" t="str">
-        <v/>
+        <v>Celestial Tower</v>
       </c>
       <c r="N141" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Deerling","count":1}]}</v>
       </c>
       <c r="O141" t="str">
         <v/>
@@ -7031,10 +7031,10 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B142" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="C142" t="str">
         <v>Route 7</v>
@@ -7067,10 +7067,10 @@
         <v>Yes</v>
       </c>
       <c r="M142" t="str">
-        <v/>
+        <v>Celestial Tower</v>
       </c>
       <c r="N142" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Deerling","count":1}]}</v>
       </c>
       <c r="O142" t="str">
         <v/>
@@ -7078,10 +7078,10 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B143" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="C143" t="str">
         <v>Route 7</v>
@@ -7114,10 +7114,10 @@
         <v>Yes</v>
       </c>
       <c r="M143" t="str">
-        <v/>
+        <v>Celestial Tower</v>
       </c>
       <c r="N143" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Deerling","count":1}]}</v>
       </c>
       <c r="O143" t="str">
         <v/>
@@ -7125,10 +7125,10 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B144" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="C144" t="str">
         <v>Route 7</v>
@@ -7161,10 +7161,10 @@
         <v>Yes</v>
       </c>
       <c r="M144" t="str">
-        <v/>
+        <v>Celestial Tower</v>
       </c>
       <c r="N144" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Deerling","count":1}]}</v>
       </c>
       <c r="O144" t="str">
         <v/>
@@ -7172,10 +7172,10 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B145" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="C145" t="str">
         <v>Route 7</v>
@@ -7208,10 +7208,10 @@
         <v>Yes</v>
       </c>
       <c r="M145" t="str">
-        <v/>
+        <v>Celestial Tower</v>
       </c>
       <c r="N145" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Deerling","count":1}]}</v>
       </c>
       <c r="O145" t="str">
         <v/>
@@ -7219,10 +7219,10 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B146" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="C146" t="str">
         <v>Route 7</v>
@@ -7255,10 +7255,10 @@
         <v>Yes</v>
       </c>
       <c r="M146" t="str">
-        <v/>
+        <v>Celestial Tower</v>
       </c>
       <c r="N146" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Deerling","count":1}]}</v>
       </c>
       <c r="O146" t="str">
         <v/>
@@ -7284,7 +7284,7 @@
         <v>34-35</v>
       </c>
       <c r="G147" t="str">
-        <v>35-38</v>
+        <v>36-39</v>
       </c>
       <c r="H147" s="1">
         <v>0.1665</v>
@@ -7313,10 +7313,10 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B148" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="C148" t="str">
         <v>Celestial Tower</v>
@@ -7331,7 +7331,7 @@
         <v>34-35</v>
       </c>
       <c r="G148" t="str">
-        <v>35-38</v>
+        <v>36-39</v>
       </c>
       <c r="H148" s="1">
         <v>0.1667</v>
@@ -7349,10 +7349,10 @@
         <v>Yes</v>
       </c>
       <c r="M148" t="str">
-        <v/>
+        <v>Mistralton City</v>
       </c>
       <c r="N148" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Swoobat","count":1}]}</v>
       </c>
       <c r="O148" t="str">
         <v/>
@@ -7360,10 +7360,10 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B149" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="C149" t="str">
         <v>Celestial Tower</v>
@@ -7378,7 +7378,7 @@
         <v>34-35</v>
       </c>
       <c r="G149" t="str">
-        <v>35-38</v>
+        <v>36-39</v>
       </c>
       <c r="H149" s="1">
         <v>0.1667</v>
@@ -7396,10 +7396,10 @@
         <v>Yes</v>
       </c>
       <c r="M149" t="str">
-        <v/>
+        <v>Mistralton City</v>
       </c>
       <c r="N149" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Swoobat","count":1}]}</v>
       </c>
       <c r="O149" t="str">
         <v/>
@@ -7407,10 +7407,10 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B150" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="C150" t="str">
         <v>Celestial Tower</v>
@@ -7425,7 +7425,7 @@
         <v>34-35</v>
       </c>
       <c r="G150" t="str">
-        <v>35-38</v>
+        <v>36-39</v>
       </c>
       <c r="H150" s="1">
         <v>0.1667</v>
@@ -7443,10 +7443,10 @@
         <v>Yes</v>
       </c>
       <c r="M150" t="str">
-        <v/>
+        <v>Mistralton City</v>
       </c>
       <c r="N150" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Swoobat","count":1}]}</v>
       </c>
       <c r="O150" t="str">
         <v/>
@@ -7454,10 +7454,10 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B151" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="C151" t="str">
         <v>Celestial Tower</v>
@@ -7472,7 +7472,7 @@
         <v>34-35</v>
       </c>
       <c r="G151" t="str">
-        <v>35-38</v>
+        <v>36-39</v>
       </c>
       <c r="H151" s="1">
         <v>0.1667</v>
@@ -7490,10 +7490,10 @@
         <v>Yes</v>
       </c>
       <c r="M151" t="str">
-        <v/>
+        <v>Mistralton City</v>
       </c>
       <c r="N151" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Swoobat","count":1}]}</v>
       </c>
       <c r="O151" t="str">
         <v/>
@@ -7501,10 +7501,10 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B152" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="C152" t="str">
         <v>Celestial Tower</v>
@@ -7519,7 +7519,7 @@
         <v>34-35</v>
       </c>
       <c r="G152" t="str">
-        <v>35-38</v>
+        <v>36-39</v>
       </c>
       <c r="H152" s="1">
         <v>0.1667</v>
@@ -7537,10 +7537,10 @@
         <v>Yes</v>
       </c>
       <c r="M152" t="str">
-        <v/>
+        <v>Mistralton City</v>
       </c>
       <c r="N152" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Swoobat","count":1}]}</v>
       </c>
       <c r="O152" t="str">
         <v/>
@@ -7660,7 +7660,7 @@
         <v>37-38</v>
       </c>
       <c r="G155" t="str">
-        <v>38-41</v>
+        <v>39-42</v>
       </c>
       <c r="H155" s="1">
         <v>0.1112</v>
@@ -7689,10 +7689,10 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v/>
+        <v>Challenge 31</v>
       </c>
       <c r="B156" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="C156" t="str">
         <v>Reversal Mountain</v>
@@ -7707,7 +7707,7 @@
         <v>37-38</v>
       </c>
       <c r="G156" t="str">
-        <v>38-41</v>
+        <v>39-42</v>
       </c>
       <c r="H156" s="1">
         <v>0.1111</v>
@@ -7725,10 +7725,10 @@
         <v>Yes</v>
       </c>
       <c r="M156" t="str">
-        <v/>
+        <v>Strange House</v>
       </c>
       <c r="N156" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Skarmory","count":1}]}</v>
       </c>
       <c r="O156" t="str">
         <v/>
@@ -7736,10 +7736,10 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v/>
+        <v>Challenge 31</v>
       </c>
       <c r="B157" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="C157" t="str">
         <v>Reversal Mountain</v>
@@ -7754,7 +7754,7 @@
         <v>37-38</v>
       </c>
       <c r="G157" t="str">
-        <v>38-41</v>
+        <v>39-42</v>
       </c>
       <c r="H157" s="1">
         <v>0.1111</v>
@@ -7772,10 +7772,10 @@
         <v>Yes</v>
       </c>
       <c r="M157" t="str">
-        <v/>
+        <v>Strange House</v>
       </c>
       <c r="N157" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Skarmory","count":1}]}</v>
       </c>
       <c r="O157" t="str">
         <v/>
@@ -7783,10 +7783,10 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v/>
+        <v>Challenge 31</v>
       </c>
       <c r="B158" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="C158" t="str">
         <v>Reversal Mountain</v>
@@ -7801,7 +7801,7 @@
         <v>37-38</v>
       </c>
       <c r="G158" t="str">
-        <v>38-41</v>
+        <v>39-42</v>
       </c>
       <c r="H158" s="1">
         <v>0.1111</v>
@@ -7819,10 +7819,10 @@
         <v>Yes</v>
       </c>
       <c r="M158" t="str">
-        <v/>
+        <v>Strange House</v>
       </c>
       <c r="N158" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Skarmory","count":1}]}</v>
       </c>
       <c r="O158" t="str">
         <v/>
@@ -7830,10 +7830,10 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v/>
+        <v>Challenge 31</v>
       </c>
       <c r="B159" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="C159" t="str">
         <v>Reversal Mountain</v>
@@ -7848,7 +7848,7 @@
         <v>37-38</v>
       </c>
       <c r="G159" t="str">
-        <v>38-41</v>
+        <v>39-42</v>
       </c>
       <c r="H159" s="1">
         <v>0.1111</v>
@@ -7866,10 +7866,10 @@
         <v>Yes</v>
       </c>
       <c r="M159" t="str">
-        <v/>
+        <v>Strange House</v>
       </c>
       <c r="N159" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Skarmory","count":1}]}</v>
       </c>
       <c r="O159" t="str">
         <v/>
@@ -7877,10 +7877,10 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v/>
+        <v>Challenge 31</v>
       </c>
       <c r="B160" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="C160" t="str">
         <v>Reversal Mountain</v>
@@ -7895,7 +7895,7 @@
         <v>37-38</v>
       </c>
       <c r="G160" t="str">
-        <v>38-41</v>
+        <v>39-42</v>
       </c>
       <c r="H160" s="1">
         <v>0.1111</v>
@@ -7913,10 +7913,10 @@
         <v>Yes</v>
       </c>
       <c r="M160" t="str">
-        <v/>
+        <v>Strange House</v>
       </c>
       <c r="N160" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Skarmory","count":1}]}</v>
       </c>
       <c r="O160" t="str">
         <v/>
@@ -7924,10 +7924,10 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v/>
+        <v>Challenge 31</v>
       </c>
       <c r="B161" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="C161" t="str">
         <v>Reversal Mountain</v>
@@ -7942,7 +7942,7 @@
         <v>37-38</v>
       </c>
       <c r="G161" t="str">
-        <v>38-41</v>
+        <v>39-42</v>
       </c>
       <c r="H161" s="1">
         <v>0.1111</v>
@@ -7960,10 +7960,10 @@
         <v>Yes</v>
       </c>
       <c r="M161" t="str">
-        <v/>
+        <v>Strange House</v>
       </c>
       <c r="N161" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Skarmory","count":1}]}</v>
       </c>
       <c r="O161" t="str">
         <v/>
@@ -7971,10 +7971,10 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v/>
+        <v>Challenge 31</v>
       </c>
       <c r="B162" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="C162" t="str">
         <v>Reversal Mountain</v>
@@ -7989,7 +7989,7 @@
         <v>37-38</v>
       </c>
       <c r="G162" t="str">
-        <v>38-41</v>
+        <v>39-42</v>
       </c>
       <c r="H162" s="1">
         <v>0.1111</v>
@@ -8007,10 +8007,10 @@
         <v>Yes</v>
       </c>
       <c r="M162" t="str">
-        <v/>
+        <v>Strange House</v>
       </c>
       <c r="N162" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Skarmory","count":1}]}</v>
       </c>
       <c r="O162" t="str">
         <v/>
@@ -8018,10 +8018,10 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v/>
+        <v>Challenge 31</v>
       </c>
       <c r="B163" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="C163" t="str">
         <v>Reversal Mountain</v>
@@ -8036,7 +8036,7 @@
         <v>37-38</v>
       </c>
       <c r="G163" t="str">
-        <v>38-41</v>
+        <v>39-42</v>
       </c>
       <c r="H163" s="1">
         <v>0.1111</v>
@@ -8054,10 +8054,10 @@
         <v>Yes</v>
       </c>
       <c r="M163" t="str">
-        <v/>
+        <v>Strange House</v>
       </c>
       <c r="N163" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Skarmory","count":1}]}</v>
       </c>
       <c r="O163" t="str">
         <v/>
@@ -8083,7 +8083,7 @@
         <v>38-39</v>
       </c>
       <c r="G164" t="str">
-        <v>39-42</v>
+        <v>40-44</v>
       </c>
       <c r="H164" s="1">
         <v>0.1</v>
@@ -8112,10 +8112,10 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="B165" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="C165" t="str">
         <v>Strange House</v>
@@ -8130,7 +8130,7 @@
         <v>38-39</v>
       </c>
       <c r="G165" t="str">
-        <v>39-42</v>
+        <v>40-44</v>
       </c>
       <c r="H165" s="1">
         <v>0.1</v>
@@ -8148,10 +8148,10 @@
         <v>Yes</v>
       </c>
       <c r="M165" t="str">
-        <v/>
+        <v>Undella Town</v>
       </c>
       <c r="N165" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Chandelure","count":1}]}</v>
       </c>
       <c r="O165" t="str">
         <v/>
@@ -8159,10 +8159,10 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="B166" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="C166" t="str">
         <v>Strange House</v>
@@ -8177,7 +8177,7 @@
         <v>38-39</v>
       </c>
       <c r="G166" t="str">
-        <v>39-42</v>
+        <v>40-44</v>
       </c>
       <c r="H166" s="1">
         <v>0.1</v>
@@ -8195,10 +8195,10 @@
         <v>Yes</v>
       </c>
       <c r="M166" t="str">
-        <v/>
+        <v>Undella Town</v>
       </c>
       <c r="N166" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Chandelure","count":1}]}</v>
       </c>
       <c r="O166" t="str">
         <v/>
@@ -8206,10 +8206,10 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="B167" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="C167" t="str">
         <v>Strange House</v>
@@ -8224,7 +8224,7 @@
         <v>38-39</v>
       </c>
       <c r="G167" t="str">
-        <v>39-42</v>
+        <v>40-44</v>
       </c>
       <c r="H167" s="1">
         <v>0.1</v>
@@ -8242,10 +8242,10 @@
         <v>Yes</v>
       </c>
       <c r="M167" t="str">
-        <v/>
+        <v>Undella Town</v>
       </c>
       <c r="N167" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Chandelure","count":1}]}</v>
       </c>
       <c r="O167" t="str">
         <v/>
@@ -8253,10 +8253,10 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="B168" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="C168" t="str">
         <v>Strange House</v>
@@ -8271,7 +8271,7 @@
         <v>38-39</v>
       </c>
       <c r="G168" t="str">
-        <v>39-42</v>
+        <v>40-44</v>
       </c>
       <c r="H168" s="1">
         <v>0.1</v>
@@ -8289,10 +8289,10 @@
         <v>Yes</v>
       </c>
       <c r="M168" t="str">
-        <v/>
+        <v>Undella Town</v>
       </c>
       <c r="N168" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Chandelure","count":1}]}</v>
       </c>
       <c r="O168" t="str">
         <v/>
@@ -8300,10 +8300,10 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="B169" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="C169" t="str">
         <v>Strange House</v>
@@ -8318,7 +8318,7 @@
         <v>38-39</v>
       </c>
       <c r="G169" t="str">
-        <v>39-42</v>
+        <v>40-44</v>
       </c>
       <c r="H169" s="1">
         <v>0.1</v>
@@ -8336,10 +8336,10 @@
         <v>Yes</v>
       </c>
       <c r="M169" t="str">
-        <v/>
+        <v>Undella Town</v>
       </c>
       <c r="N169" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Chandelure","count":1}]}</v>
       </c>
       <c r="O169" t="str">
         <v/>
@@ -8347,10 +8347,10 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="B170" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="C170" t="str">
         <v>Strange House</v>
@@ -8365,7 +8365,7 @@
         <v>38-39</v>
       </c>
       <c r="G170" t="str">
-        <v>39-42</v>
+        <v>40-44</v>
       </c>
       <c r="H170" s="1">
         <v>0.1</v>
@@ -8383,10 +8383,10 @@
         <v>Yes</v>
       </c>
       <c r="M170" t="str">
-        <v/>
+        <v>Undella Town</v>
       </c>
       <c r="N170" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Chandelure","count":1}]}</v>
       </c>
       <c r="O170" t="str">
         <v/>
@@ -8394,10 +8394,10 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="B171" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="C171" t="str">
         <v>Strange House</v>
@@ -8412,7 +8412,7 @@
         <v>38-39</v>
       </c>
       <c r="G171" t="str">
-        <v>39-42</v>
+        <v>40-44</v>
       </c>
       <c r="H171" s="1">
         <v>0.1</v>
@@ -8430,10 +8430,10 @@
         <v>Yes</v>
       </c>
       <c r="M171" t="str">
-        <v/>
+        <v>Undella Town</v>
       </c>
       <c r="N171" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Chandelure","count":1}]}</v>
       </c>
       <c r="O171" t="str">
         <v/>
@@ -8441,10 +8441,10 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="B172" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="C172" t="str">
         <v>Strange House</v>
@@ -8459,7 +8459,7 @@
         <v>38-39</v>
       </c>
       <c r="G172" t="str">
-        <v>39-42</v>
+        <v>40-44</v>
       </c>
       <c r="H172" s="1">
         <v>0.1</v>
@@ -8477,10 +8477,10 @@
         <v>Yes</v>
       </c>
       <c r="M172" t="str">
-        <v/>
+        <v>Undella Town</v>
       </c>
       <c r="N172" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Chandelure","count":1}]}</v>
       </c>
       <c r="O172" t="str">
         <v/>
@@ -8488,10 +8488,10 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="B173" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="C173" t="str">
         <v>Strange House</v>
@@ -8506,7 +8506,7 @@
         <v>38-39</v>
       </c>
       <c r="G173" t="str">
-        <v>39-42</v>
+        <v>40-44</v>
       </c>
       <c r="H173" s="1">
         <v>0.1</v>
@@ -8524,10 +8524,10 @@
         <v>Yes</v>
       </c>
       <c r="M173" t="str">
-        <v/>
+        <v>Undella Town</v>
       </c>
       <c r="N173" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Chandelure","count":1}]}</v>
       </c>
       <c r="O173" t="str">
         <v/>
@@ -8600,7 +8600,7 @@
         <v>41-42</v>
       </c>
       <c r="G175" t="str">
-        <v>42-46</v>
+        <v>43-47</v>
       </c>
       <c r="H175" s="1">
         <v>0.0837</v>
@@ -8629,10 +8629,10 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="B176" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="C176" t="str">
         <v>Undella Bay</v>
@@ -8647,7 +8647,7 @@
         <v>41-42</v>
       </c>
       <c r="G176" t="str">
-        <v>42-46</v>
+        <v>43-47</v>
       </c>
       <c r="H176" s="1">
         <v>0.0833</v>
@@ -8665,10 +8665,10 @@
         <v>No</v>
       </c>
       <c r="M176" t="str">
-        <v/>
+        <v>Route 13</v>
       </c>
       <c r="N176" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Barboach","count":1}]}</v>
       </c>
       <c r="O176" t="str">
         <v/>
@@ -8676,10 +8676,10 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="B177" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="C177" t="str">
         <v>Undella Bay</v>
@@ -8694,7 +8694,7 @@
         <v>41-42</v>
       </c>
       <c r="G177" t="str">
-        <v>42-46</v>
+        <v>43-47</v>
       </c>
       <c r="H177" s="1">
         <v>0.0833</v>
@@ -8712,10 +8712,10 @@
         <v>No</v>
       </c>
       <c r="M177" t="str">
-        <v/>
+        <v>Route 13</v>
       </c>
       <c r="N177" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Barboach","count":1}]}</v>
       </c>
       <c r="O177" t="str">
         <v/>
@@ -8723,10 +8723,10 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="B178" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="C178" t="str">
         <v>Undella Bay</v>
@@ -8741,7 +8741,7 @@
         <v>41-42</v>
       </c>
       <c r="G178" t="str">
-        <v>42-46</v>
+        <v>43-47</v>
       </c>
       <c r="H178" s="1">
         <v>0.0833</v>
@@ -8759,10 +8759,10 @@
         <v>No</v>
       </c>
       <c r="M178" t="str">
-        <v/>
+        <v>Route 13</v>
       </c>
       <c r="N178" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Barboach","count":1}]}</v>
       </c>
       <c r="O178" t="str">
         <v/>
@@ -8770,10 +8770,10 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="B179" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="C179" t="str">
         <v>Undella Bay</v>
@@ -8788,7 +8788,7 @@
         <v>41-42</v>
       </c>
       <c r="G179" t="str">
-        <v>42-46</v>
+        <v>43-47</v>
       </c>
       <c r="H179" s="1">
         <v>0.0833</v>
@@ -8806,10 +8806,10 @@
         <v>No</v>
       </c>
       <c r="M179" t="str">
-        <v/>
+        <v>Route 13</v>
       </c>
       <c r="N179" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Barboach","count":1}]}</v>
       </c>
       <c r="O179" t="str">
         <v/>
@@ -8817,10 +8817,10 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="B180" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="C180" t="str">
         <v>Undella Bay</v>
@@ -8835,7 +8835,7 @@
         <v>41-42</v>
       </c>
       <c r="G180" t="str">
-        <v>42-46</v>
+        <v>43-47</v>
       </c>
       <c r="H180" s="1">
         <v>0.0833</v>
@@ -8853,10 +8853,10 @@
         <v>No</v>
       </c>
       <c r="M180" t="str">
-        <v/>
+        <v>Route 13</v>
       </c>
       <c r="N180" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Barboach","count":1}]}</v>
       </c>
       <c r="O180" t="str">
         <v/>
@@ -8864,10 +8864,10 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="B181" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="C181" t="str">
         <v>Undella Bay</v>
@@ -8882,7 +8882,7 @@
         <v>41-42</v>
       </c>
       <c r="G181" t="str">
-        <v>42-46</v>
+        <v>43-47</v>
       </c>
       <c r="H181" s="1">
         <v>0.0833</v>
@@ -8900,10 +8900,10 @@
         <v>No</v>
       </c>
       <c r="M181" t="str">
-        <v/>
+        <v>Route 13</v>
       </c>
       <c r="N181" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Barboach","count":1}]}</v>
       </c>
       <c r="O181" t="str">
         <v/>
@@ -8911,10 +8911,10 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="B182" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="C182" t="str">
         <v>Undella Bay</v>
@@ -8929,7 +8929,7 @@
         <v>41-42</v>
       </c>
       <c r="G182" t="str">
-        <v>42-46</v>
+        <v>43-47</v>
       </c>
       <c r="H182" s="1">
         <v>0.0833</v>
@@ -8947,10 +8947,10 @@
         <v>No</v>
       </c>
       <c r="M182" t="str">
-        <v/>
+        <v>Route 13</v>
       </c>
       <c r="N182" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Barboach","count":1}]}</v>
       </c>
       <c r="O182" t="str">
         <v/>
@@ -8958,10 +8958,10 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="B183" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="C183" t="str">
         <v>Undella Bay</v>
@@ -8976,7 +8976,7 @@
         <v>41-42</v>
       </c>
       <c r="G183" t="str">
-        <v>42-46</v>
+        <v>43-47</v>
       </c>
       <c r="H183" s="1">
         <v>0.0833</v>
@@ -8994,10 +8994,10 @@
         <v>No</v>
       </c>
       <c r="M183" t="str">
-        <v/>
+        <v>Route 13</v>
       </c>
       <c r="N183" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Barboach","count":1}]}</v>
       </c>
       <c r="O183" t="str">
         <v/>
@@ -9005,10 +9005,10 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="B184" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="C184" t="str">
         <v>Undella Bay</v>
@@ -9023,7 +9023,7 @@
         <v>41-42</v>
       </c>
       <c r="G184" t="str">
-        <v>42-46</v>
+        <v>43-47</v>
       </c>
       <c r="H184" s="1">
         <v>0.0833</v>
@@ -9041,10 +9041,10 @@
         <v>No</v>
       </c>
       <c r="M184" t="str">
-        <v/>
+        <v>Route 13</v>
       </c>
       <c r="N184" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Barboach","count":1}]}</v>
       </c>
       <c r="O184" t="str">
         <v/>
@@ -9052,10 +9052,10 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="B185" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="C185" t="str">
         <v>Undella Bay</v>
@@ -9070,7 +9070,7 @@
         <v>41-42</v>
       </c>
       <c r="G185" t="str">
-        <v>42-46</v>
+        <v>43-47</v>
       </c>
       <c r="H185" s="1">
         <v>0.0833</v>
@@ -9088,10 +9088,10 @@
         <v>No</v>
       </c>
       <c r="M185" t="str">
-        <v/>
+        <v>Route 13</v>
       </c>
       <c r="N185" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Barboach","count":1}]}</v>
       </c>
       <c r="O185" t="str">
         <v/>
@@ -9099,10 +9099,10 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="B186" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="C186" t="str">
         <v>Undella Bay</v>
@@ -9117,7 +9117,7 @@
         <v>41-42</v>
       </c>
       <c r="G186" t="str">
-        <v>42-46</v>
+        <v>43-47</v>
       </c>
       <c r="H186" s="1">
         <v>0.0833</v>
@@ -9135,10 +9135,10 @@
         <v>No</v>
       </c>
       <c r="M186" t="str">
-        <v/>
+        <v>Route 13</v>
       </c>
       <c r="N186" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Barboach","count":1}]}</v>
       </c>
       <c r="O186" t="str">
         <v/>
@@ -9193,10 +9193,10 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="B188" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="C188" t="str">
         <v>Route 13</v>
@@ -9229,10 +9229,10 @@
         <v>Yes</v>
       </c>
       <c r="M188" t="str">
-        <v/>
+        <v>Route 14</v>
       </c>
       <c r="N188" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Seismitoad","count":1}]}</v>
       </c>
       <c r="O188" t="str">
         <v/>
@@ -9240,10 +9240,10 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="B189" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="C189" t="str">
         <v>Route 13</v>
@@ -9276,10 +9276,10 @@
         <v>Yes</v>
       </c>
       <c r="M189" t="str">
-        <v/>
+        <v>Route 14</v>
       </c>
       <c r="N189" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Seismitoad","count":1}]}</v>
       </c>
       <c r="O189" t="str">
         <v/>
@@ -9287,10 +9287,10 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="B190" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="C190" t="str">
         <v>Route 13</v>
@@ -9323,10 +9323,10 @@
         <v>Yes</v>
       </c>
       <c r="M190" t="str">
-        <v/>
+        <v>Route 14</v>
       </c>
       <c r="N190" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Seismitoad","count":1}]}</v>
       </c>
       <c r="O190" t="str">
         <v/>
@@ -9334,10 +9334,10 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="B191" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="C191" t="str">
         <v>Route 13</v>
@@ -9370,10 +9370,10 @@
         <v>Yes</v>
       </c>
       <c r="M191" t="str">
-        <v/>
+        <v>Route 14</v>
       </c>
       <c r="N191" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Seismitoad","count":1}]}</v>
       </c>
       <c r="O191" t="str">
         <v/>
@@ -9381,10 +9381,10 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="B192" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="C192" t="str">
         <v>Route 13</v>
@@ -9417,10 +9417,10 @@
         <v>Yes</v>
       </c>
       <c r="M192" t="str">
-        <v/>
+        <v>Route 14</v>
       </c>
       <c r="N192" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Seismitoad","count":1}]}</v>
       </c>
       <c r="O192" t="str">
         <v/>
@@ -9428,10 +9428,10 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="B193" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="C193" t="str">
         <v>Route 13</v>
@@ -9464,10 +9464,10 @@
         <v>Yes</v>
       </c>
       <c r="M193" t="str">
-        <v/>
+        <v>Route 14</v>
       </c>
       <c r="N193" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Seismitoad","count":1}]}</v>
       </c>
       <c r="O193" t="str">
         <v/>
@@ -9475,10 +9475,10 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="B194" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="C194" t="str">
         <v>Route 13</v>
@@ -9511,10 +9511,10 @@
         <v>Yes</v>
       </c>
       <c r="M194" t="str">
-        <v/>
+        <v>Route 14</v>
       </c>
       <c r="N194" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Seismitoad","count":1}]}</v>
       </c>
       <c r="O194" t="str">
         <v/>
@@ -9540,7 +9540,7 @@
         <v>43-44</v>
       </c>
       <c r="G195" t="str">
-        <v>45-49</v>
+        <v>46-50</v>
       </c>
       <c r="H195" s="1">
         <v>0.1665</v>
@@ -9569,10 +9569,10 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="B196" t="str">
-        <v/>
+        <v>Challenge 37</v>
       </c>
       <c r="C196" t="str">
         <v>Route 14</v>
@@ -9587,7 +9587,7 @@
         <v>43-44</v>
       </c>
       <c r="G196" t="str">
-        <v>45-49</v>
+        <v>46-50</v>
       </c>
       <c r="H196" s="1">
         <v>0.1667</v>
@@ -9605,10 +9605,10 @@
         <v>Yes</v>
       </c>
       <c r="M196" t="str">
-        <v/>
+        <v>Abundant Shrine</v>
       </c>
       <c r="N196" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Tropius","count":1}]}</v>
       </c>
       <c r="O196" t="str">
         <v/>
@@ -9616,10 +9616,10 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="B197" t="str">
-        <v/>
+        <v>Challenge 37</v>
       </c>
       <c r="C197" t="str">
         <v>Route 14</v>
@@ -9634,7 +9634,7 @@
         <v>43-44</v>
       </c>
       <c r="G197" t="str">
-        <v>45-49</v>
+        <v>46-50</v>
       </c>
       <c r="H197" s="1">
         <v>0.1667</v>
@@ -9652,10 +9652,10 @@
         <v>Yes</v>
       </c>
       <c r="M197" t="str">
-        <v/>
+        <v>Abundant Shrine</v>
       </c>
       <c r="N197" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Tropius","count":1}]}</v>
       </c>
       <c r="O197" t="str">
         <v/>
@@ -9663,10 +9663,10 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="B198" t="str">
-        <v/>
+        <v>Challenge 37</v>
       </c>
       <c r="C198" t="str">
         <v>Route 14</v>
@@ -9681,7 +9681,7 @@
         <v>43-44</v>
       </c>
       <c r="G198" t="str">
-        <v>45-49</v>
+        <v>46-50</v>
       </c>
       <c r="H198" s="1">
         <v>0.1667</v>
@@ -9699,10 +9699,10 @@
         <v>Yes</v>
       </c>
       <c r="M198" t="str">
-        <v/>
+        <v>Abundant Shrine</v>
       </c>
       <c r="N198" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Tropius","count":1}]}</v>
       </c>
       <c r="O198" t="str">
         <v/>
@@ -9710,10 +9710,10 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="B199" t="str">
-        <v/>
+        <v>Challenge 37</v>
       </c>
       <c r="C199" t="str">
         <v>Route 14</v>
@@ -9728,7 +9728,7 @@
         <v>43-44</v>
       </c>
       <c r="G199" t="str">
-        <v>45-49</v>
+        <v>46-50</v>
       </c>
       <c r="H199" s="1">
         <v>0.1667</v>
@@ -9746,10 +9746,10 @@
         <v>Yes</v>
       </c>
       <c r="M199" t="str">
-        <v/>
+        <v>Abundant Shrine</v>
       </c>
       <c r="N199" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Tropius","count":1}]}</v>
       </c>
       <c r="O199" t="str">
         <v/>
@@ -9757,10 +9757,10 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="B200" t="str">
-        <v/>
+        <v>Challenge 37</v>
       </c>
       <c r="C200" t="str">
         <v>Route 14</v>
@@ -9775,7 +9775,7 @@
         <v>43-44</v>
       </c>
       <c r="G200" t="str">
-        <v>45-49</v>
+        <v>46-50</v>
       </c>
       <c r="H200" s="1">
         <v>0.1667</v>
@@ -9793,10 +9793,10 @@
         <v>Yes</v>
       </c>
       <c r="M200" t="str">
-        <v/>
+        <v>Abundant Shrine</v>
       </c>
       <c r="N200" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Tropius","count":1}]}</v>
       </c>
       <c r="O200" t="str">
         <v/>
@@ -9822,7 +9822,7 @@
         <v>44-45</v>
       </c>
       <c r="G201" t="str">
-        <v>46-50</v>
+        <v>47-51</v>
       </c>
       <c r="H201" s="1">
         <v>0.2</v>
@@ -9851,10 +9851,10 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v/>
+        <v>Challenge 37</v>
       </c>
       <c r="B202" t="str">
-        <v/>
+        <v>Challenge 38</v>
       </c>
       <c r="C202" t="str">
         <v>Abundant Shrine</v>
@@ -9869,7 +9869,7 @@
         <v>44-45</v>
       </c>
       <c r="G202" t="str">
-        <v>46-50</v>
+        <v>47-51</v>
       </c>
       <c r="H202" s="1">
         <v>0.2</v>
@@ -9887,10 +9887,10 @@
         <v>Yes</v>
       </c>
       <c r="M202" t="str">
-        <v/>
+        <v>Opelucid City</v>
       </c>
       <c r="N202" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Gothitelle","count":1}]}</v>
       </c>
       <c r="O202" t="str">
         <v/>
@@ -9898,10 +9898,10 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v/>
+        <v>Challenge 37</v>
       </c>
       <c r="B203" t="str">
-        <v/>
+        <v>Challenge 38</v>
       </c>
       <c r="C203" t="str">
         <v>Abundant Shrine</v>
@@ -9916,7 +9916,7 @@
         <v>44-45</v>
       </c>
       <c r="G203" t="str">
-        <v>46-50</v>
+        <v>47-51</v>
       </c>
       <c r="H203" s="1">
         <v>0.2</v>
@@ -9934,10 +9934,10 @@
         <v>Yes</v>
       </c>
       <c r="M203" t="str">
-        <v/>
+        <v>Opelucid City</v>
       </c>
       <c r="N203" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Gothitelle","count":1}]}</v>
       </c>
       <c r="O203" t="str">
         <v/>
@@ -9945,10 +9945,10 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v/>
+        <v>Challenge 37</v>
       </c>
       <c r="B204" t="str">
-        <v/>
+        <v>Challenge 38</v>
       </c>
       <c r="C204" t="str">
         <v>Abundant Shrine</v>
@@ -9963,7 +9963,7 @@
         <v>44-45</v>
       </c>
       <c r="G204" t="str">
-        <v>46-50</v>
+        <v>47-51</v>
       </c>
       <c r="H204" s="1">
         <v>0.2</v>
@@ -9981,10 +9981,10 @@
         <v>Yes</v>
       </c>
       <c r="M204" t="str">
-        <v/>
+        <v>Opelucid City</v>
       </c>
       <c r="N204" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Gothitelle","count":1}]}</v>
       </c>
       <c r="O204" t="str">
         <v/>
@@ -9992,10 +9992,10 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v/>
+        <v>Challenge 37</v>
       </c>
       <c r="B205" t="str">
-        <v/>
+        <v>Challenge 38</v>
       </c>
       <c r="C205" t="str">
         <v>Abundant Shrine</v>
@@ -10010,7 +10010,7 @@
         <v>44-45</v>
       </c>
       <c r="G205" t="str">
-        <v>46-50</v>
+        <v>47-51</v>
       </c>
       <c r="H205" s="1">
         <v>0.2</v>
@@ -10028,10 +10028,10 @@
         <v>Yes</v>
       </c>
       <c r="M205" t="str">
-        <v/>
+        <v>Opelucid City</v>
       </c>
       <c r="N205" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Gothitelle","count":1}]}</v>
       </c>
       <c r="O205" t="str">
         <v/>
@@ -10151,7 +10151,7 @@
         <v>48-49</v>
       </c>
       <c r="G208" t="str">
-        <v>51-56</v>
+        <v>52-57</v>
       </c>
       <c r="H208" s="1">
         <v>0.2</v>
@@ -10180,10 +10180,10 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v/>
+        <v>Challenge 40</v>
       </c>
       <c r="B209" t="str">
-        <v/>
+        <v>Challenge 41</v>
       </c>
       <c r="C209" t="str">
         <v>Route 11</v>
@@ -10198,7 +10198,7 @@
         <v>48-49</v>
       </c>
       <c r="G209" t="str">
-        <v>51-56</v>
+        <v>52-57</v>
       </c>
       <c r="H209" s="1">
         <v>0.2</v>
@@ -10216,10 +10216,10 @@
         <v>No</v>
       </c>
       <c r="M209" t="str">
-        <v/>
+        <v>Village Bridge</v>
       </c>
       <c r="N209" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Shelmet","count":1}]}</v>
       </c>
       <c r="O209" t="str">
         <v/>
@@ -10227,10 +10227,10 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v/>
+        <v>Challenge 40</v>
       </c>
       <c r="B210" t="str">
-        <v/>
+        <v>Challenge 41</v>
       </c>
       <c r="C210" t="str">
         <v>Route 11</v>
@@ -10245,7 +10245,7 @@
         <v>48-49</v>
       </c>
       <c r="G210" t="str">
-        <v>51-56</v>
+        <v>52-57</v>
       </c>
       <c r="H210" s="1">
         <v>0.2</v>
@@ -10263,10 +10263,10 @@
         <v>No</v>
       </c>
       <c r="M210" t="str">
-        <v/>
+        <v>Village Bridge</v>
       </c>
       <c r="N210" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Shelmet","count":1}]}</v>
       </c>
       <c r="O210" t="str">
         <v/>
@@ -10274,10 +10274,10 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v/>
+        <v>Challenge 40</v>
       </c>
       <c r="B211" t="str">
-        <v/>
+        <v>Challenge 41</v>
       </c>
       <c r="C211" t="str">
         <v>Route 11</v>
@@ -10292,7 +10292,7 @@
         <v>48-49</v>
       </c>
       <c r="G211" t="str">
-        <v>51-56</v>
+        <v>52-57</v>
       </c>
       <c r="H211" s="1">
         <v>0.2</v>
@@ -10310,10 +10310,10 @@
         <v>No</v>
       </c>
       <c r="M211" t="str">
-        <v/>
+        <v>Village Bridge</v>
       </c>
       <c r="N211" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Shelmet","count":1}]}</v>
       </c>
       <c r="O211" t="str">
         <v/>
@@ -10321,10 +10321,10 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v/>
+        <v>Challenge 40</v>
       </c>
       <c r="B212" t="str">
-        <v/>
+        <v>Challenge 41</v>
       </c>
       <c r="C212" t="str">
         <v>Route 11</v>
@@ -10339,7 +10339,7 @@
         <v>48-49</v>
       </c>
       <c r="G212" t="str">
-        <v>51-56</v>
+        <v>52-57</v>
       </c>
       <c r="H212" s="1">
         <v>0.2</v>
@@ -10357,10 +10357,10 @@
         <v>No</v>
       </c>
       <c r="M212" t="str">
-        <v/>
+        <v>Village Bridge</v>
       </c>
       <c r="N212" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Shelmet","count":1}]}</v>
       </c>
       <c r="O212" t="str">
         <v/>
@@ -10386,7 +10386,7 @@
         <v>49-50</v>
       </c>
       <c r="G213" t="str">
-        <v>52-57</v>
+        <v>53-58</v>
       </c>
       <c r="H213" s="1">
         <v>0.1665</v>
@@ -10415,10 +10415,10 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v/>
+        <v>Challenge 41</v>
       </c>
       <c r="B214" t="str">
-        <v/>
+        <v>Challenge 42</v>
       </c>
       <c r="C214" t="str">
         <v>Village Bridge</v>
@@ -10433,7 +10433,7 @@
         <v>49-50</v>
       </c>
       <c r="G214" t="str">
-        <v>52-57</v>
+        <v>53-58</v>
       </c>
       <c r="H214" s="1">
         <v>0.1667</v>
@@ -10451,10 +10451,10 @@
         <v>Yes</v>
       </c>
       <c r="M214" t="str">
-        <v/>
+        <v>Route 12</v>
       </c>
       <c r="N214" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Azumarill","count":1}]}</v>
       </c>
       <c r="O214" t="str">
         <v/>
@@ -10462,10 +10462,10 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v/>
+        <v>Challenge 41</v>
       </c>
       <c r="B215" t="str">
-        <v/>
+        <v>Challenge 42</v>
       </c>
       <c r="C215" t="str">
         <v>Village Bridge</v>
@@ -10480,7 +10480,7 @@
         <v>49-50</v>
       </c>
       <c r="G215" t="str">
-        <v>52-57</v>
+        <v>53-58</v>
       </c>
       <c r="H215" s="1">
         <v>0.1667</v>
@@ -10498,10 +10498,10 @@
         <v>Yes</v>
       </c>
       <c r="M215" t="str">
-        <v/>
+        <v>Route 12</v>
       </c>
       <c r="N215" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Azumarill","count":1}]}</v>
       </c>
       <c r="O215" t="str">
         <v/>
@@ -10509,10 +10509,10 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v/>
+        <v>Challenge 41</v>
       </c>
       <c r="B216" t="str">
-        <v/>
+        <v>Challenge 42</v>
       </c>
       <c r="C216" t="str">
         <v>Village Bridge</v>
@@ -10527,7 +10527,7 @@
         <v>49-50</v>
       </c>
       <c r="G216" t="str">
-        <v>52-57</v>
+        <v>53-58</v>
       </c>
       <c r="H216" s="1">
         <v>0.1667</v>
@@ -10545,10 +10545,10 @@
         <v>Yes</v>
       </c>
       <c r="M216" t="str">
-        <v/>
+        <v>Route 12</v>
       </c>
       <c r="N216" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Azumarill","count":1}]}</v>
       </c>
       <c r="O216" t="str">
         <v/>
@@ -10556,10 +10556,10 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v/>
+        <v>Challenge 41</v>
       </c>
       <c r="B217" t="str">
-        <v/>
+        <v>Challenge 42</v>
       </c>
       <c r="C217" t="str">
         <v>Village Bridge</v>
@@ -10574,7 +10574,7 @@
         <v>49-50</v>
       </c>
       <c r="G217" t="str">
-        <v>52-57</v>
+        <v>53-58</v>
       </c>
       <c r="H217" s="1">
         <v>0.1667</v>
@@ -10592,10 +10592,10 @@
         <v>Yes</v>
       </c>
       <c r="M217" t="str">
-        <v/>
+        <v>Route 12</v>
       </c>
       <c r="N217" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Azumarill","count":1}]}</v>
       </c>
       <c r="O217" t="str">
         <v/>
@@ -10603,10 +10603,10 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v/>
+        <v>Challenge 41</v>
       </c>
       <c r="B218" t="str">
-        <v/>
+        <v>Challenge 42</v>
       </c>
       <c r="C218" t="str">
         <v>Village Bridge</v>
@@ -10621,7 +10621,7 @@
         <v>49-50</v>
       </c>
       <c r="G218" t="str">
-        <v>52-57</v>
+        <v>53-58</v>
       </c>
       <c r="H218" s="1">
         <v>0.1667</v>
@@ -10639,10 +10639,10 @@
         <v>Yes</v>
       </c>
       <c r="M218" t="str">
-        <v/>
+        <v>Route 12</v>
       </c>
       <c r="N218" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Azumarill","count":1}]}</v>
       </c>
       <c r="O218" t="str">
         <v/>
@@ -10668,7 +10668,7 @@
         <v>50-51</v>
       </c>
       <c r="G219" t="str">
-        <v>53-58</v>
+        <v>54-59</v>
       </c>
       <c r="H219" s="1">
         <v>0.1426</v>
@@ -10697,10 +10697,10 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v/>
+        <v>Challenge 42</v>
       </c>
       <c r="B220" t="str">
-        <v/>
+        <v>Challenge 43</v>
       </c>
       <c r="C220" t="str">
         <v>Route 12</v>
@@ -10715,7 +10715,7 @@
         <v>50-51</v>
       </c>
       <c r="G220" t="str">
-        <v>53-58</v>
+        <v>54-59</v>
       </c>
       <c r="H220" s="1">
         <v>0.1429</v>
@@ -10733,10 +10733,10 @@
         <v>Yes</v>
       </c>
       <c r="M220" t="str">
-        <v/>
+        <v>Route 9</v>
       </c>
       <c r="N220" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Vespiquen","count":1}]}</v>
       </c>
       <c r="O220" t="str">
         <v/>
@@ -10744,10 +10744,10 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v/>
+        <v>Challenge 42</v>
       </c>
       <c r="B221" t="str">
-        <v/>
+        <v>Challenge 43</v>
       </c>
       <c r="C221" t="str">
         <v>Route 12</v>
@@ -10762,7 +10762,7 @@
         <v>50-51</v>
       </c>
       <c r="G221" t="str">
-        <v>53-58</v>
+        <v>54-59</v>
       </c>
       <c r="H221" s="1">
         <v>0.1429</v>
@@ -10780,10 +10780,10 @@
         <v>Yes</v>
       </c>
       <c r="M221" t="str">
-        <v/>
+        <v>Route 9</v>
       </c>
       <c r="N221" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Vespiquen","count":1}]}</v>
       </c>
       <c r="O221" t="str">
         <v/>
@@ -10791,10 +10791,10 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v/>
+        <v>Challenge 42</v>
       </c>
       <c r="B222" t="str">
-        <v/>
+        <v>Challenge 43</v>
       </c>
       <c r="C222" t="str">
         <v>Route 12</v>
@@ -10809,7 +10809,7 @@
         <v>50-51</v>
       </c>
       <c r="G222" t="str">
-        <v>53-58</v>
+        <v>54-59</v>
       </c>
       <c r="H222" s="1">
         <v>0.1429</v>
@@ -10827,10 +10827,10 @@
         <v>Yes</v>
       </c>
       <c r="M222" t="str">
-        <v/>
+        <v>Route 9</v>
       </c>
       <c r="N222" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Vespiquen","count":1}]}</v>
       </c>
       <c r="O222" t="str">
         <v/>
@@ -10838,10 +10838,10 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v/>
+        <v>Challenge 42</v>
       </c>
       <c r="B223" t="str">
-        <v/>
+        <v>Challenge 43</v>
       </c>
       <c r="C223" t="str">
         <v>Route 12</v>
@@ -10856,7 +10856,7 @@
         <v>50-51</v>
       </c>
       <c r="G223" t="str">
-        <v>53-58</v>
+        <v>54-59</v>
       </c>
       <c r="H223" s="1">
         <v>0.1429</v>
@@ -10874,10 +10874,10 @@
         <v>Yes</v>
       </c>
       <c r="M223" t="str">
-        <v/>
+        <v>Route 9</v>
       </c>
       <c r="N223" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Vespiquen","count":1}]}</v>
       </c>
       <c r="O223" t="str">
         <v/>
@@ -10885,10 +10885,10 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v/>
+        <v>Challenge 42</v>
       </c>
       <c r="B224" t="str">
-        <v/>
+        <v>Challenge 43</v>
       </c>
       <c r="C224" t="str">
         <v>Route 12</v>
@@ -10903,7 +10903,7 @@
         <v>50-51</v>
       </c>
       <c r="G224" t="str">
-        <v>53-58</v>
+        <v>54-59</v>
       </c>
       <c r="H224" s="1">
         <v>0.1429</v>
@@ -10921,10 +10921,10 @@
         <v>Yes</v>
       </c>
       <c r="M224" t="str">
-        <v/>
+        <v>Route 9</v>
       </c>
       <c r="N224" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Vespiquen","count":1}]}</v>
       </c>
       <c r="O224" t="str">
         <v/>
@@ -10932,10 +10932,10 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v/>
+        <v>Challenge 42</v>
       </c>
       <c r="B225" t="str">
-        <v/>
+        <v>Challenge 43</v>
       </c>
       <c r="C225" t="str">
         <v>Route 12</v>
@@ -10950,7 +10950,7 @@
         <v>50-51</v>
       </c>
       <c r="G225" t="str">
-        <v>53-58</v>
+        <v>54-59</v>
       </c>
       <c r="H225" s="1">
         <v>0.1429</v>
@@ -10968,10 +10968,10 @@
         <v>Yes</v>
       </c>
       <c r="M225" t="str">
-        <v/>
+        <v>Route 9</v>
       </c>
       <c r="N225" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Vespiquen","count":1}]}</v>
       </c>
       <c r="O225" t="str">
         <v/>
@@ -10997,7 +10997,7 @@
         <v>51-52</v>
       </c>
       <c r="G226" t="str">
-        <v>55-60</v>
+        <v>56-61</v>
       </c>
       <c r="H226" s="1">
         <v>0.1665</v>
@@ -11026,10 +11026,10 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v/>
+        <v>Challenge 43</v>
       </c>
       <c r="B227" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="C227" t="str">
         <v>Route 9</v>
@@ -11044,7 +11044,7 @@
         <v>51-52</v>
       </c>
       <c r="G227" t="str">
-        <v>55-60</v>
+        <v>56-61</v>
       </c>
       <c r="H227" s="1">
         <v>0.1667</v>
@@ -11062,10 +11062,10 @@
         <v>Yes</v>
       </c>
       <c r="M227" t="str">
-        <v/>
+        <v>Humilau City</v>
       </c>
       <c r="N227" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Gigalith","count":1}]}</v>
       </c>
       <c r="O227" t="str">
         <v/>
@@ -11073,10 +11073,10 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v/>
+        <v>Challenge 43</v>
       </c>
       <c r="B228" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="C228" t="str">
         <v>Route 9</v>
@@ -11091,7 +11091,7 @@
         <v>51-52</v>
       </c>
       <c r="G228" t="str">
-        <v>55-60</v>
+        <v>56-61</v>
       </c>
       <c r="H228" s="1">
         <v>0.1667</v>
@@ -11109,10 +11109,10 @@
         <v>Yes</v>
       </c>
       <c r="M228" t="str">
-        <v/>
+        <v>Humilau City</v>
       </c>
       <c r="N228" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Gigalith","count":1}]}</v>
       </c>
       <c r="O228" t="str">
         <v/>
@@ -11120,10 +11120,10 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v/>
+        <v>Challenge 43</v>
       </c>
       <c r="B229" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="C229" t="str">
         <v>Route 9</v>
@@ -11138,7 +11138,7 @@
         <v>51-52</v>
       </c>
       <c r="G229" t="str">
-        <v>55-60</v>
+        <v>56-61</v>
       </c>
       <c r="H229" s="1">
         <v>0.1667</v>
@@ -11156,10 +11156,10 @@
         <v>Yes</v>
       </c>
       <c r="M229" t="str">
-        <v/>
+        <v>Humilau City</v>
       </c>
       <c r="N229" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Gigalith","count":1}]}</v>
       </c>
       <c r="O229" t="str">
         <v/>
@@ -11167,10 +11167,10 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v/>
+        <v>Challenge 43</v>
       </c>
       <c r="B230" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="C230" t="str">
         <v>Route 9</v>
@@ -11185,7 +11185,7 @@
         <v>51-52</v>
       </c>
       <c r="G230" t="str">
-        <v>55-60</v>
+        <v>56-61</v>
       </c>
       <c r="H230" s="1">
         <v>0.1667</v>
@@ -11203,10 +11203,10 @@
         <v>Yes</v>
       </c>
       <c r="M230" t="str">
-        <v/>
+        <v>Humilau City</v>
       </c>
       <c r="N230" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Gigalith","count":1}]}</v>
       </c>
       <c r="O230" t="str">
         <v/>
@@ -11214,10 +11214,10 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v/>
+        <v>Challenge 43</v>
       </c>
       <c r="B231" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="C231" t="str">
         <v>Route 9</v>
@@ -11232,7 +11232,7 @@
         <v>51-52</v>
       </c>
       <c r="G231" t="str">
-        <v>55-60</v>
+        <v>56-61</v>
       </c>
       <c r="H231" s="1">
         <v>0.1667</v>
@@ -11250,10 +11250,10 @@
         <v>Yes</v>
       </c>
       <c r="M231" t="str">
-        <v/>
+        <v>Humilau City</v>
       </c>
       <c r="N231" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Gigalith","count":1}]}</v>
       </c>
       <c r="O231" t="str">
         <v/>
@@ -11326,7 +11326,7 @@
         <v>53-54</v>
       </c>
       <c r="G233" t="str">
-        <v>58-63</v>
+        <v>59-64</v>
       </c>
       <c r="H233" s="1">
         <v>0.1</v>
@@ -11355,10 +11355,10 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v/>
+        <v>Challenge 45</v>
       </c>
       <c r="B234" t="str">
-        <v/>
+        <v>Challenge 46</v>
       </c>
       <c r="C234" t="str">
         <v>Humilau Sea</v>
@@ -11373,7 +11373,7 @@
         <v>53-54</v>
       </c>
       <c r="G234" t="str">
-        <v>58-63</v>
+        <v>59-64</v>
       </c>
       <c r="H234" s="1">
         <v>0.1</v>
@@ -11391,10 +11391,10 @@
         <v>No</v>
       </c>
       <c r="M234" t="str">
-        <v/>
+        <v>Humilau Gym</v>
       </c>
       <c r="N234" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Dewgong","count":1}]}</v>
       </c>
       <c r="O234" t="str">
         <v/>
@@ -11402,10 +11402,10 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v/>
+        <v>Challenge 45</v>
       </c>
       <c r="B235" t="str">
-        <v/>
+        <v>Challenge 46</v>
       </c>
       <c r="C235" t="str">
         <v>Humilau Sea</v>
@@ -11420,7 +11420,7 @@
         <v>53-54</v>
       </c>
       <c r="G235" t="str">
-        <v>58-63</v>
+        <v>59-64</v>
       </c>
       <c r="H235" s="1">
         <v>0.1</v>
@@ -11438,10 +11438,10 @@
         <v>No</v>
       </c>
       <c r="M235" t="str">
-        <v/>
+        <v>Humilau Gym</v>
       </c>
       <c r="N235" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Dewgong","count":1}]}</v>
       </c>
       <c r="O235" t="str">
         <v/>
@@ -11449,10 +11449,10 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v/>
+        <v>Challenge 45</v>
       </c>
       <c r="B236" t="str">
-        <v/>
+        <v>Challenge 46</v>
       </c>
       <c r="C236" t="str">
         <v>Humilau Sea</v>
@@ -11467,7 +11467,7 @@
         <v>53-54</v>
       </c>
       <c r="G236" t="str">
-        <v>58-63</v>
+        <v>59-64</v>
       </c>
       <c r="H236" s="1">
         <v>0.1</v>
@@ -11485,10 +11485,10 @@
         <v>No</v>
       </c>
       <c r="M236" t="str">
-        <v/>
+        <v>Humilau Gym</v>
       </c>
       <c r="N236" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Dewgong","count":1}]}</v>
       </c>
       <c r="O236" t="str">
         <v/>
@@ -11496,10 +11496,10 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v/>
+        <v>Challenge 45</v>
       </c>
       <c r="B237" t="str">
-        <v/>
+        <v>Challenge 46</v>
       </c>
       <c r="C237" t="str">
         <v>Humilau Sea</v>
@@ -11514,7 +11514,7 @@
         <v>53-54</v>
       </c>
       <c r="G237" t="str">
-        <v>58-63</v>
+        <v>59-64</v>
       </c>
       <c r="H237" s="1">
         <v>0.1</v>
@@ -11532,10 +11532,10 @@
         <v>No</v>
       </c>
       <c r="M237" t="str">
-        <v/>
+        <v>Humilau Gym</v>
       </c>
       <c r="N237" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Dewgong","count":1}]}</v>
       </c>
       <c r="O237" t="str">
         <v/>
@@ -11543,10 +11543,10 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v/>
+        <v>Challenge 45</v>
       </c>
       <c r="B238" t="str">
-        <v/>
+        <v>Challenge 46</v>
       </c>
       <c r="C238" t="str">
         <v>Humilau Sea</v>
@@ -11561,7 +11561,7 @@
         <v>53-54</v>
       </c>
       <c r="G238" t="str">
-        <v>58-63</v>
+        <v>59-64</v>
       </c>
       <c r="H238" s="1">
         <v>0.1</v>
@@ -11579,10 +11579,10 @@
         <v>No</v>
       </c>
       <c r="M238" t="str">
-        <v/>
+        <v>Humilau Gym</v>
       </c>
       <c r="N238" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Dewgong","count":1}]}</v>
       </c>
       <c r="O238" t="str">
         <v/>
@@ -11590,10 +11590,10 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v/>
+        <v>Challenge 45</v>
       </c>
       <c r="B239" t="str">
-        <v/>
+        <v>Challenge 46</v>
       </c>
       <c r="C239" t="str">
         <v>Humilau Sea</v>
@@ -11608,7 +11608,7 @@
         <v>53-54</v>
       </c>
       <c r="G239" t="str">
-        <v>58-63</v>
+        <v>59-64</v>
       </c>
       <c r="H239" s="1">
         <v>0.1</v>
@@ -11626,10 +11626,10 @@
         <v>No</v>
       </c>
       <c r="M239" t="str">
-        <v/>
+        <v>Humilau Gym</v>
       </c>
       <c r="N239" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Dewgong","count":1}]}</v>
       </c>
       <c r="O239" t="str">
         <v/>
@@ -11637,10 +11637,10 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v/>
+        <v>Challenge 45</v>
       </c>
       <c r="B240" t="str">
-        <v/>
+        <v>Challenge 46</v>
       </c>
       <c r="C240" t="str">
         <v>Humilau Sea</v>
@@ -11655,7 +11655,7 @@
         <v>53-54</v>
       </c>
       <c r="G240" t="str">
-        <v>58-63</v>
+        <v>59-64</v>
       </c>
       <c r="H240" s="1">
         <v>0.1</v>
@@ -11673,10 +11673,10 @@
         <v>No</v>
       </c>
       <c r="M240" t="str">
-        <v/>
+        <v>Humilau Gym</v>
       </c>
       <c r="N240" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Dewgong","count":1}]}</v>
       </c>
       <c r="O240" t="str">
         <v/>
@@ -11684,10 +11684,10 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v/>
+        <v>Challenge 45</v>
       </c>
       <c r="B241" t="str">
-        <v/>
+        <v>Challenge 46</v>
       </c>
       <c r="C241" t="str">
         <v>Humilau Sea</v>
@@ -11702,7 +11702,7 @@
         <v>53-54</v>
       </c>
       <c r="G241" t="str">
-        <v>58-63</v>
+        <v>59-64</v>
       </c>
       <c r="H241" s="1">
         <v>0.1</v>
@@ -11720,10 +11720,10 @@
         <v>No</v>
       </c>
       <c r="M241" t="str">
-        <v/>
+        <v>Humilau Gym</v>
       </c>
       <c r="N241" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Dewgong","count":1}]}</v>
       </c>
       <c r="O241" t="str">
         <v/>
@@ -11731,10 +11731,10 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v/>
+        <v>Challenge 45</v>
       </c>
       <c r="B242" t="str">
-        <v/>
+        <v>Challenge 46</v>
       </c>
       <c r="C242" t="str">
         <v>Humilau Sea</v>
@@ -11749,7 +11749,7 @@
         <v>53-54</v>
       </c>
       <c r="G242" t="str">
-        <v>58-63</v>
+        <v>59-64</v>
       </c>
       <c r="H242" s="1">
         <v>0.1</v>
@@ -11767,10 +11767,10 @@
         <v>No</v>
       </c>
       <c r="M242" t="str">
-        <v/>
+        <v>Humilau Gym</v>
       </c>
       <c r="N242" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Dewgong","count":1}]}</v>
       </c>
       <c r="O242" t="str">
         <v/>
@@ -11843,7 +11843,7 @@
         <v>56-57</v>
       </c>
       <c r="G244" t="str">
-        <v>60-66</v>
+        <v>62-68</v>
       </c>
       <c r="H244" s="1">
         <v>0.1426</v>
@@ -11872,10 +11872,10 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v/>
+        <v>Challenge 47</v>
       </c>
       <c r="B245" t="str">
-        <v/>
+        <v>Challenge 48</v>
       </c>
       <c r="C245" t="str">
         <v>Route 21</v>
@@ -11890,7 +11890,7 @@
         <v>56-57</v>
       </c>
       <c r="G245" t="str">
-        <v>60-66</v>
+        <v>62-68</v>
       </c>
       <c r="H245" s="1">
         <v>0.1429</v>
@@ -11908,10 +11908,10 @@
         <v>Yes</v>
       </c>
       <c r="M245" t="str">
-        <v/>
+        <v>Seaside Cave</v>
       </c>
       <c r="N245" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Crawdaunt","count":1}]}</v>
       </c>
       <c r="O245" t="str">
         <v/>
@@ -11919,10 +11919,10 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v/>
+        <v>Challenge 47</v>
       </c>
       <c r="B246" t="str">
-        <v/>
+        <v>Challenge 48</v>
       </c>
       <c r="C246" t="str">
         <v>Route 21</v>
@@ -11937,7 +11937,7 @@
         <v>56-57</v>
       </c>
       <c r="G246" t="str">
-        <v>60-66</v>
+        <v>62-68</v>
       </c>
       <c r="H246" s="1">
         <v>0.1429</v>
@@ -11955,10 +11955,10 @@
         <v>Yes</v>
       </c>
       <c r="M246" t="str">
-        <v/>
+        <v>Seaside Cave</v>
       </c>
       <c r="N246" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Crawdaunt","count":1}]}</v>
       </c>
       <c r="O246" t="str">
         <v/>
@@ -11966,10 +11966,10 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v/>
+        <v>Challenge 47</v>
       </c>
       <c r="B247" t="str">
-        <v/>
+        <v>Challenge 48</v>
       </c>
       <c r="C247" t="str">
         <v>Route 21</v>
@@ -11984,7 +11984,7 @@
         <v>56-57</v>
       </c>
       <c r="G247" t="str">
-        <v>60-66</v>
+        <v>62-68</v>
       </c>
       <c r="H247" s="1">
         <v>0.1429</v>
@@ -12002,10 +12002,10 @@
         <v>Yes</v>
       </c>
       <c r="M247" t="str">
-        <v/>
+        <v>Seaside Cave</v>
       </c>
       <c r="N247" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Crawdaunt","count":1}]}</v>
       </c>
       <c r="O247" t="str">
         <v/>
@@ -12013,10 +12013,10 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v/>
+        <v>Challenge 47</v>
       </c>
       <c r="B248" t="str">
-        <v/>
+        <v>Challenge 48</v>
       </c>
       <c r="C248" t="str">
         <v>Route 21</v>
@@ -12031,7 +12031,7 @@
         <v>56-57</v>
       </c>
       <c r="G248" t="str">
-        <v>60-66</v>
+        <v>62-68</v>
       </c>
       <c r="H248" s="1">
         <v>0.1429</v>
@@ -12049,10 +12049,10 @@
         <v>Yes</v>
       </c>
       <c r="M248" t="str">
-        <v/>
+        <v>Seaside Cave</v>
       </c>
       <c r="N248" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Crawdaunt","count":1}]}</v>
       </c>
       <c r="O248" t="str">
         <v/>
@@ -12060,10 +12060,10 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v/>
+        <v>Challenge 47</v>
       </c>
       <c r="B249" t="str">
-        <v/>
+        <v>Challenge 48</v>
       </c>
       <c r="C249" t="str">
         <v>Route 21</v>
@@ -12078,7 +12078,7 @@
         <v>56-57</v>
       </c>
       <c r="G249" t="str">
-        <v>60-66</v>
+        <v>62-68</v>
       </c>
       <c r="H249" s="1">
         <v>0.1429</v>
@@ -12096,10 +12096,10 @@
         <v>Yes</v>
       </c>
       <c r="M249" t="str">
-        <v/>
+        <v>Seaside Cave</v>
       </c>
       <c r="N249" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Crawdaunt","count":1}]}</v>
       </c>
       <c r="O249" t="str">
         <v/>
@@ -12107,10 +12107,10 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v/>
+        <v>Challenge 47</v>
       </c>
       <c r="B250" t="str">
-        <v/>
+        <v>Challenge 48</v>
       </c>
       <c r="C250" t="str">
         <v>Route 21</v>
@@ -12125,7 +12125,7 @@
         <v>56-57</v>
       </c>
       <c r="G250" t="str">
-        <v>60-66</v>
+        <v>62-68</v>
       </c>
       <c r="H250" s="1">
         <v>0.1429</v>
@@ -12143,10 +12143,10 @@
         <v>Yes</v>
       </c>
       <c r="M250" t="str">
-        <v/>
+        <v>Seaside Cave</v>
       </c>
       <c r="N250" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Crawdaunt","count":1}]}</v>
       </c>
       <c r="O250" t="str">
         <v/>
@@ -12172,7 +12172,7 @@
         <v>57-58</v>
       </c>
       <c r="G251" t="str">
-        <v>62-68</v>
+        <v>63-69</v>
       </c>
       <c r="H251" s="1">
         <v>0.1665</v>
@@ -12201,10 +12201,10 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v/>
+        <v>Challenge 48</v>
       </c>
       <c r="B252" t="str">
-        <v/>
+        <v>Challenge 49</v>
       </c>
       <c r="C252" t="str">
         <v>Seaside Cave</v>
@@ -12219,7 +12219,7 @@
         <v>57-58</v>
       </c>
       <c r="G252" t="str">
-        <v>62-68</v>
+        <v>63-69</v>
       </c>
       <c r="H252" s="1">
         <v>0.1667</v>
@@ -12237,10 +12237,10 @@
         <v>Yes</v>
       </c>
       <c r="M252" t="str">
-        <v/>
+        <v>Route 22</v>
       </c>
       <c r="N252" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Carracosta","count":1}]}</v>
       </c>
       <c r="O252" t="str">
         <v/>
@@ -12248,10 +12248,10 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v/>
+        <v>Challenge 48</v>
       </c>
       <c r="B253" t="str">
-        <v/>
+        <v>Challenge 49</v>
       </c>
       <c r="C253" t="str">
         <v>Seaside Cave</v>
@@ -12266,7 +12266,7 @@
         <v>57-58</v>
       </c>
       <c r="G253" t="str">
-        <v>62-68</v>
+        <v>63-69</v>
       </c>
       <c r="H253" s="1">
         <v>0.1667</v>
@@ -12284,10 +12284,10 @@
         <v>Yes</v>
       </c>
       <c r="M253" t="str">
-        <v/>
+        <v>Route 22</v>
       </c>
       <c r="N253" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Carracosta","count":1}]}</v>
       </c>
       <c r="O253" t="str">
         <v/>
@@ -12295,10 +12295,10 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v/>
+        <v>Challenge 48</v>
       </c>
       <c r="B254" t="str">
-        <v/>
+        <v>Challenge 49</v>
       </c>
       <c r="C254" t="str">
         <v>Seaside Cave</v>
@@ -12313,7 +12313,7 @@
         <v>57-58</v>
       </c>
       <c r="G254" t="str">
-        <v>62-68</v>
+        <v>63-69</v>
       </c>
       <c r="H254" s="1">
         <v>0.1667</v>
@@ -12331,10 +12331,10 @@
         <v>Yes</v>
       </c>
       <c r="M254" t="str">
-        <v/>
+        <v>Route 22</v>
       </c>
       <c r="N254" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Carracosta","count":1}]}</v>
       </c>
       <c r="O254" t="str">
         <v/>
@@ -12342,10 +12342,10 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v/>
+        <v>Challenge 48</v>
       </c>
       <c r="B255" t="str">
-        <v/>
+        <v>Challenge 49</v>
       </c>
       <c r="C255" t="str">
         <v>Seaside Cave</v>
@@ -12360,7 +12360,7 @@
         <v>57-58</v>
       </c>
       <c r="G255" t="str">
-        <v>62-68</v>
+        <v>63-69</v>
       </c>
       <c r="H255" s="1">
         <v>0.1667</v>
@@ -12378,10 +12378,10 @@
         <v>Yes</v>
       </c>
       <c r="M255" t="str">
-        <v/>
+        <v>Route 22</v>
       </c>
       <c r="N255" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Carracosta","count":1}]}</v>
       </c>
       <c r="O255" t="str">
         <v/>
@@ -12389,10 +12389,10 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v/>
+        <v>Challenge 48</v>
       </c>
       <c r="B256" t="str">
-        <v/>
+        <v>Challenge 49</v>
       </c>
       <c r="C256" t="str">
         <v>Seaside Cave</v>
@@ -12407,7 +12407,7 @@
         <v>57-58</v>
       </c>
       <c r="G256" t="str">
-        <v>62-68</v>
+        <v>63-69</v>
       </c>
       <c r="H256" s="1">
         <v>0.1667</v>
@@ -12425,10 +12425,10 @@
         <v>Yes</v>
       </c>
       <c r="M256" t="str">
-        <v/>
+        <v>Route 22</v>
       </c>
       <c r="N256" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Carracosta","count":1}]}</v>
       </c>
       <c r="O256" t="str">
         <v/>
@@ -12454,7 +12454,7 @@
         <v>58-59</v>
       </c>
       <c r="G257" t="str">
-        <v>63-69</v>
+        <v>65-71</v>
       </c>
       <c r="H257" s="1">
         <v>0.25</v>
@@ -12483,10 +12483,10 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v/>
+        <v>Challenge 49</v>
       </c>
       <c r="B258" t="str">
-        <v/>
+        <v>Challenge 50</v>
       </c>
       <c r="C258" t="str">
         <v>Route 22</v>
@@ -12501,7 +12501,7 @@
         <v>58-59</v>
       </c>
       <c r="G258" t="str">
-        <v>63-69</v>
+        <v>65-71</v>
       </c>
       <c r="H258" s="1">
         <v>0.25</v>
@@ -12519,10 +12519,10 @@
         <v>No</v>
       </c>
       <c r="M258" t="str">
-        <v/>
+        <v>P2 Laboratory</v>
       </c>
       <c r="N258" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Amoonguss","count":1}]}</v>
       </c>
       <c r="O258" t="str">
         <v/>
@@ -12530,10 +12530,10 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v/>
+        <v>Challenge 49</v>
       </c>
       <c r="B259" t="str">
-        <v/>
+        <v>Challenge 50</v>
       </c>
       <c r="C259" t="str">
         <v>Route 22</v>
@@ -12548,7 +12548,7 @@
         <v>58-59</v>
       </c>
       <c r="G259" t="str">
-        <v>63-69</v>
+        <v>65-71</v>
       </c>
       <c r="H259" s="1">
         <v>0.25</v>
@@ -12566,10 +12566,10 @@
         <v>No</v>
       </c>
       <c r="M259" t="str">
-        <v/>
+        <v>P2 Laboratory</v>
       </c>
       <c r="N259" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Amoonguss","count":1}]}</v>
       </c>
       <c r="O259" t="str">
         <v/>
@@ -12577,10 +12577,10 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v/>
+        <v>Challenge 49</v>
       </c>
       <c r="B260" t="str">
-        <v/>
+        <v>Challenge 50</v>
       </c>
       <c r="C260" t="str">
         <v>Route 22</v>
@@ -12595,7 +12595,7 @@
         <v>58-59</v>
       </c>
       <c r="G260" t="str">
-        <v>63-69</v>
+        <v>65-71</v>
       </c>
       <c r="H260" s="1">
         <v>0.25</v>
@@ -12613,10 +12613,10 @@
         <v>No</v>
       </c>
       <c r="M260" t="str">
-        <v/>
+        <v>P2 Laboratory</v>
       </c>
       <c r="N260" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Amoonguss","count":1}]}</v>
       </c>
       <c r="O260" t="str">
         <v/>
@@ -12642,7 +12642,7 @@
         <v>59-60</v>
       </c>
       <c r="G261" t="str">
-        <v>65-71</v>
+        <v>66-72</v>
       </c>
       <c r="H261" s="1">
         <v>0.25</v>
@@ -12671,10 +12671,10 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v/>
+        <v>Challenge 50</v>
       </c>
       <c r="B262" t="str">
-        <v/>
+        <v>Challenge 51</v>
       </c>
       <c r="C262" t="str">
         <v>P2 Laboratory</v>
@@ -12689,7 +12689,7 @@
         <v>59-60</v>
       </c>
       <c r="G262" t="str">
-        <v>65-71</v>
+        <v>66-72</v>
       </c>
       <c r="H262" s="1">
         <v>0.25</v>
@@ -12707,10 +12707,10 @@
         <v>No</v>
       </c>
       <c r="M262" t="str">
-        <v/>
+        <v>Wellspring Cave</v>
       </c>
       <c r="N262" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Klinklang","count":1}]}</v>
       </c>
       <c r="O262" t="str">
         <v/>
@@ -12718,10 +12718,10 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v/>
+        <v>Challenge 50</v>
       </c>
       <c r="B263" t="str">
-        <v/>
+        <v>Challenge 51</v>
       </c>
       <c r="C263" t="str">
         <v>P2 Laboratory</v>
@@ -12736,7 +12736,7 @@
         <v>59-60</v>
       </c>
       <c r="G263" t="str">
-        <v>65-71</v>
+        <v>66-72</v>
       </c>
       <c r="H263" s="1">
         <v>0.25</v>
@@ -12754,10 +12754,10 @@
         <v>No</v>
       </c>
       <c r="M263" t="str">
-        <v/>
+        <v>Wellspring Cave</v>
       </c>
       <c r="N263" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Klinklang","count":1}]}</v>
       </c>
       <c r="O263" t="str">
         <v/>
@@ -12765,10 +12765,10 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v/>
+        <v>Challenge 50</v>
       </c>
       <c r="B264" t="str">
-        <v/>
+        <v>Challenge 51</v>
       </c>
       <c r="C264" t="str">
         <v>P2 Laboratory</v>
@@ -12783,7 +12783,7 @@
         <v>59-60</v>
       </c>
       <c r="G264" t="str">
-        <v>65-71</v>
+        <v>66-72</v>
       </c>
       <c r="H264" s="1">
         <v>0.25</v>
@@ -12801,10 +12801,10 @@
         <v>No</v>
       </c>
       <c r="M264" t="str">
-        <v/>
+        <v>Wellspring Cave</v>
       </c>
       <c r="N264" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Klinklang","count":1}]}</v>
       </c>
       <c r="O264" t="str">
         <v/>
@@ -12830,7 +12830,7 @@
         <v>60-61</v>
       </c>
       <c r="G265" t="str">
-        <v>66-72</v>
+        <v>67-73</v>
       </c>
       <c r="H265" s="1">
         <v>0.3334</v>
@@ -12859,10 +12859,10 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v/>
+        <v>Challenge 51</v>
       </c>
       <c r="B266" t="str">
-        <v/>
+        <v>Challenge 52</v>
       </c>
       <c r="C266" t="str">
         <v>Wellspring Cave</v>
@@ -12877,7 +12877,7 @@
         <v>60-61</v>
       </c>
       <c r="G266" t="str">
-        <v>66-72</v>
+        <v>67-73</v>
       </c>
       <c r="H266" s="1">
         <v>0.3333</v>
@@ -12895,10 +12895,10 @@
         <v>No</v>
       </c>
       <c r="M266" t="str">
-        <v/>
+        <v>Giant Chasm</v>
       </c>
       <c r="N266" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Grimer","count":1}]}</v>
       </c>
       <c r="O266" t="str">
         <v/>
@@ -12906,10 +12906,10 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v/>
+        <v>Challenge 51</v>
       </c>
       <c r="B267" t="str">
-        <v/>
+        <v>Challenge 52</v>
       </c>
       <c r="C267" t="str">
         <v>Wellspring Cave</v>
@@ -12924,7 +12924,7 @@
         <v>60-61</v>
       </c>
       <c r="G267" t="str">
-        <v>66-72</v>
+        <v>67-73</v>
       </c>
       <c r="H267" s="1">
         <v>0.3333</v>
@@ -12942,10 +12942,10 @@
         <v>No</v>
       </c>
       <c r="M267" t="str">
-        <v/>
+        <v>Giant Chasm</v>
       </c>
       <c r="N267" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Grimer","count":1}]}</v>
       </c>
       <c r="O267" t="str">
         <v/>
@@ -12971,7 +12971,7 @@
         <v>62-63</v>
       </c>
       <c r="G268" t="str">
-        <v>68-74</v>
+        <v>69-75</v>
       </c>
       <c r="H268" s="1">
         <v>0.091</v>
@@ -13000,10 +13000,10 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v/>
+        <v>Challenge 52</v>
       </c>
       <c r="B269" t="str">
-        <v/>
+        <v>Challenge 53</v>
       </c>
       <c r="C269" t="str">
         <v>Giant Chasm</v>
@@ -13018,7 +13018,7 @@
         <v>62-63</v>
       </c>
       <c r="G269" t="str">
-        <v>68-74</v>
+        <v>69-75</v>
       </c>
       <c r="H269" s="1">
         <v>0.0909</v>
@@ -13036,10 +13036,10 @@
         <v>Yes</v>
       </c>
       <c r="M269" t="str">
-        <v/>
+        <v>Route 23</v>
       </c>
       <c r="N269" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Delibird","count":1}]}</v>
       </c>
       <c r="O269" t="str">
         <v/>
@@ -13047,10 +13047,10 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v/>
+        <v>Challenge 52</v>
       </c>
       <c r="B270" t="str">
-        <v/>
+        <v>Challenge 53</v>
       </c>
       <c r="C270" t="str">
         <v>Giant Chasm</v>
@@ -13065,7 +13065,7 @@
         <v>62-63</v>
       </c>
       <c r="G270" t="str">
-        <v>68-74</v>
+        <v>69-75</v>
       </c>
       <c r="H270" s="1">
         <v>0.0909</v>
@@ -13083,10 +13083,10 @@
         <v>Yes</v>
       </c>
       <c r="M270" t="str">
-        <v/>
+        <v>Route 23</v>
       </c>
       <c r="N270" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Delibird","count":1}]}</v>
       </c>
       <c r="O270" t="str">
         <v/>
@@ -13094,10 +13094,10 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v/>
+        <v>Challenge 52</v>
       </c>
       <c r="B271" t="str">
-        <v/>
+        <v>Challenge 53</v>
       </c>
       <c r="C271" t="str">
         <v>Giant Chasm</v>
@@ -13112,7 +13112,7 @@
         <v>62-63</v>
       </c>
       <c r="G271" t="str">
-        <v>68-74</v>
+        <v>69-75</v>
       </c>
       <c r="H271" s="1">
         <v>0.0909</v>
@@ -13130,10 +13130,10 @@
         <v>Yes</v>
       </c>
       <c r="M271" t="str">
-        <v/>
+        <v>Route 23</v>
       </c>
       <c r="N271" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Delibird","count":1}]}</v>
       </c>
       <c r="O271" t="str">
         <v/>
@@ -13141,10 +13141,10 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v/>
+        <v>Challenge 52</v>
       </c>
       <c r="B272" t="str">
-        <v/>
+        <v>Challenge 53</v>
       </c>
       <c r="C272" t="str">
         <v>Giant Chasm</v>
@@ -13159,7 +13159,7 @@
         <v>62-63</v>
       </c>
       <c r="G272" t="str">
-        <v>68-74</v>
+        <v>69-75</v>
       </c>
       <c r="H272" s="1">
         <v>0.0909</v>
@@ -13177,10 +13177,10 @@
         <v>Yes</v>
       </c>
       <c r="M272" t="str">
-        <v/>
+        <v>Route 23</v>
       </c>
       <c r="N272" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Delibird","count":1}]}</v>
       </c>
       <c r="O272" t="str">
         <v/>
@@ -13188,10 +13188,10 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v/>
+        <v>Challenge 52</v>
       </c>
       <c r="B273" t="str">
-        <v/>
+        <v>Challenge 53</v>
       </c>
       <c r="C273" t="str">
         <v>Giant Chasm</v>
@@ -13206,7 +13206,7 @@
         <v>62-63</v>
       </c>
       <c r="G273" t="str">
-        <v>68-74</v>
+        <v>69-75</v>
       </c>
       <c r="H273" s="1">
         <v>0.0909</v>
@@ -13224,10 +13224,10 @@
         <v>Yes</v>
       </c>
       <c r="M273" t="str">
-        <v/>
+        <v>Route 23</v>
       </c>
       <c r="N273" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Delibird","count":1}]}</v>
       </c>
       <c r="O273" t="str">
         <v/>
@@ -13235,10 +13235,10 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v/>
+        <v>Challenge 52</v>
       </c>
       <c r="B274" t="str">
-        <v/>
+        <v>Challenge 53</v>
       </c>
       <c r="C274" t="str">
         <v>Giant Chasm</v>
@@ -13253,7 +13253,7 @@
         <v>62-63</v>
       </c>
       <c r="G274" t="str">
-        <v>68-74</v>
+        <v>69-75</v>
       </c>
       <c r="H274" s="1">
         <v>0.0909</v>
@@ -13271,10 +13271,10 @@
         <v>Yes</v>
       </c>
       <c r="M274" t="str">
-        <v/>
+        <v>Route 23</v>
       </c>
       <c r="N274" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Delibird","count":1}]}</v>
       </c>
       <c r="O274" t="str">
         <v/>
@@ -13282,10 +13282,10 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v/>
+        <v>Challenge 52</v>
       </c>
       <c r="B275" t="str">
-        <v/>
+        <v>Challenge 53</v>
       </c>
       <c r="C275" t="str">
         <v>Giant Chasm</v>
@@ -13300,7 +13300,7 @@
         <v>62-63</v>
       </c>
       <c r="G275" t="str">
-        <v>68-74</v>
+        <v>69-75</v>
       </c>
       <c r="H275" s="1">
         <v>0.0909</v>
@@ -13318,10 +13318,10 @@
         <v>Yes</v>
       </c>
       <c r="M275" t="str">
-        <v/>
+        <v>Route 23</v>
       </c>
       <c r="N275" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Delibird","count":1}]}</v>
       </c>
       <c r="O275" t="str">
         <v/>
@@ -13329,10 +13329,10 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v/>
+        <v>Challenge 52</v>
       </c>
       <c r="B276" t="str">
-        <v/>
+        <v>Challenge 53</v>
       </c>
       <c r="C276" t="str">
         <v>Giant Chasm</v>
@@ -13347,7 +13347,7 @@
         <v>62-63</v>
       </c>
       <c r="G276" t="str">
-        <v>68-74</v>
+        <v>69-75</v>
       </c>
       <c r="H276" s="1">
         <v>0.0909</v>
@@ -13365,10 +13365,10 @@
         <v>Yes</v>
       </c>
       <c r="M276" t="str">
-        <v/>
+        <v>Route 23</v>
       </c>
       <c r="N276" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Delibird","count":1}]}</v>
       </c>
       <c r="O276" t="str">
         <v/>
@@ -13376,10 +13376,10 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v/>
+        <v>Challenge 52</v>
       </c>
       <c r="B277" t="str">
-        <v/>
+        <v>Challenge 53</v>
       </c>
       <c r="C277" t="str">
         <v>Giant Chasm</v>
@@ -13394,7 +13394,7 @@
         <v>62-63</v>
       </c>
       <c r="G277" t="str">
-        <v>68-74</v>
+        <v>69-75</v>
       </c>
       <c r="H277" s="1">
         <v>0.0909</v>
@@ -13412,10 +13412,10 @@
         <v>Yes</v>
       </c>
       <c r="M277" t="str">
-        <v/>
+        <v>Route 23</v>
       </c>
       <c r="N277" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Delibird","count":1}]}</v>
       </c>
       <c r="O277" t="str">
         <v/>
@@ -13423,10 +13423,10 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v/>
+        <v>Challenge 52</v>
       </c>
       <c r="B278" t="str">
-        <v/>
+        <v>Challenge 53</v>
       </c>
       <c r="C278" t="str">
         <v>Giant Chasm</v>
@@ -13441,7 +13441,7 @@
         <v>62-63</v>
       </c>
       <c r="G278" t="str">
-        <v>68-74</v>
+        <v>69-75</v>
       </c>
       <c r="H278" s="1">
         <v>0.0909</v>
@@ -13459,10 +13459,10 @@
         <v>Yes</v>
       </c>
       <c r="M278" t="str">
-        <v/>
+        <v>Route 23</v>
       </c>
       <c r="N278" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Delibird","count":1}]}</v>
       </c>
       <c r="O278" t="str">
         <v/>
@@ -13488,7 +13488,7 @@
         <v>63-64</v>
       </c>
       <c r="G279" t="str">
-        <v>69-75</v>
+        <v>70-77</v>
       </c>
       <c r="H279" s="1">
         <v>0.1112</v>
@@ -13517,10 +13517,10 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v/>
+        <v>Challenge 53</v>
       </c>
       <c r="B280" t="str">
-        <v/>
+        <v>Challenge 54</v>
       </c>
       <c r="C280" t="str">
         <v>Route 23</v>
@@ -13535,7 +13535,7 @@
         <v>63-64</v>
       </c>
       <c r="G280" t="str">
-        <v>69-75</v>
+        <v>70-77</v>
       </c>
       <c r="H280" s="1">
         <v>0.1111</v>
@@ -13553,10 +13553,10 @@
         <v>Yes</v>
       </c>
       <c r="M280" t="str">
-        <v/>
+        <v>Victory Road</v>
       </c>
       <c r="N280" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Sneasel","count":1}]}</v>
       </c>
       <c r="O280" t="str">
         <v/>
@@ -13564,10 +13564,10 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v/>
+        <v>Challenge 53</v>
       </c>
       <c r="B281" t="str">
-        <v/>
+        <v>Challenge 54</v>
       </c>
       <c r="C281" t="str">
         <v>Route 23</v>
@@ -13582,7 +13582,7 @@
         <v>63-64</v>
       </c>
       <c r="G281" t="str">
-        <v>69-75</v>
+        <v>70-77</v>
       </c>
       <c r="H281" s="1">
         <v>0.1111</v>
@@ -13600,10 +13600,10 @@
         <v>Yes</v>
       </c>
       <c r="M281" t="str">
-        <v/>
+        <v>Victory Road</v>
       </c>
       <c r="N281" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Sneasel","count":1}]}</v>
       </c>
       <c r="O281" t="str">
         <v/>
@@ -13611,10 +13611,10 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v/>
+        <v>Challenge 53</v>
       </c>
       <c r="B282" t="str">
-        <v/>
+        <v>Challenge 54</v>
       </c>
       <c r="C282" t="str">
         <v>Route 23</v>
@@ -13629,7 +13629,7 @@
         <v>63-64</v>
       </c>
       <c r="G282" t="str">
-        <v>69-75</v>
+        <v>70-77</v>
       </c>
       <c r="H282" s="1">
         <v>0.1111</v>
@@ -13647,10 +13647,10 @@
         <v>Yes</v>
       </c>
       <c r="M282" t="str">
-        <v/>
+        <v>Victory Road</v>
       </c>
       <c r="N282" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Sneasel","count":1}]}</v>
       </c>
       <c r="O282" t="str">
         <v/>
@@ -13658,10 +13658,10 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v/>
+        <v>Challenge 53</v>
       </c>
       <c r="B283" t="str">
-        <v/>
+        <v>Challenge 54</v>
       </c>
       <c r="C283" t="str">
         <v>Route 23</v>
@@ -13676,7 +13676,7 @@
         <v>63-64</v>
       </c>
       <c r="G283" t="str">
-        <v>69-75</v>
+        <v>70-77</v>
       </c>
       <c r="H283" s="1">
         <v>0.1111</v>
@@ -13694,10 +13694,10 @@
         <v>Yes</v>
       </c>
       <c r="M283" t="str">
-        <v/>
+        <v>Victory Road</v>
       </c>
       <c r="N283" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Sneasel","count":1}]}</v>
       </c>
       <c r="O283" t="str">
         <v/>
@@ -13705,10 +13705,10 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v/>
+        <v>Challenge 53</v>
       </c>
       <c r="B284" t="str">
-        <v/>
+        <v>Challenge 54</v>
       </c>
       <c r="C284" t="str">
         <v>Route 23</v>
@@ -13723,7 +13723,7 @@
         <v>63-64</v>
       </c>
       <c r="G284" t="str">
-        <v>69-75</v>
+        <v>70-77</v>
       </c>
       <c r="H284" s="1">
         <v>0.1111</v>
@@ -13741,10 +13741,10 @@
         <v>Yes</v>
       </c>
       <c r="M284" t="str">
-        <v/>
+        <v>Victory Road</v>
       </c>
       <c r="N284" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Sneasel","count":1}]}</v>
       </c>
       <c r="O284" t="str">
         <v/>
@@ -13752,10 +13752,10 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v/>
+        <v>Challenge 53</v>
       </c>
       <c r="B285" t="str">
-        <v/>
+        <v>Challenge 54</v>
       </c>
       <c r="C285" t="str">
         <v>Route 23</v>
@@ -13770,7 +13770,7 @@
         <v>63-64</v>
       </c>
       <c r="G285" t="str">
-        <v>69-75</v>
+        <v>70-77</v>
       </c>
       <c r="H285" s="1">
         <v>0.1111</v>
@@ -13788,10 +13788,10 @@
         <v>Yes</v>
       </c>
       <c r="M285" t="str">
-        <v/>
+        <v>Victory Road</v>
       </c>
       <c r="N285" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Sneasel","count":1}]}</v>
       </c>
       <c r="O285" t="str">
         <v/>
@@ -13799,10 +13799,10 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v/>
+        <v>Challenge 53</v>
       </c>
       <c r="B286" t="str">
-        <v/>
+        <v>Challenge 54</v>
       </c>
       <c r="C286" t="str">
         <v>Route 23</v>
@@ -13817,7 +13817,7 @@
         <v>63-64</v>
       </c>
       <c r="G286" t="str">
-        <v>69-75</v>
+        <v>70-77</v>
       </c>
       <c r="H286" s="1">
         <v>0.1111</v>
@@ -13835,10 +13835,10 @@
         <v>Yes</v>
       </c>
       <c r="M286" t="str">
-        <v/>
+        <v>Victory Road</v>
       </c>
       <c r="N286" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Sneasel","count":1}]}</v>
       </c>
       <c r="O286" t="str">
         <v/>
@@ -13846,10 +13846,10 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v/>
+        <v>Challenge 53</v>
       </c>
       <c r="B287" t="str">
-        <v/>
+        <v>Challenge 54</v>
       </c>
       <c r="C287" t="str">
         <v>Route 23</v>
@@ -13864,7 +13864,7 @@
         <v>63-64</v>
       </c>
       <c r="G287" t="str">
-        <v>69-75</v>
+        <v>70-77</v>
       </c>
       <c r="H287" s="1">
         <v>0.1111</v>
@@ -13882,10 +13882,10 @@
         <v>Yes</v>
       </c>
       <c r="M287" t="str">
-        <v/>
+        <v>Victory Road</v>
       </c>
       <c r="N287" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Sneasel","count":1}]}</v>
       </c>
       <c r="O287" t="str">
         <v/>
@@ -13911,7 +13911,7 @@
         <v>64-65</v>
       </c>
       <c r="G288" t="str">
-        <v>70-77</v>
+        <v>72-79</v>
       </c>
       <c r="H288" s="1">
         <v>0.1426</v>
@@ -13940,10 +13940,10 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v/>
+        <v>Challenge 54</v>
       </c>
       <c r="B289" t="str">
-        <v/>
+        <v>Challenge 55</v>
       </c>
       <c r="C289" t="str">
         <v>Victory Road</v>
@@ -13958,7 +13958,7 @@
         <v>64-65</v>
       </c>
       <c r="G289" t="str">
-        <v>70-77</v>
+        <v>72-79</v>
       </c>
       <c r="H289" s="1">
         <v>0.1429</v>
@@ -13976,10 +13976,10 @@
         <v>Yes</v>
       </c>
       <c r="M289" t="str">
-        <v/>
+        <v>Unova Pokemon League</v>
       </c>
       <c r="N289" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Golurk","count":1}]}</v>
       </c>
       <c r="O289" t="str">
         <v/>
@@ -13987,10 +13987,10 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v/>
+        <v>Challenge 54</v>
       </c>
       <c r="B290" t="str">
-        <v/>
+        <v>Challenge 55</v>
       </c>
       <c r="C290" t="str">
         <v>Victory Road</v>
@@ -14005,7 +14005,7 @@
         <v>64-65</v>
       </c>
       <c r="G290" t="str">
-        <v>70-77</v>
+        <v>72-79</v>
       </c>
       <c r="H290" s="1">
         <v>0.1429</v>
@@ -14023,10 +14023,10 @@
         <v>Yes</v>
       </c>
       <c r="M290" t="str">
-        <v/>
+        <v>Unova Pokemon League</v>
       </c>
       <c r="N290" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Golurk","count":1}]}</v>
       </c>
       <c r="O290" t="str">
         <v/>
@@ -14034,10 +14034,10 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v/>
+        <v>Challenge 54</v>
       </c>
       <c r="B291" t="str">
-        <v/>
+        <v>Challenge 55</v>
       </c>
       <c r="C291" t="str">
         <v>Victory Road</v>
@@ -14052,7 +14052,7 @@
         <v>64-65</v>
       </c>
       <c r="G291" t="str">
-        <v>70-77</v>
+        <v>72-79</v>
       </c>
       <c r="H291" s="1">
         <v>0.1429</v>
@@ -14070,10 +14070,10 @@
         <v>Yes</v>
       </c>
       <c r="M291" t="str">
-        <v/>
+        <v>Unova Pokemon League</v>
       </c>
       <c r="N291" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Golurk","count":1}]}</v>
       </c>
       <c r="O291" t="str">
         <v/>
@@ -14081,10 +14081,10 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v/>
+        <v>Challenge 54</v>
       </c>
       <c r="B292" t="str">
-        <v/>
+        <v>Challenge 55</v>
       </c>
       <c r="C292" t="str">
         <v>Victory Road</v>
@@ -14099,7 +14099,7 @@
         <v>64-65</v>
       </c>
       <c r="G292" t="str">
-        <v>70-77</v>
+        <v>72-79</v>
       </c>
       <c r="H292" s="1">
         <v>0.1429</v>
@@ -14117,10 +14117,10 @@
         <v>Yes</v>
       </c>
       <c r="M292" t="str">
-        <v/>
+        <v>Unova Pokemon League</v>
       </c>
       <c r="N292" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Golurk","count":1}]}</v>
       </c>
       <c r="O292" t="str">
         <v/>
@@ -14128,10 +14128,10 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v/>
+        <v>Challenge 54</v>
       </c>
       <c r="B293" t="str">
-        <v/>
+        <v>Challenge 55</v>
       </c>
       <c r="C293" t="str">
         <v>Victory Road</v>
@@ -14146,7 +14146,7 @@
         <v>64-65</v>
       </c>
       <c r="G293" t="str">
-        <v>70-77</v>
+        <v>72-79</v>
       </c>
       <c r="H293" s="1">
         <v>0.1429</v>
@@ -14164,10 +14164,10 @@
         <v>Yes</v>
       </c>
       <c r="M293" t="str">
-        <v/>
+        <v>Unova Pokemon League</v>
       </c>
       <c r="N293" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Golurk","count":1}]}</v>
       </c>
       <c r="O293" t="str">
         <v/>
@@ -14175,10 +14175,10 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v/>
+        <v>Challenge 54</v>
       </c>
       <c r="B294" t="str">
-        <v/>
+        <v>Challenge 55</v>
       </c>
       <c r="C294" t="str">
         <v>Victory Road</v>
@@ -14193,7 +14193,7 @@
         <v>64-65</v>
       </c>
       <c r="G294" t="str">
-        <v>70-77</v>
+        <v>72-79</v>
       </c>
       <c r="H294" s="1">
         <v>0.1429</v>
@@ -14211,10 +14211,10 @@
         <v>Yes</v>
       </c>
       <c r="M294" t="str">
-        <v/>
+        <v>Unova Pokemon League</v>
       </c>
       <c r="N294" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Golurk","count":1}]}</v>
       </c>
       <c r="O294" t="str">
         <v/>
@@ -14316,10 +14316,10 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v/>
+        <v>Extra Challenge A Condition</v>
       </c>
       <c r="B297" t="str">
-        <v/>
+        <v>Extra Challenge A 1</v>
       </c>
       <c r="C297" t="str">
         <v>Route 8</v>
@@ -14352,10 +14352,10 @@
         <v>Yes</v>
       </c>
       <c r="M297" t="str">
-        <v/>
+        <v>Moor of Icirrus</v>
       </c>
       <c r="N297" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Crobat","count":10}]}</v>
       </c>
       <c r="O297" t="str">
         <v/>
@@ -14363,10 +14363,10 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v/>
+        <v>Extra Challenge A Condition</v>
       </c>
       <c r="B298" t="str">
-        <v/>
+        <v>Extra Challenge A 1</v>
       </c>
       <c r="C298" t="str">
         <v>Route 8</v>
@@ -14399,10 +14399,10 @@
         <v>Yes</v>
       </c>
       <c r="M298" t="str">
-        <v/>
+        <v>Moor of Icirrus</v>
       </c>
       <c r="N298" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Crobat","count":10}]}</v>
       </c>
       <c r="O298" t="str">
         <v/>
@@ -14410,10 +14410,10 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v/>
+        <v>Extra Challenge A Condition</v>
       </c>
       <c r="B299" t="str">
-        <v/>
+        <v>Extra Challenge A 1</v>
       </c>
       <c r="C299" t="str">
         <v>Route 8</v>
@@ -14446,10 +14446,10 @@
         <v>Yes</v>
       </c>
       <c r="M299" t="str">
-        <v/>
+        <v>Moor of Icirrus</v>
       </c>
       <c r="N299" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Crobat","count":10}]}</v>
       </c>
       <c r="O299" t="str">
         <v/>
@@ -14457,10 +14457,10 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v/>
+        <v>Extra Challenge A Condition</v>
       </c>
       <c r="B300" t="str">
-        <v/>
+        <v>Extra Challenge A 1</v>
       </c>
       <c r="C300" t="str">
         <v>Route 8</v>
@@ -14493,10 +14493,10 @@
         <v>Yes</v>
       </c>
       <c r="M300" t="str">
-        <v/>
+        <v>Moor of Icirrus</v>
       </c>
       <c r="N300" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Crobat","count":10}]}</v>
       </c>
       <c r="O300" t="str">
         <v/>
@@ -14551,10 +14551,10 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v/>
+        <v>Extra Challenge A 1</v>
       </c>
       <c r="B302" t="str">
-        <v/>
+        <v>Extra Challenge A 2</v>
       </c>
       <c r="C302" t="str">
         <v>Moor of Icirrus</v>
@@ -14587,10 +14587,10 @@
         <v>No</v>
       </c>
       <c r="M302" t="str">
-        <v/>
+        <v>Icirrus City</v>
       </c>
       <c r="N302" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Shelmet","count":10}]}</v>
       </c>
       <c r="O302" t="str">
         <v/>
@@ -14598,10 +14598,10 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v/>
+        <v>Extra Challenge A 1</v>
       </c>
       <c r="B303" t="str">
-        <v/>
+        <v>Extra Challenge A 2</v>
       </c>
       <c r="C303" t="str">
         <v>Moor of Icirrus</v>
@@ -14634,10 +14634,10 @@
         <v>No</v>
       </c>
       <c r="M303" t="str">
-        <v/>
+        <v>Icirrus City</v>
       </c>
       <c r="N303" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Shelmet","count":10}]}</v>
       </c>
       <c r="O303" t="str">
         <v/>
@@ -14692,10 +14692,10 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v/>
+        <v>Extra Challenge A 2</v>
       </c>
       <c r="B305" t="str">
-        <v/>
+        <v>Extra Challenge A 3</v>
       </c>
       <c r="C305" t="str">
         <v>Icirrus City</v>
@@ -14728,10 +14728,10 @@
         <v>No</v>
       </c>
       <c r="M305" t="str">
-        <v/>
+        <v>Dragonspiral Tower</v>
       </c>
       <c r="N305" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Lapras","count":10}]}</v>
       </c>
       <c r="O305" t="str">
         <v/>
@@ -14739,10 +14739,10 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v/>
+        <v>Extra Challenge A 2</v>
       </c>
       <c r="B306" t="str">
-        <v/>
+        <v>Extra Challenge A 3</v>
       </c>
       <c r="C306" t="str">
         <v>Icirrus City</v>
@@ -14775,10 +14775,10 @@
         <v>No</v>
       </c>
       <c r="M306" t="str">
-        <v/>
+        <v>Dragonspiral Tower</v>
       </c>
       <c r="N306" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Lapras","count":10}]}</v>
       </c>
       <c r="O306" t="str">
         <v/>
@@ -14833,10 +14833,10 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v/>
+        <v>Extra Challenge A 3</v>
       </c>
       <c r="B308" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="C308" t="str">
         <v>Dragonspiral Tower</v>
@@ -14869,10 +14869,10 @@
         <v>Yes</v>
       </c>
       <c r="M308" t="str">
-        <v/>
+        <v>Twist Mountain</v>
       </c>
       <c r="N308" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Beartic","count":10}]}</v>
       </c>
       <c r="O308" t="str">
         <v/>
@@ -14880,10 +14880,10 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v/>
+        <v>Extra Challenge A 3</v>
       </c>
       <c r="B309" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="C309" t="str">
         <v>Dragonspiral Tower</v>
@@ -14916,10 +14916,10 @@
         <v>Yes</v>
       </c>
       <c r="M309" t="str">
-        <v/>
+        <v>Twist Mountain</v>
       </c>
       <c r="N309" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Beartic","count":10}]}</v>
       </c>
       <c r="O309" t="str">
         <v/>
@@ -14927,10 +14927,10 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v/>
+        <v>Extra Challenge A 3</v>
       </c>
       <c r="B310" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="C310" t="str">
         <v>Dragonspiral Tower</v>
@@ -14963,10 +14963,10 @@
         <v>Yes</v>
       </c>
       <c r="M310" t="str">
-        <v/>
+        <v>Twist Mountain</v>
       </c>
       <c r="N310" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Beartic","count":10}]}</v>
       </c>
       <c r="O310" t="str">
         <v/>
@@ -14974,10 +14974,10 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v/>
+        <v>Extra Challenge A 3</v>
       </c>
       <c r="B311" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="C311" t="str">
         <v>Dragonspiral Tower</v>
@@ -15010,10 +15010,10 @@
         <v>Yes</v>
       </c>
       <c r="M311" t="str">
-        <v/>
+        <v>Twist Mountain</v>
       </c>
       <c r="N311" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Beartic","count":10}]}</v>
       </c>
       <c r="O311" t="str">
         <v/>
@@ -15021,10 +15021,10 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v/>
+        <v>Extra Challenge A 3</v>
       </c>
       <c r="B312" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="C312" t="str">
         <v>Dragonspiral Tower</v>
@@ -15057,10 +15057,10 @@
         <v>Yes</v>
       </c>
       <c r="M312" t="str">
-        <v/>
+        <v>Twist Mountain</v>
       </c>
       <c r="N312" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Beartic","count":10}]}</v>
       </c>
       <c r="O312" t="str">
         <v/>
@@ -15068,10 +15068,10 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v/>
+        <v>Extra Challenge A 3</v>
       </c>
       <c r="B313" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="C313" t="str">
         <v>Dragonspiral Tower</v>
@@ -15104,10 +15104,10 @@
         <v>Yes</v>
       </c>
       <c r="M313" t="str">
-        <v/>
+        <v>Twist Mountain</v>
       </c>
       <c r="N313" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Beartic","count":10}]}</v>
       </c>
       <c r="O313" t="str">
         <v/>
@@ -15162,10 +15162,10 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="B315" t="str">
-        <v/>
+        <v>Extra Challenge A 5</v>
       </c>
       <c r="C315" t="str">
         <v>Twist Mountain</v>
@@ -15198,10 +15198,10 @@
         <v>Yes</v>
       </c>
       <c r="M315" t="str">
-        <v/>
+        <v>Underground Ruins</v>
       </c>
       <c r="N315" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Vanilluxe","count":10}]}</v>
       </c>
       <c r="O315" t="str">
         <v/>
@@ -15209,10 +15209,10 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="B316" t="str">
-        <v/>
+        <v>Extra Challenge A 5</v>
       </c>
       <c r="C316" t="str">
         <v>Twist Mountain</v>
@@ -15245,10 +15245,10 @@
         <v>Yes</v>
       </c>
       <c r="M316" t="str">
-        <v/>
+        <v>Underground Ruins</v>
       </c>
       <c r="N316" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Vanilluxe","count":10}]}</v>
       </c>
       <c r="O316" t="str">
         <v/>
@@ -15256,10 +15256,10 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="B317" t="str">
-        <v/>
+        <v>Extra Challenge A 5</v>
       </c>
       <c r="C317" t="str">
         <v>Twist Mountain</v>
@@ -15292,10 +15292,10 @@
         <v>Yes</v>
       </c>
       <c r="M317" t="str">
-        <v/>
+        <v>Underground Ruins</v>
       </c>
       <c r="N317" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Vanilluxe","count":10}]}</v>
       </c>
       <c r="O317" t="str">
         <v/>
@@ -15303,10 +15303,10 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="B318" t="str">
-        <v/>
+        <v>Extra Challenge A 5</v>
       </c>
       <c r="C318" t="str">
         <v>Twist Mountain</v>
@@ -15339,10 +15339,10 @@
         <v>Yes</v>
       </c>
       <c r="M318" t="str">
-        <v/>
+        <v>Underground Ruins</v>
       </c>
       <c r="N318" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Vanilluxe","count":10}]}</v>
       </c>
       <c r="O318" t="str">
         <v/>
@@ -15350,10 +15350,10 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="B319" t="str">
-        <v/>
+        <v>Extra Challenge A 5</v>
       </c>
       <c r="C319" t="str">
         <v>Twist Mountain</v>
@@ -15386,10 +15386,10 @@
         <v>Yes</v>
       </c>
       <c r="M319" t="str">
-        <v/>
+        <v>Underground Ruins</v>
       </c>
       <c r="N319" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Vanilluxe","count":10}]}</v>
       </c>
       <c r="O319" t="str">
         <v/>
@@ -15397,10 +15397,10 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="B320" t="str">
-        <v/>
+        <v>Extra Challenge A 5</v>
       </c>
       <c r="C320" t="str">
         <v>Twist Mountain</v>
@@ -15433,10 +15433,10 @@
         <v>Yes</v>
       </c>
       <c r="M320" t="str">
-        <v/>
+        <v>Underground Ruins</v>
       </c>
       <c r="N320" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Vanilluxe","count":10}]}</v>
       </c>
       <c r="O320" t="str">
         <v/>
@@ -15444,10 +15444,10 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="B321" t="str">
-        <v/>
+        <v>Extra Challenge A 5</v>
       </c>
       <c r="C321" t="str">
         <v>Twist Mountain</v>
@@ -15480,10 +15480,10 @@
         <v>Yes</v>
       </c>
       <c r="M321" t="str">
-        <v/>
+        <v>Underground Ruins</v>
       </c>
       <c r="N321" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Vanilluxe","count":10}]}</v>
       </c>
       <c r="O321" t="str">
         <v/>
@@ -15509,7 +15509,7 @@
         <v>60-60</v>
       </c>
       <c r="G322" t="str">
-        <v>72-79</v>
+        <v>73-80</v>
       </c>
       <c r="H322" s="1">
         <v>0.1112</v>
@@ -15538,7 +15538,7 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v/>
+        <v>Extra Challenge A 5</v>
       </c>
       <c r="B323" t="str">
         <v/>
@@ -15556,7 +15556,7 @@
         <v>60-60</v>
       </c>
       <c r="G323" t="str">
-        <v>72-79</v>
+        <v>73-80</v>
       </c>
       <c r="H323" s="1">
         <v>0.1111</v>
@@ -15585,7 +15585,7 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v/>
+        <v>Extra Challenge A 5</v>
       </c>
       <c r="B324" t="str">
         <v/>
@@ -15603,7 +15603,7 @@
         <v>60-60</v>
       </c>
       <c r="G324" t="str">
-        <v>72-79</v>
+        <v>73-80</v>
       </c>
       <c r="H324" s="1">
         <v>0.1111</v>
@@ -15632,7 +15632,7 @@
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v/>
+        <v>Extra Challenge A 5</v>
       </c>
       <c r="B325" t="str">
         <v/>
@@ -15650,7 +15650,7 @@
         <v>60-60</v>
       </c>
       <c r="G325" t="str">
-        <v>72-79</v>
+        <v>73-80</v>
       </c>
       <c r="H325" s="1">
         <v>0.1111</v>
@@ -15679,7 +15679,7 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v/>
+        <v>Extra Challenge A 5</v>
       </c>
       <c r="B326" t="str">
         <v/>
@@ -15697,7 +15697,7 @@
         <v>60-60</v>
       </c>
       <c r="G326" t="str">
-        <v>72-79</v>
+        <v>73-80</v>
       </c>
       <c r="H326" s="1">
         <v>0.1111</v>
@@ -15726,7 +15726,7 @@
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v/>
+        <v>Extra Challenge A 5</v>
       </c>
       <c r="B327" t="str">
         <v/>
@@ -15744,7 +15744,7 @@
         <v>60-60</v>
       </c>
       <c r="G327" t="str">
-        <v>72-79</v>
+        <v>73-80</v>
       </c>
       <c r="H327" s="1">
         <v>0.1111</v>
@@ -15773,7 +15773,7 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v/>
+        <v>Extra Challenge A 5</v>
       </c>
       <c r="B328" t="str">
         <v/>
@@ -15791,7 +15791,7 @@
         <v>60-60</v>
       </c>
       <c r="G328" t="str">
-        <v>72-79</v>
+        <v>73-80</v>
       </c>
       <c r="H328" s="1">
         <v>0.1111</v>
@@ -15820,7 +15820,7 @@
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v/>
+        <v>Extra Challenge A 5</v>
       </c>
       <c r="B329" t="str">
         <v/>
@@ -15838,7 +15838,7 @@
         <v>60-60</v>
       </c>
       <c r="G329" t="str">
-        <v>72-79</v>
+        <v>73-80</v>
       </c>
       <c r="H329" s="1">
         <v>0.1111</v>
@@ -15867,7 +15867,7 @@
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v/>
+        <v>Extra Challenge A 5</v>
       </c>
       <c r="B330" t="str">
         <v/>
@@ -15885,7 +15885,7 @@
         <v>60-60</v>
       </c>
       <c r="G330" t="str">
-        <v>72-79</v>
+        <v>73-80</v>
       </c>
       <c r="H330" s="1">
         <v>0.1111</v>
@@ -15961,10 +15961,10 @@
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v/>
+        <v>Extra Challenge B Condition</v>
       </c>
       <c r="B332" t="str">
-        <v/>
+        <v>Extra Challenge B 1</v>
       </c>
       <c r="C332" t="str">
         <v>Route 15</v>
@@ -15997,10 +15997,10 @@
         <v>Yes</v>
       </c>
       <c r="M332" t="str">
-        <v/>
+        <v>Striaton City</v>
       </c>
       <c r="N332" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Tyranitar","count":10}]}</v>
       </c>
       <c r="O332" t="str">
         <v/>
@@ -16008,10 +16008,10 @@
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v/>
+        <v>Extra Challenge B Condition</v>
       </c>
       <c r="B333" t="str">
-        <v/>
+        <v>Extra Challenge B 1</v>
       </c>
       <c r="C333" t="str">
         <v>Route 15</v>
@@ -16044,10 +16044,10 @@
         <v>Yes</v>
       </c>
       <c r="M333" t="str">
-        <v/>
+        <v>Striaton City</v>
       </c>
       <c r="N333" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Tyranitar","count":10}]}</v>
       </c>
       <c r="O333" t="str">
         <v/>
@@ -16055,10 +16055,10 @@
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v/>
+        <v>Extra Challenge B Condition</v>
       </c>
       <c r="B334" t="str">
-        <v/>
+        <v>Extra Challenge B 1</v>
       </c>
       <c r="C334" t="str">
         <v>Route 15</v>
@@ -16091,10 +16091,10 @@
         <v>Yes</v>
       </c>
       <c r="M334" t="str">
-        <v/>
+        <v>Striaton City</v>
       </c>
       <c r="N334" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Tyranitar","count":10}]}</v>
       </c>
       <c r="O334" t="str">
         <v/>
@@ -16102,10 +16102,10 @@
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v/>
+        <v>Extra Challenge B Condition</v>
       </c>
       <c r="B335" t="str">
-        <v/>
+        <v>Extra Challenge B 1</v>
       </c>
       <c r="C335" t="str">
         <v>Route 15</v>
@@ -16138,10 +16138,10 @@
         <v>Yes</v>
       </c>
       <c r="M335" t="str">
-        <v/>
+        <v>Striaton City</v>
       </c>
       <c r="N335" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Tyranitar","count":10}]}</v>
       </c>
       <c r="O335" t="str">
         <v/>
@@ -16149,10 +16149,10 @@
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v/>
+        <v>Extra Challenge B Condition</v>
       </c>
       <c r="B336" t="str">
-        <v/>
+        <v>Extra Challenge B 1</v>
       </c>
       <c r="C336" t="str">
         <v>Route 15</v>
@@ -16185,10 +16185,10 @@
         <v>Yes</v>
       </c>
       <c r="M336" t="str">
-        <v/>
+        <v>Striaton City</v>
       </c>
       <c r="N336" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Tyranitar","count":10}]}</v>
       </c>
       <c r="O336" t="str">
         <v/>
@@ -16243,10 +16243,10 @@
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v/>
+        <v>Extra Challenge B 1</v>
       </c>
       <c r="B338" t="str">
-        <v/>
+        <v>Extra Challenge B 2</v>
       </c>
       <c r="C338" t="str">
         <v>Striaton City</v>
@@ -16279,10 +16279,10 @@
         <v>No</v>
       </c>
       <c r="M338" t="str">
-        <v/>
+        <v>Dreamyard</v>
       </c>
       <c r="N338" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Wigglytuff","count":10}]}</v>
       </c>
       <c r="O338" t="str">
         <v/>
@@ -16290,10 +16290,10 @@
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v/>
+        <v>Extra Challenge B 1</v>
       </c>
       <c r="B339" t="str">
-        <v/>
+        <v>Extra Challenge B 2</v>
       </c>
       <c r="C339" t="str">
         <v>Striaton City</v>
@@ -16326,10 +16326,10 @@
         <v>No</v>
       </c>
       <c r="M339" t="str">
-        <v/>
+        <v>Dreamyard</v>
       </c>
       <c r="N339" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Wigglytuff","count":10}]}</v>
       </c>
       <c r="O339" t="str">
         <v/>
@@ -16337,10 +16337,10 @@
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v/>
+        <v>Extra Challenge B 1</v>
       </c>
       <c r="B340" t="str">
-        <v/>
+        <v>Extra Challenge B 2</v>
       </c>
       <c r="C340" t="str">
         <v>Striaton City</v>
@@ -16373,10 +16373,10 @@
         <v>No</v>
       </c>
       <c r="M340" t="str">
-        <v/>
+        <v>Dreamyard</v>
       </c>
       <c r="N340" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Wigglytuff","count":10}]}</v>
       </c>
       <c r="O340" t="str">
         <v/>
@@ -16431,10 +16431,10 @@
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v/>
+        <v>Extra Challenge B 2</v>
       </c>
       <c r="B342" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="C342" t="str">
         <v>Dreamyard</v>
@@ -16467,10 +16467,10 @@
         <v>No</v>
       </c>
       <c r="M342" t="str">
-        <v/>
+        <v>Route 18</v>
       </c>
       <c r="N342" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Munna","count":10}]}</v>
       </c>
       <c r="O342" t="str">
         <v/>
@@ -16478,10 +16478,10 @@
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v/>
+        <v>Extra Challenge B 2</v>
       </c>
       <c r="B343" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="C343" t="str">
         <v>Dreamyard</v>
@@ -16514,10 +16514,10 @@
         <v>No</v>
       </c>
       <c r="M343" t="str">
-        <v/>
+        <v>Route 18</v>
       </c>
       <c r="N343" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Munna","count":10}]}</v>
       </c>
       <c r="O343" t="str">
         <v/>
@@ -16572,10 +16572,10 @@
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B345" t="str">
-        <v/>
+        <v>Extra Challenge B 4</v>
       </c>
       <c r="C345" t="str">
         <v>Route 18</v>
@@ -16608,10 +16608,10 @@
         <v>Yes</v>
       </c>
       <c r="M345" t="str">
-        <v/>
+        <v>Route 17</v>
       </c>
       <c r="N345" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Scrafty","count":10}]}</v>
       </c>
       <c r="O345" t="str">
         <v/>
@@ -16619,10 +16619,10 @@
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B346" t="str">
-        <v/>
+        <v>Extra Challenge B 4</v>
       </c>
       <c r="C346" t="str">
         <v>Route 18</v>
@@ -16655,10 +16655,10 @@
         <v>Yes</v>
       </c>
       <c r="M346" t="str">
-        <v/>
+        <v>Route 17</v>
       </c>
       <c r="N346" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Scrafty","count":10}]}</v>
       </c>
       <c r="O346" t="str">
         <v/>
@@ -16666,10 +16666,10 @@
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B347" t="str">
-        <v/>
+        <v>Extra Challenge B 4</v>
       </c>
       <c r="C347" t="str">
         <v>Route 18</v>
@@ -16702,10 +16702,10 @@
         <v>Yes</v>
       </c>
       <c r="M347" t="str">
-        <v/>
+        <v>Route 17</v>
       </c>
       <c r="N347" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Scrafty","count":10}]}</v>
       </c>
       <c r="O347" t="str">
         <v/>
@@ -16713,10 +16713,10 @@
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B348" t="str">
-        <v/>
+        <v>Extra Challenge B 4</v>
       </c>
       <c r="C348" t="str">
         <v>Route 18</v>
@@ -16749,10 +16749,10 @@
         <v>Yes</v>
       </c>
       <c r="M348" t="str">
-        <v/>
+        <v>Route 17</v>
       </c>
       <c r="N348" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Scrafty","count":10}]}</v>
       </c>
       <c r="O348" t="str">
         <v/>
@@ -16778,7 +16778,7 @@
         <v>70-70</v>
       </c>
       <c r="G349" t="str">
-        <v>72-79</v>
+        <v>73-80</v>
       </c>
       <c r="H349" s="1">
         <v>0.5</v>
@@ -16807,7 +16807,7 @@
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v/>
+        <v>Extra Challenge B 4</v>
       </c>
       <c r="B350" t="str">
         <v/>
@@ -16825,7 +16825,7 @@
         <v>70-70</v>
       </c>
       <c r="G350" t="str">
-        <v>72-79</v>
+        <v>73-80</v>
       </c>
       <c r="H350" s="1">
         <v>0.5</v>
@@ -16901,10 +16901,10 @@
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v/>
+        <v>Extra Challenge C Condition</v>
       </c>
       <c r="B352" t="str">
-        <v/>
+        <v>Extra Challenge C 1</v>
       </c>
       <c r="C352" t="str">
         <v>Route 1</v>
@@ -16937,10 +16937,10 @@
         <v>No</v>
       </c>
       <c r="M352" t="str">
-        <v/>
+        <v>Nuvema Town</v>
       </c>
       <c r="N352" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Oshawott","count":10}]}</v>
       </c>
       <c r="O352" t="str">
         <v/>
@@ -16995,10 +16995,10 @@
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v/>
+        <v>Extra Challenge C 1</v>
       </c>
       <c r="B354" t="str">
-        <v/>
+        <v>Extra Challenge C 2</v>
       </c>
       <c r="C354" t="str">
         <v>Nuvema Town</v>
@@ -17031,10 +17031,10 @@
         <v>No</v>
       </c>
       <c r="M354" t="str">
-        <v/>
+        <v>Route 2</v>
       </c>
       <c r="N354" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Flaaffy","count":10}]}</v>
       </c>
       <c r="O354" t="str">
         <v/>
@@ -17042,10 +17042,10 @@
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v/>
+        <v>Extra Challenge C 1</v>
       </c>
       <c r="B355" t="str">
-        <v/>
+        <v>Extra Challenge C 2</v>
       </c>
       <c r="C355" t="str">
         <v>Nuvema Town</v>
@@ -17078,10 +17078,10 @@
         <v>No</v>
       </c>
       <c r="M355" t="str">
-        <v/>
+        <v>Route 2</v>
       </c>
       <c r="N355" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Flaaffy","count":10}]}</v>
       </c>
       <c r="O355" t="str">
         <v/>
@@ -17089,10 +17089,10 @@
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v/>
+        <v>Extra Challenge C 1</v>
       </c>
       <c r="B356" t="str">
-        <v/>
+        <v>Extra Challenge C 2</v>
       </c>
       <c r="C356" t="str">
         <v>Nuvema Town</v>
@@ -17125,10 +17125,10 @@
         <v>No</v>
       </c>
       <c r="M356" t="str">
-        <v/>
+        <v>Route 2</v>
       </c>
       <c r="N356" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Flaaffy","count":10}]}</v>
       </c>
       <c r="O356" t="str">
         <v/>
@@ -17183,10 +17183,10 @@
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v/>
+        <v>Extra Challenge C 2</v>
       </c>
       <c r="B358" t="str">
-        <v/>
+        <v>Extra Challenge C 3</v>
       </c>
       <c r="C358" t="str">
         <v>Route 2</v>
@@ -17219,10 +17219,10 @@
         <v>No</v>
       </c>
       <c r="M358" t="str">
-        <v/>
+        <v>Route 3</v>
       </c>
       <c r="N358" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Slaking","count":10}]}</v>
       </c>
       <c r="O358" t="str">
         <v/>
@@ -17230,10 +17230,10 @@
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v/>
+        <v>Extra Challenge C 2</v>
       </c>
       <c r="B359" t="str">
-        <v/>
+        <v>Extra Challenge C 3</v>
       </c>
       <c r="C359" t="str">
         <v>Route 2</v>
@@ -17266,10 +17266,10 @@
         <v>No</v>
       </c>
       <c r="M359" t="str">
-        <v/>
+        <v>Route 3</v>
       </c>
       <c r="N359" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Slaking","count":10}]}</v>
       </c>
       <c r="O359" t="str">
         <v/>
@@ -17277,10 +17277,10 @@
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v/>
+        <v>Extra Challenge C 2</v>
       </c>
       <c r="B360" t="str">
-        <v/>
+        <v>Extra Challenge C 3</v>
       </c>
       <c r="C360" t="str">
         <v>Route 2</v>
@@ -17313,10 +17313,10 @@
         <v>No</v>
       </c>
       <c r="M360" t="str">
-        <v/>
+        <v>Route 3</v>
       </c>
       <c r="N360" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Slaking","count":10}]}</v>
       </c>
       <c r="O360" t="str">
         <v/>
@@ -17324,10 +17324,10 @@
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v/>
+        <v>Extra Challenge C 2</v>
       </c>
       <c r="B361" t="str">
-        <v/>
+        <v>Extra Challenge C 3</v>
       </c>
       <c r="C361" t="str">
         <v>Route 2</v>
@@ -17360,10 +17360,10 @@
         <v>No</v>
       </c>
       <c r="M361" t="str">
-        <v/>
+        <v>Route 3</v>
       </c>
       <c r="N361" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Slaking","count":10}]}</v>
       </c>
       <c r="O361" t="str">
         <v/>
@@ -17371,10 +17371,10 @@
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v/>
+        <v>Extra Challenge C 2</v>
       </c>
       <c r="B362" t="str">
-        <v/>
+        <v>Extra Challenge C 3</v>
       </c>
       <c r="C362" t="str">
         <v>Route 2</v>
@@ -17407,10 +17407,10 @@
         <v>No</v>
       </c>
       <c r="M362" t="str">
-        <v/>
+        <v>Route 3</v>
       </c>
       <c r="N362" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Slaking","count":10}]}</v>
       </c>
       <c r="O362" t="str">
         <v/>
@@ -17465,10 +17465,10 @@
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v/>
+        <v>Extra Challenge C 3</v>
       </c>
       <c r="B364" t="str">
-        <v/>
+        <v>Extra Challenge C 4</v>
       </c>
       <c r="C364" t="str">
         <v>Route 3</v>
@@ -17501,10 +17501,10 @@
         <v>No</v>
       </c>
       <c r="M364" t="str">
-        <v/>
+        <v>Moor of Icirrus Depths</v>
       </c>
       <c r="N364" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Electivire","count":10}]}</v>
       </c>
       <c r="O364" t="str">
         <v/>
@@ -17512,10 +17512,10 @@
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v/>
+        <v>Extra Challenge C 3</v>
       </c>
       <c r="B365" t="str">
-        <v/>
+        <v>Extra Challenge C 4</v>
       </c>
       <c r="C365" t="str">
         <v>Route 3</v>
@@ -17548,10 +17548,10 @@
         <v>No</v>
       </c>
       <c r="M365" t="str">
-        <v/>
+        <v>Moor of Icirrus Depths</v>
       </c>
       <c r="N365" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Electivire","count":10}]}</v>
       </c>
       <c r="O365" t="str">
         <v/>
@@ -17559,10 +17559,10 @@
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v/>
+        <v>Extra Challenge C 3</v>
       </c>
       <c r="B366" t="str">
-        <v/>
+        <v>Extra Challenge C 4</v>
       </c>
       <c r="C366" t="str">
         <v>Route 3</v>
@@ -17595,10 +17595,10 @@
         <v>No</v>
       </c>
       <c r="M366" t="str">
-        <v/>
+        <v>Moor of Icirrus Depths</v>
       </c>
       <c r="N366" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Electivire","count":10}]}</v>
       </c>
       <c r="O366" t="str">
         <v/>
@@ -17606,10 +17606,10 @@
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v/>
+        <v>Extra Challenge C 3</v>
       </c>
       <c r="B367" t="str">
-        <v/>
+        <v>Extra Challenge C 4</v>
       </c>
       <c r="C367" t="str">
         <v>Route 3</v>
@@ -17642,10 +17642,10 @@
         <v>No</v>
       </c>
       <c r="M367" t="str">
-        <v/>
+        <v>Moor of Icirrus Depths</v>
       </c>
       <c r="N367" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Electivire","count":10}]}</v>
       </c>
       <c r="O367" t="str">
         <v/>
@@ -17700,7 +17700,7 @@
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v/>
+        <v>Extra Challenge C 4</v>
       </c>
       <c r="B369" t="str">
         <v/>
@@ -17747,7 +17747,7 @@
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v/>
+        <v>Extra Challenge C 4</v>
       </c>
       <c r="B370" t="str">
         <v/>
@@ -17794,7 +17794,7 @@
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v/>
+        <v>Extra Challenge C 4</v>
       </c>
       <c r="B371" t="str">
         <v/>
@@ -17935,10 +17935,10 @@
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v/>
+        <v>Extra Challenge D 1</v>
       </c>
       <c r="B374" t="str">
-        <v/>
+        <v>Extra Challenge D 2</v>
       </c>
       <c r="C374" t="str">
         <v>Nacrene City</v>
@@ -17971,10 +17971,10 @@
         <v>No</v>
       </c>
       <c r="M374" t="str">
-        <v/>
+        <v>Pinwheel Forest</v>
       </c>
       <c r="N374" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Stoutland","count":10}]}</v>
       </c>
       <c r="O374" t="str">
         <v/>
@@ -17982,10 +17982,10 @@
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v/>
+        <v>Extra Challenge D 1</v>
       </c>
       <c r="B375" t="str">
-        <v/>
+        <v>Extra Challenge D 2</v>
       </c>
       <c r="C375" t="str">
         <v>Nacrene City</v>
@@ -18018,10 +18018,10 @@
         <v>No</v>
       </c>
       <c r="M375" t="str">
-        <v/>
+        <v>Pinwheel Forest</v>
       </c>
       <c r="N375" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Stoutland","count":10}]}</v>
       </c>
       <c r="O375" t="str">
         <v/>
@@ -18029,10 +18029,10 @@
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v/>
+        <v>Extra Challenge D 1</v>
       </c>
       <c r="B376" t="str">
-        <v/>
+        <v>Extra Challenge D 2</v>
       </c>
       <c r="C376" t="str">
         <v>Nacrene City</v>
@@ -18065,10 +18065,10 @@
         <v>No</v>
       </c>
       <c r="M376" t="str">
-        <v/>
+        <v>Pinwheel Forest</v>
       </c>
       <c r="N376" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Stoutland","count":10}]}</v>
       </c>
       <c r="O376" t="str">
         <v/>
@@ -18123,10 +18123,10 @@
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v/>
+        <v>Extra Challenge D 2</v>
       </c>
       <c r="B378" t="str">
-        <v/>
+        <v>Extra Challenge D 3</v>
       </c>
       <c r="C378" t="str">
         <v>Pinwheel Forest</v>
@@ -18159,10 +18159,10 @@
         <v>No</v>
       </c>
       <c r="M378" t="str">
-        <v/>
+        <v>Cave of Being</v>
       </c>
       <c r="N378" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Tangrowth","count":10}]}</v>
       </c>
       <c r="O378" t="str">
         <v/>
@@ -18170,10 +18170,10 @@
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v/>
+        <v>Extra Challenge D 2</v>
       </c>
       <c r="B379" t="str">
-        <v/>
+        <v>Extra Challenge D 3</v>
       </c>
       <c r="C379" t="str">
         <v>Pinwheel Forest</v>
@@ -18206,10 +18206,10 @@
         <v>No</v>
       </c>
       <c r="M379" t="str">
-        <v/>
+        <v>Cave of Being</v>
       </c>
       <c r="N379" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Tangrowth","count":10}]}</v>
       </c>
       <c r="O379" t="str">
         <v/>
@@ -18217,10 +18217,10 @@
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v/>
+        <v>Extra Challenge D 2</v>
       </c>
       <c r="B380" t="str">
-        <v/>
+        <v>Extra Challenge D 3</v>
       </c>
       <c r="C380" t="str">
         <v>Pinwheel Forest</v>
@@ -18253,10 +18253,10 @@
         <v>No</v>
       </c>
       <c r="M380" t="str">
-        <v/>
+        <v>Cave of Being</v>
       </c>
       <c r="N380" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Tangrowth","count":10}]}</v>
       </c>
       <c r="O380" t="str">
         <v/>
@@ -18311,10 +18311,10 @@
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v/>
+        <v>Extra Challenge D 3</v>
       </c>
       <c r="B382" t="str">
-        <v/>
+        <v>Extra Challenge D 4</v>
       </c>
       <c r="C382" t="str">
         <v>Cave of Being</v>
@@ -18347,10 +18347,10 @@
         <v>No</v>
       </c>
       <c r="M382" t="str">
-        <v/>
+        <v>Liberty Garden</v>
       </c>
       <c r="N382" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Simipour","count":10}]}</v>
       </c>
       <c r="O382" t="str">
         <v/>
@@ -18358,10 +18358,10 @@
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v/>
+        <v>Extra Challenge D 3</v>
       </c>
       <c r="B383" t="str">
-        <v/>
+        <v>Extra Challenge D 4</v>
       </c>
       <c r="C383" t="str">
         <v>Cave of Being</v>
@@ -18394,10 +18394,10 @@
         <v>No</v>
       </c>
       <c r="M383" t="str">
-        <v/>
+        <v>Liberty Garden</v>
       </c>
       <c r="N383" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Simipour","count":10}]}</v>
       </c>
       <c r="O383" t="str">
         <v/>
@@ -18405,10 +18405,10 @@
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v/>
+        <v>Extra Challenge D 3</v>
       </c>
       <c r="B384" t="str">
-        <v/>
+        <v>Extra Challenge D 4</v>
       </c>
       <c r="C384" t="str">
         <v>Cave of Being</v>
@@ -18441,10 +18441,10 @@
         <v>No</v>
       </c>
       <c r="M384" t="str">
-        <v/>
+        <v>Liberty Garden</v>
       </c>
       <c r="N384" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Simipour","count":10}]}</v>
       </c>
       <c r="O384" t="str">
         <v/>
@@ -18452,10 +18452,10 @@
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v/>
+        <v>Extra Challenge D 3</v>
       </c>
       <c r="B385" t="str">
-        <v/>
+        <v>Extra Challenge D 4</v>
       </c>
       <c r="C385" t="str">
         <v>Cave of Being</v>
@@ -18488,10 +18488,10 @@
         <v>No</v>
       </c>
       <c r="M385" t="str">
-        <v/>
+        <v>Liberty Garden</v>
       </c>
       <c r="N385" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Simipour","count":10}]}</v>
       </c>
       <c r="O385" t="str">
         <v/>
@@ -18499,10 +18499,10 @@
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v/>
+        <v>Extra Challenge D 3</v>
       </c>
       <c r="B386" t="str">
-        <v/>
+        <v>Extra Challenge D 4</v>
       </c>
       <c r="C386" t="str">
         <v>Cave of Being</v>
@@ -18535,10 +18535,10 @@
         <v>No</v>
       </c>
       <c r="M386" t="str">
-        <v/>
+        <v>Liberty Garden</v>
       </c>
       <c r="N386" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Simipour","count":10}]}</v>
       </c>
       <c r="O386" t="str">
         <v/>
@@ -18593,7 +18593,7 @@
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v/>
+        <v>Extra Challenge D 4</v>
       </c>
       <c r="B388" t="str">
         <v/>
@@ -18640,7 +18640,7 @@
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v/>
+        <v>Extra Challenge D 4</v>
       </c>
       <c r="B389" t="str">
         <v/>
@@ -18734,10 +18734,10 @@
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v/>
+        <v>Extra Challenge E Condition</v>
       </c>
       <c r="B391" t="str">
-        <v/>
+        <v>Extra Challenge E 1</v>
       </c>
       <c r="C391" t="str">
         <v>Route 10</v>
@@ -18770,10 +18770,10 @@
         <v>Yes</v>
       </c>
       <c r="M391" t="str">
-        <v/>
+        <v>Nature Sanctuary</v>
       </c>
       <c r="N391" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Vullaby","count":10}]}</v>
       </c>
       <c r="O391" t="str">
         <v/>
@@ -18781,10 +18781,10 @@
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v/>
+        <v>Extra Challenge E Condition</v>
       </c>
       <c r="B392" t="str">
-        <v/>
+        <v>Extra Challenge E 1</v>
       </c>
       <c r="C392" t="str">
         <v>Route 10</v>
@@ -18817,10 +18817,10 @@
         <v>Yes</v>
       </c>
       <c r="M392" t="str">
-        <v/>
+        <v>Nature Sanctuary</v>
       </c>
       <c r="N392" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Vullaby","count":10}]}</v>
       </c>
       <c r="O392" t="str">
         <v/>
@@ -18828,10 +18828,10 @@
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v/>
+        <v>Extra Challenge E Condition</v>
       </c>
       <c r="B393" t="str">
-        <v/>
+        <v>Extra Challenge E 1</v>
       </c>
       <c r="C393" t="str">
         <v>Route 10</v>
@@ -18864,10 +18864,10 @@
         <v>Yes</v>
       </c>
       <c r="M393" t="str">
-        <v/>
+        <v>Nature Sanctuary</v>
       </c>
       <c r="N393" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Vullaby","count":10}]}</v>
       </c>
       <c r="O393" t="str">
         <v/>
@@ -18875,10 +18875,10 @@
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v/>
+        <v>Extra Challenge E Condition</v>
       </c>
       <c r="B394" t="str">
-        <v/>
+        <v>Extra Challenge E 1</v>
       </c>
       <c r="C394" t="str">
         <v>Route 10</v>
@@ -18911,10 +18911,10 @@
         <v>Yes</v>
       </c>
       <c r="M394" t="str">
-        <v/>
+        <v>Nature Sanctuary</v>
       </c>
       <c r="N394" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Vullaby","count":10}]}</v>
       </c>
       <c r="O394" t="str">
         <v/>
@@ -18922,10 +18922,10 @@
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v/>
+        <v>Extra Challenge E Condition</v>
       </c>
       <c r="B395" t="str">
-        <v/>
+        <v>Extra Challenge E 1</v>
       </c>
       <c r="C395" t="str">
         <v>Route 10</v>
@@ -18958,10 +18958,10 @@
         <v>Yes</v>
       </c>
       <c r="M395" t="str">
-        <v/>
+        <v>Nature Sanctuary</v>
       </c>
       <c r="N395" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Vullaby","count":10}]}</v>
       </c>
       <c r="O395" t="str">
         <v/>
@@ -19016,10 +19016,10 @@
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v/>
+        <v>Extra Challenge E 1</v>
       </c>
       <c r="B397" t="str">
-        <v/>
+        <v>Extra Challenge E 2</v>
       </c>
       <c r="C397" t="str">
         <v>Nature Sanctuary</v>
@@ -19052,10 +19052,10 @@
         <v>No</v>
       </c>
       <c r="M397" t="str">
-        <v/>
+        <v>Route 24</v>
       </c>
       <c r="N397" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Ninetales","count":10}]}</v>
       </c>
       <c r="O397" t="str">
         <v/>
@@ -19063,10 +19063,10 @@
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v/>
+        <v>Extra Challenge E 1</v>
       </c>
       <c r="B398" t="str">
-        <v/>
+        <v>Extra Challenge E 2</v>
       </c>
       <c r="C398" t="str">
         <v>Nature Sanctuary</v>
@@ -19099,10 +19099,10 @@
         <v>No</v>
       </c>
       <c r="M398" t="str">
-        <v/>
+        <v>Route 24</v>
       </c>
       <c r="N398" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Ninetales","count":10}]}</v>
       </c>
       <c r="O398" t="str">
         <v/>
@@ -19110,10 +19110,10 @@
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v/>
+        <v>Extra Challenge E 1</v>
       </c>
       <c r="B399" t="str">
-        <v/>
+        <v>Extra Challenge E 2</v>
       </c>
       <c r="C399" t="str">
         <v>Nature Sanctuary</v>
@@ -19146,10 +19146,10 @@
         <v>No</v>
       </c>
       <c r="M399" t="str">
-        <v/>
+        <v>Route 24</v>
       </c>
       <c r="N399" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Ninetales","count":10}]}</v>
       </c>
       <c r="O399" t="str">
         <v/>
@@ -19204,10 +19204,10 @@
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v/>
+        <v>Extra Challenge E 2</v>
       </c>
       <c r="B401" t="str">
-        <v/>
+        <v>Extra Challenge E 3</v>
       </c>
       <c r="C401" t="str">
         <v>Route 24</v>
@@ -19240,10 +19240,10 @@
         <v>No</v>
       </c>
       <c r="M401" t="str">
-        <v/>
+        <v>Route 25</v>
       </c>
       <c r="N401" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Beartic","count":10}]}</v>
       </c>
       <c r="O401" t="str">
         <v/>
@@ -19298,10 +19298,10 @@
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v/>
+        <v>Extra Challenge E 3</v>
       </c>
       <c r="B403" t="str">
-        <v/>
+        <v>Extra Challenge E 4</v>
       </c>
       <c r="C403" t="str">
         <v>Route 25</v>
@@ -19334,10 +19334,10 @@
         <v>No</v>
       </c>
       <c r="M403" t="str">
-        <v/>
+        <v>Abundant Shrine Depths</v>
       </c>
       <c r="N403" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Bouffalant","count":10}]}</v>
       </c>
       <c r="O403" t="str">
         <v/>
@@ -19392,7 +19392,7 @@
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v/>
+        <v>Extra Challenge E 4</v>
       </c>
       <c r="B405" t="str">
         <v/>
@@ -19439,7 +19439,7 @@
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v/>
+        <v>Extra Challenge E 4</v>
       </c>
       <c r="B406" t="str">
         <v/>
@@ -19533,10 +19533,10 @@
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v/>
+        <v>Condition to Final Challenge</v>
       </c>
       <c r="B408" t="str">
-        <v/>
+        <v>Dragonspire Clouds</v>
       </c>
       <c r="C408" t="str">
         <v>Dragonspire Clouds</v>
@@ -19572,7 +19572,7 @@
         <v/>
       </c>
       <c r="N408" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Zekrom","count":1},{"species":"Kyurem","count":1},{"species":"Reshiram","count":1}]}</v>
       </c>
       <c r="O408" t="str">
         <v/>
@@ -19580,10 +19580,10 @@
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v/>
+        <v>Condition to Final Challenge</v>
       </c>
       <c r="B409" t="str">
-        <v/>
+        <v>Dragonspire Clouds</v>
       </c>
       <c r="C409" t="str">
         <v>Dragonspire Clouds</v>
@@ -19619,7 +19619,7 @@
         <v/>
       </c>
       <c r="N409" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Zekrom","count":1},{"species":"Kyurem","count":1},{"species":"Reshiram","count":1}]}</v>
       </c>
       <c r="O409" t="str">
         <v/>

--- a/5_Unova_Data.xlsx
+++ b/5_Unova_Data.xlsx
@@ -2960,7 +2960,7 @@
         <v>10-11</v>
       </c>
       <c r="G55" t="str">
-        <v>8-10</v>
+        <v>9-11</v>
       </c>
       <c r="H55" s="1">
         <v>0.1426</v>
@@ -3007,7 +3007,7 @@
         <v>10-11</v>
       </c>
       <c r="G56" t="str">
-        <v>8-10</v>
+        <v>9-11</v>
       </c>
       <c r="H56" s="1">
         <v>0.1429</v>
@@ -3054,7 +3054,7 @@
         <v>10-11</v>
       </c>
       <c r="G57" t="str">
-        <v>8-10</v>
+        <v>9-11</v>
       </c>
       <c r="H57" s="1">
         <v>0.1429</v>
@@ -3101,7 +3101,7 @@
         <v>10-11</v>
       </c>
       <c r="G58" t="str">
-        <v>8-10</v>
+        <v>9-11</v>
       </c>
       <c r="H58" s="1">
         <v>0.1429</v>
@@ -3148,7 +3148,7 @@
         <v>10-11</v>
       </c>
       <c r="G59" t="str">
-        <v>8-10</v>
+        <v>9-11</v>
       </c>
       <c r="H59" s="1">
         <v>0.1429</v>
@@ -3195,7 +3195,7 @@
         <v>10-11</v>
       </c>
       <c r="G60" t="str">
-        <v>8-10</v>
+        <v>9-11</v>
       </c>
       <c r="H60" s="1">
         <v>0.1429</v>
@@ -3242,7 +3242,7 @@
         <v>10-11</v>
       </c>
       <c r="G61" t="str">
-        <v>8-10</v>
+        <v>9-11</v>
       </c>
       <c r="H61" s="1">
         <v>0.1429</v>
@@ -3336,7 +3336,7 @@
         <v>13-14</v>
       </c>
       <c r="G63" t="str">
-        <v>11-13</v>
+        <v>12-15</v>
       </c>
       <c r="H63" s="1">
         <v>0.1665</v>
@@ -3383,7 +3383,7 @@
         <v>13-14</v>
       </c>
       <c r="G64" t="str">
-        <v>11-13</v>
+        <v>12-15</v>
       </c>
       <c r="H64" s="1">
         <v>0.1667</v>
@@ -3430,7 +3430,7 @@
         <v>13-14</v>
       </c>
       <c r="G65" t="str">
-        <v>11-13</v>
+        <v>12-15</v>
       </c>
       <c r="H65" s="1">
         <v>0.1667</v>
@@ -3477,7 +3477,7 @@
         <v>13-14</v>
       </c>
       <c r="G66" t="str">
-        <v>11-13</v>
+        <v>12-15</v>
       </c>
       <c r="H66" s="1">
         <v>0.1667</v>
@@ -3524,7 +3524,7 @@
         <v>13-14</v>
       </c>
       <c r="G67" t="str">
-        <v>11-13</v>
+        <v>12-15</v>
       </c>
       <c r="H67" s="1">
         <v>0.1667</v>
@@ -3571,7 +3571,7 @@
         <v>13-14</v>
       </c>
       <c r="G68" t="str">
-        <v>11-13</v>
+        <v>12-15</v>
       </c>
       <c r="H68" s="1">
         <v>0.1667</v>
@@ -3759,7 +3759,7 @@
         <v>15-16</v>
       </c>
       <c r="G72" t="str">
-        <v>14-17</v>
+        <v>15-18</v>
       </c>
       <c r="H72" s="1">
         <v>0.091</v>
@@ -3806,7 +3806,7 @@
         <v>15-16</v>
       </c>
       <c r="G73" t="str">
-        <v>14-17</v>
+        <v>15-18</v>
       </c>
       <c r="H73" s="1">
         <v>0.0909</v>
@@ -3853,7 +3853,7 @@
         <v>15-16</v>
       </c>
       <c r="G74" t="str">
-        <v>14-17</v>
+        <v>15-18</v>
       </c>
       <c r="H74" s="1">
         <v>0.0909</v>
@@ -3900,7 +3900,7 @@
         <v>15-16</v>
       </c>
       <c r="G75" t="str">
-        <v>14-17</v>
+        <v>15-18</v>
       </c>
       <c r="H75" s="1">
         <v>0.0909</v>
@@ -3947,7 +3947,7 @@
         <v>15-16</v>
       </c>
       <c r="G76" t="str">
-        <v>14-17</v>
+        <v>15-18</v>
       </c>
       <c r="H76" s="1">
         <v>0.0909</v>
@@ -3994,7 +3994,7 @@
         <v>15-16</v>
       </c>
       <c r="G77" t="str">
-        <v>14-17</v>
+        <v>15-18</v>
       </c>
       <c r="H77" s="1">
         <v>0.0909</v>
@@ -4041,7 +4041,7 @@
         <v>15-16</v>
       </c>
       <c r="G78" t="str">
-        <v>14-17</v>
+        <v>15-18</v>
       </c>
       <c r="H78" s="1">
         <v>0.0909</v>
@@ -4088,7 +4088,7 @@
         <v>15-16</v>
       </c>
       <c r="G79" t="str">
-        <v>14-17</v>
+        <v>15-18</v>
       </c>
       <c r="H79" s="1">
         <v>0.0909</v>
@@ -4135,7 +4135,7 @@
         <v>15-16</v>
       </c>
       <c r="G80" t="str">
-        <v>14-17</v>
+        <v>15-18</v>
       </c>
       <c r="H80" s="1">
         <v>0.0909</v>
@@ -4182,7 +4182,7 @@
         <v>15-16</v>
       </c>
       <c r="G81" t="str">
-        <v>14-17</v>
+        <v>15-18</v>
       </c>
       <c r="H81" s="1">
         <v>0.0909</v>
@@ -4229,7 +4229,7 @@
         <v>15-16</v>
       </c>
       <c r="G82" t="str">
-        <v>14-17</v>
+        <v>15-18</v>
       </c>
       <c r="H82" s="1">
         <v>0.0909</v>
@@ -5169,7 +5169,7 @@
         <v>21-22</v>
       </c>
       <c r="G102" t="str">
-        <v>21-24</v>
+        <v>22-25</v>
       </c>
       <c r="H102" s="1">
         <v>0.1112</v>
@@ -5216,7 +5216,7 @@
         <v>21-22</v>
       </c>
       <c r="G103" t="str">
-        <v>21-24</v>
+        <v>22-25</v>
       </c>
       <c r="H103" s="1">
         <v>0.1111</v>
@@ -5263,7 +5263,7 @@
         <v>21-22</v>
       </c>
       <c r="G104" t="str">
-        <v>21-24</v>
+        <v>22-25</v>
       </c>
       <c r="H104" s="1">
         <v>0.1111</v>
@@ -5310,7 +5310,7 @@
         <v>21-22</v>
       </c>
       <c r="G105" t="str">
-        <v>21-24</v>
+        <v>22-25</v>
       </c>
       <c r="H105" s="1">
         <v>0.1111</v>
@@ -5357,7 +5357,7 @@
         <v>21-22</v>
       </c>
       <c r="G106" t="str">
-        <v>21-24</v>
+        <v>22-25</v>
       </c>
       <c r="H106" s="1">
         <v>0.1111</v>
@@ -5404,7 +5404,7 @@
         <v>21-22</v>
       </c>
       <c r="G107" t="str">
-        <v>21-24</v>
+        <v>22-25</v>
       </c>
       <c r="H107" s="1">
         <v>0.1111</v>
@@ -5451,7 +5451,7 @@
         <v>21-22</v>
       </c>
       <c r="G108" t="str">
-        <v>21-24</v>
+        <v>22-25</v>
       </c>
       <c r="H108" s="1">
         <v>0.1111</v>
@@ -5498,7 +5498,7 @@
         <v>21-22</v>
       </c>
       <c r="G109" t="str">
-        <v>21-24</v>
+        <v>22-25</v>
       </c>
       <c r="H109" s="1">
         <v>0.1111</v>
@@ -5545,7 +5545,7 @@
         <v>21-22</v>
       </c>
       <c r="G110" t="str">
-        <v>21-24</v>
+        <v>22-25</v>
       </c>
       <c r="H110" s="1">
         <v>0.1111</v>
@@ -5733,7 +5733,7 @@
         <v>24-25</v>
       </c>
       <c r="G114" t="str">
-        <v>24-27</v>
+        <v>25-28</v>
       </c>
       <c r="H114" s="1">
         <v>0.1665</v>
@@ -5780,7 +5780,7 @@
         <v>24-25</v>
       </c>
       <c r="G115" t="str">
-        <v>24-27</v>
+        <v>25-28</v>
       </c>
       <c r="H115" s="1">
         <v>0.1667</v>
@@ -5827,7 +5827,7 @@
         <v>24-25</v>
       </c>
       <c r="G116" t="str">
-        <v>24-27</v>
+        <v>25-28</v>
       </c>
       <c r="H116" s="1">
         <v>0.1667</v>
@@ -5874,7 +5874,7 @@
         <v>24-25</v>
       </c>
       <c r="G117" t="str">
-        <v>24-27</v>
+        <v>25-28</v>
       </c>
       <c r="H117" s="1">
         <v>0.1667</v>
@@ -5921,7 +5921,7 @@
         <v>24-25</v>
       </c>
       <c r="G118" t="str">
-        <v>24-27</v>
+        <v>25-28</v>
       </c>
       <c r="H118" s="1">
         <v>0.1667</v>
@@ -5968,7 +5968,7 @@
         <v>24-25</v>
       </c>
       <c r="G119" t="str">
-        <v>24-27</v>
+        <v>25-28</v>
       </c>
       <c r="H119" s="1">
         <v>0.1667</v>
@@ -6485,7 +6485,7 @@
         <v>27-28</v>
       </c>
       <c r="G130" t="str">
-        <v>27-30</v>
+        <v>28-31</v>
       </c>
       <c r="H130" s="1">
         <v>0.125</v>
@@ -6532,7 +6532,7 @@
         <v>27-28</v>
       </c>
       <c r="G131" t="str">
-        <v>27-30</v>
+        <v>28-31</v>
       </c>
       <c r="H131" s="1">
         <v>0.125</v>
@@ -6579,7 +6579,7 @@
         <v>27-28</v>
       </c>
       <c r="G132" t="str">
-        <v>27-30</v>
+        <v>28-31</v>
       </c>
       <c r="H132" s="1">
         <v>0.125</v>
@@ -6626,7 +6626,7 @@
         <v>27-28</v>
       </c>
       <c r="G133" t="str">
-        <v>27-30</v>
+        <v>28-31</v>
       </c>
       <c r="H133" s="1">
         <v>0.125</v>
@@ -6673,7 +6673,7 @@
         <v>27-28</v>
       </c>
       <c r="G134" t="str">
-        <v>27-30</v>
+        <v>28-31</v>
       </c>
       <c r="H134" s="1">
         <v>0.125</v>
@@ -6720,7 +6720,7 @@
         <v>27-28</v>
       </c>
       <c r="G135" t="str">
-        <v>27-30</v>
+        <v>28-31</v>
       </c>
       <c r="H135" s="1">
         <v>0.125</v>
@@ -6767,7 +6767,7 @@
         <v>27-28</v>
       </c>
       <c r="G136" t="str">
-        <v>27-30</v>
+        <v>28-31</v>
       </c>
       <c r="H136" s="1">
         <v>0.125</v>
@@ -6814,7 +6814,7 @@
         <v>27-28</v>
       </c>
       <c r="G137" t="str">
-        <v>27-30</v>
+        <v>28-31</v>
       </c>
       <c r="H137" s="1">
         <v>0.125</v>
@@ -6908,7 +6908,7 @@
         <v>29-30</v>
       </c>
       <c r="G139" t="str">
-        <v>30-33</v>
+        <v>31-34</v>
       </c>
       <c r="H139" s="1">
         <v>0.1</v>
@@ -6955,7 +6955,7 @@
         <v>29-30</v>
       </c>
       <c r="G140" t="str">
-        <v>30-33</v>
+        <v>31-34</v>
       </c>
       <c r="H140" s="1">
         <v>0.1</v>
@@ -7002,7 +7002,7 @@
         <v>29-30</v>
       </c>
       <c r="G141" t="str">
-        <v>30-33</v>
+        <v>31-34</v>
       </c>
       <c r="H141" s="1">
         <v>0.1</v>
@@ -7049,7 +7049,7 @@
         <v>29-30</v>
       </c>
       <c r="G142" t="str">
-        <v>30-33</v>
+        <v>31-34</v>
       </c>
       <c r="H142" s="1">
         <v>0.1</v>
@@ -7096,7 +7096,7 @@
         <v>29-30</v>
       </c>
       <c r="G143" t="str">
-        <v>30-33</v>
+        <v>31-34</v>
       </c>
       <c r="H143" s="1">
         <v>0.1</v>
@@ -7143,7 +7143,7 @@
         <v>29-30</v>
       </c>
       <c r="G144" t="str">
-        <v>30-33</v>
+        <v>31-34</v>
       </c>
       <c r="H144" s="1">
         <v>0.1</v>
@@ -7190,7 +7190,7 @@
         <v>29-30</v>
       </c>
       <c r="G145" t="str">
-        <v>30-33</v>
+        <v>31-34</v>
       </c>
       <c r="H145" s="1">
         <v>0.1</v>
@@ -7237,7 +7237,7 @@
         <v>29-30</v>
       </c>
       <c r="G146" t="str">
-        <v>30-33</v>
+        <v>31-34</v>
       </c>
       <c r="H146" s="1">
         <v>0.1</v>
@@ -7284,7 +7284,7 @@
         <v>29-30</v>
       </c>
       <c r="G147" t="str">
-        <v>30-33</v>
+        <v>31-34</v>
       </c>
       <c r="H147" s="1">
         <v>0.1</v>
@@ -7331,7 +7331,7 @@
         <v>29-30</v>
       </c>
       <c r="G148" t="str">
-        <v>30-33</v>
+        <v>31-34</v>
       </c>
       <c r="H148" s="1">
         <v>0.1</v>
@@ -7378,7 +7378,7 @@
         <v>30-31</v>
       </c>
       <c r="G149" t="str">
-        <v>31-34</v>
+        <v>32-35</v>
       </c>
       <c r="H149" s="1">
         <v>0.125</v>
@@ -7425,7 +7425,7 @@
         <v>30-31</v>
       </c>
       <c r="G150" t="str">
-        <v>31-34</v>
+        <v>32-35</v>
       </c>
       <c r="H150" s="1">
         <v>0.125</v>
@@ -7472,7 +7472,7 @@
         <v>30-31</v>
       </c>
       <c r="G151" t="str">
-        <v>31-34</v>
+        <v>32-35</v>
       </c>
       <c r="H151" s="1">
         <v>0.125</v>
@@ -7519,7 +7519,7 @@
         <v>30-31</v>
       </c>
       <c r="G152" t="str">
-        <v>31-34</v>
+        <v>32-35</v>
       </c>
       <c r="H152" s="1">
         <v>0.125</v>
@@ -7566,7 +7566,7 @@
         <v>30-31</v>
       </c>
       <c r="G153" t="str">
-        <v>31-34</v>
+        <v>32-35</v>
       </c>
       <c r="H153" s="1">
         <v>0.125</v>
@@ -7613,7 +7613,7 @@
         <v>30-31</v>
       </c>
       <c r="G154" t="str">
-        <v>31-34</v>
+        <v>32-35</v>
       </c>
       <c r="H154" s="1">
         <v>0.125</v>
@@ -7660,7 +7660,7 @@
         <v>30-31</v>
       </c>
       <c r="G155" t="str">
-        <v>31-34</v>
+        <v>32-35</v>
       </c>
       <c r="H155" s="1">
         <v>0.125</v>
@@ -7707,7 +7707,7 @@
         <v>30-31</v>
       </c>
       <c r="G156" t="str">
-        <v>31-34</v>
+        <v>32-35</v>
       </c>
       <c r="H156" s="1">
         <v>0.125</v>
@@ -7801,7 +7801,7 @@
         <v>32-33</v>
       </c>
       <c r="G158" t="str">
-        <v>34-37</v>
+        <v>35-38</v>
       </c>
       <c r="H158" s="1">
         <v>0.1112</v>
@@ -7848,7 +7848,7 @@
         <v>32-33</v>
       </c>
       <c r="G159" t="str">
-        <v>34-37</v>
+        <v>35-38</v>
       </c>
       <c r="H159" s="1">
         <v>0.1111</v>
@@ -7895,7 +7895,7 @@
         <v>32-33</v>
       </c>
       <c r="G160" t="str">
-        <v>34-37</v>
+        <v>35-38</v>
       </c>
       <c r="H160" s="1">
         <v>0.1111</v>
@@ -7942,7 +7942,7 @@
         <v>32-33</v>
       </c>
       <c r="G161" t="str">
-        <v>34-37</v>
+        <v>35-38</v>
       </c>
       <c r="H161" s="1">
         <v>0.1111</v>
@@ -7989,7 +7989,7 @@
         <v>32-33</v>
       </c>
       <c r="G162" t="str">
-        <v>34-37</v>
+        <v>35-38</v>
       </c>
       <c r="H162" s="1">
         <v>0.1111</v>
@@ -8036,7 +8036,7 @@
         <v>32-33</v>
       </c>
       <c r="G163" t="str">
-        <v>34-37</v>
+        <v>35-38</v>
       </c>
       <c r="H163" s="1">
         <v>0.1111</v>
@@ -8083,7 +8083,7 @@
         <v>32-33</v>
       </c>
       <c r="G164" t="str">
-        <v>34-37</v>
+        <v>35-38</v>
       </c>
       <c r="H164" s="1">
         <v>0.1111</v>
@@ -8130,7 +8130,7 @@
         <v>32-33</v>
       </c>
       <c r="G165" t="str">
-        <v>34-37</v>
+        <v>35-38</v>
       </c>
       <c r="H165" s="1">
         <v>0.1111</v>
@@ -8177,7 +8177,7 @@
         <v>32-33</v>
       </c>
       <c r="G166" t="str">
-        <v>34-37</v>
+        <v>35-38</v>
       </c>
       <c r="H166" s="1">
         <v>0.1111</v>
@@ -8224,7 +8224,7 @@
         <v>34-35</v>
       </c>
       <c r="G167" t="str">
-        <v>36-39</v>
+        <v>37-40</v>
       </c>
       <c r="H167" s="1">
         <v>0.1665</v>
@@ -8271,7 +8271,7 @@
         <v>34-35</v>
       </c>
       <c r="G168" t="str">
-        <v>36-39</v>
+        <v>37-40</v>
       </c>
       <c r="H168" s="1">
         <v>0.1667</v>
@@ -8318,7 +8318,7 @@
         <v>34-35</v>
       </c>
       <c r="G169" t="str">
-        <v>36-39</v>
+        <v>37-40</v>
       </c>
       <c r="H169" s="1">
         <v>0.1667</v>
@@ -8365,7 +8365,7 @@
         <v>34-35</v>
       </c>
       <c r="G170" t="str">
-        <v>36-39</v>
+        <v>37-40</v>
       </c>
       <c r="H170" s="1">
         <v>0.1667</v>
@@ -8412,7 +8412,7 @@
         <v>34-35</v>
       </c>
       <c r="G171" t="str">
-        <v>36-39</v>
+        <v>37-40</v>
       </c>
       <c r="H171" s="1">
         <v>0.1667</v>
@@ -8459,7 +8459,7 @@
         <v>34-35</v>
       </c>
       <c r="G172" t="str">
-        <v>36-39</v>
+        <v>37-40</v>
       </c>
       <c r="H172" s="1">
         <v>0.1667</v>
@@ -8976,7 +8976,7 @@
         <v>38-39</v>
       </c>
       <c r="G183" t="str">
-        <v>40-44</v>
+        <v>41-45</v>
       </c>
       <c r="H183" s="1">
         <v>0.1</v>
@@ -9023,7 +9023,7 @@
         <v>38-39</v>
       </c>
       <c r="G184" t="str">
-        <v>40-44</v>
+        <v>41-45</v>
       </c>
       <c r="H184" s="1">
         <v>0.1</v>
@@ -9070,7 +9070,7 @@
         <v>38-39</v>
       </c>
       <c r="G185" t="str">
-        <v>40-44</v>
+        <v>41-45</v>
       </c>
       <c r="H185" s="1">
         <v>0.1</v>
@@ -9117,7 +9117,7 @@
         <v>38-39</v>
       </c>
       <c r="G186" t="str">
-        <v>40-44</v>
+        <v>41-45</v>
       </c>
       <c r="H186" s="1">
         <v>0.1</v>
@@ -9164,7 +9164,7 @@
         <v>38-39</v>
       </c>
       <c r="G187" t="str">
-        <v>40-44</v>
+        <v>41-45</v>
       </c>
       <c r="H187" s="1">
         <v>0.1</v>
@@ -9211,7 +9211,7 @@
         <v>38-39</v>
       </c>
       <c r="G188" t="str">
-        <v>40-44</v>
+        <v>41-45</v>
       </c>
       <c r="H188" s="1">
         <v>0.1</v>
@@ -9258,7 +9258,7 @@
         <v>38-39</v>
       </c>
       <c r="G189" t="str">
-        <v>40-44</v>
+        <v>41-45</v>
       </c>
       <c r="H189" s="1">
         <v>0.1</v>
@@ -9305,7 +9305,7 @@
         <v>38-39</v>
       </c>
       <c r="G190" t="str">
-        <v>40-44</v>
+        <v>41-45</v>
       </c>
       <c r="H190" s="1">
         <v>0.1</v>
@@ -9352,7 +9352,7 @@
         <v>38-39</v>
       </c>
       <c r="G191" t="str">
-        <v>40-44</v>
+        <v>41-45</v>
       </c>
       <c r="H191" s="1">
         <v>0.1</v>
@@ -9399,7 +9399,7 @@
         <v>38-39</v>
       </c>
       <c r="G192" t="str">
-        <v>40-44</v>
+        <v>41-45</v>
       </c>
       <c r="H192" s="1">
         <v>0.1</v>
@@ -9493,7 +9493,7 @@
         <v>41-42</v>
       </c>
       <c r="G194" t="str">
-        <v>43-47</v>
+        <v>44-48</v>
       </c>
       <c r="H194" s="1">
         <v>0.0837</v>
@@ -9540,7 +9540,7 @@
         <v>41-42</v>
       </c>
       <c r="G195" t="str">
-        <v>43-47</v>
+        <v>44-48</v>
       </c>
       <c r="H195" s="1">
         <v>0.0833</v>
@@ -9587,7 +9587,7 @@
         <v>41-42</v>
       </c>
       <c r="G196" t="str">
-        <v>43-47</v>
+        <v>44-48</v>
       </c>
       <c r="H196" s="1">
         <v>0.0833</v>
@@ -9634,7 +9634,7 @@
         <v>41-42</v>
       </c>
       <c r="G197" t="str">
-        <v>43-47</v>
+        <v>44-48</v>
       </c>
       <c r="H197" s="1">
         <v>0.0833</v>
@@ -9681,7 +9681,7 @@
         <v>41-42</v>
       </c>
       <c r="G198" t="str">
-        <v>43-47</v>
+        <v>44-48</v>
       </c>
       <c r="H198" s="1">
         <v>0.0833</v>
@@ -9728,7 +9728,7 @@
         <v>41-42</v>
       </c>
       <c r="G199" t="str">
-        <v>43-47</v>
+        <v>44-48</v>
       </c>
       <c r="H199" s="1">
         <v>0.0833</v>
@@ -9775,7 +9775,7 @@
         <v>41-42</v>
       </c>
       <c r="G200" t="str">
-        <v>43-47</v>
+        <v>44-48</v>
       </c>
       <c r="H200" s="1">
         <v>0.0833</v>
@@ -9822,7 +9822,7 @@
         <v>41-42</v>
       </c>
       <c r="G201" t="str">
-        <v>43-47</v>
+        <v>44-48</v>
       </c>
       <c r="H201" s="1">
         <v>0.0833</v>
@@ -9869,7 +9869,7 @@
         <v>41-42</v>
       </c>
       <c r="G202" t="str">
-        <v>43-47</v>
+        <v>44-48</v>
       </c>
       <c r="H202" s="1">
         <v>0.0833</v>
@@ -9916,7 +9916,7 @@
         <v>41-42</v>
       </c>
       <c r="G203" t="str">
-        <v>43-47</v>
+        <v>44-48</v>
       </c>
       <c r="H203" s="1">
         <v>0.0833</v>
@@ -9963,7 +9963,7 @@
         <v>41-42</v>
       </c>
       <c r="G204" t="str">
-        <v>43-47</v>
+        <v>44-48</v>
       </c>
       <c r="H204" s="1">
         <v>0.0833</v>
@@ -10010,7 +10010,7 @@
         <v>41-42</v>
       </c>
       <c r="G205" t="str">
-        <v>43-47</v>
+        <v>44-48</v>
       </c>
       <c r="H205" s="1">
         <v>0.0833</v>
@@ -10057,7 +10057,7 @@
         <v>42-43</v>
       </c>
       <c r="G206" t="str">
-        <v>44-48</v>
+        <v>45-49</v>
       </c>
       <c r="H206" s="1">
         <v>0.125</v>
@@ -10104,7 +10104,7 @@
         <v>42-43</v>
       </c>
       <c r="G207" t="str">
-        <v>44-48</v>
+        <v>45-49</v>
       </c>
       <c r="H207" s="1">
         <v>0.125</v>
@@ -10151,7 +10151,7 @@
         <v>42-43</v>
       </c>
       <c r="G208" t="str">
-        <v>44-48</v>
+        <v>45-49</v>
       </c>
       <c r="H208" s="1">
         <v>0.125</v>
@@ -10198,7 +10198,7 @@
         <v>42-43</v>
       </c>
       <c r="G209" t="str">
-        <v>44-48</v>
+        <v>45-49</v>
       </c>
       <c r="H209" s="1">
         <v>0.125</v>
@@ -10245,7 +10245,7 @@
         <v>42-43</v>
       </c>
       <c r="G210" t="str">
-        <v>44-48</v>
+        <v>45-49</v>
       </c>
       <c r="H210" s="1">
         <v>0.125</v>
@@ -10292,7 +10292,7 @@
         <v>42-43</v>
       </c>
       <c r="G211" t="str">
-        <v>44-48</v>
+        <v>45-49</v>
       </c>
       <c r="H211" s="1">
         <v>0.125</v>
@@ -10339,7 +10339,7 @@
         <v>42-43</v>
       </c>
       <c r="G212" t="str">
-        <v>44-48</v>
+        <v>45-49</v>
       </c>
       <c r="H212" s="1">
         <v>0.125</v>
@@ -10386,7 +10386,7 @@
         <v>42-43</v>
       </c>
       <c r="G213" t="str">
-        <v>44-48</v>
+        <v>45-49</v>
       </c>
       <c r="H213" s="1">
         <v>0.125</v>
@@ -10433,7 +10433,7 @@
         <v>43-44</v>
       </c>
       <c r="G214" t="str">
-        <v>46-50</v>
+        <v>47-51</v>
       </c>
       <c r="H214" s="1">
         <v>0.1665</v>
@@ -10480,7 +10480,7 @@
         <v>43-44</v>
       </c>
       <c r="G215" t="str">
-        <v>46-50</v>
+        <v>47-51</v>
       </c>
       <c r="H215" s="1">
         <v>0.1667</v>
@@ -10527,7 +10527,7 @@
         <v>43-44</v>
       </c>
       <c r="G216" t="str">
-        <v>46-50</v>
+        <v>47-51</v>
       </c>
       <c r="H216" s="1">
         <v>0.1667</v>
@@ -10574,7 +10574,7 @@
         <v>43-44</v>
       </c>
       <c r="G217" t="str">
-        <v>46-50</v>
+        <v>47-51</v>
       </c>
       <c r="H217" s="1">
         <v>0.1667</v>
@@ -10621,7 +10621,7 @@
         <v>43-44</v>
       </c>
       <c r="G218" t="str">
-        <v>46-50</v>
+        <v>47-51</v>
       </c>
       <c r="H218" s="1">
         <v>0.1667</v>
@@ -10668,7 +10668,7 @@
         <v>43-44</v>
       </c>
       <c r="G219" t="str">
-        <v>46-50</v>
+        <v>47-51</v>
       </c>
       <c r="H219" s="1">
         <v>0.1667</v>
@@ -10715,7 +10715,7 @@
         <v>44-45</v>
       </c>
       <c r="G220" t="str">
-        <v>47-51</v>
+        <v>48-52</v>
       </c>
       <c r="H220" s="1">
         <v>0.2</v>
@@ -10762,7 +10762,7 @@
         <v>44-45</v>
       </c>
       <c r="G221" t="str">
-        <v>47-51</v>
+        <v>48-52</v>
       </c>
       <c r="H221" s="1">
         <v>0.2</v>
@@ -10809,7 +10809,7 @@
         <v>44-45</v>
       </c>
       <c r="G222" t="str">
-        <v>47-51</v>
+        <v>48-52</v>
       </c>
       <c r="H222" s="1">
         <v>0.2</v>
@@ -10856,7 +10856,7 @@
         <v>44-45</v>
       </c>
       <c r="G223" t="str">
-        <v>47-51</v>
+        <v>48-52</v>
       </c>
       <c r="H223" s="1">
         <v>0.2</v>
@@ -10903,7 +10903,7 @@
         <v>44-45</v>
       </c>
       <c r="G224" t="str">
-        <v>47-51</v>
+        <v>48-52</v>
       </c>
       <c r="H224" s="1">
         <v>0.2</v>
@@ -11044,7 +11044,7 @@
         <v>48-49</v>
       </c>
       <c r="G227" t="str">
-        <v>52-57</v>
+        <v>53-58</v>
       </c>
       <c r="H227" s="1">
         <v>0.2</v>
@@ -11091,7 +11091,7 @@
         <v>48-49</v>
       </c>
       <c r="G228" t="str">
-        <v>52-57</v>
+        <v>53-58</v>
       </c>
       <c r="H228" s="1">
         <v>0.2</v>
@@ -11138,7 +11138,7 @@
         <v>48-49</v>
       </c>
       <c r="G229" t="str">
-        <v>52-57</v>
+        <v>53-58</v>
       </c>
       <c r="H229" s="1">
         <v>0.2</v>
@@ -11185,7 +11185,7 @@
         <v>48-49</v>
       </c>
       <c r="G230" t="str">
-        <v>52-57</v>
+        <v>53-58</v>
       </c>
       <c r="H230" s="1">
         <v>0.2</v>
@@ -11232,7 +11232,7 @@
         <v>48-49</v>
       </c>
       <c r="G231" t="str">
-        <v>52-57</v>
+        <v>53-58</v>
       </c>
       <c r="H231" s="1">
         <v>0.2</v>
@@ -11279,7 +11279,7 @@
         <v>49-50</v>
       </c>
       <c r="G232" t="str">
-        <v>53-58</v>
+        <v>54-59</v>
       </c>
       <c r="H232" s="1">
         <v>0.1665</v>
@@ -11326,7 +11326,7 @@
         <v>49-50</v>
       </c>
       <c r="G233" t="str">
-        <v>53-58</v>
+        <v>54-59</v>
       </c>
       <c r="H233" s="1">
         <v>0.1667</v>
@@ -11373,7 +11373,7 @@
         <v>49-50</v>
       </c>
       <c r="G234" t="str">
-        <v>53-58</v>
+        <v>54-59</v>
       </c>
       <c r="H234" s="1">
         <v>0.1667</v>
@@ -11420,7 +11420,7 @@
         <v>49-50</v>
       </c>
       <c r="G235" t="str">
-        <v>53-58</v>
+        <v>54-59</v>
       </c>
       <c r="H235" s="1">
         <v>0.1667</v>
@@ -11467,7 +11467,7 @@
         <v>49-50</v>
       </c>
       <c r="G236" t="str">
-        <v>53-58</v>
+        <v>54-59</v>
       </c>
       <c r="H236" s="1">
         <v>0.1667</v>
@@ -11514,7 +11514,7 @@
         <v>49-50</v>
       </c>
       <c r="G237" t="str">
-        <v>53-58</v>
+        <v>54-59</v>
       </c>
       <c r="H237" s="1">
         <v>0.1667</v>
@@ -11561,7 +11561,7 @@
         <v>50-51</v>
       </c>
       <c r="G238" t="str">
-        <v>54-59</v>
+        <v>56-61</v>
       </c>
       <c r="H238" s="1">
         <v>0.1426</v>
@@ -11608,7 +11608,7 @@
         <v>50-51</v>
       </c>
       <c r="G239" t="str">
-        <v>54-59</v>
+        <v>56-61</v>
       </c>
       <c r="H239" s="1">
         <v>0.1429</v>
@@ -11655,7 +11655,7 @@
         <v>50-51</v>
       </c>
       <c r="G240" t="str">
-        <v>54-59</v>
+        <v>56-61</v>
       </c>
       <c r="H240" s="1">
         <v>0.1429</v>
@@ -11702,7 +11702,7 @@
         <v>50-51</v>
       </c>
       <c r="G241" t="str">
-        <v>54-59</v>
+        <v>56-61</v>
       </c>
       <c r="H241" s="1">
         <v>0.1429</v>
@@ -11749,7 +11749,7 @@
         <v>50-51</v>
       </c>
       <c r="G242" t="str">
-        <v>54-59</v>
+        <v>56-61</v>
       </c>
       <c r="H242" s="1">
         <v>0.1429</v>
@@ -11796,7 +11796,7 @@
         <v>50-51</v>
       </c>
       <c r="G243" t="str">
-        <v>54-59</v>
+        <v>56-61</v>
       </c>
       <c r="H243" s="1">
         <v>0.1429</v>
@@ -11843,7 +11843,7 @@
         <v>50-51</v>
       </c>
       <c r="G244" t="str">
-        <v>54-59</v>
+        <v>56-61</v>
       </c>
       <c r="H244" s="1">
         <v>0.1429</v>
@@ -11890,7 +11890,7 @@
         <v>51-52</v>
       </c>
       <c r="G245" t="str">
-        <v>56-61</v>
+        <v>57-62</v>
       </c>
       <c r="H245" s="1">
         <v>0.1665</v>
@@ -11937,7 +11937,7 @@
         <v>51-52</v>
       </c>
       <c r="G246" t="str">
-        <v>56-61</v>
+        <v>57-62</v>
       </c>
       <c r="H246" s="1">
         <v>0.1667</v>
@@ -11984,7 +11984,7 @@
         <v>51-52</v>
       </c>
       <c r="G247" t="str">
-        <v>56-61</v>
+        <v>57-62</v>
       </c>
       <c r="H247" s="1">
         <v>0.1667</v>
@@ -12031,7 +12031,7 @@
         <v>51-52</v>
       </c>
       <c r="G248" t="str">
-        <v>56-61</v>
+        <v>57-62</v>
       </c>
       <c r="H248" s="1">
         <v>0.1667</v>
@@ -12078,7 +12078,7 @@
         <v>51-52</v>
       </c>
       <c r="G249" t="str">
-        <v>56-61</v>
+        <v>57-62</v>
       </c>
       <c r="H249" s="1">
         <v>0.1667</v>
@@ -12125,7 +12125,7 @@
         <v>51-52</v>
       </c>
       <c r="G250" t="str">
-        <v>56-61</v>
+        <v>57-62</v>
       </c>
       <c r="H250" s="1">
         <v>0.1667</v>
@@ -12219,7 +12219,7 @@
         <v>53-54</v>
       </c>
       <c r="G252" t="str">
-        <v>59-64</v>
+        <v>60-66</v>
       </c>
       <c r="H252" s="1">
         <v>0.1</v>
@@ -12266,7 +12266,7 @@
         <v>53-54</v>
       </c>
       <c r="G253" t="str">
-        <v>59-64</v>
+        <v>60-66</v>
       </c>
       <c r="H253" s="1">
         <v>0.1</v>
@@ -12313,7 +12313,7 @@
         <v>53-54</v>
       </c>
       <c r="G254" t="str">
-        <v>59-64</v>
+        <v>60-66</v>
       </c>
       <c r="H254" s="1">
         <v>0.1</v>
@@ -12360,7 +12360,7 @@
         <v>53-54</v>
       </c>
       <c r="G255" t="str">
-        <v>59-64</v>
+        <v>60-66</v>
       </c>
       <c r="H255" s="1">
         <v>0.1</v>
@@ -12407,7 +12407,7 @@
         <v>53-54</v>
       </c>
       <c r="G256" t="str">
-        <v>59-64</v>
+        <v>60-66</v>
       </c>
       <c r="H256" s="1">
         <v>0.1</v>
@@ -12454,7 +12454,7 @@
         <v>53-54</v>
       </c>
       <c r="G257" t="str">
-        <v>59-64</v>
+        <v>60-66</v>
       </c>
       <c r="H257" s="1">
         <v>0.1</v>
@@ -12501,7 +12501,7 @@
         <v>53-54</v>
       </c>
       <c r="G258" t="str">
-        <v>59-64</v>
+        <v>60-66</v>
       </c>
       <c r="H258" s="1">
         <v>0.1</v>
@@ -12548,7 +12548,7 @@
         <v>53-54</v>
       </c>
       <c r="G259" t="str">
-        <v>59-64</v>
+        <v>60-66</v>
       </c>
       <c r="H259" s="1">
         <v>0.1</v>
@@ -12595,7 +12595,7 @@
         <v>53-54</v>
       </c>
       <c r="G260" t="str">
-        <v>59-64</v>
+        <v>60-66</v>
       </c>
       <c r="H260" s="1">
         <v>0.1</v>
@@ -12642,7 +12642,7 @@
         <v>53-54</v>
       </c>
       <c r="G261" t="str">
-        <v>59-64</v>
+        <v>60-66</v>
       </c>
       <c r="H261" s="1">
         <v>0.1</v>
@@ -12736,7 +12736,7 @@
         <v>56-57</v>
       </c>
       <c r="G263" t="str">
-        <v>62-68</v>
+        <v>63-69</v>
       </c>
       <c r="H263" s="1">
         <v>0.1426</v>
@@ -12783,7 +12783,7 @@
         <v>56-57</v>
       </c>
       <c r="G264" t="str">
-        <v>62-68</v>
+        <v>63-69</v>
       </c>
       <c r="H264" s="1">
         <v>0.1429</v>
@@ -12830,7 +12830,7 @@
         <v>56-57</v>
       </c>
       <c r="G265" t="str">
-        <v>62-68</v>
+        <v>63-69</v>
       </c>
       <c r="H265" s="1">
         <v>0.1429</v>
@@ -12877,7 +12877,7 @@
         <v>56-57</v>
       </c>
       <c r="G266" t="str">
-        <v>62-68</v>
+        <v>63-69</v>
       </c>
       <c r="H266" s="1">
         <v>0.1429</v>
@@ -12924,7 +12924,7 @@
         <v>56-57</v>
       </c>
       <c r="G267" t="str">
-        <v>62-68</v>
+        <v>63-69</v>
       </c>
       <c r="H267" s="1">
         <v>0.1429</v>
@@ -12971,7 +12971,7 @@
         <v>56-57</v>
       </c>
       <c r="G268" t="str">
-        <v>62-68</v>
+        <v>63-69</v>
       </c>
       <c r="H268" s="1">
         <v>0.1429</v>
@@ -13018,7 +13018,7 @@
         <v>56-57</v>
       </c>
       <c r="G269" t="str">
-        <v>62-68</v>
+        <v>63-69</v>
       </c>
       <c r="H269" s="1">
         <v>0.1429</v>
@@ -13065,7 +13065,7 @@
         <v>57-58</v>
       </c>
       <c r="G270" t="str">
-        <v>63-69</v>
+        <v>64-70</v>
       </c>
       <c r="H270" s="1">
         <v>0.1665</v>
@@ -13112,7 +13112,7 @@
         <v>57-58</v>
       </c>
       <c r="G271" t="str">
-        <v>63-69</v>
+        <v>64-70</v>
       </c>
       <c r="H271" s="1">
         <v>0.1667</v>
@@ -13159,7 +13159,7 @@
         <v>57-58</v>
       </c>
       <c r="G272" t="str">
-        <v>63-69</v>
+        <v>64-70</v>
       </c>
       <c r="H272" s="1">
         <v>0.1667</v>
@@ -13206,7 +13206,7 @@
         <v>57-58</v>
       </c>
       <c r="G273" t="str">
-        <v>63-69</v>
+        <v>64-70</v>
       </c>
       <c r="H273" s="1">
         <v>0.1667</v>
@@ -13253,7 +13253,7 @@
         <v>57-58</v>
       </c>
       <c r="G274" t="str">
-        <v>63-69</v>
+        <v>64-70</v>
       </c>
       <c r="H274" s="1">
         <v>0.1667</v>
@@ -13300,7 +13300,7 @@
         <v>57-58</v>
       </c>
       <c r="G275" t="str">
-        <v>63-69</v>
+        <v>64-70</v>
       </c>
       <c r="H275" s="1">
         <v>0.1667</v>
@@ -13347,7 +13347,7 @@
         <v>58-59</v>
       </c>
       <c r="G276" t="str">
-        <v>65-71</v>
+        <v>66-72</v>
       </c>
       <c r="H276" s="1">
         <v>0.25</v>
@@ -13394,7 +13394,7 @@
         <v>58-59</v>
       </c>
       <c r="G277" t="str">
-        <v>65-71</v>
+        <v>66-72</v>
       </c>
       <c r="H277" s="1">
         <v>0.25</v>
@@ -13441,7 +13441,7 @@
         <v>58-59</v>
       </c>
       <c r="G278" t="str">
-        <v>65-71</v>
+        <v>66-72</v>
       </c>
       <c r="H278" s="1">
         <v>0.25</v>
@@ -13488,7 +13488,7 @@
         <v>58-59</v>
       </c>
       <c r="G279" t="str">
-        <v>65-71</v>
+        <v>66-72</v>
       </c>
       <c r="H279" s="1">
         <v>0.25</v>
@@ -13535,7 +13535,7 @@
         <v>59-60</v>
       </c>
       <c r="G280" t="str">
-        <v>66-72</v>
+        <v>67-73</v>
       </c>
       <c r="H280" s="1">
         <v>0.25</v>
@@ -13582,7 +13582,7 @@
         <v>59-60</v>
       </c>
       <c r="G281" t="str">
-        <v>66-72</v>
+        <v>67-73</v>
       </c>
       <c r="H281" s="1">
         <v>0.25</v>
@@ -13629,7 +13629,7 @@
         <v>59-60</v>
       </c>
       <c r="G282" t="str">
-        <v>66-72</v>
+        <v>67-73</v>
       </c>
       <c r="H282" s="1">
         <v>0.25</v>
@@ -13676,7 +13676,7 @@
         <v>59-60</v>
       </c>
       <c r="G283" t="str">
-        <v>66-72</v>
+        <v>67-73</v>
       </c>
       <c r="H283" s="1">
         <v>0.25</v>
@@ -13723,7 +13723,7 @@
         <v>60-61</v>
       </c>
       <c r="G284" t="str">
-        <v>67-73</v>
+        <v>69-75</v>
       </c>
       <c r="H284" s="1">
         <v>0.3334</v>
@@ -13770,7 +13770,7 @@
         <v>60-61</v>
       </c>
       <c r="G285" t="str">
-        <v>67-73</v>
+        <v>69-75</v>
       </c>
       <c r="H285" s="1">
         <v>0.3333</v>
@@ -13817,7 +13817,7 @@
         <v>60-61</v>
       </c>
       <c r="G286" t="str">
-        <v>67-73</v>
+        <v>69-75</v>
       </c>
       <c r="H286" s="1">
         <v>0.3333</v>
@@ -13864,7 +13864,7 @@
         <v>62-63</v>
       </c>
       <c r="G287" t="str">
-        <v>69-75</v>
+        <v>70-77</v>
       </c>
       <c r="H287" s="1">
         <v>0.091</v>
@@ -13911,7 +13911,7 @@
         <v>62-63</v>
       </c>
       <c r="G288" t="str">
-        <v>69-75</v>
+        <v>70-77</v>
       </c>
       <c r="H288" s="1">
         <v>0.0909</v>
@@ -13958,7 +13958,7 @@
         <v>62-63</v>
       </c>
       <c r="G289" t="str">
-        <v>69-75</v>
+        <v>70-77</v>
       </c>
       <c r="H289" s="1">
         <v>0.0909</v>
@@ -14005,7 +14005,7 @@
         <v>62-63</v>
       </c>
       <c r="G290" t="str">
-        <v>69-75</v>
+        <v>70-77</v>
       </c>
       <c r="H290" s="1">
         <v>0.0909</v>
@@ -14052,7 +14052,7 @@
         <v>62-63</v>
       </c>
       <c r="G291" t="str">
-        <v>69-75</v>
+        <v>70-77</v>
       </c>
       <c r="H291" s="1">
         <v>0.0909</v>
@@ -14099,7 +14099,7 @@
         <v>62-63</v>
       </c>
       <c r="G292" t="str">
-        <v>69-75</v>
+        <v>70-77</v>
       </c>
       <c r="H292" s="1">
         <v>0.0909</v>
@@ -14146,7 +14146,7 @@
         <v>62-63</v>
       </c>
       <c r="G293" t="str">
-        <v>69-75</v>
+        <v>70-77</v>
       </c>
       <c r="H293" s="1">
         <v>0.0909</v>
@@ -14193,7 +14193,7 @@
         <v>62-63</v>
       </c>
       <c r="G294" t="str">
-        <v>69-75</v>
+        <v>70-77</v>
       </c>
       <c r="H294" s="1">
         <v>0.0909</v>
@@ -14240,7 +14240,7 @@
         <v>62-63</v>
       </c>
       <c r="G295" t="str">
-        <v>69-75</v>
+        <v>70-77</v>
       </c>
       <c r="H295" s="1">
         <v>0.0909</v>
@@ -14287,7 +14287,7 @@
         <v>62-63</v>
       </c>
       <c r="G296" t="str">
-        <v>69-75</v>
+        <v>70-77</v>
       </c>
       <c r="H296" s="1">
         <v>0.0909</v>
@@ -14334,7 +14334,7 @@
         <v>62-63</v>
       </c>
       <c r="G297" t="str">
-        <v>69-75</v>
+        <v>70-77</v>
       </c>
       <c r="H297" s="1">
         <v>0.0909</v>
@@ -14381,7 +14381,7 @@
         <v>63-64</v>
       </c>
       <c r="G298" t="str">
-        <v>70-77</v>
+        <v>72-79</v>
       </c>
       <c r="H298" s="1">
         <v>0.1112</v>
@@ -14428,7 +14428,7 @@
         <v>63-64</v>
       </c>
       <c r="G299" t="str">
-        <v>70-77</v>
+        <v>72-79</v>
       </c>
       <c r="H299" s="1">
         <v>0.1111</v>
@@ -14475,7 +14475,7 @@
         <v>63-64</v>
       </c>
       <c r="G300" t="str">
-        <v>70-77</v>
+        <v>72-79</v>
       </c>
       <c r="H300" s="1">
         <v>0.1111</v>
@@ -14522,7 +14522,7 @@
         <v>63-64</v>
       </c>
       <c r="G301" t="str">
-        <v>70-77</v>
+        <v>72-79</v>
       </c>
       <c r="H301" s="1">
         <v>0.1111</v>
@@ -14569,7 +14569,7 @@
         <v>63-64</v>
       </c>
       <c r="G302" t="str">
-        <v>70-77</v>
+        <v>72-79</v>
       </c>
       <c r="H302" s="1">
         <v>0.1111</v>
@@ -14616,7 +14616,7 @@
         <v>63-64</v>
       </c>
       <c r="G303" t="str">
-        <v>70-77</v>
+        <v>72-79</v>
       </c>
       <c r="H303" s="1">
         <v>0.1111</v>
@@ -14663,7 +14663,7 @@
         <v>63-64</v>
       </c>
       <c r="G304" t="str">
-        <v>70-77</v>
+        <v>72-79</v>
       </c>
       <c r="H304" s="1">
         <v>0.1111</v>
@@ -14710,7 +14710,7 @@
         <v>63-64</v>
       </c>
       <c r="G305" t="str">
-        <v>70-77</v>
+        <v>72-79</v>
       </c>
       <c r="H305" s="1">
         <v>0.1111</v>
@@ -14757,7 +14757,7 @@
         <v>63-64</v>
       </c>
       <c r="G306" t="str">
-        <v>70-77</v>
+        <v>72-79</v>
       </c>
       <c r="H306" s="1">
         <v>0.1111</v>
@@ -14804,7 +14804,7 @@
         <v>64-65</v>
       </c>
       <c r="G307" t="str">
-        <v>72-79</v>
+        <v>73-80</v>
       </c>
       <c r="H307" s="1">
         <v>0.1426</v>
@@ -14851,7 +14851,7 @@
         <v>64-65</v>
       </c>
       <c r="G308" t="str">
-        <v>72-79</v>
+        <v>73-80</v>
       </c>
       <c r="H308" s="1">
         <v>0.1429</v>
@@ -14898,7 +14898,7 @@
         <v>64-65</v>
       </c>
       <c r="G309" t="str">
-        <v>72-79</v>
+        <v>73-80</v>
       </c>
       <c r="H309" s="1">
         <v>0.1429</v>
@@ -14945,7 +14945,7 @@
         <v>64-65</v>
       </c>
       <c r="G310" t="str">
-        <v>72-79</v>
+        <v>73-80</v>
       </c>
       <c r="H310" s="1">
         <v>0.1429</v>
@@ -14992,7 +14992,7 @@
         <v>64-65</v>
       </c>
       <c r="G311" t="str">
-        <v>72-79</v>
+        <v>73-80</v>
       </c>
       <c r="H311" s="1">
         <v>0.1429</v>
@@ -15039,7 +15039,7 @@
         <v>64-65</v>
       </c>
       <c r="G312" t="str">
-        <v>72-79</v>
+        <v>73-80</v>
       </c>
       <c r="H312" s="1">
         <v>0.1429</v>
@@ -15086,7 +15086,7 @@
         <v>64-65</v>
       </c>
       <c r="G313" t="str">
-        <v>72-79</v>
+        <v>73-80</v>
       </c>
       <c r="H313" s="1">
         <v>0.1429</v>
@@ -16167,7 +16167,7 @@
         <v>53-54</v>
       </c>
       <c r="G336" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H336" s="1">
         <v>0.125</v>
@@ -16214,7 +16214,7 @@
         <v>53-54</v>
       </c>
       <c r="G337" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H337" s="1">
         <v>0.125</v>
@@ -16261,7 +16261,7 @@
         <v>53-54</v>
       </c>
       <c r="G338" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H338" s="1">
         <v>0.125</v>
@@ -16308,7 +16308,7 @@
         <v>53-54</v>
       </c>
       <c r="G339" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H339" s="1">
         <v>0.125</v>
@@ -16355,7 +16355,7 @@
         <v>53-54</v>
       </c>
       <c r="G340" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H340" s="1">
         <v>0.125</v>
@@ -16402,7 +16402,7 @@
         <v>53-54</v>
       </c>
       <c r="G341" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H341" s="1">
         <v>0.125</v>
@@ -16449,7 +16449,7 @@
         <v>53-54</v>
       </c>
       <c r="G342" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H342" s="1">
         <v>0.125</v>
@@ -16496,7 +16496,7 @@
         <v>53-54</v>
       </c>
       <c r="G343" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H343" s="1">
         <v>0.125</v>
@@ -17201,7 +17201,7 @@
         <v>61-62</v>
       </c>
       <c r="G358" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H358" s="1">
         <v>0.2</v>
@@ -17248,7 +17248,7 @@
         <v>61-62</v>
       </c>
       <c r="G359" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H359" s="1">
         <v>0.2</v>
@@ -17295,7 +17295,7 @@
         <v>61-62</v>
       </c>
       <c r="G360" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H360" s="1">
         <v>0.2</v>
@@ -17342,7 +17342,7 @@
         <v>61-62</v>
       </c>
       <c r="G361" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H361" s="1">
         <v>0.2</v>
@@ -17389,7 +17389,7 @@
         <v>61-62</v>
       </c>
       <c r="G362" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H362" s="1">
         <v>0.2</v>
